--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
@@ -1684,7 +1684,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Stream 1a - Entry fee margin, SIP</t>
+          <t>Stream 1a - Entry fee, SIP</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
@@ -1704,7 +1704,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Stream 1b - Entry fee margin, SPOT</t>
+          <t>Stream 1b - Entry fee, SPOT</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
@@ -2984,60 +2984,60 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Share of agent-driven acquisition - UAE</t>
+          <t>Share of salesforce deployed - UAE</t>
         </is>
       </c>
       <c r="B106" s="19" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>% of agent output</t>
+          <t>% of salesforce</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>CLIENT INPUT 2026-08-20: THE AGENT NETWORK OPERATES IN INDIA ONLY. Outside India acquisition is marketing spend, referrals and organic only. ⚠ THIS CONTRADICTS THE ARCHITECTURE BRIEF, which allocates agents across every region through its channel-to-region mix and argues that the agent network is Indian and 'must recruit non-Indian agents before it reaches the other South Asian market at all' - wording that assumes agents are already selling to the UAE diaspora. The client instruction is taken as authoritative and the brief's mix is superseded. Must sum to 100%.</t>
+          <t>REVISED 2026-08-20. An earlier cut put 100% in India, which left the UAE - the licensed home market - with no people selling at all. There will be a salesforce outside India; it is simply SALARIED rather than commission-only. FOR REVENUE THE DISTINCTION DOES NOT MATTER: both are people acquiring customers at some productivity. ⚠ IT MATTERS ENORMOUSLY FOR COST - a Dubai salesperson and an Indian commission agent are not remotely the same expense, and this split MUST be cost-weighted when the cost build lands. India stays high because a large agent pool is cheapest to build there; UAE is weighted for being the core licensed market. ⚠ NOT the same thing as stream 6: that is B2B, partners white-labelling the platform onto their own customer books, and is not a consumer sales channel at all. Must sum to 100%. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Share of agent-driven acquisition - Oman and Bahrain</t>
+          <t>Share of salesforce deployed - Oman and Bahrain</t>
         </is>
       </c>
       <c r="B107" s="19" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>% of agent output</t>
+          <t>% of salesforce</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>CLIENT INPUT 2026-08-20: THE AGENT NETWORK OPERATES IN INDIA ONLY. Outside India acquisition is marketing spend, referrals and organic only. ⚠ THIS CONTRADICTS THE ARCHITECTURE BRIEF, which allocates agents across every region through its channel-to-region mix and argues that the agent network is Indian and 'must recruit non-Indian agents before it reaches the other South Asian market at all' - wording that assumes agents are already selling to the UAE diaspora. The client instruction is taken as authoritative and the brief's mix is superseded. Must sum to 100%.</t>
+          <t>REVISED 2026-08-20. An earlier cut put 100% in India, which left the UAE - the licensed home market - with no people selling at all. There will be a salesforce outside India; it is simply SALARIED rather than commission-only. FOR REVENUE THE DISTINCTION DOES NOT MATTER: both are people acquiring customers at some productivity. ⚠ IT MATTERS ENORMOUSLY FOR COST - a Dubai salesperson and an Indian commission agent are not remotely the same expense, and this split MUST be cost-weighted when the cost build lands. India stays high because a large agent pool is cheapest to build there; UAE is weighted for being the core licensed market. ⚠ NOT the same thing as stream 6: that is B2B, partners white-labelling the platform onto their own customer books, and is not a consumer sales channel at all. Must sum to 100%. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Share of agent-driven acquisition - India</t>
+          <t>Share of salesforce deployed - India</t>
         </is>
       </c>
       <c r="B108" s="19" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>% of agent output</t>
+          <t>% of salesforce</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CLIENT INPUT 2026-08-20: THE AGENT NETWORK OPERATES IN INDIA ONLY. Outside India acquisition is marketing spend, referrals and organic only. ⚠ THIS CONTRADICTS THE ARCHITECTURE BRIEF, which allocates agents across every region through its channel-to-region mix and argues that the agent network is Indian and 'must recruit non-Indian agents before it reaches the other South Asian market at all' - wording that assumes agents are already selling to the UAE diaspora. The client instruction is taken as authoritative and the brief's mix is superseded. Must sum to 100%.</t>
+          <t>REVISED 2026-08-20. An earlier cut put 100% in India, which left the UAE - the licensed home market - with no people selling at all. There will be a salesforce outside India; it is simply SALARIED rather than commission-only. FOR REVENUE THE DISTINCTION DOES NOT MATTER: both are people acquiring customers at some productivity. ⚠ IT MATTERS ENORMOUSLY FOR COST - a Dubai salesperson and an Indian commission agent are not remotely the same expense, and this split MUST be cost-weighted when the cost build lands. India stays high because a large agent pool is cheapest to build there; UAE is weighted for being the core licensed market. ⚠ NOT the same thing as stream 6: that is B2B, partners white-labelling the platform onto their own customer books, and is not a consumer sales channel at all. Must sum to 100%. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Self-custody leakage</t>
+          <t>Gold moved out of Aurumix's control</t>
         </is>
       </c>
       <c r="B127" s="32">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Gold withdrawn to a customer's own wallet. Free to Aurumix but it leaves AUM. ASSUMPTION.</t>
+          <t>RELABELLED 2026-08-21 after the client correctly objected to the old name, 'self-custody leakage'. THE GOLD DOES NOT LEAVE THE VAULT: a token moving to a customer's own wallet sells nothing and burns nothing, so calling it an AUM decrease was wrong. What it does leave is Aurumix's COLLATERAL-ELIGIBLE base - Aurumix cannot foreclose on a token sitting in a private wallet, so that gold can no longer back a credit limit. In this model AUM has exactly ONE consumer, the card credit limit, so the arithmetic was always right and only the label was misleading. ⚠ THAT ONE-CONSUMER PROPERTY IS WHAT MAKES THIS SAFE: if a later build points anything else at AUM - a custody fee, a reported-AUM headline - this row must be split in two first. Contrast the redemption line, which IS gold genuinely gone. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Self-custody leakage</t>
+          <t>Gold moved out of Aurumix's control</t>
         </is>
       </c>
       <c r="B31" s="38">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Gold withdrawn to a customer's own wallet. Free to Aurumix but it leaves AUM. ASSUMPTION.</t>
+          <t>RELABELLED 2026-08-21 after the client correctly objected to the old name, 'self-custody leakage'. THE GOLD DOES NOT LEAVE THE VAULT: a token moving to a customer's own wallet sells nothing and burns nothing, so calling it an AUM decrease was wrong. What it does leave is Aurumix's COLLATERAL-ELIGIBLE base - Aurumix cannot foreclose on a token sitting in a private wallet, so that gold can no longer back a credit limit. In this model AUM has exactly ONE consumer, the card credit limit, so the arithmetic was always right and only the label was misleading. ⚠ THAT ONE-CONSUMER PROPERTY IS WHAT MAKES THIS SAFE: if a later build points anything else at AUM - a custody fee, a reported-AUM headline - this row must be split in two first. Contrast the redemption line, which IS gold genuinely gone. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE163"/>
+  <dimension ref="A1:AE164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7969,7 +7969,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Open-region share total (renormalisation base)</t>
+          <t>Open-region salesforce share (renormalisation base)</t>
         </is>
       </c>
       <c r="B21" s="23" t="inlineStr">
@@ -7977,120 +7977,120 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(C2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(C2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="D21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(D2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(D2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="E21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(E2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(E2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="F21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(F2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(F2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="G21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(G2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(G2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="H21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(H2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(H2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(I2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(I2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="J21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(J2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(J2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="K21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(K2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(K2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="L21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(L2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(L2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(M2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(M2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="N21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(N2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(N2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="O21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(O2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(O2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="P21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(P2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(P2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(Q2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(Q2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="R21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(R2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(R2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="S21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(S2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(S2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="T21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(T2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(T2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="U21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(U2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(U2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="V21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(V2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(V2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="W21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(W2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(W2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="X21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(X2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(X2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="Y21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(Y2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(Y2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="Z21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(Z2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(Z2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="AA21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(AA2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(AA2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="AB21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(AB2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(AB2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="AC21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(AC2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(AC2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="AD21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(AD2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(AD2&gt;=Assumptions!$B$54,1,0)</f>
-        <v/>
-      </c>
-      <c r="AE21" s="50">
-        <f>Assumptions!$B$164*1+Assumptions!$B$165*IF(AE2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$166*IF(AE2&gt;=Assumptions!$B$54,1,0)</f>
+      <c r="C21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(C2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(C2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(D2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(D2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="E21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(E2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(E2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(F2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(F2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(G2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(G2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(H2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(H2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="I21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(I2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(I2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(J2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(J2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(K2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(K2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(L2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(L2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(M2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(M2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(N2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(N2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(O2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(O2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="P21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(P2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(P2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(Q2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(Q2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="R21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(R2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(R2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="S21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(S2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(S2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="T21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(T2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(T2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="U21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(U2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(U2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="V21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(V2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(V2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="W21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(W2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(W2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="X21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(X2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(X2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(Y2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(Y2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(Z2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(Z2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(AA2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(AA2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="AB21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(AB2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(AB2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="AC21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(AC2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(AC2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(AD2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(AD2&gt;=Assumptions!$B$54,1,0)</f>
+        <v/>
+      </c>
+      <c r="AE21" s="47">
+        <f>Assumptions!$B$106*1+Assumptions!$B$107*IF(AE2&gt;=Assumptions!$B$53,1,0)+Assumptions!$B$108*IF(AE2&gt;=Assumptions!$B$54,1,0)</f>
         <v/>
       </c>
     </row>
@@ -8398,119 +8398,119 @@
         </is>
       </c>
       <c r="C26" s="53">
-        <f>C24+C25+C20*Assumptions!$B$106</f>
+        <f>C24+C25+IF(C21=0,0,C20*Assumptions!$B$106/C21*1)</f>
         <v/>
       </c>
       <c r="D26" s="53">
-        <f>D24+D25+D20*Assumptions!$B$106</f>
+        <f>D24+D25+IF(D21=0,0,D20*Assumptions!$B$106/D21*1)</f>
         <v/>
       </c>
       <c r="E26" s="53">
-        <f>E24+E25+E20*Assumptions!$B$106</f>
+        <f>E24+E25+IF(E21=0,0,E20*Assumptions!$B$106/E21*1)</f>
         <v/>
       </c>
       <c r="F26" s="53">
-        <f>F24+F25+F20*Assumptions!$B$106</f>
+        <f>F24+F25+IF(F21=0,0,F20*Assumptions!$B$106/F21*1)</f>
         <v/>
       </c>
       <c r="G26" s="53">
-        <f>G24+G25+G20*Assumptions!$B$106</f>
+        <f>G24+G25+IF(G21=0,0,G20*Assumptions!$B$106/G21*1)</f>
         <v/>
       </c>
       <c r="H26" s="53">
-        <f>H24+H25+H20*Assumptions!$B$106</f>
+        <f>H24+H25+IF(H21=0,0,H20*Assumptions!$B$106/H21*1)</f>
         <v/>
       </c>
       <c r="I26" s="53">
-        <f>I24+I25+I20*Assumptions!$B$106</f>
+        <f>I24+I25+IF(I21=0,0,I20*Assumptions!$B$106/I21*1)</f>
         <v/>
       </c>
       <c r="J26" s="53">
-        <f>J24+J25+J20*Assumptions!$B$106</f>
+        <f>J24+J25+IF(J21=0,0,J20*Assumptions!$B$106/J21*1)</f>
         <v/>
       </c>
       <c r="K26" s="53">
-        <f>K24+K25+K20*Assumptions!$B$106</f>
+        <f>K24+K25+IF(K21=0,0,K20*Assumptions!$B$106/K21*1)</f>
         <v/>
       </c>
       <c r="L26" s="53">
-        <f>L24+L25+L20*Assumptions!$B$106</f>
+        <f>L24+L25+IF(L21=0,0,L20*Assumptions!$B$106/L21*1)</f>
         <v/>
       </c>
       <c r="M26" s="53">
-        <f>M24+M25+M20*Assumptions!$B$106</f>
+        <f>M24+M25+IF(M21=0,0,M20*Assumptions!$B$106/M21*1)</f>
         <v/>
       </c>
       <c r="N26" s="53">
-        <f>N24+N25+N20*Assumptions!$B$106</f>
+        <f>N24+N25+IF(N21=0,0,N20*Assumptions!$B$106/N21*1)</f>
         <v/>
       </c>
       <c r="O26" s="53">
-        <f>O24+O25+O20*Assumptions!$B$106</f>
+        <f>O24+O25+IF(O21=0,0,O20*Assumptions!$B$106/O21*1)</f>
         <v/>
       </c>
       <c r="P26" s="53">
-        <f>P24+P25+P20*Assumptions!$B$106</f>
+        <f>P24+P25+IF(P21=0,0,P20*Assumptions!$B$106/P21*1)</f>
         <v/>
       </c>
       <c r="Q26" s="53">
-        <f>Q24+Q25+Q20*Assumptions!$B$106</f>
+        <f>Q24+Q25+IF(Q21=0,0,Q20*Assumptions!$B$106/Q21*1)</f>
         <v/>
       </c>
       <c r="R26" s="53">
-        <f>R24+R25+R20*Assumptions!$B$106</f>
+        <f>R24+R25+IF(R21=0,0,R20*Assumptions!$B$106/R21*1)</f>
         <v/>
       </c>
       <c r="S26" s="53">
-        <f>S24+S25+S20*Assumptions!$B$106</f>
+        <f>S24+S25+IF(S21=0,0,S20*Assumptions!$B$106/S21*1)</f>
         <v/>
       </c>
       <c r="T26" s="53">
-        <f>T24+T25+T20*Assumptions!$B$106</f>
+        <f>T24+T25+IF(T21=0,0,T20*Assumptions!$B$106/T21*1)</f>
         <v/>
       </c>
       <c r="U26" s="53">
-        <f>U24+U25+U20*Assumptions!$B$106</f>
+        <f>U24+U25+IF(U21=0,0,U20*Assumptions!$B$106/U21*1)</f>
         <v/>
       </c>
       <c r="V26" s="53">
-        <f>V24+V25+V20*Assumptions!$B$106</f>
+        <f>V24+V25+IF(V21=0,0,V20*Assumptions!$B$106/V21*1)</f>
         <v/>
       </c>
       <c r="W26" s="53">
-        <f>W24+W25+W20*Assumptions!$B$106</f>
+        <f>W24+W25+IF(W21=0,0,W20*Assumptions!$B$106/W21*1)</f>
         <v/>
       </c>
       <c r="X26" s="53">
-        <f>X24+X25+X20*Assumptions!$B$106</f>
+        <f>X24+X25+IF(X21=0,0,X20*Assumptions!$B$106/X21*1)</f>
         <v/>
       </c>
       <c r="Y26" s="53">
-        <f>Y24+Y25+Y20*Assumptions!$B$106</f>
+        <f>Y24+Y25+IF(Y21=0,0,Y20*Assumptions!$B$106/Y21*1)</f>
         <v/>
       </c>
       <c r="Z26" s="53">
-        <f>Z24+Z25+Z20*Assumptions!$B$106</f>
+        <f>Z24+Z25+IF(Z21=0,0,Z20*Assumptions!$B$106/Z21*1)</f>
         <v/>
       </c>
       <c r="AA26" s="53">
-        <f>AA24+AA25+AA20*Assumptions!$B$106</f>
+        <f>AA24+AA25+IF(AA21=0,0,AA20*Assumptions!$B$106/AA21*1)</f>
         <v/>
       </c>
       <c r="AB26" s="53">
-        <f>AB24+AB25+AB20*Assumptions!$B$106</f>
+        <f>AB24+AB25+IF(AB21=0,0,AB20*Assumptions!$B$106/AB21*1)</f>
         <v/>
       </c>
       <c r="AC26" s="53">
-        <f>AC24+AC25+AC20*Assumptions!$B$106</f>
+        <f>AC24+AC25+IF(AC21=0,0,AC20*Assumptions!$B$106/AC21*1)</f>
         <v/>
       </c>
       <c r="AD26" s="53">
-        <f>AD24+AD25+AD20*Assumptions!$B$106</f>
+        <f>AD24+AD25+IF(AD21=0,0,AD20*Assumptions!$B$106/AD21*1)</f>
         <v/>
       </c>
       <c r="AE26" s="53">
-        <f>AE24+AE25+AE20*Assumptions!$B$106</f>
+        <f>AE24+AE25+IF(AE21=0,0,AE20*Assumptions!$B$106/AE21*1)</f>
         <v/>
       </c>
     </row>
@@ -9668,7 +9668,7 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AUM decay rate (holder-weighted)</t>
+          <t xml:space="preserve">  Collateral-eligible AUM decay rate (holder-weighted)</t>
         </is>
       </c>
       <c r="B36" s="23" t="inlineStr">
@@ -11332,7 +11332,7 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stream 1a - Entry fee margin, SIP</t>
+          <t xml:space="preserve">  Stream 1a - Entry fee, SIP</t>
         </is>
       </c>
       <c r="B49" s="23" t="inlineStr">
@@ -11341,126 +11341,126 @@
         </is>
       </c>
       <c r="C49" s="54">
-        <f>C33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>C33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="D49" s="54">
-        <f>D33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>D33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="E49" s="54">
-        <f>E33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>E33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="F49" s="54">
-        <f>F33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>F33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="G49" s="54">
-        <f>G33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>G33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="H49" s="54">
-        <f>H33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>H33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="I49" s="54">
-        <f>I33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>I33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="J49" s="54">
-        <f>J33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>J33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="K49" s="54">
-        <f>K33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>K33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="L49" s="54">
-        <f>L33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>L33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="M49" s="54">
-        <f>M33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>M33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="N49" s="54">
-        <f>N33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>N33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="O49" s="54">
-        <f>O33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>O33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="P49" s="54">
-        <f>P33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>P33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Q49" s="54">
-        <f>Q33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Q33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="R49" s="54">
-        <f>R33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>R33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="S49" s="54">
-        <f>S33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>S33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="T49" s="54">
-        <f>T33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>T33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="U49" s="54">
-        <f>U33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>U33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="V49" s="54">
-        <f>V33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>V33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="W49" s="54">
-        <f>W33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>W33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="X49" s="54">
-        <f>X33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>X33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Y49" s="54">
-        <f>Y33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Y33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Z49" s="54">
-        <f>Z33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Z33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AA49" s="54">
-        <f>AA33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AA33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AB49" s="54">
-        <f>AB33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AB33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AC49" s="54">
-        <f>AC33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AC33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AD49" s="54">
-        <f>AD33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AD33*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AE49" s="54">
-        <f>AE33*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AE33*Assumptions!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stream 1b - Entry fee margin, SPOT</t>
+          <t xml:space="preserve">  Stream 1b - Entry fee, SPOT</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
@@ -11469,119 +11469,119 @@
         </is>
       </c>
       <c r="C50" s="54">
-        <f>C34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>C34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="D50" s="54">
-        <f>D34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>D34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="E50" s="54">
-        <f>E34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>E34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="F50" s="54">
-        <f>F34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>F34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="G50" s="54">
-        <f>G34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>G34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="H50" s="54">
-        <f>H34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>H34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="I50" s="54">
-        <f>I34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>I34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="J50" s="54">
-        <f>J34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>J34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="K50" s="54">
-        <f>K34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>K34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="L50" s="54">
-        <f>L34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>L34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="M50" s="54">
-        <f>M34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>M34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="N50" s="54">
-        <f>N34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>N34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="O50" s="54">
-        <f>O34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>O34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="P50" s="54">
-        <f>P34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>P34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Q50" s="54">
-        <f>Q34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Q34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="R50" s="54">
-        <f>R34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>R34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="S50" s="54">
-        <f>S34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>S34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="T50" s="54">
-        <f>T34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>T34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="U50" s="54">
-        <f>U34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>U34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="V50" s="54">
-        <f>V34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>V34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="W50" s="54">
-        <f>W34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>W34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="X50" s="54">
-        <f>X34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>X34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Y50" s="54">
-        <f>Y34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Y34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Z50" s="54">
-        <f>Z34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Z34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AA50" s="54">
-        <f>AA34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AA34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AB50" s="54">
-        <f>AB34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AB34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AC50" s="54">
-        <f>AC34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AC34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AD50" s="54">
-        <f>AD34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AD34*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AE50" s="54">
-        <f>AE34*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AE34*Assumptions!$B$8</f>
         <v/>
       </c>
     </row>
@@ -12785,119 +12785,119 @@
         </is>
       </c>
       <c r="C62" s="53">
-        <f>C60+C61+C20*Assumptions!$B$107</f>
+        <f>C60+C61+IF(C21=0,0,C20*Assumptions!$B$107/C21*IF(C2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="D62" s="53">
-        <f>D60+D61+D20*Assumptions!$B$107</f>
+        <f>D60+D61+IF(D21=0,0,D20*Assumptions!$B$107/D21*IF(D2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="E62" s="53">
-        <f>E60+E61+E20*Assumptions!$B$107</f>
+        <f>E60+E61+IF(E21=0,0,E20*Assumptions!$B$107/E21*IF(E2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="F62" s="53">
-        <f>F60+F61+F20*Assumptions!$B$107</f>
+        <f>F60+F61+IF(F21=0,0,F20*Assumptions!$B$107/F21*IF(F2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="G62" s="53">
-        <f>G60+G61+G20*Assumptions!$B$107</f>
+        <f>G60+G61+IF(G21=0,0,G20*Assumptions!$B$107/G21*IF(G2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="H62" s="53">
-        <f>H60+H61+H20*Assumptions!$B$107</f>
+        <f>H60+H61+IF(H21=0,0,H20*Assumptions!$B$107/H21*IF(H2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="I62" s="53">
-        <f>I60+I61+I20*Assumptions!$B$107</f>
+        <f>I60+I61+IF(I21=0,0,I20*Assumptions!$B$107/I21*IF(I2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="J62" s="53">
-        <f>J60+J61+J20*Assumptions!$B$107</f>
+        <f>J60+J61+IF(J21=0,0,J20*Assumptions!$B$107/J21*IF(J2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="K62" s="53">
-        <f>K60+K61+K20*Assumptions!$B$107</f>
+        <f>K60+K61+IF(K21=0,0,K20*Assumptions!$B$107/K21*IF(K2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="L62" s="53">
-        <f>L60+L61+L20*Assumptions!$B$107</f>
+        <f>L60+L61+IF(L21=0,0,L20*Assumptions!$B$107/L21*IF(L2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="M62" s="53">
-        <f>M60+M61+M20*Assumptions!$B$107</f>
+        <f>M60+M61+IF(M21=0,0,M20*Assumptions!$B$107/M21*IF(M2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="N62" s="53">
-        <f>N60+N61+N20*Assumptions!$B$107</f>
+        <f>N60+N61+IF(N21=0,0,N20*Assumptions!$B$107/N21*IF(N2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="O62" s="53">
-        <f>O60+O61+O20*Assumptions!$B$107</f>
+        <f>O60+O61+IF(O21=0,0,O20*Assumptions!$B$107/O21*IF(O2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="P62" s="53">
-        <f>P60+P61+P20*Assumptions!$B$107</f>
+        <f>P60+P61+IF(P21=0,0,P20*Assumptions!$B$107/P21*IF(P2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="Q62" s="53">
-        <f>Q60+Q61+Q20*Assumptions!$B$107</f>
+        <f>Q60+Q61+IF(Q21=0,0,Q20*Assumptions!$B$107/Q21*IF(Q2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="R62" s="53">
-        <f>R60+R61+R20*Assumptions!$B$107</f>
+        <f>R60+R61+IF(R21=0,0,R20*Assumptions!$B$107/R21*IF(R2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="S62" s="53">
-        <f>S60+S61+S20*Assumptions!$B$107</f>
+        <f>S60+S61+IF(S21=0,0,S20*Assumptions!$B$107/S21*IF(S2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="T62" s="53">
-        <f>T60+T61+T20*Assumptions!$B$107</f>
+        <f>T60+T61+IF(T21=0,0,T20*Assumptions!$B$107/T21*IF(T2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="U62" s="53">
-        <f>U60+U61+U20*Assumptions!$B$107</f>
+        <f>U60+U61+IF(U21=0,0,U20*Assumptions!$B$107/U21*IF(U2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="V62" s="53">
-        <f>V60+V61+V20*Assumptions!$B$107</f>
+        <f>V60+V61+IF(V21=0,0,V20*Assumptions!$B$107/V21*IF(V2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="W62" s="53">
-        <f>W60+W61+W20*Assumptions!$B$107</f>
+        <f>W60+W61+IF(W21=0,0,W20*Assumptions!$B$107/W21*IF(W2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="X62" s="53">
-        <f>X60+X61+X20*Assumptions!$B$107</f>
+        <f>X60+X61+IF(X21=0,0,X20*Assumptions!$B$107/X21*IF(X2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="Y62" s="53">
-        <f>Y60+Y61+Y20*Assumptions!$B$107</f>
+        <f>Y60+Y61+IF(Y21=0,0,Y20*Assumptions!$B$107/Y21*IF(Y2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="Z62" s="53">
-        <f>Z60+Z61+Z20*Assumptions!$B$107</f>
+        <f>Z60+Z61+IF(Z21=0,0,Z20*Assumptions!$B$107/Z21*IF(Z2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="AA62" s="53">
-        <f>AA60+AA61+AA20*Assumptions!$B$107</f>
+        <f>AA60+AA61+IF(AA21=0,0,AA20*Assumptions!$B$107/AA21*IF(AA2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="AB62" s="53">
-        <f>AB60+AB61+AB20*Assumptions!$B$107</f>
+        <f>AB60+AB61+IF(AB21=0,0,AB20*Assumptions!$B$107/AB21*IF(AB2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="AC62" s="53">
-        <f>AC60+AC61+AC20*Assumptions!$B$107</f>
+        <f>AC60+AC61+IF(AC21=0,0,AC20*Assumptions!$B$107/AC21*IF(AC2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="AD62" s="53">
-        <f>AD60+AD61+AD20*Assumptions!$B$107</f>
+        <f>AD60+AD61+IF(AD21=0,0,AD20*Assumptions!$B$107/AD21*IF(AD2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
       <c r="AE62" s="53">
-        <f>AE60+AE61+AE20*Assumptions!$B$107</f>
+        <f>AE60+AE61+IF(AE21=0,0,AE20*Assumptions!$B$107/AE21*IF(AE2&gt;=Assumptions!$B$53,1,0))</f>
         <v/>
       </c>
     </row>
@@ -14055,7 +14055,7 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AUM decay rate (holder-weighted)</t>
+          <t xml:space="preserve">  Collateral-eligible AUM decay rate (holder-weighted)</t>
         </is>
       </c>
       <c r="B72" s="23" t="inlineStr">
@@ -15719,7 +15719,7 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stream 1a - Entry fee margin, SIP</t>
+          <t xml:space="preserve">  Stream 1a - Entry fee, SIP</t>
         </is>
       </c>
       <c r="B85" s="23" t="inlineStr">
@@ -15728,126 +15728,126 @@
         </is>
       </c>
       <c r="C85" s="54">
-        <f>C69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>C69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="D85" s="54">
-        <f>D69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>D69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="E85" s="54">
-        <f>E69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>E69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="F85" s="54">
-        <f>F69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>F69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="G85" s="54">
-        <f>G69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>G69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="H85" s="54">
-        <f>H69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>H69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="I85" s="54">
-        <f>I69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>I69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="J85" s="54">
-        <f>J69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>J69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="K85" s="54">
-        <f>K69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>K69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="L85" s="54">
-        <f>L69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>L69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="M85" s="54">
-        <f>M69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>M69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="N85" s="54">
-        <f>N69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>N69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="O85" s="54">
-        <f>O69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>O69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="P85" s="54">
-        <f>P69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>P69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Q85" s="54">
-        <f>Q69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Q69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="R85" s="54">
-        <f>R69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>R69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="S85" s="54">
-        <f>S69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>S69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="T85" s="54">
-        <f>T69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>T69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="U85" s="54">
-        <f>U69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>U69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="V85" s="54">
-        <f>V69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>V69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="W85" s="54">
-        <f>W69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>W69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="X85" s="54">
-        <f>X69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>X69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Y85" s="54">
-        <f>Y69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Y69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Z85" s="54">
-        <f>Z69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Z69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AA85" s="54">
-        <f>AA69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AA69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AB85" s="54">
-        <f>AB69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AB69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AC85" s="54">
-        <f>AC69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AC69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AD85" s="54">
-        <f>AD69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AD69*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AE85" s="54">
-        <f>AE69*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AE69*Assumptions!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stream 1b - Entry fee margin, SPOT</t>
+          <t xml:space="preserve">  Stream 1b - Entry fee, SPOT</t>
         </is>
       </c>
       <c r="B86" s="23" t="inlineStr">
@@ -15856,119 +15856,119 @@
         </is>
       </c>
       <c r="C86" s="54">
-        <f>C70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>C70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="D86" s="54">
-        <f>D70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>D70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="E86" s="54">
-        <f>E70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>E70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="F86" s="54">
-        <f>F70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>F70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="G86" s="54">
-        <f>G70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>G70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="H86" s="54">
-        <f>H70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>H70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="I86" s="54">
-        <f>I70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>I70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="J86" s="54">
-        <f>J70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>J70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="K86" s="54">
-        <f>K70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>K70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="L86" s="54">
-        <f>L70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>L70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="M86" s="54">
-        <f>M70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>M70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="N86" s="54">
-        <f>N70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>N70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="O86" s="54">
-        <f>O70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>O70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="P86" s="54">
-        <f>P70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>P70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Q86" s="54">
-        <f>Q70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Q70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="R86" s="54">
-        <f>R70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>R70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="S86" s="54">
-        <f>S70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>S70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="T86" s="54">
-        <f>T70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>T70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="U86" s="54">
-        <f>U70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>U70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="V86" s="54">
-        <f>V70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>V70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="W86" s="54">
-        <f>W70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>W70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="X86" s="54">
-        <f>X70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>X70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Y86" s="54">
-        <f>Y70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Y70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Z86" s="54">
-        <f>Z70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Z70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AA86" s="54">
-        <f>AA70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AA70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AB86" s="54">
-        <f>AB70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AB70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AC86" s="54">
-        <f>AC70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AC70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AD86" s="54">
-        <f>AD70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AD70*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AE86" s="54">
-        <f>AE70*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AE70*Assumptions!$B$8</f>
         <v/>
       </c>
     </row>
@@ -17172,119 +17172,119 @@
         </is>
       </c>
       <c r="C98" s="53">
-        <f>C96+C97+C20*Assumptions!$B$108</f>
+        <f>C96+C97+IF(C21=0,0,C20*Assumptions!$B$108/C21*IF(C2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="D98" s="53">
-        <f>D96+D97+D20*Assumptions!$B$108</f>
+        <f>D96+D97+IF(D21=0,0,D20*Assumptions!$B$108/D21*IF(D2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="E98" s="53">
-        <f>E96+E97+E20*Assumptions!$B$108</f>
+        <f>E96+E97+IF(E21=0,0,E20*Assumptions!$B$108/E21*IF(E2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="F98" s="53">
-        <f>F96+F97+F20*Assumptions!$B$108</f>
+        <f>F96+F97+IF(F21=0,0,F20*Assumptions!$B$108/F21*IF(F2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="G98" s="53">
-        <f>G96+G97+G20*Assumptions!$B$108</f>
+        <f>G96+G97+IF(G21=0,0,G20*Assumptions!$B$108/G21*IF(G2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="H98" s="53">
-        <f>H96+H97+H20*Assumptions!$B$108</f>
+        <f>H96+H97+IF(H21=0,0,H20*Assumptions!$B$108/H21*IF(H2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="I98" s="53">
-        <f>I96+I97+I20*Assumptions!$B$108</f>
+        <f>I96+I97+IF(I21=0,0,I20*Assumptions!$B$108/I21*IF(I2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="J98" s="53">
-        <f>J96+J97+J20*Assumptions!$B$108</f>
+        <f>J96+J97+IF(J21=0,0,J20*Assumptions!$B$108/J21*IF(J2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="K98" s="53">
-        <f>K96+K97+K20*Assumptions!$B$108</f>
+        <f>K96+K97+IF(K21=0,0,K20*Assumptions!$B$108/K21*IF(K2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="L98" s="53">
-        <f>L96+L97+L20*Assumptions!$B$108</f>
+        <f>L96+L97+IF(L21=0,0,L20*Assumptions!$B$108/L21*IF(L2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="M98" s="53">
-        <f>M96+M97+M20*Assumptions!$B$108</f>
+        <f>M96+M97+IF(M21=0,0,M20*Assumptions!$B$108/M21*IF(M2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="N98" s="53">
-        <f>N96+N97+N20*Assumptions!$B$108</f>
+        <f>N96+N97+IF(N21=0,0,N20*Assumptions!$B$108/N21*IF(N2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="O98" s="53">
-        <f>O96+O97+O20*Assumptions!$B$108</f>
+        <f>O96+O97+IF(O21=0,0,O20*Assumptions!$B$108/O21*IF(O2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="P98" s="53">
-        <f>P96+P97+P20*Assumptions!$B$108</f>
+        <f>P96+P97+IF(P21=0,0,P20*Assumptions!$B$108/P21*IF(P2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="Q98" s="53">
-        <f>Q96+Q97+Q20*Assumptions!$B$108</f>
+        <f>Q96+Q97+IF(Q21=0,0,Q20*Assumptions!$B$108/Q21*IF(Q2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="R98" s="53">
-        <f>R96+R97+R20*Assumptions!$B$108</f>
+        <f>R96+R97+IF(R21=0,0,R20*Assumptions!$B$108/R21*IF(R2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="S98" s="53">
-        <f>S96+S97+S20*Assumptions!$B$108</f>
+        <f>S96+S97+IF(S21=0,0,S20*Assumptions!$B$108/S21*IF(S2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="T98" s="53">
-        <f>T96+T97+T20*Assumptions!$B$108</f>
+        <f>T96+T97+IF(T21=0,0,T20*Assumptions!$B$108/T21*IF(T2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="U98" s="53">
-        <f>U96+U97+U20*Assumptions!$B$108</f>
+        <f>U96+U97+IF(U21=0,0,U20*Assumptions!$B$108/U21*IF(U2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="V98" s="53">
-        <f>V96+V97+V20*Assumptions!$B$108</f>
+        <f>V96+V97+IF(V21=0,0,V20*Assumptions!$B$108/V21*IF(V2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="W98" s="53">
-        <f>W96+W97+W20*Assumptions!$B$108</f>
+        <f>W96+W97+IF(W21=0,0,W20*Assumptions!$B$108/W21*IF(W2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="X98" s="53">
-        <f>X96+X97+X20*Assumptions!$B$108</f>
+        <f>X96+X97+IF(X21=0,0,X20*Assumptions!$B$108/X21*IF(X2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="Y98" s="53">
-        <f>Y96+Y97+Y20*Assumptions!$B$108</f>
+        <f>Y96+Y97+IF(Y21=0,0,Y20*Assumptions!$B$108/Y21*IF(Y2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="Z98" s="53">
-        <f>Z96+Z97+Z20*Assumptions!$B$108</f>
+        <f>Z96+Z97+IF(Z21=0,0,Z20*Assumptions!$B$108/Z21*IF(Z2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="AA98" s="53">
-        <f>AA96+AA97+AA20*Assumptions!$B$108</f>
+        <f>AA96+AA97+IF(AA21=0,0,AA20*Assumptions!$B$108/AA21*IF(AA2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="AB98" s="53">
-        <f>AB96+AB97+AB20*Assumptions!$B$108</f>
+        <f>AB96+AB97+IF(AB21=0,0,AB20*Assumptions!$B$108/AB21*IF(AB2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="AC98" s="53">
-        <f>AC96+AC97+AC20*Assumptions!$B$108</f>
+        <f>AC96+AC97+IF(AC21=0,0,AC20*Assumptions!$B$108/AC21*IF(AC2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="AD98" s="53">
-        <f>AD96+AD97+AD20*Assumptions!$B$108</f>
+        <f>AD96+AD97+IF(AD21=0,0,AD20*Assumptions!$B$108/AD21*IF(AD2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
       <c r="AE98" s="53">
-        <f>AE96+AE97+AE20*Assumptions!$B$108</f>
+        <f>AE96+AE97+IF(AE21=0,0,AE20*Assumptions!$B$108/AE21*IF(AE2&gt;=Assumptions!$B$54,1,0))</f>
         <v/>
       </c>
     </row>
@@ -18442,7 +18442,7 @@
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AUM decay rate (holder-weighted)</t>
+          <t xml:space="preserve">  Collateral-eligible AUM decay rate (holder-weighted)</t>
         </is>
       </c>
       <c r="B108" s="23" t="inlineStr">
@@ -20106,7 +20106,7 @@
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stream 1a - Entry fee margin, SIP</t>
+          <t xml:space="preserve">  Stream 1a - Entry fee, SIP</t>
         </is>
       </c>
       <c r="B121" s="23" t="inlineStr">
@@ -20115,126 +20115,126 @@
         </is>
       </c>
       <c r="C121" s="54">
-        <f>C105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>C105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="D121" s="54">
-        <f>D105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>D105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="E121" s="54">
-        <f>E105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>E105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="F121" s="54">
-        <f>F105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>F105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="G121" s="54">
-        <f>G105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>G105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="H121" s="54">
-        <f>H105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>H105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="I121" s="54">
-        <f>I105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>I105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="J121" s="54">
-        <f>J105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>J105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="K121" s="54">
-        <f>K105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>K105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="L121" s="54">
-        <f>L105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>L105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="M121" s="54">
-        <f>M105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>M105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="N121" s="54">
-        <f>N105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>N105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="O121" s="54">
-        <f>O105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>O105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="P121" s="54">
-        <f>P105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>P105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Q121" s="54">
-        <f>Q105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Q105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="R121" s="54">
-        <f>R105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>R105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="S121" s="54">
-        <f>S105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>S105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="T121" s="54">
-        <f>T105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>T105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="U121" s="54">
-        <f>U105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>U105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="V121" s="54">
-        <f>V105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>V105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="W121" s="54">
-        <f>W105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>W105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="X121" s="54">
-        <f>X105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>X105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Y121" s="54">
-        <f>Y105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Y105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Z121" s="54">
-        <f>Z105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Z105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AA121" s="54">
-        <f>AA105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AA105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AB121" s="54">
-        <f>AB105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AB105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AC121" s="54">
-        <f>AC105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AC105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AD121" s="54">
-        <f>AD105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AD105*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AE121" s="54">
-        <f>AE105*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AE105*Assumptions!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stream 1b - Entry fee margin, SPOT</t>
+          <t xml:space="preserve">  Stream 1b - Entry fee, SPOT</t>
         </is>
       </c>
       <c r="B122" s="23" t="inlineStr">
@@ -20243,119 +20243,119 @@
         </is>
       </c>
       <c r="C122" s="54">
-        <f>C106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>C106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="D122" s="54">
-        <f>D106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>D106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="E122" s="54">
-        <f>E106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>E106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="F122" s="54">
-        <f>F106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>F106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="G122" s="54">
-        <f>G106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>G106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="H122" s="54">
-        <f>H106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>H106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="I122" s="54">
-        <f>I106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>I106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="J122" s="54">
-        <f>J106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>J106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="K122" s="54">
-        <f>K106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>K106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="L122" s="54">
-        <f>L106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>L106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="M122" s="54">
-        <f>M106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>M106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="N122" s="54">
-        <f>N106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>N106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="O122" s="54">
-        <f>O106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>O106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="P122" s="54">
-        <f>P106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>P106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Q122" s="54">
-        <f>Q106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Q106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="R122" s="54">
-        <f>R106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>R106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="S122" s="54">
-        <f>S106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>S106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="T122" s="54">
-        <f>T106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>T106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="U122" s="54">
-        <f>U106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>U106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="V122" s="54">
-        <f>V106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>V106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="W122" s="54">
-        <f>W106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>W106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="X122" s="54">
-        <f>X106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>X106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Y122" s="54">
-        <f>Y106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Y106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="Z122" s="54">
-        <f>Z106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>Z106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AA122" s="54">
-        <f>AA106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AA106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AB122" s="54">
-        <f>AB106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AB106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AC122" s="54">
-        <f>AC106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AC106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AD122" s="54">
-        <f>AD106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AD106*Assumptions!$B$8</f>
         <v/>
       </c>
       <c r="AE122" s="54">
-        <f>AE106*(Assumptions!$B$8-(1-Assumptions!$B$8)*Assumptions!$B$9)</f>
+        <f>AE106*Assumptions!$B$8</f>
         <v/>
       </c>
     </row>
@@ -22361,9 +22361,9 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>AUM</t>
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>Grams purchased</t>
         </is>
       </c>
       <c r="B143" s="23" t="inlineStr">
@@ -22371,255 +22371,255 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C143" s="54">
+      <c r="C143" s="53">
+        <f>C35+C71+C107</f>
+        <v/>
+      </c>
+      <c r="D143" s="53">
+        <f>D35+D71+D107</f>
+        <v/>
+      </c>
+      <c r="E143" s="53">
+        <f>E35+E71+E107</f>
+        <v/>
+      </c>
+      <c r="F143" s="53">
+        <f>F35+F71+F107</f>
+        <v/>
+      </c>
+      <c r="G143" s="53">
+        <f>G35+G71+G107</f>
+        <v/>
+      </c>
+      <c r="H143" s="53">
+        <f>H35+H71+H107</f>
+        <v/>
+      </c>
+      <c r="I143" s="53">
+        <f>I35+I71+I107</f>
+        <v/>
+      </c>
+      <c r="J143" s="53">
+        <f>J35+J71+J107</f>
+        <v/>
+      </c>
+      <c r="K143" s="53">
+        <f>K35+K71+K107</f>
+        <v/>
+      </c>
+      <c r="L143" s="53">
+        <f>L35+L71+L107</f>
+        <v/>
+      </c>
+      <c r="M143" s="53">
+        <f>M35+M71+M107</f>
+        <v/>
+      </c>
+      <c r="N143" s="53">
+        <f>N35+N71+N107</f>
+        <v/>
+      </c>
+      <c r="O143" s="53">
+        <f>O35+O71+O107</f>
+        <v/>
+      </c>
+      <c r="P143" s="53">
+        <f>P35+P71+P107</f>
+        <v/>
+      </c>
+      <c r="Q143" s="53">
+        <f>Q35+Q71+Q107</f>
+        <v/>
+      </c>
+      <c r="R143" s="53">
+        <f>R35+R71+R107</f>
+        <v/>
+      </c>
+      <c r="S143" s="53">
+        <f>S35+S71+S107</f>
+        <v/>
+      </c>
+      <c r="T143" s="53">
+        <f>T35+T71+T107</f>
+        <v/>
+      </c>
+      <c r="U143" s="53">
+        <f>U35+U71+U107</f>
+        <v/>
+      </c>
+      <c r="V143" s="53">
+        <f>V35+V71+V107</f>
+        <v/>
+      </c>
+      <c r="W143" s="53">
+        <f>W35+W71+W107</f>
+        <v/>
+      </c>
+      <c r="X143" s="53">
+        <f>X35+X71+X107</f>
+        <v/>
+      </c>
+      <c r="Y143" s="53">
+        <f>Y35+Y71+Y107</f>
+        <v/>
+      </c>
+      <c r="Z143" s="53">
+        <f>Z35+Z71+Z107</f>
+        <v/>
+      </c>
+      <c r="AA143" s="53">
+        <f>AA35+AA71+AA107</f>
+        <v/>
+      </c>
+      <c r="AB143" s="53">
+        <f>AB35+AB71+AB107</f>
+        <v/>
+      </c>
+      <c r="AC143" s="53">
+        <f>AC35+AC71+AC107</f>
+        <v/>
+      </c>
+      <c r="AD143" s="53">
+        <f>AD35+AD71+AD107</f>
+        <v/>
+      </c>
+      <c r="AE143" s="53">
+        <f>AE35+AE71+AE107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>COLLATERAL-ELIGIBLE AUM</t>
+        </is>
+      </c>
+      <c r="B144" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C144" s="54">
         <f>C38+C74+C110</f>
         <v/>
       </c>
-      <c r="D143" s="54">
+      <c r="D144" s="54">
         <f>D38+D74+D110</f>
         <v/>
       </c>
-      <c r="E143" s="54">
+      <c r="E144" s="54">
         <f>E38+E74+E110</f>
         <v/>
       </c>
-      <c r="F143" s="54">
+      <c r="F144" s="54">
         <f>F38+F74+F110</f>
         <v/>
       </c>
-      <c r="G143" s="54">
+      <c r="G144" s="54">
         <f>G38+G74+G110</f>
         <v/>
       </c>
-      <c r="H143" s="54">
+      <c r="H144" s="54">
         <f>H38+H74+H110</f>
         <v/>
       </c>
-      <c r="I143" s="54">
+      <c r="I144" s="54">
         <f>I38+I74+I110</f>
         <v/>
       </c>
-      <c r="J143" s="54">
+      <c r="J144" s="54">
         <f>J38+J74+J110</f>
         <v/>
       </c>
-      <c r="K143" s="54">
+      <c r="K144" s="54">
         <f>K38+K74+K110</f>
         <v/>
       </c>
-      <c r="L143" s="54">
+      <c r="L144" s="54">
         <f>L38+L74+L110</f>
         <v/>
       </c>
-      <c r="M143" s="54">
+      <c r="M144" s="54">
         <f>M38+M74+M110</f>
         <v/>
       </c>
-      <c r="N143" s="54">
+      <c r="N144" s="54">
         <f>N38+N74+N110</f>
         <v/>
       </c>
-      <c r="O143" s="54">
+      <c r="O144" s="54">
         <f>O38+O74+O110</f>
         <v/>
       </c>
-      <c r="P143" s="54">
+      <c r="P144" s="54">
         <f>P38+P74+P110</f>
         <v/>
       </c>
-      <c r="Q143" s="54">
+      <c r="Q144" s="54">
         <f>Q38+Q74+Q110</f>
         <v/>
       </c>
-      <c r="R143" s="54">
+      <c r="R144" s="54">
         <f>R38+R74+R110</f>
         <v/>
       </c>
-      <c r="S143" s="54">
+      <c r="S144" s="54">
         <f>S38+S74+S110</f>
         <v/>
       </c>
-      <c r="T143" s="54">
+      <c r="T144" s="54">
         <f>T38+T74+T110</f>
         <v/>
       </c>
-      <c r="U143" s="54">
+      <c r="U144" s="54">
         <f>U38+U74+U110</f>
         <v/>
       </c>
-      <c r="V143" s="54">
+      <c r="V144" s="54">
         <f>V38+V74+V110</f>
         <v/>
       </c>
-      <c r="W143" s="54">
+      <c r="W144" s="54">
         <f>W38+W74+W110</f>
         <v/>
       </c>
-      <c r="X143" s="54">
+      <c r="X144" s="54">
         <f>X38+X74+X110</f>
         <v/>
       </c>
-      <c r="Y143" s="54">
+      <c r="Y144" s="54">
         <f>Y38+Y74+Y110</f>
         <v/>
       </c>
-      <c r="Z143" s="54">
+      <c r="Z144" s="54">
         <f>Z38+Z74+Z110</f>
         <v/>
       </c>
-      <c r="AA143" s="54">
+      <c r="AA144" s="54">
         <f>AA38+AA74+AA110</f>
         <v/>
       </c>
-      <c r="AB143" s="54">
+      <c r="AB144" s="54">
         <f>AB38+AB74+AB110</f>
         <v/>
       </c>
-      <c r="AC143" s="54">
+      <c r="AC144" s="54">
         <f>AC38+AC74+AC110</f>
         <v/>
       </c>
-      <c r="AD143" s="54">
+      <c r="AD144" s="54">
         <f>AD38+AD74+AD110</f>
         <v/>
       </c>
-      <c r="AE143" s="54">
+      <c r="AE144" s="54">
         <f>AE38+AE74+AE110</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>Cleared the six-payment gate</t>
-        </is>
-      </c>
-      <c r="B144" s="23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C144" s="44">
-        <f>C40+C76+C112</f>
-        <v/>
-      </c>
-      <c r="D144" s="44">
-        <f>D40+D76+D112</f>
-        <v/>
-      </c>
-      <c r="E144" s="44">
-        <f>E40+E76+E112</f>
-        <v/>
-      </c>
-      <c r="F144" s="44">
-        <f>F40+F76+F112</f>
-        <v/>
-      </c>
-      <c r="G144" s="44">
-        <f>G40+G76+G112</f>
-        <v/>
-      </c>
-      <c r="H144" s="44">
-        <f>H40+H76+H112</f>
-        <v/>
-      </c>
-      <c r="I144" s="44">
-        <f>I40+I76+I112</f>
-        <v/>
-      </c>
-      <c r="J144" s="44">
-        <f>J40+J76+J112</f>
-        <v/>
-      </c>
-      <c r="K144" s="44">
-        <f>K40+K76+K112</f>
-        <v/>
-      </c>
-      <c r="L144" s="44">
-        <f>L40+L76+L112</f>
-        <v/>
-      </c>
-      <c r="M144" s="44">
-        <f>M40+M76+M112</f>
-        <v/>
-      </c>
-      <c r="N144" s="44">
-        <f>N40+N76+N112</f>
-        <v/>
-      </c>
-      <c r="O144" s="44">
-        <f>O40+O76+O112</f>
-        <v/>
-      </c>
-      <c r="P144" s="44">
-        <f>P40+P76+P112</f>
-        <v/>
-      </c>
-      <c r="Q144" s="44">
-        <f>Q40+Q76+Q112</f>
-        <v/>
-      </c>
-      <c r="R144" s="44">
-        <f>R40+R76+R112</f>
-        <v/>
-      </c>
-      <c r="S144" s="44">
-        <f>S40+S76+S112</f>
-        <v/>
-      </c>
-      <c r="T144" s="44">
-        <f>T40+T76+T112</f>
-        <v/>
-      </c>
-      <c r="U144" s="44">
-        <f>U40+U76+U112</f>
-        <v/>
-      </c>
-      <c r="V144" s="44">
-        <f>V40+V76+V112</f>
-        <v/>
-      </c>
-      <c r="W144" s="44">
-        <f>W40+W76+W112</f>
-        <v/>
-      </c>
-      <c r="X144" s="44">
-        <f>X40+X76+X112</f>
-        <v/>
-      </c>
-      <c r="Y144" s="44">
-        <f>Y40+Y76+Y112</f>
-        <v/>
-      </c>
-      <c r="Z144" s="44">
-        <f>Z40+Z76+Z112</f>
-        <v/>
-      </c>
-      <c r="AA144" s="44">
-        <f>AA40+AA76+AA112</f>
-        <v/>
-      </c>
-      <c r="AB144" s="44">
-        <f>AB40+AB76+AB112</f>
-        <v/>
-      </c>
-      <c r="AC144" s="44">
-        <f>AC40+AC76+AC112</f>
-        <v/>
-      </c>
-      <c r="AD144" s="44">
-        <f>AD40+AD76+AD112</f>
-        <v/>
-      </c>
-      <c r="AE144" s="44">
-        <f>AE40+AE76+AE112</f>
         <v/>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>SIP contributions</t>
+          <t>Cleared the six-payment gate</t>
         </is>
       </c>
       <c r="B145" s="23" t="inlineStr">
@@ -22627,127 +22627,127 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C145" s="54">
-        <f>C33+C69+C105</f>
-        <v/>
-      </c>
-      <c r="D145" s="54">
-        <f>D33+D69+D105</f>
-        <v/>
-      </c>
-      <c r="E145" s="54">
-        <f>E33+E69+E105</f>
-        <v/>
-      </c>
-      <c r="F145" s="54">
-        <f>F33+F69+F105</f>
-        <v/>
-      </c>
-      <c r="G145" s="54">
-        <f>G33+G69+G105</f>
-        <v/>
-      </c>
-      <c r="H145" s="54">
-        <f>H33+H69+H105</f>
-        <v/>
-      </c>
-      <c r="I145" s="54">
-        <f>I33+I69+I105</f>
-        <v/>
-      </c>
-      <c r="J145" s="54">
-        <f>J33+J69+J105</f>
-        <v/>
-      </c>
-      <c r="K145" s="54">
-        <f>K33+K69+K105</f>
-        <v/>
-      </c>
-      <c r="L145" s="54">
-        <f>L33+L69+L105</f>
-        <v/>
-      </c>
-      <c r="M145" s="54">
-        <f>M33+M69+M105</f>
-        <v/>
-      </c>
-      <c r="N145" s="54">
-        <f>N33+N69+N105</f>
-        <v/>
-      </c>
-      <c r="O145" s="54">
-        <f>O33+O69+O105</f>
-        <v/>
-      </c>
-      <c r="P145" s="54">
-        <f>P33+P69+P105</f>
-        <v/>
-      </c>
-      <c r="Q145" s="54">
-        <f>Q33+Q69+Q105</f>
-        <v/>
-      </c>
-      <c r="R145" s="54">
-        <f>R33+R69+R105</f>
-        <v/>
-      </c>
-      <c r="S145" s="54">
-        <f>S33+S69+S105</f>
-        <v/>
-      </c>
-      <c r="T145" s="54">
-        <f>T33+T69+T105</f>
-        <v/>
-      </c>
-      <c r="U145" s="54">
-        <f>U33+U69+U105</f>
-        <v/>
-      </c>
-      <c r="V145" s="54">
-        <f>V33+V69+V105</f>
-        <v/>
-      </c>
-      <c r="W145" s="54">
-        <f>W33+W69+W105</f>
-        <v/>
-      </c>
-      <c r="X145" s="54">
-        <f>X33+X69+X105</f>
-        <v/>
-      </c>
-      <c r="Y145" s="54">
-        <f>Y33+Y69+Y105</f>
-        <v/>
-      </c>
-      <c r="Z145" s="54">
-        <f>Z33+Z69+Z105</f>
-        <v/>
-      </c>
-      <c r="AA145" s="54">
-        <f>AA33+AA69+AA105</f>
-        <v/>
-      </c>
-      <c r="AB145" s="54">
-        <f>AB33+AB69+AB105</f>
-        <v/>
-      </c>
-      <c r="AC145" s="54">
-        <f>AC33+AC69+AC105</f>
-        <v/>
-      </c>
-      <c r="AD145" s="54">
-        <f>AD33+AD69+AD105</f>
-        <v/>
-      </c>
-      <c r="AE145" s="54">
-        <f>AE33+AE69+AE105</f>
+      <c r="C145" s="44">
+        <f>C40+C76+C112</f>
+        <v/>
+      </c>
+      <c r="D145" s="44">
+        <f>D40+D76+D112</f>
+        <v/>
+      </c>
+      <c r="E145" s="44">
+        <f>E40+E76+E112</f>
+        <v/>
+      </c>
+      <c r="F145" s="44">
+        <f>F40+F76+F112</f>
+        <v/>
+      </c>
+      <c r="G145" s="44">
+        <f>G40+G76+G112</f>
+        <v/>
+      </c>
+      <c r="H145" s="44">
+        <f>H40+H76+H112</f>
+        <v/>
+      </c>
+      <c r="I145" s="44">
+        <f>I40+I76+I112</f>
+        <v/>
+      </c>
+      <c r="J145" s="44">
+        <f>J40+J76+J112</f>
+        <v/>
+      </c>
+      <c r="K145" s="44">
+        <f>K40+K76+K112</f>
+        <v/>
+      </c>
+      <c r="L145" s="44">
+        <f>L40+L76+L112</f>
+        <v/>
+      </c>
+      <c r="M145" s="44">
+        <f>M40+M76+M112</f>
+        <v/>
+      </c>
+      <c r="N145" s="44">
+        <f>N40+N76+N112</f>
+        <v/>
+      </c>
+      <c r="O145" s="44">
+        <f>O40+O76+O112</f>
+        <v/>
+      </c>
+      <c r="P145" s="44">
+        <f>P40+P76+P112</f>
+        <v/>
+      </c>
+      <c r="Q145" s="44">
+        <f>Q40+Q76+Q112</f>
+        <v/>
+      </c>
+      <c r="R145" s="44">
+        <f>R40+R76+R112</f>
+        <v/>
+      </c>
+      <c r="S145" s="44">
+        <f>S40+S76+S112</f>
+        <v/>
+      </c>
+      <c r="T145" s="44">
+        <f>T40+T76+T112</f>
+        <v/>
+      </c>
+      <c r="U145" s="44">
+        <f>U40+U76+U112</f>
+        <v/>
+      </c>
+      <c r="V145" s="44">
+        <f>V40+V76+V112</f>
+        <v/>
+      </c>
+      <c r="W145" s="44">
+        <f>W40+W76+W112</f>
+        <v/>
+      </c>
+      <c r="X145" s="44">
+        <f>X40+X76+X112</f>
+        <v/>
+      </c>
+      <c r="Y145" s="44">
+        <f>Y40+Y76+Y112</f>
+        <v/>
+      </c>
+      <c r="Z145" s="44">
+        <f>Z40+Z76+Z112</f>
+        <v/>
+      </c>
+      <c r="AA145" s="44">
+        <f>AA40+AA76+AA112</f>
+        <v/>
+      </c>
+      <c r="AB145" s="44">
+        <f>AB40+AB76+AB112</f>
+        <v/>
+      </c>
+      <c r="AC145" s="44">
+        <f>AC40+AC76+AC112</f>
+        <v/>
+      </c>
+      <c r="AD145" s="44">
+        <f>AD40+AD76+AD112</f>
+        <v/>
+      </c>
+      <c r="AE145" s="44">
+        <f>AE40+AE76+AE112</f>
         <v/>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>Spot purchase volume</t>
+          <t>SIP contributions</t>
         </is>
       </c>
       <c r="B146" s="23" t="inlineStr">
@@ -22756,126 +22756,126 @@
         </is>
       </c>
       <c r="C146" s="54">
-        <f>C34+C70+C106</f>
+        <f>C33+C69+C105</f>
         <v/>
       </c>
       <c r="D146" s="54">
-        <f>D34+D70+D106</f>
+        <f>D33+D69+D105</f>
         <v/>
       </c>
       <c r="E146" s="54">
-        <f>E34+E70+E106</f>
+        <f>E33+E69+E105</f>
         <v/>
       </c>
       <c r="F146" s="54">
-        <f>F34+F70+F106</f>
+        <f>F33+F69+F105</f>
         <v/>
       </c>
       <c r="G146" s="54">
-        <f>G34+G70+G106</f>
+        <f>G33+G69+G105</f>
         <v/>
       </c>
       <c r="H146" s="54">
-        <f>H34+H70+H106</f>
+        <f>H33+H69+H105</f>
         <v/>
       </c>
       <c r="I146" s="54">
-        <f>I34+I70+I106</f>
+        <f>I33+I69+I105</f>
         <v/>
       </c>
       <c r="J146" s="54">
-        <f>J34+J70+J106</f>
+        <f>J33+J69+J105</f>
         <v/>
       </c>
       <c r="K146" s="54">
-        <f>K34+K70+K106</f>
+        <f>K33+K69+K105</f>
         <v/>
       </c>
       <c r="L146" s="54">
-        <f>L34+L70+L106</f>
+        <f>L33+L69+L105</f>
         <v/>
       </c>
       <c r="M146" s="54">
-        <f>M34+M70+M106</f>
+        <f>M33+M69+M105</f>
         <v/>
       </c>
       <c r="N146" s="54">
-        <f>N34+N70+N106</f>
+        <f>N33+N69+N105</f>
         <v/>
       </c>
       <c r="O146" s="54">
-        <f>O34+O70+O106</f>
+        <f>O33+O69+O105</f>
         <v/>
       </c>
       <c r="P146" s="54">
-        <f>P34+P70+P106</f>
+        <f>P33+P69+P105</f>
         <v/>
       </c>
       <c r="Q146" s="54">
-        <f>Q34+Q70+Q106</f>
+        <f>Q33+Q69+Q105</f>
         <v/>
       </c>
       <c r="R146" s="54">
-        <f>R34+R70+R106</f>
+        <f>R33+R69+R105</f>
         <v/>
       </c>
       <c r="S146" s="54">
-        <f>S34+S70+S106</f>
+        <f>S33+S69+S105</f>
         <v/>
       </c>
       <c r="T146" s="54">
-        <f>T34+T70+T106</f>
+        <f>T33+T69+T105</f>
         <v/>
       </c>
       <c r="U146" s="54">
-        <f>U34+U70+U106</f>
+        <f>U33+U69+U105</f>
         <v/>
       </c>
       <c r="V146" s="54">
-        <f>V34+V70+V106</f>
+        <f>V33+V69+V105</f>
         <v/>
       </c>
       <c r="W146" s="54">
-        <f>W34+W70+W106</f>
+        <f>W33+W69+W105</f>
         <v/>
       </c>
       <c r="X146" s="54">
-        <f>X34+X70+X106</f>
+        <f>X33+X69+X105</f>
         <v/>
       </c>
       <c r="Y146" s="54">
-        <f>Y34+Y70+Y106</f>
+        <f>Y33+Y69+Y105</f>
         <v/>
       </c>
       <c r="Z146" s="54">
-        <f>Z34+Z70+Z106</f>
+        <f>Z33+Z69+Z105</f>
         <v/>
       </c>
       <c r="AA146" s="54">
-        <f>AA34+AA70+AA106</f>
+        <f>AA33+AA69+AA105</f>
         <v/>
       </c>
       <c r="AB146" s="54">
-        <f>AB34+AB70+AB106</f>
+        <f>AB33+AB69+AB105</f>
         <v/>
       </c>
       <c r="AC146" s="54">
-        <f>AC34+AC70+AC106</f>
+        <f>AC33+AC69+AC105</f>
         <v/>
       </c>
       <c r="AD146" s="54">
-        <f>AD34+AD70+AD106</f>
+        <f>AD33+AD69+AD105</f>
         <v/>
       </c>
       <c r="AE146" s="54">
-        <f>AE34+AE70+AE106</f>
+        <f>AE33+AE69+AE105</f>
         <v/>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>Card spend</t>
+          <t>Spot purchase volume</t>
         </is>
       </c>
       <c r="B147" s="23" t="inlineStr">
@@ -22884,382 +22884,382 @@
         </is>
       </c>
       <c r="C147" s="54">
-        <f>C46+C82+C118</f>
+        <f>C34+C70+C106</f>
         <v/>
       </c>
       <c r="D147" s="54">
-        <f>D46+D82+D118</f>
+        <f>D34+D70+D106</f>
         <v/>
       </c>
       <c r="E147" s="54">
-        <f>E46+E82+E118</f>
+        <f>E34+E70+E106</f>
         <v/>
       </c>
       <c r="F147" s="54">
-        <f>F46+F82+F118</f>
+        <f>F34+F70+F106</f>
         <v/>
       </c>
       <c r="G147" s="54">
-        <f>G46+G82+G118</f>
+        <f>G34+G70+G106</f>
         <v/>
       </c>
       <c r="H147" s="54">
-        <f>H46+H82+H118</f>
+        <f>H34+H70+H106</f>
         <v/>
       </c>
       <c r="I147" s="54">
-        <f>I46+I82+I118</f>
+        <f>I34+I70+I106</f>
         <v/>
       </c>
       <c r="J147" s="54">
-        <f>J46+J82+J118</f>
+        <f>J34+J70+J106</f>
         <v/>
       </c>
       <c r="K147" s="54">
-        <f>K46+K82+K118</f>
+        <f>K34+K70+K106</f>
         <v/>
       </c>
       <c r="L147" s="54">
-        <f>L46+L82+L118</f>
+        <f>L34+L70+L106</f>
         <v/>
       </c>
       <c r="M147" s="54">
-        <f>M46+M82+M118</f>
+        <f>M34+M70+M106</f>
         <v/>
       </c>
       <c r="N147" s="54">
-        <f>N46+N82+N118</f>
+        <f>N34+N70+N106</f>
         <v/>
       </c>
       <c r="O147" s="54">
-        <f>O46+O82+O118</f>
+        <f>O34+O70+O106</f>
         <v/>
       </c>
       <c r="P147" s="54">
-        <f>P46+P82+P118</f>
+        <f>P34+P70+P106</f>
         <v/>
       </c>
       <c r="Q147" s="54">
-        <f>Q46+Q82+Q118</f>
+        <f>Q34+Q70+Q106</f>
         <v/>
       </c>
       <c r="R147" s="54">
-        <f>R46+R82+R118</f>
+        <f>R34+R70+R106</f>
         <v/>
       </c>
       <c r="S147" s="54">
-        <f>S46+S82+S118</f>
+        <f>S34+S70+S106</f>
         <v/>
       </c>
       <c r="T147" s="54">
-        <f>T46+T82+T118</f>
+        <f>T34+T70+T106</f>
         <v/>
       </c>
       <c r="U147" s="54">
-        <f>U46+U82+U118</f>
+        <f>U34+U70+U106</f>
         <v/>
       </c>
       <c r="V147" s="54">
-        <f>V46+V82+V118</f>
+        <f>V34+V70+V106</f>
         <v/>
       </c>
       <c r="W147" s="54">
-        <f>W46+W82+W118</f>
+        <f>W34+W70+W106</f>
         <v/>
       </c>
       <c r="X147" s="54">
-        <f>X46+X82+X118</f>
+        <f>X34+X70+X106</f>
         <v/>
       </c>
       <c r="Y147" s="54">
-        <f>Y46+Y82+Y118</f>
+        <f>Y34+Y70+Y106</f>
         <v/>
       </c>
       <c r="Z147" s="54">
-        <f>Z46+Z82+Z118</f>
+        <f>Z34+Z70+Z106</f>
         <v/>
       </c>
       <c r="AA147" s="54">
-        <f>AA46+AA82+AA118</f>
+        <f>AA34+AA70+AA106</f>
         <v/>
       </c>
       <c r="AB147" s="54">
-        <f>AB46+AB82+AB118</f>
+        <f>AB34+AB70+AB106</f>
         <v/>
       </c>
       <c r="AC147" s="54">
-        <f>AC46+AC82+AC118</f>
+        <f>AC34+AC70+AC106</f>
         <v/>
       </c>
       <c r="AD147" s="54">
-        <f>AD46+AD82+AD118</f>
+        <f>AD34+AD70+AD106</f>
         <v/>
       </c>
       <c r="AE147" s="54">
-        <f>AE46+AE82+AE118</f>
+        <f>AE34+AE70+AE106</f>
         <v/>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>CHECK: paying + holders = cumulative ever acquired</t>
+          <t>Card spend</t>
         </is>
       </c>
       <c r="B148" s="23" t="inlineStr">
         <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="C148" s="58">
-        <f>C137+C138-C139</f>
-        <v/>
-      </c>
-      <c r="D148" s="58">
-        <f>D137+D138-D139</f>
-        <v/>
-      </c>
-      <c r="E148" s="58">
-        <f>E137+E138-E139</f>
-        <v/>
-      </c>
-      <c r="F148" s="58">
-        <f>F137+F138-F139</f>
-        <v/>
-      </c>
-      <c r="G148" s="58">
-        <f>G137+G138-G139</f>
-        <v/>
-      </c>
-      <c r="H148" s="58">
-        <f>H137+H138-H139</f>
-        <v/>
-      </c>
-      <c r="I148" s="58">
-        <f>I137+I138-I139</f>
-        <v/>
-      </c>
-      <c r="J148" s="58">
-        <f>J137+J138-J139</f>
-        <v/>
-      </c>
-      <c r="K148" s="58">
-        <f>K137+K138-K139</f>
-        <v/>
-      </c>
-      <c r="L148" s="58">
-        <f>L137+L138-L139</f>
-        <v/>
-      </c>
-      <c r="M148" s="58">
-        <f>M137+M138-M139</f>
-        <v/>
-      </c>
-      <c r="N148" s="58">
-        <f>N137+N138-N139</f>
-        <v/>
-      </c>
-      <c r="O148" s="58">
-        <f>O137+O138-O139</f>
-        <v/>
-      </c>
-      <c r="P148" s="58">
-        <f>P137+P138-P139</f>
-        <v/>
-      </c>
-      <c r="Q148" s="58">
-        <f>Q137+Q138-Q139</f>
-        <v/>
-      </c>
-      <c r="R148" s="58">
-        <f>R137+R138-R139</f>
-        <v/>
-      </c>
-      <c r="S148" s="58">
-        <f>S137+S138-S139</f>
-        <v/>
-      </c>
-      <c r="T148" s="58">
-        <f>T137+T138-T139</f>
-        <v/>
-      </c>
-      <c r="U148" s="58">
-        <f>U137+U138-U139</f>
-        <v/>
-      </c>
-      <c r="V148" s="58">
-        <f>V137+V138-V139</f>
-        <v/>
-      </c>
-      <c r="W148" s="58">
-        <f>W137+W138-W139</f>
-        <v/>
-      </c>
-      <c r="X148" s="58">
-        <f>X137+X138-X139</f>
-        <v/>
-      </c>
-      <c r="Y148" s="58">
-        <f>Y137+Y138-Y139</f>
-        <v/>
-      </c>
-      <c r="Z148" s="58">
-        <f>Z137+Z138-Z139</f>
-        <v/>
-      </c>
-      <c r="AA148" s="58">
-        <f>AA137+AA138-AA139</f>
-        <v/>
-      </c>
-      <c r="AB148" s="58">
-        <f>AB137+AB138-AB139</f>
-        <v/>
-      </c>
-      <c r="AC148" s="58">
-        <f>AC137+AC138-AC139</f>
-        <v/>
-      </c>
-      <c r="AD148" s="58">
-        <f>AD137+AD138-AD139</f>
-        <v/>
-      </c>
-      <c r="AE148" s="58">
-        <f>AE137+AE138-AE139</f>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C148" s="54">
+        <f>C46+C82+C118</f>
+        <v/>
+      </c>
+      <c r="D148" s="54">
+        <f>D46+D82+D118</f>
+        <v/>
+      </c>
+      <c r="E148" s="54">
+        <f>E46+E82+E118</f>
+        <v/>
+      </c>
+      <c r="F148" s="54">
+        <f>F46+F82+F118</f>
+        <v/>
+      </c>
+      <c r="G148" s="54">
+        <f>G46+G82+G118</f>
+        <v/>
+      </c>
+      <c r="H148" s="54">
+        <f>H46+H82+H118</f>
+        <v/>
+      </c>
+      <c r="I148" s="54">
+        <f>I46+I82+I118</f>
+        <v/>
+      </c>
+      <c r="J148" s="54">
+        <f>J46+J82+J118</f>
+        <v/>
+      </c>
+      <c r="K148" s="54">
+        <f>K46+K82+K118</f>
+        <v/>
+      </c>
+      <c r="L148" s="54">
+        <f>L46+L82+L118</f>
+        <v/>
+      </c>
+      <c r="M148" s="54">
+        <f>M46+M82+M118</f>
+        <v/>
+      </c>
+      <c r="N148" s="54">
+        <f>N46+N82+N118</f>
+        <v/>
+      </c>
+      <c r="O148" s="54">
+        <f>O46+O82+O118</f>
+        <v/>
+      </c>
+      <c r="P148" s="54">
+        <f>P46+P82+P118</f>
+        <v/>
+      </c>
+      <c r="Q148" s="54">
+        <f>Q46+Q82+Q118</f>
+        <v/>
+      </c>
+      <c r="R148" s="54">
+        <f>R46+R82+R118</f>
+        <v/>
+      </c>
+      <c r="S148" s="54">
+        <f>S46+S82+S118</f>
+        <v/>
+      </c>
+      <c r="T148" s="54">
+        <f>T46+T82+T118</f>
+        <v/>
+      </c>
+      <c r="U148" s="54">
+        <f>U46+U82+U118</f>
+        <v/>
+      </c>
+      <c r="V148" s="54">
+        <f>V46+V82+V118</f>
+        <v/>
+      </c>
+      <c r="W148" s="54">
+        <f>W46+W82+W118</f>
+        <v/>
+      </c>
+      <c r="X148" s="54">
+        <f>X46+X82+X118</f>
+        <v/>
+      </c>
+      <c r="Y148" s="54">
+        <f>Y46+Y82+Y118</f>
+        <v/>
+      </c>
+      <c r="Z148" s="54">
+        <f>Z46+Z82+Z118</f>
+        <v/>
+      </c>
+      <c r="AA148" s="54">
+        <f>AA46+AA82+AA118</f>
+        <v/>
+      </c>
+      <c r="AB148" s="54">
+        <f>AB46+AB82+AB118</f>
+        <v/>
+      </c>
+      <c r="AC148" s="54">
+        <f>AC46+AC82+AC118</f>
+        <v/>
+      </c>
+      <c r="AD148" s="54">
+        <f>AD46+AD82+AD118</f>
+        <v/>
+      </c>
+      <c r="AE148" s="54">
+        <f>AE46+AE82+AE118</f>
         <v/>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AUM per paying customer (memo)</t>
+          <t>CHECK: paying + holders = cumulative ever acquired</t>
         </is>
       </c>
       <c r="B149" s="23" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C149" s="54">
-        <f>IF(C137=0,0,C143/C137)</f>
-        <v/>
-      </c>
-      <c r="D149" s="54">
-        <f>IF(D137=0,0,D143/D137)</f>
-        <v/>
-      </c>
-      <c r="E149" s="54">
-        <f>IF(E137=0,0,E143/E137)</f>
-        <v/>
-      </c>
-      <c r="F149" s="54">
-        <f>IF(F137=0,0,F143/F137)</f>
-        <v/>
-      </c>
-      <c r="G149" s="54">
-        <f>IF(G137=0,0,G143/G137)</f>
-        <v/>
-      </c>
-      <c r="H149" s="54">
-        <f>IF(H137=0,0,H143/H137)</f>
-        <v/>
-      </c>
-      <c r="I149" s="54">
-        <f>IF(I137=0,0,I143/I137)</f>
-        <v/>
-      </c>
-      <c r="J149" s="54">
-        <f>IF(J137=0,0,J143/J137)</f>
-        <v/>
-      </c>
-      <c r="K149" s="54">
-        <f>IF(K137=0,0,K143/K137)</f>
-        <v/>
-      </c>
-      <c r="L149" s="54">
-        <f>IF(L137=0,0,L143/L137)</f>
-        <v/>
-      </c>
-      <c r="M149" s="54">
-        <f>IF(M137=0,0,M143/M137)</f>
-        <v/>
-      </c>
-      <c r="N149" s="54">
-        <f>IF(N137=0,0,N143/N137)</f>
-        <v/>
-      </c>
-      <c r="O149" s="54">
-        <f>IF(O137=0,0,O143/O137)</f>
-        <v/>
-      </c>
-      <c r="P149" s="54">
-        <f>IF(P137=0,0,P143/P137)</f>
-        <v/>
-      </c>
-      <c r="Q149" s="54">
-        <f>IF(Q137=0,0,Q143/Q137)</f>
-        <v/>
-      </c>
-      <c r="R149" s="54">
-        <f>IF(R137=0,0,R143/R137)</f>
-        <v/>
-      </c>
-      <c r="S149" s="54">
-        <f>IF(S137=0,0,S143/S137)</f>
-        <v/>
-      </c>
-      <c r="T149" s="54">
-        <f>IF(T137=0,0,T143/T137)</f>
-        <v/>
-      </c>
-      <c r="U149" s="54">
-        <f>IF(U137=0,0,U143/U137)</f>
-        <v/>
-      </c>
-      <c r="V149" s="54">
-        <f>IF(V137=0,0,V143/V137)</f>
-        <v/>
-      </c>
-      <c r="W149" s="54">
-        <f>IF(W137=0,0,W143/W137)</f>
-        <v/>
-      </c>
-      <c r="X149" s="54">
-        <f>IF(X137=0,0,X143/X137)</f>
-        <v/>
-      </c>
-      <c r="Y149" s="54">
-        <f>IF(Y137=0,0,Y143/Y137)</f>
-        <v/>
-      </c>
-      <c r="Z149" s="54">
-        <f>IF(Z137=0,0,Z143/Z137)</f>
-        <v/>
-      </c>
-      <c r="AA149" s="54">
-        <f>IF(AA137=0,0,AA143/AA137)</f>
-        <v/>
-      </c>
-      <c r="AB149" s="54">
-        <f>IF(AB137=0,0,AB143/AB137)</f>
-        <v/>
-      </c>
-      <c r="AC149" s="54">
-        <f>IF(AC137=0,0,AC143/AC137)</f>
-        <v/>
-      </c>
-      <c r="AD149" s="54">
-        <f>IF(AD137=0,0,AD143/AD137)</f>
-        <v/>
-      </c>
-      <c r="AE149" s="54">
-        <f>IF(AE137=0,0,AE143/AE137)</f>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="C149" s="58">
+        <f>C137+C138-C139</f>
+        <v/>
+      </c>
+      <c r="D149" s="58">
+        <f>D137+D138-D139</f>
+        <v/>
+      </c>
+      <c r="E149" s="58">
+        <f>E137+E138-E139</f>
+        <v/>
+      </c>
+      <c r="F149" s="58">
+        <f>F137+F138-F139</f>
+        <v/>
+      </c>
+      <c r="G149" s="58">
+        <f>G137+G138-G139</f>
+        <v/>
+      </c>
+      <c r="H149" s="58">
+        <f>H137+H138-H139</f>
+        <v/>
+      </c>
+      <c r="I149" s="58">
+        <f>I137+I138-I139</f>
+        <v/>
+      </c>
+      <c r="J149" s="58">
+        <f>J137+J138-J139</f>
+        <v/>
+      </c>
+      <c r="K149" s="58">
+        <f>K137+K138-K139</f>
+        <v/>
+      </c>
+      <c r="L149" s="58">
+        <f>L137+L138-L139</f>
+        <v/>
+      </c>
+      <c r="M149" s="58">
+        <f>M137+M138-M139</f>
+        <v/>
+      </c>
+      <c r="N149" s="58">
+        <f>N137+N138-N139</f>
+        <v/>
+      </c>
+      <c r="O149" s="58">
+        <f>O137+O138-O139</f>
+        <v/>
+      </c>
+      <c r="P149" s="58">
+        <f>P137+P138-P139</f>
+        <v/>
+      </c>
+      <c r="Q149" s="58">
+        <f>Q137+Q138-Q139</f>
+        <v/>
+      </c>
+      <c r="R149" s="58">
+        <f>R137+R138-R139</f>
+        <v/>
+      </c>
+      <c r="S149" s="58">
+        <f>S137+S138-S139</f>
+        <v/>
+      </c>
+      <c r="T149" s="58">
+        <f>T137+T138-T139</f>
+        <v/>
+      </c>
+      <c r="U149" s="58">
+        <f>U137+U138-U139</f>
+        <v/>
+      </c>
+      <c r="V149" s="58">
+        <f>V137+V138-V139</f>
+        <v/>
+      </c>
+      <c r="W149" s="58">
+        <f>W137+W138-W139</f>
+        <v/>
+      </c>
+      <c r="X149" s="58">
+        <f>X137+X138-X139</f>
+        <v/>
+      </c>
+      <c r="Y149" s="58">
+        <f>Y137+Y138-Y139</f>
+        <v/>
+      </c>
+      <c r="Z149" s="58">
+        <f>Z137+Z138-Z139</f>
+        <v/>
+      </c>
+      <c r="AA149" s="58">
+        <f>AA137+AA138-AA139</f>
+        <v/>
+      </c>
+      <c r="AB149" s="58">
+        <f>AB137+AB138-AB139</f>
+        <v/>
+      </c>
+      <c r="AC149" s="58">
+        <f>AC137+AC138-AC139</f>
+        <v/>
+      </c>
+      <c r="AD149" s="58">
+        <f>AD137+AD138-AD139</f>
+        <v/>
+      </c>
+      <c r="AE149" s="58">
+        <f>AE137+AE138-AE139</f>
         <v/>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total credit capacity across cardholders (memo)</t>
+          <t xml:space="preserve">  Collateral-eligible AUM per paying customer (memo)</t>
         </is>
       </c>
       <c r="B150" s="23" t="inlineStr">
@@ -23268,382 +23268,382 @@
         </is>
       </c>
       <c r="C150" s="54">
-        <f>C41*C42+C77*C78+C113*C114</f>
+        <f>IF(C137=0,0,C144/C137)</f>
         <v/>
       </c>
       <c r="D150" s="54">
-        <f>D41*D42+D77*D78+D113*D114</f>
+        <f>IF(D137=0,0,D144/D137)</f>
         <v/>
       </c>
       <c r="E150" s="54">
-        <f>E41*E42+E77*E78+E113*E114</f>
+        <f>IF(E137=0,0,E144/E137)</f>
         <v/>
       </c>
       <c r="F150" s="54">
-        <f>F41*F42+F77*F78+F113*F114</f>
+        <f>IF(F137=0,0,F144/F137)</f>
         <v/>
       </c>
       <c r="G150" s="54">
-        <f>G41*G42+G77*G78+G113*G114</f>
+        <f>IF(G137=0,0,G144/G137)</f>
         <v/>
       </c>
       <c r="H150" s="54">
-        <f>H41*H42+H77*H78+H113*H114</f>
+        <f>IF(H137=0,0,H144/H137)</f>
         <v/>
       </c>
       <c r="I150" s="54">
-        <f>I41*I42+I77*I78+I113*I114</f>
+        <f>IF(I137=0,0,I144/I137)</f>
         <v/>
       </c>
       <c r="J150" s="54">
-        <f>J41*J42+J77*J78+J113*J114</f>
+        <f>IF(J137=0,0,J144/J137)</f>
         <v/>
       </c>
       <c r="K150" s="54">
-        <f>K41*K42+K77*K78+K113*K114</f>
+        <f>IF(K137=0,0,K144/K137)</f>
         <v/>
       </c>
       <c r="L150" s="54">
-        <f>L41*L42+L77*L78+L113*L114</f>
+        <f>IF(L137=0,0,L144/L137)</f>
         <v/>
       </c>
       <c r="M150" s="54">
-        <f>M41*M42+M77*M78+M113*M114</f>
+        <f>IF(M137=0,0,M144/M137)</f>
         <v/>
       </c>
       <c r="N150" s="54">
-        <f>N41*N42+N77*N78+N113*N114</f>
+        <f>IF(N137=0,0,N144/N137)</f>
         <v/>
       </c>
       <c r="O150" s="54">
-        <f>O41*O42+O77*O78+O113*O114</f>
+        <f>IF(O137=0,0,O144/O137)</f>
         <v/>
       </c>
       <c r="P150" s="54">
-        <f>P41*P42+P77*P78+P113*P114</f>
+        <f>IF(P137=0,0,P144/P137)</f>
         <v/>
       </c>
       <c r="Q150" s="54">
-        <f>Q41*Q42+Q77*Q78+Q113*Q114</f>
+        <f>IF(Q137=0,0,Q144/Q137)</f>
         <v/>
       </c>
       <c r="R150" s="54">
-        <f>R41*R42+R77*R78+R113*R114</f>
+        <f>IF(R137=0,0,R144/R137)</f>
         <v/>
       </c>
       <c r="S150" s="54">
-        <f>S41*S42+S77*S78+S113*S114</f>
+        <f>IF(S137=0,0,S144/S137)</f>
         <v/>
       </c>
       <c r="T150" s="54">
-        <f>T41*T42+T77*T78+T113*T114</f>
+        <f>IF(T137=0,0,T144/T137)</f>
         <v/>
       </c>
       <c r="U150" s="54">
-        <f>U41*U42+U77*U78+U113*U114</f>
+        <f>IF(U137=0,0,U144/U137)</f>
         <v/>
       </c>
       <c r="V150" s="54">
-        <f>V41*V42+V77*V78+V113*V114</f>
+        <f>IF(V137=0,0,V144/V137)</f>
         <v/>
       </c>
       <c r="W150" s="54">
-        <f>W41*W42+W77*W78+W113*W114</f>
+        <f>IF(W137=0,0,W144/W137)</f>
         <v/>
       </c>
       <c r="X150" s="54">
-        <f>X41*X42+X77*X78+X113*X114</f>
+        <f>IF(X137=0,0,X144/X137)</f>
         <v/>
       </c>
       <c r="Y150" s="54">
-        <f>Y41*Y42+Y77*Y78+Y113*Y114</f>
+        <f>IF(Y137=0,0,Y144/Y137)</f>
         <v/>
       </c>
       <c r="Z150" s="54">
-        <f>Z41*Z42+Z77*Z78+Z113*Z114</f>
+        <f>IF(Z137=0,0,Z144/Z137)</f>
         <v/>
       </c>
       <c r="AA150" s="54">
-        <f>AA41*AA42+AA77*AA78+AA113*AA114</f>
+        <f>IF(AA137=0,0,AA144/AA137)</f>
         <v/>
       </c>
       <c r="AB150" s="54">
-        <f>AB41*AB42+AB77*AB78+AB113*AB114</f>
+        <f>IF(AB137=0,0,AB144/AB137)</f>
         <v/>
       </c>
       <c r="AC150" s="54">
-        <f>AC41*AC42+AC77*AC78+AC113*AC114</f>
+        <f>IF(AC137=0,0,AC144/AC137)</f>
         <v/>
       </c>
       <c r="AD150" s="54">
-        <f>AD41*AD42+AD77*AD78+AD113*AD114</f>
+        <f>IF(AD137=0,0,AD144/AD137)</f>
         <v/>
       </c>
       <c r="AE150" s="54">
-        <f>AE41*AE42+AE77*AE78+AE113*AE114</f>
+        <f>IF(AE137=0,0,AE144/AE137)</f>
         <v/>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Total credit capacity across cardholders (memo)</t>
+        </is>
+      </c>
+      <c r="B151" s="23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C151" s="54">
+        <f>C41*C42+C77*C78+C113*C114</f>
+        <v/>
+      </c>
+      <c r="D151" s="54">
+        <f>D41*D42+D77*D78+D113*D114</f>
+        <v/>
+      </c>
+      <c r="E151" s="54">
+        <f>E41*E42+E77*E78+E113*E114</f>
+        <v/>
+      </c>
+      <c r="F151" s="54">
+        <f>F41*F42+F77*F78+F113*F114</f>
+        <v/>
+      </c>
+      <c r="G151" s="54">
+        <f>G41*G42+G77*G78+G113*G114</f>
+        <v/>
+      </c>
+      <c r="H151" s="54">
+        <f>H41*H42+H77*H78+H113*H114</f>
+        <v/>
+      </c>
+      <c r="I151" s="54">
+        <f>I41*I42+I77*I78+I113*I114</f>
+        <v/>
+      </c>
+      <c r="J151" s="54">
+        <f>J41*J42+J77*J78+J113*J114</f>
+        <v/>
+      </c>
+      <c r="K151" s="54">
+        <f>K41*K42+K77*K78+K113*K114</f>
+        <v/>
+      </c>
+      <c r="L151" s="54">
+        <f>L41*L42+L77*L78+L113*L114</f>
+        <v/>
+      </c>
+      <c r="M151" s="54">
+        <f>M41*M42+M77*M78+M113*M114</f>
+        <v/>
+      </c>
+      <c r="N151" s="54">
+        <f>N41*N42+N77*N78+N113*N114</f>
+        <v/>
+      </c>
+      <c r="O151" s="54">
+        <f>O41*O42+O77*O78+O113*O114</f>
+        <v/>
+      </c>
+      <c r="P151" s="54">
+        <f>P41*P42+P77*P78+P113*P114</f>
+        <v/>
+      </c>
+      <c r="Q151" s="54">
+        <f>Q41*Q42+Q77*Q78+Q113*Q114</f>
+        <v/>
+      </c>
+      <c r="R151" s="54">
+        <f>R41*R42+R77*R78+R113*R114</f>
+        <v/>
+      </c>
+      <c r="S151" s="54">
+        <f>S41*S42+S77*S78+S113*S114</f>
+        <v/>
+      </c>
+      <c r="T151" s="54">
+        <f>T41*T42+T77*T78+T113*T114</f>
+        <v/>
+      </c>
+      <c r="U151" s="54">
+        <f>U41*U42+U77*U78+U113*U114</f>
+        <v/>
+      </c>
+      <c r="V151" s="54">
+        <f>V41*V42+V77*V78+V113*V114</f>
+        <v/>
+      </c>
+      <c r="W151" s="54">
+        <f>W41*W42+W77*W78+W113*W114</f>
+        <v/>
+      </c>
+      <c r="X151" s="54">
+        <f>X41*X42+X77*X78+X113*X114</f>
+        <v/>
+      </c>
+      <c r="Y151" s="54">
+        <f>Y41*Y42+Y77*Y78+Y113*Y114</f>
+        <v/>
+      </c>
+      <c r="Z151" s="54">
+        <f>Z41*Z42+Z77*Z78+Z113*Z114</f>
+        <v/>
+      </c>
+      <c r="AA151" s="54">
+        <f>AA41*AA42+AA77*AA78+AA113*AA114</f>
+        <v/>
+      </c>
+      <c r="AB151" s="54">
+        <f>AB41*AB42+AB77*AB78+AB113*AB114</f>
+        <v/>
+      </c>
+      <c r="AC151" s="54">
+        <f>AC41*AC42+AC77*AC78+AC113*AC114</f>
+        <v/>
+      </c>
+      <c r="AD151" s="54">
+        <f>AD41*AD42+AD77*AD78+AD113*AD114</f>
+        <v/>
+      </c>
+      <c r="AE151" s="54">
+        <f>AE41*AE42+AE77*AE78+AE113*AE114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">  CHECK: card spend vs credit capacity (must be &lt;= 1.00)</t>
         </is>
       </c>
-      <c r="B151" s="23" t="inlineStr">
+      <c r="B152" s="23" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C151" s="59">
-        <f>IF(C150=0,0,((C46+C82+C118)/C7)/C150)</f>
-        <v/>
-      </c>
-      <c r="D151" s="59">
-        <f>IF(D150=0,0,((D46+D82+D118)/D7)/D150)</f>
-        <v/>
-      </c>
-      <c r="E151" s="59">
-        <f>IF(E150=0,0,((E46+E82+E118)/E7)/E150)</f>
-        <v/>
-      </c>
-      <c r="F151" s="59">
-        <f>IF(F150=0,0,((F46+F82+F118)/F7)/F150)</f>
-        <v/>
-      </c>
-      <c r="G151" s="59">
-        <f>IF(G150=0,0,((G46+G82+G118)/G7)/G150)</f>
-        <v/>
-      </c>
-      <c r="H151" s="59">
-        <f>IF(H150=0,0,((H46+H82+H118)/H7)/H150)</f>
-        <v/>
-      </c>
-      <c r="I151" s="59">
-        <f>IF(I150=0,0,((I46+I82+I118)/I7)/I150)</f>
-        <v/>
-      </c>
-      <c r="J151" s="59">
-        <f>IF(J150=0,0,((J46+J82+J118)/J7)/J150)</f>
-        <v/>
-      </c>
-      <c r="K151" s="59">
-        <f>IF(K150=0,0,((K46+K82+K118)/K7)/K150)</f>
-        <v/>
-      </c>
-      <c r="L151" s="59">
-        <f>IF(L150=0,0,((L46+L82+L118)/L7)/L150)</f>
-        <v/>
-      </c>
-      <c r="M151" s="59">
-        <f>IF(M150=0,0,((M46+M82+M118)/M7)/M150)</f>
-        <v/>
-      </c>
-      <c r="N151" s="59">
-        <f>IF(N150=0,0,((N46+N82+N118)/N7)/N150)</f>
-        <v/>
-      </c>
-      <c r="O151" s="59">
-        <f>IF(O150=0,0,((O46+O82+O118)/O7)/O150)</f>
-        <v/>
-      </c>
-      <c r="P151" s="59">
-        <f>IF(P150=0,0,((P46+P82+P118)/P7)/P150)</f>
-        <v/>
-      </c>
-      <c r="Q151" s="59">
-        <f>IF(Q150=0,0,((Q46+Q82+Q118)/Q7)/Q150)</f>
-        <v/>
-      </c>
-      <c r="R151" s="59">
-        <f>IF(R150=0,0,((R46+R82+R118)/R7)/R150)</f>
-        <v/>
-      </c>
-      <c r="S151" s="59">
-        <f>IF(S150=0,0,((S46+S82+S118)/S7)/S150)</f>
-        <v/>
-      </c>
-      <c r="T151" s="59">
-        <f>IF(T150=0,0,((T46+T82+T118)/T7)/T150)</f>
-        <v/>
-      </c>
-      <c r="U151" s="59">
-        <f>IF(U150=0,0,((U46+U82+U118)/U7)/U150)</f>
-        <v/>
-      </c>
-      <c r="V151" s="59">
-        <f>IF(V150=0,0,((V46+V82+V118)/V7)/V150)</f>
-        <v/>
-      </c>
-      <c r="W151" s="59">
-        <f>IF(W150=0,0,((W46+W82+W118)/W7)/W150)</f>
-        <v/>
-      </c>
-      <c r="X151" s="59">
-        <f>IF(X150=0,0,((X46+X82+X118)/X7)/X150)</f>
-        <v/>
-      </c>
-      <c r="Y151" s="59">
-        <f>IF(Y150=0,0,((Y46+Y82+Y118)/Y7)/Y150)</f>
-        <v/>
-      </c>
-      <c r="Z151" s="59">
-        <f>IF(Z150=0,0,((Z46+Z82+Z118)/Z7)/Z150)</f>
-        <v/>
-      </c>
-      <c r="AA151" s="59">
-        <f>IF(AA150=0,0,((AA46+AA82+AA118)/AA7)/AA150)</f>
-        <v/>
-      </c>
-      <c r="AB151" s="59">
-        <f>IF(AB150=0,0,((AB46+AB82+AB118)/AB7)/AB150)</f>
-        <v/>
-      </c>
-      <c r="AC151" s="59">
-        <f>IF(AC150=0,0,((AC46+AC82+AC118)/AC7)/AC150)</f>
-        <v/>
-      </c>
-      <c r="AD151" s="59">
-        <f>IF(AD150=0,0,((AD46+AD82+AD118)/AD7)/AD150)</f>
-        <v/>
-      </c>
-      <c r="AE151" s="59">
-        <f>IF(AE150=0,0,((AE46+AE82+AE118)/AE7)/AE150)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>Stream 1a - Entry fee margin, SIP</t>
-        </is>
-      </c>
-      <c r="B153" s="23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C153" s="54">
-        <f>C49+C85+C121</f>
-        <v/>
-      </c>
-      <c r="D153" s="54">
-        <f>D49+D85+D121</f>
-        <v/>
-      </c>
-      <c r="E153" s="54">
-        <f>E49+E85+E121</f>
-        <v/>
-      </c>
-      <c r="F153" s="54">
-        <f>F49+F85+F121</f>
-        <v/>
-      </c>
-      <c r="G153" s="54">
-        <f>G49+G85+G121</f>
-        <v/>
-      </c>
-      <c r="H153" s="54">
-        <f>H49+H85+H121</f>
-        <v/>
-      </c>
-      <c r="I153" s="54">
-        <f>I49+I85+I121</f>
-        <v/>
-      </c>
-      <c r="J153" s="54">
-        <f>J49+J85+J121</f>
-        <v/>
-      </c>
-      <c r="K153" s="54">
-        <f>K49+K85+K121</f>
-        <v/>
-      </c>
-      <c r="L153" s="54">
-        <f>L49+L85+L121</f>
-        <v/>
-      </c>
-      <c r="M153" s="54">
-        <f>M49+M85+M121</f>
-        <v/>
-      </c>
-      <c r="N153" s="54">
-        <f>N49+N85+N121</f>
-        <v/>
-      </c>
-      <c r="O153" s="54">
-        <f>O49+O85+O121</f>
-        <v/>
-      </c>
-      <c r="P153" s="54">
-        <f>P49+P85+P121</f>
-        <v/>
-      </c>
-      <c r="Q153" s="54">
-        <f>Q49+Q85+Q121</f>
-        <v/>
-      </c>
-      <c r="R153" s="54">
-        <f>R49+R85+R121</f>
-        <v/>
-      </c>
-      <c r="S153" s="54">
-        <f>S49+S85+S121</f>
-        <v/>
-      </c>
-      <c r="T153" s="54">
-        <f>T49+T85+T121</f>
-        <v/>
-      </c>
-      <c r="U153" s="54">
-        <f>U49+U85+U121</f>
-        <v/>
-      </c>
-      <c r="V153" s="54">
-        <f>V49+V85+V121</f>
-        <v/>
-      </c>
-      <c r="W153" s="54">
-        <f>W49+W85+W121</f>
-        <v/>
-      </c>
-      <c r="X153" s="54">
-        <f>X49+X85+X121</f>
-        <v/>
-      </c>
-      <c r="Y153" s="54">
-        <f>Y49+Y85+Y121</f>
-        <v/>
-      </c>
-      <c r="Z153" s="54">
-        <f>Z49+Z85+Z121</f>
-        <v/>
-      </c>
-      <c r="AA153" s="54">
-        <f>AA49+AA85+AA121</f>
-        <v/>
-      </c>
-      <c r="AB153" s="54">
-        <f>AB49+AB85+AB121</f>
-        <v/>
-      </c>
-      <c r="AC153" s="54">
-        <f>AC49+AC85+AC121</f>
-        <v/>
-      </c>
-      <c r="AD153" s="54">
-        <f>AD49+AD85+AD121</f>
-        <v/>
-      </c>
-      <c r="AE153" s="54">
-        <f>AE49+AE85+AE121</f>
+      <c r="C152" s="59">
+        <f>IF(C151=0,0,((C46+C82+C118)/C7)/C151)</f>
+        <v/>
+      </c>
+      <c r="D152" s="59">
+        <f>IF(D151=0,0,((D46+D82+D118)/D7)/D151)</f>
+        <v/>
+      </c>
+      <c r="E152" s="59">
+        <f>IF(E151=0,0,((E46+E82+E118)/E7)/E151)</f>
+        <v/>
+      </c>
+      <c r="F152" s="59">
+        <f>IF(F151=0,0,((F46+F82+F118)/F7)/F151)</f>
+        <v/>
+      </c>
+      <c r="G152" s="59">
+        <f>IF(G151=0,0,((G46+G82+G118)/G7)/G151)</f>
+        <v/>
+      </c>
+      <c r="H152" s="59">
+        <f>IF(H151=0,0,((H46+H82+H118)/H7)/H151)</f>
+        <v/>
+      </c>
+      <c r="I152" s="59">
+        <f>IF(I151=0,0,((I46+I82+I118)/I7)/I151)</f>
+        <v/>
+      </c>
+      <c r="J152" s="59">
+        <f>IF(J151=0,0,((J46+J82+J118)/J7)/J151)</f>
+        <v/>
+      </c>
+      <c r="K152" s="59">
+        <f>IF(K151=0,0,((K46+K82+K118)/K7)/K151)</f>
+        <v/>
+      </c>
+      <c r="L152" s="59">
+        <f>IF(L151=0,0,((L46+L82+L118)/L7)/L151)</f>
+        <v/>
+      </c>
+      <c r="M152" s="59">
+        <f>IF(M151=0,0,((M46+M82+M118)/M7)/M151)</f>
+        <v/>
+      </c>
+      <c r="N152" s="59">
+        <f>IF(N151=0,0,((N46+N82+N118)/N7)/N151)</f>
+        <v/>
+      </c>
+      <c r="O152" s="59">
+        <f>IF(O151=0,0,((O46+O82+O118)/O7)/O151)</f>
+        <v/>
+      </c>
+      <c r="P152" s="59">
+        <f>IF(P151=0,0,((P46+P82+P118)/P7)/P151)</f>
+        <v/>
+      </c>
+      <c r="Q152" s="59">
+        <f>IF(Q151=0,0,((Q46+Q82+Q118)/Q7)/Q151)</f>
+        <v/>
+      </c>
+      <c r="R152" s="59">
+        <f>IF(R151=0,0,((R46+R82+R118)/R7)/R151)</f>
+        <v/>
+      </c>
+      <c r="S152" s="59">
+        <f>IF(S151=0,0,((S46+S82+S118)/S7)/S151)</f>
+        <v/>
+      </c>
+      <c r="T152" s="59">
+        <f>IF(T151=0,0,((T46+T82+T118)/T7)/T151)</f>
+        <v/>
+      </c>
+      <c r="U152" s="59">
+        <f>IF(U151=0,0,((U46+U82+U118)/U7)/U151)</f>
+        <v/>
+      </c>
+      <c r="V152" s="59">
+        <f>IF(V151=0,0,((V46+V82+V118)/V7)/V151)</f>
+        <v/>
+      </c>
+      <c r="W152" s="59">
+        <f>IF(W151=0,0,((W46+W82+W118)/W7)/W151)</f>
+        <v/>
+      </c>
+      <c r="X152" s="59">
+        <f>IF(X151=0,0,((X46+X82+X118)/X7)/X151)</f>
+        <v/>
+      </c>
+      <c r="Y152" s="59">
+        <f>IF(Y151=0,0,((Y46+Y82+Y118)/Y7)/Y151)</f>
+        <v/>
+      </c>
+      <c r="Z152" s="59">
+        <f>IF(Z151=0,0,((Z46+Z82+Z118)/Z7)/Z151)</f>
+        <v/>
+      </c>
+      <c r="AA152" s="59">
+        <f>IF(AA151=0,0,((AA46+AA82+AA118)/AA7)/AA151)</f>
+        <v/>
+      </c>
+      <c r="AB152" s="59">
+        <f>IF(AB151=0,0,((AB46+AB82+AB118)/AB7)/AB151)</f>
+        <v/>
+      </c>
+      <c r="AC152" s="59">
+        <f>IF(AC151=0,0,((AC46+AC82+AC118)/AC7)/AC151)</f>
+        <v/>
+      </c>
+      <c r="AD152" s="59">
+        <f>IF(AD151=0,0,((AD46+AD82+AD118)/AD7)/AD151)</f>
+        <v/>
+      </c>
+      <c r="AE152" s="59">
+        <f>IF(AE151=0,0,((AE46+AE82+AE118)/AE7)/AE151)</f>
         <v/>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>Stream 1b - Entry fee margin, SPOT</t>
+          <t>Stream 1a - Entry fee, SIP</t>
         </is>
       </c>
       <c r="B154" s="23" t="inlineStr">
@@ -23652,126 +23652,126 @@
         </is>
       </c>
       <c r="C154" s="54">
-        <f>C50+C86+C122</f>
+        <f>C49+C85+C121</f>
         <v/>
       </c>
       <c r="D154" s="54">
-        <f>D50+D86+D122</f>
+        <f>D49+D85+D121</f>
         <v/>
       </c>
       <c r="E154" s="54">
-        <f>E50+E86+E122</f>
+        <f>E49+E85+E121</f>
         <v/>
       </c>
       <c r="F154" s="54">
-        <f>F50+F86+F122</f>
+        <f>F49+F85+F121</f>
         <v/>
       </c>
       <c r="G154" s="54">
-        <f>G50+G86+G122</f>
+        <f>G49+G85+G121</f>
         <v/>
       </c>
       <c r="H154" s="54">
-        <f>H50+H86+H122</f>
+        <f>H49+H85+H121</f>
         <v/>
       </c>
       <c r="I154" s="54">
-        <f>I50+I86+I122</f>
+        <f>I49+I85+I121</f>
         <v/>
       </c>
       <c r="J154" s="54">
-        <f>J50+J86+J122</f>
+        <f>J49+J85+J121</f>
         <v/>
       </c>
       <c r="K154" s="54">
-        <f>K50+K86+K122</f>
+        <f>K49+K85+K121</f>
         <v/>
       </c>
       <c r="L154" s="54">
-        <f>L50+L86+L122</f>
+        <f>L49+L85+L121</f>
         <v/>
       </c>
       <c r="M154" s="54">
-        <f>M50+M86+M122</f>
+        <f>M49+M85+M121</f>
         <v/>
       </c>
       <c r="N154" s="54">
-        <f>N50+N86+N122</f>
+        <f>N49+N85+N121</f>
         <v/>
       </c>
       <c r="O154" s="54">
-        <f>O50+O86+O122</f>
+        <f>O49+O85+O121</f>
         <v/>
       </c>
       <c r="P154" s="54">
-        <f>P50+P86+P122</f>
+        <f>P49+P85+P121</f>
         <v/>
       </c>
       <c r="Q154" s="54">
-        <f>Q50+Q86+Q122</f>
+        <f>Q49+Q85+Q121</f>
         <v/>
       </c>
       <c r="R154" s="54">
-        <f>R50+R86+R122</f>
+        <f>R49+R85+R121</f>
         <v/>
       </c>
       <c r="S154" s="54">
-        <f>S50+S86+S122</f>
+        <f>S49+S85+S121</f>
         <v/>
       </c>
       <c r="T154" s="54">
-        <f>T50+T86+T122</f>
+        <f>T49+T85+T121</f>
         <v/>
       </c>
       <c r="U154" s="54">
-        <f>U50+U86+U122</f>
+        <f>U49+U85+U121</f>
         <v/>
       </c>
       <c r="V154" s="54">
-        <f>V50+V86+V122</f>
+        <f>V49+V85+V121</f>
         <v/>
       </c>
       <c r="W154" s="54">
-        <f>W50+W86+W122</f>
+        <f>W49+W85+W121</f>
         <v/>
       </c>
       <c r="X154" s="54">
-        <f>X50+X86+X122</f>
+        <f>X49+X85+X121</f>
         <v/>
       </c>
       <c r="Y154" s="54">
-        <f>Y50+Y86+Y122</f>
+        <f>Y49+Y85+Y121</f>
         <v/>
       </c>
       <c r="Z154" s="54">
-        <f>Z50+Z86+Z122</f>
+        <f>Z49+Z85+Z121</f>
         <v/>
       </c>
       <c r="AA154" s="54">
-        <f>AA50+AA86+AA122</f>
+        <f>AA49+AA85+AA121</f>
         <v/>
       </c>
       <c r="AB154" s="54">
-        <f>AB50+AB86+AB122</f>
+        <f>AB49+AB85+AB121</f>
         <v/>
       </c>
       <c r="AC154" s="54">
-        <f>AC50+AC86+AC122</f>
+        <f>AC49+AC85+AC121</f>
         <v/>
       </c>
       <c r="AD154" s="54">
-        <f>AD50+AD86+AD122</f>
+        <f>AD49+AD85+AD121</f>
         <v/>
       </c>
       <c r="AE154" s="54">
-        <f>AE50+AE86+AE122</f>
+        <f>AE49+AE85+AE121</f>
         <v/>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>Stream 2 - Card interchange</t>
+          <t>Stream 1b - Entry fee, SPOT</t>
         </is>
       </c>
       <c r="B155" s="23" t="inlineStr">
@@ -23780,126 +23780,126 @@
         </is>
       </c>
       <c r="C155" s="54">
-        <f>C51+C87+C123</f>
+        <f>C50+C86+C122</f>
         <v/>
       </c>
       <c r="D155" s="54">
-        <f>D51+D87+D123</f>
+        <f>D50+D86+D122</f>
         <v/>
       </c>
       <c r="E155" s="54">
-        <f>E51+E87+E123</f>
+        <f>E50+E86+E122</f>
         <v/>
       </c>
       <c r="F155" s="54">
-        <f>F51+F87+F123</f>
+        <f>F50+F86+F122</f>
         <v/>
       </c>
       <c r="G155" s="54">
-        <f>G51+G87+G123</f>
+        <f>G50+G86+G122</f>
         <v/>
       </c>
       <c r="H155" s="54">
-        <f>H51+H87+H123</f>
+        <f>H50+H86+H122</f>
         <v/>
       </c>
       <c r="I155" s="54">
-        <f>I51+I87+I123</f>
+        <f>I50+I86+I122</f>
         <v/>
       </c>
       <c r="J155" s="54">
-        <f>J51+J87+J123</f>
+        <f>J50+J86+J122</f>
         <v/>
       </c>
       <c r="K155" s="54">
-        <f>K51+K87+K123</f>
+        <f>K50+K86+K122</f>
         <v/>
       </c>
       <c r="L155" s="54">
-        <f>L51+L87+L123</f>
+        <f>L50+L86+L122</f>
         <v/>
       </c>
       <c r="M155" s="54">
-        <f>M51+M87+M123</f>
+        <f>M50+M86+M122</f>
         <v/>
       </c>
       <c r="N155" s="54">
-        <f>N51+N87+N123</f>
+        <f>N50+N86+N122</f>
         <v/>
       </c>
       <c r="O155" s="54">
-        <f>O51+O87+O123</f>
+        <f>O50+O86+O122</f>
         <v/>
       </c>
       <c r="P155" s="54">
-        <f>P51+P87+P123</f>
+        <f>P50+P86+P122</f>
         <v/>
       </c>
       <c r="Q155" s="54">
-        <f>Q51+Q87+Q123</f>
+        <f>Q50+Q86+Q122</f>
         <v/>
       </c>
       <c r="R155" s="54">
-        <f>R51+R87+R123</f>
+        <f>R50+R86+R122</f>
         <v/>
       </c>
       <c r="S155" s="54">
-        <f>S51+S87+S123</f>
+        <f>S50+S86+S122</f>
         <v/>
       </c>
       <c r="T155" s="54">
-        <f>T51+T87+T123</f>
+        <f>T50+T86+T122</f>
         <v/>
       </c>
       <c r="U155" s="54">
-        <f>U51+U87+U123</f>
+        <f>U50+U86+U122</f>
         <v/>
       </c>
       <c r="V155" s="54">
-        <f>V51+V87+V123</f>
+        <f>V50+V86+V122</f>
         <v/>
       </c>
       <c r="W155" s="54">
-        <f>W51+W87+W123</f>
+        <f>W50+W86+W122</f>
         <v/>
       </c>
       <c r="X155" s="54">
-        <f>X51+X87+X123</f>
+        <f>X50+X86+X122</f>
         <v/>
       </c>
       <c r="Y155" s="54">
-        <f>Y51+Y87+Y123</f>
+        <f>Y50+Y86+Y122</f>
         <v/>
       </c>
       <c r="Z155" s="54">
-        <f>Z51+Z87+Z123</f>
+        <f>Z50+Z86+Z122</f>
         <v/>
       </c>
       <c r="AA155" s="54">
-        <f>AA51+AA87+AA123</f>
+        <f>AA50+AA86+AA122</f>
         <v/>
       </c>
       <c r="AB155" s="54">
-        <f>AB51+AB87+AB123</f>
+        <f>AB50+AB86+AB122</f>
         <v/>
       </c>
       <c r="AC155" s="54">
-        <f>AC51+AC87+AC123</f>
+        <f>AC50+AC86+AC122</f>
         <v/>
       </c>
       <c r="AD155" s="54">
-        <f>AD51+AD87+AD123</f>
+        <f>AD50+AD86+AD122</f>
         <v/>
       </c>
       <c r="AE155" s="54">
-        <f>AE51+AE87+AE123</f>
+        <f>AE50+AE86+AE122</f>
         <v/>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>Stream 3 - Family plan and Digital Will</t>
+          <t>Stream 2 - Card interchange</t>
         </is>
       </c>
       <c r="B156" s="23" t="inlineStr">
@@ -23908,126 +23908,126 @@
         </is>
       </c>
       <c r="C156" s="54">
-        <f>C52+C88+C124</f>
+        <f>C51+C87+C123</f>
         <v/>
       </c>
       <c r="D156" s="54">
-        <f>D52+D88+D124</f>
+        <f>D51+D87+D123</f>
         <v/>
       </c>
       <c r="E156" s="54">
-        <f>E52+E88+E124</f>
+        <f>E51+E87+E123</f>
         <v/>
       </c>
       <c r="F156" s="54">
-        <f>F52+F88+F124</f>
+        <f>F51+F87+F123</f>
         <v/>
       </c>
       <c r="G156" s="54">
-        <f>G52+G88+G124</f>
+        <f>G51+G87+G123</f>
         <v/>
       </c>
       <c r="H156" s="54">
-        <f>H52+H88+H124</f>
+        <f>H51+H87+H123</f>
         <v/>
       </c>
       <c r="I156" s="54">
-        <f>I52+I88+I124</f>
+        <f>I51+I87+I123</f>
         <v/>
       </c>
       <c r="J156" s="54">
-        <f>J52+J88+J124</f>
+        <f>J51+J87+J123</f>
         <v/>
       </c>
       <c r="K156" s="54">
-        <f>K52+K88+K124</f>
+        <f>K51+K87+K123</f>
         <v/>
       </c>
       <c r="L156" s="54">
-        <f>L52+L88+L124</f>
+        <f>L51+L87+L123</f>
         <v/>
       </c>
       <c r="M156" s="54">
-        <f>M52+M88+M124</f>
+        <f>M51+M87+M123</f>
         <v/>
       </c>
       <c r="N156" s="54">
-        <f>N52+N88+N124</f>
+        <f>N51+N87+N123</f>
         <v/>
       </c>
       <c r="O156" s="54">
-        <f>O52+O88+O124</f>
+        <f>O51+O87+O123</f>
         <v/>
       </c>
       <c r="P156" s="54">
-        <f>P52+P88+P124</f>
+        <f>P51+P87+P123</f>
         <v/>
       </c>
       <c r="Q156" s="54">
-        <f>Q52+Q88+Q124</f>
+        <f>Q51+Q87+Q123</f>
         <v/>
       </c>
       <c r="R156" s="54">
-        <f>R52+R88+R124</f>
+        <f>R51+R87+R123</f>
         <v/>
       </c>
       <c r="S156" s="54">
-        <f>S52+S88+S124</f>
+        <f>S51+S87+S123</f>
         <v/>
       </c>
       <c r="T156" s="54">
-        <f>T52+T88+T124</f>
+        <f>T51+T87+T123</f>
         <v/>
       </c>
       <c r="U156" s="54">
-        <f>U52+U88+U124</f>
+        <f>U51+U87+U123</f>
         <v/>
       </c>
       <c r="V156" s="54">
-        <f>V52+V88+V124</f>
+        <f>V51+V87+V123</f>
         <v/>
       </c>
       <c r="W156" s="54">
-        <f>W52+W88+W124</f>
+        <f>W51+W87+W123</f>
         <v/>
       </c>
       <c r="X156" s="54">
-        <f>X52+X88+X124</f>
+        <f>X51+X87+X123</f>
         <v/>
       </c>
       <c r="Y156" s="54">
-        <f>Y52+Y88+Y124</f>
+        <f>Y51+Y87+Y123</f>
         <v/>
       </c>
       <c r="Z156" s="54">
-        <f>Z52+Z88+Z124</f>
+        <f>Z51+Z87+Z123</f>
         <v/>
       </c>
       <c r="AA156" s="54">
-        <f>AA52+AA88+AA124</f>
+        <f>AA51+AA87+AA123</f>
         <v/>
       </c>
       <c r="AB156" s="54">
-        <f>AB52+AB88+AB124</f>
+        <f>AB51+AB87+AB123</f>
         <v/>
       </c>
       <c r="AC156" s="54">
-        <f>AC52+AC88+AC124</f>
+        <f>AC51+AC87+AC123</f>
         <v/>
       </c>
       <c r="AD156" s="54">
-        <f>AD52+AD88+AD124</f>
+        <f>AD51+AD87+AD123</f>
         <v/>
       </c>
       <c r="AE156" s="54">
-        <f>AE52+AE88+AE124</f>
+        <f>AE51+AE87+AE123</f>
         <v/>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>Stream 4 - Cardholder fees</t>
+          <t>Stream 3 - Family plan and Digital Will</t>
         </is>
       </c>
       <c r="B157" s="23" t="inlineStr">
@@ -24036,126 +24036,126 @@
         </is>
       </c>
       <c r="C157" s="54">
-        <f>C53+C89+C125</f>
+        <f>C52+C88+C124</f>
         <v/>
       </c>
       <c r="D157" s="54">
-        <f>D53+D89+D125</f>
+        <f>D52+D88+D124</f>
         <v/>
       </c>
       <c r="E157" s="54">
-        <f>E53+E89+E125</f>
+        <f>E52+E88+E124</f>
         <v/>
       </c>
       <c r="F157" s="54">
-        <f>F53+F89+F125</f>
+        <f>F52+F88+F124</f>
         <v/>
       </c>
       <c r="G157" s="54">
-        <f>G53+G89+G125</f>
+        <f>G52+G88+G124</f>
         <v/>
       </c>
       <c r="H157" s="54">
-        <f>H53+H89+H125</f>
+        <f>H52+H88+H124</f>
         <v/>
       </c>
       <c r="I157" s="54">
-        <f>I53+I89+I125</f>
+        <f>I52+I88+I124</f>
         <v/>
       </c>
       <c r="J157" s="54">
-        <f>J53+J89+J125</f>
+        <f>J52+J88+J124</f>
         <v/>
       </c>
       <c r="K157" s="54">
-        <f>K53+K89+K125</f>
+        <f>K52+K88+K124</f>
         <v/>
       </c>
       <c r="L157" s="54">
-        <f>L53+L89+L125</f>
+        <f>L52+L88+L124</f>
         <v/>
       </c>
       <c r="M157" s="54">
-        <f>M53+M89+M125</f>
+        <f>M52+M88+M124</f>
         <v/>
       </c>
       <c r="N157" s="54">
-        <f>N53+N89+N125</f>
+        <f>N52+N88+N124</f>
         <v/>
       </c>
       <c r="O157" s="54">
-        <f>O53+O89+O125</f>
+        <f>O52+O88+O124</f>
         <v/>
       </c>
       <c r="P157" s="54">
-        <f>P53+P89+P125</f>
+        <f>P52+P88+P124</f>
         <v/>
       </c>
       <c r="Q157" s="54">
-        <f>Q53+Q89+Q125</f>
+        <f>Q52+Q88+Q124</f>
         <v/>
       </c>
       <c r="R157" s="54">
-        <f>R53+R89+R125</f>
+        <f>R52+R88+R124</f>
         <v/>
       </c>
       <c r="S157" s="54">
-        <f>S53+S89+S125</f>
+        <f>S52+S88+S124</f>
         <v/>
       </c>
       <c r="T157" s="54">
-        <f>T53+T89+T125</f>
+        <f>T52+T88+T124</f>
         <v/>
       </c>
       <c r="U157" s="54">
-        <f>U53+U89+U125</f>
+        <f>U52+U88+U124</f>
         <v/>
       </c>
       <c r="V157" s="54">
-        <f>V53+V89+V125</f>
+        <f>V52+V88+V124</f>
         <v/>
       </c>
       <c r="W157" s="54">
-        <f>W53+W89+W125</f>
+        <f>W52+W88+W124</f>
         <v/>
       </c>
       <c r="X157" s="54">
-        <f>X53+X89+X125</f>
+        <f>X52+X88+X124</f>
         <v/>
       </c>
       <c r="Y157" s="54">
-        <f>Y53+Y89+Y125</f>
+        <f>Y52+Y88+Y124</f>
         <v/>
       </c>
       <c r="Z157" s="54">
-        <f>Z53+Z89+Z125</f>
+        <f>Z52+Z88+Z124</f>
         <v/>
       </c>
       <c r="AA157" s="54">
-        <f>AA53+AA89+AA125</f>
+        <f>AA52+AA88+AA124</f>
         <v/>
       </c>
       <c r="AB157" s="54">
-        <f>AB53+AB89+AB125</f>
+        <f>AB52+AB88+AB124</f>
         <v/>
       </c>
       <c r="AC157" s="54">
-        <f>AC53+AC89+AC125</f>
+        <f>AC52+AC88+AC124</f>
         <v/>
       </c>
       <c r="AD157" s="54">
-        <f>AD53+AD89+AD125</f>
+        <f>AD52+AD88+AD124</f>
         <v/>
       </c>
       <c r="AE157" s="54">
-        <f>AE53+AE89+AE125</f>
+        <f>AE52+AE88+AE124</f>
         <v/>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>Stream 5 - Lending revenue share</t>
+          <t>Stream 4 - Cardholder fees</t>
         </is>
       </c>
       <c r="B158" s="23" t="inlineStr">
@@ -24164,759 +24164,887 @@
         </is>
       </c>
       <c r="C158" s="54">
-        <f>C55+C91+C127</f>
+        <f>C53+C89+C125</f>
         <v/>
       </c>
       <c r="D158" s="54">
-        <f>D55+D91+D127</f>
+        <f>D53+D89+D125</f>
         <v/>
       </c>
       <c r="E158" s="54">
-        <f>E55+E91+E127</f>
+        <f>E53+E89+E125</f>
         <v/>
       </c>
       <c r="F158" s="54">
-        <f>F55+F91+F127</f>
+        <f>F53+F89+F125</f>
         <v/>
       </c>
       <c r="G158" s="54">
-        <f>G55+G91+G127</f>
+        <f>G53+G89+G125</f>
         <v/>
       </c>
       <c r="H158" s="54">
-        <f>H55+H91+H127</f>
+        <f>H53+H89+H125</f>
         <v/>
       </c>
       <c r="I158" s="54">
-        <f>I55+I91+I127</f>
+        <f>I53+I89+I125</f>
         <v/>
       </c>
       <c r="J158" s="54">
-        <f>J55+J91+J127</f>
+        <f>J53+J89+J125</f>
         <v/>
       </c>
       <c r="K158" s="54">
-        <f>K55+K91+K127</f>
+        <f>K53+K89+K125</f>
         <v/>
       </c>
       <c r="L158" s="54">
-        <f>L55+L91+L127</f>
+        <f>L53+L89+L125</f>
         <v/>
       </c>
       <c r="M158" s="54">
-        <f>M55+M91+M127</f>
+        <f>M53+M89+M125</f>
         <v/>
       </c>
       <c r="N158" s="54">
-        <f>N55+N91+N127</f>
+        <f>N53+N89+N125</f>
         <v/>
       </c>
       <c r="O158" s="54">
-        <f>O55+O91+O127</f>
+        <f>O53+O89+O125</f>
         <v/>
       </c>
       <c r="P158" s="54">
-        <f>P55+P91+P127</f>
+        <f>P53+P89+P125</f>
         <v/>
       </c>
       <c r="Q158" s="54">
-        <f>Q55+Q91+Q127</f>
+        <f>Q53+Q89+Q125</f>
         <v/>
       </c>
       <c r="R158" s="54">
-        <f>R55+R91+R127</f>
+        <f>R53+R89+R125</f>
         <v/>
       </c>
       <c r="S158" s="54">
-        <f>S55+S91+S127</f>
+        <f>S53+S89+S125</f>
         <v/>
       </c>
       <c r="T158" s="54">
-        <f>T55+T91+T127</f>
+        <f>T53+T89+T125</f>
         <v/>
       </c>
       <c r="U158" s="54">
-        <f>U55+U91+U127</f>
+        <f>U53+U89+U125</f>
         <v/>
       </c>
       <c r="V158" s="54">
-        <f>V55+V91+V127</f>
+        <f>V53+V89+V125</f>
         <v/>
       </c>
       <c r="W158" s="54">
-        <f>W55+W91+W127</f>
+        <f>W53+W89+W125</f>
         <v/>
       </c>
       <c r="X158" s="54">
-        <f>X55+X91+X127</f>
+        <f>X53+X89+X125</f>
         <v/>
       </c>
       <c r="Y158" s="54">
-        <f>Y55+Y91+Y127</f>
+        <f>Y53+Y89+Y125</f>
         <v/>
       </c>
       <c r="Z158" s="54">
-        <f>Z55+Z91+Z127</f>
+        <f>Z53+Z89+Z125</f>
         <v/>
       </c>
       <c r="AA158" s="54">
-        <f>AA55+AA91+AA127</f>
+        <f>AA53+AA89+AA125</f>
         <v/>
       </c>
       <c r="AB158" s="54">
-        <f>AB55+AB91+AB127</f>
+        <f>AB53+AB89+AB125</f>
         <v/>
       </c>
       <c r="AC158" s="54">
-        <f>AC55+AC91+AC127</f>
+        <f>AC53+AC89+AC125</f>
         <v/>
       </c>
       <c r="AD158" s="54">
-        <f>AD55+AD91+AD127</f>
+        <f>AD53+AD89+AD125</f>
         <v/>
       </c>
       <c r="AE158" s="54">
-        <f>AE55+AE91+AE127</f>
+        <f>AE53+AE89+AE125</f>
         <v/>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>Redemption events (memo - drives cost, not revenue)</t>
+          <t>Stream 5 - Lending revenue share</t>
         </is>
       </c>
       <c r="B159" s="23" t="inlineStr">
         <is>
-          <t>events</t>
-        </is>
-      </c>
-      <c r="C159" s="44">
-        <f>C56+C92+C128</f>
-        <v/>
-      </c>
-      <c r="D159" s="44">
-        <f>D56+D92+D128</f>
-        <v/>
-      </c>
-      <c r="E159" s="44">
-        <f>E56+E92+E128</f>
-        <v/>
-      </c>
-      <c r="F159" s="44">
-        <f>F56+F92+F128</f>
-        <v/>
-      </c>
-      <c r="G159" s="44">
-        <f>G56+G92+G128</f>
-        <v/>
-      </c>
-      <c r="H159" s="44">
-        <f>H56+H92+H128</f>
-        <v/>
-      </c>
-      <c r="I159" s="44">
-        <f>I56+I92+I128</f>
-        <v/>
-      </c>
-      <c r="J159" s="44">
-        <f>J56+J92+J128</f>
-        <v/>
-      </c>
-      <c r="K159" s="44">
-        <f>K56+K92+K128</f>
-        <v/>
-      </c>
-      <c r="L159" s="44">
-        <f>L56+L92+L128</f>
-        <v/>
-      </c>
-      <c r="M159" s="44">
-        <f>M56+M92+M128</f>
-        <v/>
-      </c>
-      <c r="N159" s="44">
-        <f>N56+N92+N128</f>
-        <v/>
-      </c>
-      <c r="O159" s="44">
-        <f>O56+O92+O128</f>
-        <v/>
-      </c>
-      <c r="P159" s="44">
-        <f>P56+P92+P128</f>
-        <v/>
-      </c>
-      <c r="Q159" s="44">
-        <f>Q56+Q92+Q128</f>
-        <v/>
-      </c>
-      <c r="R159" s="44">
-        <f>R56+R92+R128</f>
-        <v/>
-      </c>
-      <c r="S159" s="44">
-        <f>S56+S92+S128</f>
-        <v/>
-      </c>
-      <c r="T159" s="44">
-        <f>T56+T92+T128</f>
-        <v/>
-      </c>
-      <c r="U159" s="44">
-        <f>U56+U92+U128</f>
-        <v/>
-      </c>
-      <c r="V159" s="44">
-        <f>V56+V92+V128</f>
-        <v/>
-      </c>
-      <c r="W159" s="44">
-        <f>W56+W92+W128</f>
-        <v/>
-      </c>
-      <c r="X159" s="44">
-        <f>X56+X92+X128</f>
-        <v/>
-      </c>
-      <c r="Y159" s="44">
-        <f>Y56+Y92+Y128</f>
-        <v/>
-      </c>
-      <c r="Z159" s="44">
-        <f>Z56+Z92+Z128</f>
-        <v/>
-      </c>
-      <c r="AA159" s="44">
-        <f>AA56+AA92+AA128</f>
-        <v/>
-      </c>
-      <c r="AB159" s="44">
-        <f>AB56+AB92+AB128</f>
-        <v/>
-      </c>
-      <c r="AC159" s="44">
-        <f>AC56+AC92+AC128</f>
-        <v/>
-      </c>
-      <c r="AD159" s="44">
-        <f>AD56+AD92+AD128</f>
-        <v/>
-      </c>
-      <c r="AE159" s="44">
-        <f>AE56+AE92+AE128</f>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C159" s="54">
+        <f>C55+C91+C127</f>
+        <v/>
+      </c>
+      <c r="D159" s="54">
+        <f>D55+D91+D127</f>
+        <v/>
+      </c>
+      <c r="E159" s="54">
+        <f>E55+E91+E127</f>
+        <v/>
+      </c>
+      <c r="F159" s="54">
+        <f>F55+F91+F127</f>
+        <v/>
+      </c>
+      <c r="G159" s="54">
+        <f>G55+G91+G127</f>
+        <v/>
+      </c>
+      <c r="H159" s="54">
+        <f>H55+H91+H127</f>
+        <v/>
+      </c>
+      <c r="I159" s="54">
+        <f>I55+I91+I127</f>
+        <v/>
+      </c>
+      <c r="J159" s="54">
+        <f>J55+J91+J127</f>
+        <v/>
+      </c>
+      <c r="K159" s="54">
+        <f>K55+K91+K127</f>
+        <v/>
+      </c>
+      <c r="L159" s="54">
+        <f>L55+L91+L127</f>
+        <v/>
+      </c>
+      <c r="M159" s="54">
+        <f>M55+M91+M127</f>
+        <v/>
+      </c>
+      <c r="N159" s="54">
+        <f>N55+N91+N127</f>
+        <v/>
+      </c>
+      <c r="O159" s="54">
+        <f>O55+O91+O127</f>
+        <v/>
+      </c>
+      <c r="P159" s="54">
+        <f>P55+P91+P127</f>
+        <v/>
+      </c>
+      <c r="Q159" s="54">
+        <f>Q55+Q91+Q127</f>
+        <v/>
+      </c>
+      <c r="R159" s="54">
+        <f>R55+R91+R127</f>
+        <v/>
+      </c>
+      <c r="S159" s="54">
+        <f>S55+S91+S127</f>
+        <v/>
+      </c>
+      <c r="T159" s="54">
+        <f>T55+T91+T127</f>
+        <v/>
+      </c>
+      <c r="U159" s="54">
+        <f>U55+U91+U127</f>
+        <v/>
+      </c>
+      <c r="V159" s="54">
+        <f>V55+V91+V127</f>
+        <v/>
+      </c>
+      <c r="W159" s="54">
+        <f>W55+W91+W127</f>
+        <v/>
+      </c>
+      <c r="X159" s="54">
+        <f>X55+X91+X127</f>
+        <v/>
+      </c>
+      <c r="Y159" s="54">
+        <f>Y55+Y91+Y127</f>
+        <v/>
+      </c>
+      <c r="Z159" s="54">
+        <f>Z55+Z91+Z127</f>
+        <v/>
+      </c>
+      <c r="AA159" s="54">
+        <f>AA55+AA91+AA127</f>
+        <v/>
+      </c>
+      <c r="AB159" s="54">
+        <f>AB55+AB91+AB127</f>
+        <v/>
+      </c>
+      <c r="AC159" s="54">
+        <f>AC55+AC91+AC127</f>
+        <v/>
+      </c>
+      <c r="AD159" s="54">
+        <f>AD55+AD91+AD127</f>
+        <v/>
+      </c>
+      <c r="AE159" s="54">
+        <f>AE55+AE91+AE127</f>
         <v/>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
+          <t>Redemption events (memo - drives cost, not revenue)</t>
+        </is>
+      </c>
+      <c r="B160" s="23" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="C160" s="44">
+        <f>C56+C92+C128</f>
+        <v/>
+      </c>
+      <c r="D160" s="44">
+        <f>D56+D92+D128</f>
+        <v/>
+      </c>
+      <c r="E160" s="44">
+        <f>E56+E92+E128</f>
+        <v/>
+      </c>
+      <c r="F160" s="44">
+        <f>F56+F92+F128</f>
+        <v/>
+      </c>
+      <c r="G160" s="44">
+        <f>G56+G92+G128</f>
+        <v/>
+      </c>
+      <c r="H160" s="44">
+        <f>H56+H92+H128</f>
+        <v/>
+      </c>
+      <c r="I160" s="44">
+        <f>I56+I92+I128</f>
+        <v/>
+      </c>
+      <c r="J160" s="44">
+        <f>J56+J92+J128</f>
+        <v/>
+      </c>
+      <c r="K160" s="44">
+        <f>K56+K92+K128</f>
+        <v/>
+      </c>
+      <c r="L160" s="44">
+        <f>L56+L92+L128</f>
+        <v/>
+      </c>
+      <c r="M160" s="44">
+        <f>M56+M92+M128</f>
+        <v/>
+      </c>
+      <c r="N160" s="44">
+        <f>N56+N92+N128</f>
+        <v/>
+      </c>
+      <c r="O160" s="44">
+        <f>O56+O92+O128</f>
+        <v/>
+      </c>
+      <c r="P160" s="44">
+        <f>P56+P92+P128</f>
+        <v/>
+      </c>
+      <c r="Q160" s="44">
+        <f>Q56+Q92+Q128</f>
+        <v/>
+      </c>
+      <c r="R160" s="44">
+        <f>R56+R92+R128</f>
+        <v/>
+      </c>
+      <c r="S160" s="44">
+        <f>S56+S92+S128</f>
+        <v/>
+      </c>
+      <c r="T160" s="44">
+        <f>T56+T92+T128</f>
+        <v/>
+      </c>
+      <c r="U160" s="44">
+        <f>U56+U92+U128</f>
+        <v/>
+      </c>
+      <c r="V160" s="44">
+        <f>V56+V92+V128</f>
+        <v/>
+      </c>
+      <c r="W160" s="44">
+        <f>W56+W92+W128</f>
+        <v/>
+      </c>
+      <c r="X160" s="44">
+        <f>X56+X92+X128</f>
+        <v/>
+      </c>
+      <c r="Y160" s="44">
+        <f>Y56+Y92+Y128</f>
+        <v/>
+      </c>
+      <c r="Z160" s="44">
+        <f>Z56+Z92+Z128</f>
+        <v/>
+      </c>
+      <c r="AA160" s="44">
+        <f>AA56+AA92+AA128</f>
+        <v/>
+      </c>
+      <c r="AB160" s="44">
+        <f>AB56+AB92+AB128</f>
+        <v/>
+      </c>
+      <c r="AC160" s="44">
+        <f>AC56+AC92+AC128</f>
+        <v/>
+      </c>
+      <c r="AD160" s="44">
+        <f>AD56+AD92+AD128</f>
+        <v/>
+      </c>
+      <c r="AE160" s="44">
+        <f>AE56+AE92+AE128</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
           <t>Card authorisations (memo - drives cost, not revenue)</t>
         </is>
       </c>
-      <c r="B160" s="23" t="inlineStr">
+      <c r="B161" s="23" t="inlineStr">
         <is>
           <t>events</t>
         </is>
       </c>
-      <c r="C160" s="44">
+      <c r="C161" s="44">
         <f>C48+C84+C120</f>
         <v/>
       </c>
-      <c r="D160" s="44">
+      <c r="D161" s="44">
         <f>D48+D84+D120</f>
         <v/>
       </c>
-      <c r="E160" s="44">
+      <c r="E161" s="44">
         <f>E48+E84+E120</f>
         <v/>
       </c>
-      <c r="F160" s="44">
+      <c r="F161" s="44">
         <f>F48+F84+F120</f>
         <v/>
       </c>
-      <c r="G160" s="44">
+      <c r="G161" s="44">
         <f>G48+G84+G120</f>
         <v/>
       </c>
-      <c r="H160" s="44">
+      <c r="H161" s="44">
         <f>H48+H84+H120</f>
         <v/>
       </c>
-      <c r="I160" s="44">
+      <c r="I161" s="44">
         <f>I48+I84+I120</f>
         <v/>
       </c>
-      <c r="J160" s="44">
+      <c r="J161" s="44">
         <f>J48+J84+J120</f>
         <v/>
       </c>
-      <c r="K160" s="44">
+      <c r="K161" s="44">
         <f>K48+K84+K120</f>
         <v/>
       </c>
-      <c r="L160" s="44">
+      <c r="L161" s="44">
         <f>L48+L84+L120</f>
         <v/>
       </c>
-      <c r="M160" s="44">
+      <c r="M161" s="44">
         <f>M48+M84+M120</f>
         <v/>
       </c>
-      <c r="N160" s="44">
+      <c r="N161" s="44">
         <f>N48+N84+N120</f>
         <v/>
       </c>
-      <c r="O160" s="44">
+      <c r="O161" s="44">
         <f>O48+O84+O120</f>
         <v/>
       </c>
-      <c r="P160" s="44">
+      <c r="P161" s="44">
         <f>P48+P84+P120</f>
         <v/>
       </c>
-      <c r="Q160" s="44">
+      <c r="Q161" s="44">
         <f>Q48+Q84+Q120</f>
         <v/>
       </c>
-      <c r="R160" s="44">
+      <c r="R161" s="44">
         <f>R48+R84+R120</f>
         <v/>
       </c>
-      <c r="S160" s="44">
+      <c r="S161" s="44">
         <f>S48+S84+S120</f>
         <v/>
       </c>
-      <c r="T160" s="44">
+      <c r="T161" s="44">
         <f>T48+T84+T120</f>
         <v/>
       </c>
-      <c r="U160" s="44">
+      <c r="U161" s="44">
         <f>U48+U84+U120</f>
         <v/>
       </c>
-      <c r="V160" s="44">
+      <c r="V161" s="44">
         <f>V48+V84+V120</f>
         <v/>
       </c>
-      <c r="W160" s="44">
+      <c r="W161" s="44">
         <f>W48+W84+W120</f>
         <v/>
       </c>
-      <c r="X160" s="44">
+      <c r="X161" s="44">
         <f>X48+X84+X120</f>
         <v/>
       </c>
-      <c r="Y160" s="44">
+      <c r="Y161" s="44">
         <f>Y48+Y84+Y120</f>
         <v/>
       </c>
-      <c r="Z160" s="44">
+      <c r="Z161" s="44">
         <f>Z48+Z84+Z120</f>
         <v/>
       </c>
-      <c r="AA160" s="44">
+      <c r="AA161" s="44">
         <f>AA48+AA84+AA120</f>
         <v/>
       </c>
-      <c r="AB160" s="44">
+      <c r="AB161" s="44">
         <f>AB48+AB84+AB120</f>
         <v/>
       </c>
-      <c r="AC160" s="44">
+      <c r="AC161" s="44">
         <f>AC48+AC84+AC120</f>
         <v/>
       </c>
-      <c r="AD160" s="44">
+      <c r="AD161" s="44">
         <f>AD48+AD84+AD120</f>
         <v/>
       </c>
-      <c r="AE160" s="44">
+      <c r="AE161" s="44">
         <f>AE48+AE84+AE120</f>
         <v/>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="3" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t>TOTAL NET REVENUE</t>
         </is>
       </c>
-      <c r="B161" s="23" t="inlineStr">
+      <c r="B162" s="23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="C161" s="56">
+      <c r="C162" s="56">
         <f>C57+C93+C129+C133</f>
         <v/>
       </c>
-      <c r="D161" s="56">
+      <c r="D162" s="56">
         <f>D57+D93+D129+D133</f>
         <v/>
       </c>
-      <c r="E161" s="56">
+      <c r="E162" s="56">
         <f>E57+E93+E129+E133</f>
         <v/>
       </c>
-      <c r="F161" s="56">
+      <c r="F162" s="56">
         <f>F57+F93+F129+F133</f>
         <v/>
       </c>
-      <c r="G161" s="56">
+      <c r="G162" s="56">
         <f>G57+G93+G129+G133</f>
         <v/>
       </c>
-      <c r="H161" s="56">
+      <c r="H162" s="56">
         <f>H57+H93+H129+H133</f>
         <v/>
       </c>
-      <c r="I161" s="56">
+      <c r="I162" s="56">
         <f>I57+I93+I129+I133</f>
         <v/>
       </c>
-      <c r="J161" s="56">
+      <c r="J162" s="56">
         <f>J57+J93+J129+J133</f>
         <v/>
       </c>
-      <c r="K161" s="56">
+      <c r="K162" s="56">
         <f>K57+K93+K129+K133</f>
         <v/>
       </c>
-      <c r="L161" s="56">
+      <c r="L162" s="56">
         <f>L57+L93+L129+L133</f>
         <v/>
       </c>
-      <c r="M161" s="56">
+      <c r="M162" s="56">
         <f>M57+M93+M129+M133</f>
         <v/>
       </c>
-      <c r="N161" s="56">
+      <c r="N162" s="56">
         <f>N57+N93+N129+N133</f>
         <v/>
       </c>
-      <c r="O161" s="56">
+      <c r="O162" s="56">
         <f>O57+O93+O129+O133</f>
         <v/>
       </c>
-      <c r="P161" s="56">
+      <c r="P162" s="56">
         <f>P57+P93+P129+P133</f>
         <v/>
       </c>
-      <c r="Q161" s="56">
+      <c r="Q162" s="56">
         <f>Q57+Q93+Q129+Q133</f>
         <v/>
       </c>
-      <c r="R161" s="56">
+      <c r="R162" s="56">
         <f>R57+R93+R129+R133</f>
         <v/>
       </c>
-      <c r="S161" s="56">
+      <c r="S162" s="56">
         <f>S57+S93+S129+S133</f>
         <v/>
       </c>
-      <c r="T161" s="56">
+      <c r="T162" s="56">
         <f>T57+T93+T129+T133</f>
         <v/>
       </c>
-      <c r="U161" s="56">
+      <c r="U162" s="56">
         <f>U57+U93+U129+U133</f>
         <v/>
       </c>
-      <c r="V161" s="56">
+      <c r="V162" s="56">
         <f>V57+V93+V129+V133</f>
         <v/>
       </c>
-      <c r="W161" s="56">
+      <c r="W162" s="56">
         <f>W57+W93+W129+W133</f>
         <v/>
       </c>
-      <c r="X161" s="56">
+      <c r="X162" s="56">
         <f>X57+X93+X129+X133</f>
         <v/>
       </c>
-      <c r="Y161" s="56">
+      <c r="Y162" s="56">
         <f>Y57+Y93+Y129+Y133</f>
         <v/>
       </c>
-      <c r="Z161" s="56">
+      <c r="Z162" s="56">
         <f>Z57+Z93+Z129+Z133</f>
         <v/>
       </c>
-      <c r="AA161" s="56">
+      <c r="AA162" s="56">
         <f>AA57+AA93+AA129+AA133</f>
         <v/>
       </c>
-      <c r="AB161" s="56">
+      <c r="AB162" s="56">
         <f>AB57+AB93+AB129+AB133</f>
         <v/>
       </c>
-      <c r="AC161" s="56">
+      <c r="AC162" s="56">
         <f>AC57+AC93+AC129+AC133</f>
         <v/>
       </c>
-      <c r="AD161" s="56">
+      <c r="AD162" s="56">
         <f>AD57+AD93+AD129+AD133</f>
         <v/>
       </c>
-      <c r="AE161" s="56">
+      <c r="AE162" s="56">
         <f>AE57+AE93+AE129+AE133</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="6" t="inlineStr">
-        <is>
-          <t>Net revenue per paying customer (annualised)</t>
-        </is>
-      </c>
-      <c r="B162" s="23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C162" s="54">
-        <f>IF(C137=0,0,C161/C137/C7*12)</f>
-        <v/>
-      </c>
-      <c r="D162" s="54">
-        <f>IF(D137=0,0,D161/D137/D7*12)</f>
-        <v/>
-      </c>
-      <c r="E162" s="54">
-        <f>IF(E137=0,0,E161/E137/E7*12)</f>
-        <v/>
-      </c>
-      <c r="F162" s="54">
-        <f>IF(F137=0,0,F161/F137/F7*12)</f>
-        <v/>
-      </c>
-      <c r="G162" s="54">
-        <f>IF(G137=0,0,G161/G137/G7*12)</f>
-        <v/>
-      </c>
-      <c r="H162" s="54">
-        <f>IF(H137=0,0,H161/H137/H7*12)</f>
-        <v/>
-      </c>
-      <c r="I162" s="54">
-        <f>IF(I137=0,0,I161/I137/I7*12)</f>
-        <v/>
-      </c>
-      <c r="J162" s="54">
-        <f>IF(J137=0,0,J161/J137/J7*12)</f>
-        <v/>
-      </c>
-      <c r="K162" s="54">
-        <f>IF(K137=0,0,K161/K137/K7*12)</f>
-        <v/>
-      </c>
-      <c r="L162" s="54">
-        <f>IF(L137=0,0,L161/L137/L7*12)</f>
-        <v/>
-      </c>
-      <c r="M162" s="54">
-        <f>IF(M137=0,0,M161/M137/M7*12)</f>
-        <v/>
-      </c>
-      <c r="N162" s="54">
-        <f>IF(N137=0,0,N161/N137/N7*12)</f>
-        <v/>
-      </c>
-      <c r="O162" s="54">
-        <f>IF(O137=0,0,O161/O137/O7*12)</f>
-        <v/>
-      </c>
-      <c r="P162" s="54">
-        <f>IF(P137=0,0,P161/P137/P7*12)</f>
-        <v/>
-      </c>
-      <c r="Q162" s="54">
-        <f>IF(Q137=0,0,Q161/Q137/Q7*12)</f>
-        <v/>
-      </c>
-      <c r="R162" s="54">
-        <f>IF(R137=0,0,R161/R137/R7*12)</f>
-        <v/>
-      </c>
-      <c r="S162" s="54">
-        <f>IF(S137=0,0,S161/S137/S7*12)</f>
-        <v/>
-      </c>
-      <c r="T162" s="54">
-        <f>IF(T137=0,0,T161/T137/T7*12)</f>
-        <v/>
-      </c>
-      <c r="U162" s="54">
-        <f>IF(U137=0,0,U161/U137/U7*12)</f>
-        <v/>
-      </c>
-      <c r="V162" s="54">
-        <f>IF(V137=0,0,V161/V137/V7*12)</f>
-        <v/>
-      </c>
-      <c r="W162" s="54">
-        <f>IF(W137=0,0,W161/W137/W7*12)</f>
-        <v/>
-      </c>
-      <c r="X162" s="54">
-        <f>IF(X137=0,0,X161/X137/X7*12)</f>
-        <v/>
-      </c>
-      <c r="Y162" s="54">
-        <f>IF(Y137=0,0,Y161/Y137/Y7*12)</f>
-        <v/>
-      </c>
-      <c r="Z162" s="54">
-        <f>IF(Z137=0,0,Z161/Z137/Z7*12)</f>
-        <v/>
-      </c>
-      <c r="AA162" s="54">
-        <f>IF(AA137=0,0,AA161/AA137/AA7*12)</f>
-        <v/>
-      </c>
-      <c r="AB162" s="54">
-        <f>IF(AB137=0,0,AB161/AB137/AB7*12)</f>
-        <v/>
-      </c>
-      <c r="AC162" s="54">
-        <f>IF(AC137=0,0,AC161/AC137/AC7*12)</f>
-        <v/>
-      </c>
-      <c r="AD162" s="54">
-        <f>IF(AD137=0,0,AD161/AD137/AD7*12)</f>
-        <v/>
-      </c>
-      <c r="AE162" s="54">
-        <f>IF(AE137=0,0,AE161/AE137/AE7*12)</f>
         <v/>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
+          <t>Net revenue per paying customer (annualised)</t>
+        </is>
+      </c>
+      <c r="B163" s="23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C163" s="54">
+        <f>IF(C137=0,0,C162/C137/C7*12)</f>
+        <v/>
+      </c>
+      <c r="D163" s="54">
+        <f>IF(D137=0,0,D162/D137/D7*12)</f>
+        <v/>
+      </c>
+      <c r="E163" s="54">
+        <f>IF(E137=0,0,E162/E137/E7*12)</f>
+        <v/>
+      </c>
+      <c r="F163" s="54">
+        <f>IF(F137=0,0,F162/F137/F7*12)</f>
+        <v/>
+      </c>
+      <c r="G163" s="54">
+        <f>IF(G137=0,0,G162/G137/G7*12)</f>
+        <v/>
+      </c>
+      <c r="H163" s="54">
+        <f>IF(H137=0,0,H162/H137/H7*12)</f>
+        <v/>
+      </c>
+      <c r="I163" s="54">
+        <f>IF(I137=0,0,I162/I137/I7*12)</f>
+        <v/>
+      </c>
+      <c r="J163" s="54">
+        <f>IF(J137=0,0,J162/J137/J7*12)</f>
+        <v/>
+      </c>
+      <c r="K163" s="54">
+        <f>IF(K137=0,0,K162/K137/K7*12)</f>
+        <v/>
+      </c>
+      <c r="L163" s="54">
+        <f>IF(L137=0,0,L162/L137/L7*12)</f>
+        <v/>
+      </c>
+      <c r="M163" s="54">
+        <f>IF(M137=0,0,M162/M137/M7*12)</f>
+        <v/>
+      </c>
+      <c r="N163" s="54">
+        <f>IF(N137=0,0,N162/N137/N7*12)</f>
+        <v/>
+      </c>
+      <c r="O163" s="54">
+        <f>IF(O137=0,0,O162/O137/O7*12)</f>
+        <v/>
+      </c>
+      <c r="P163" s="54">
+        <f>IF(P137=0,0,P162/P137/P7*12)</f>
+        <v/>
+      </c>
+      <c r="Q163" s="54">
+        <f>IF(Q137=0,0,Q162/Q137/Q7*12)</f>
+        <v/>
+      </c>
+      <c r="R163" s="54">
+        <f>IF(R137=0,0,R162/R137/R7*12)</f>
+        <v/>
+      </c>
+      <c r="S163" s="54">
+        <f>IF(S137=0,0,S162/S137/S7*12)</f>
+        <v/>
+      </c>
+      <c r="T163" s="54">
+        <f>IF(T137=0,0,T162/T137/T7*12)</f>
+        <v/>
+      </c>
+      <c r="U163" s="54">
+        <f>IF(U137=0,0,U162/U137/U7*12)</f>
+        <v/>
+      </c>
+      <c r="V163" s="54">
+        <f>IF(V137=0,0,V162/V137/V7*12)</f>
+        <v/>
+      </c>
+      <c r="W163" s="54">
+        <f>IF(W137=0,0,W162/W137/W7*12)</f>
+        <v/>
+      </c>
+      <c r="X163" s="54">
+        <f>IF(X137=0,0,X162/X137/X7*12)</f>
+        <v/>
+      </c>
+      <c r="Y163" s="54">
+        <f>IF(Y137=0,0,Y162/Y137/Y7*12)</f>
+        <v/>
+      </c>
+      <c r="Z163" s="54">
+        <f>IF(Z137=0,0,Z162/Z137/Z7*12)</f>
+        <v/>
+      </c>
+      <c r="AA163" s="54">
+        <f>IF(AA137=0,0,AA162/AA137/AA7*12)</f>
+        <v/>
+      </c>
+      <c r="AB163" s="54">
+        <f>IF(AB137=0,0,AB162/AB137/AB7*12)</f>
+        <v/>
+      </c>
+      <c r="AC163" s="54">
+        <f>IF(AC137=0,0,AC162/AC137/AC7*12)</f>
+        <v/>
+      </c>
+      <c r="AD163" s="54">
+        <f>IF(AD137=0,0,AD162/AD137/AD7*12)</f>
+        <v/>
+      </c>
+      <c r="AE163" s="54">
+        <f>IF(AE137=0,0,AE162/AE137/AE7*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
           <t>CHECK: regional subtotals + B2B = sum of streams</t>
         </is>
       </c>
-      <c r="B163" s="23" t="inlineStr">
+      <c r="B164" s="23" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="C163" s="58">
-        <f>C161-(C153+C154+C155+C156+C157+C158+C133)</f>
-        <v/>
-      </c>
-      <c r="D163" s="58">
-        <f>D161-(D153+D154+D155+D156+D157+D158+D133)</f>
-        <v/>
-      </c>
-      <c r="E163" s="58">
-        <f>E161-(E153+E154+E155+E156+E157+E158+E133)</f>
-        <v/>
-      </c>
-      <c r="F163" s="58">
-        <f>F161-(F153+F154+F155+F156+F157+F158+F133)</f>
-        <v/>
-      </c>
-      <c r="G163" s="58">
-        <f>G161-(G153+G154+G155+G156+G157+G158+G133)</f>
-        <v/>
-      </c>
-      <c r="H163" s="58">
-        <f>H161-(H153+H154+H155+H156+H157+H158+H133)</f>
-        <v/>
-      </c>
-      <c r="I163" s="58">
-        <f>I161-(I153+I154+I155+I156+I157+I158+I133)</f>
-        <v/>
-      </c>
-      <c r="J163" s="58">
-        <f>J161-(J153+J154+J155+J156+J157+J158+J133)</f>
-        <v/>
-      </c>
-      <c r="K163" s="58">
-        <f>K161-(K153+K154+K155+K156+K157+K158+K133)</f>
-        <v/>
-      </c>
-      <c r="L163" s="58">
-        <f>L161-(L153+L154+L155+L156+L157+L158+L133)</f>
-        <v/>
-      </c>
-      <c r="M163" s="58">
-        <f>M161-(M153+M154+M155+M156+M157+M158+M133)</f>
-        <v/>
-      </c>
-      <c r="N163" s="58">
-        <f>N161-(N153+N154+N155+N156+N157+N158+N133)</f>
-        <v/>
-      </c>
-      <c r="O163" s="58">
-        <f>O161-(O153+O154+O155+O156+O157+O158+O133)</f>
-        <v/>
-      </c>
-      <c r="P163" s="58">
-        <f>P161-(P153+P154+P155+P156+P157+P158+P133)</f>
-        <v/>
-      </c>
-      <c r="Q163" s="58">
-        <f>Q161-(Q153+Q154+Q155+Q156+Q157+Q158+Q133)</f>
-        <v/>
-      </c>
-      <c r="R163" s="58">
-        <f>R161-(R153+R154+R155+R156+R157+R158+R133)</f>
-        <v/>
-      </c>
-      <c r="S163" s="58">
-        <f>S161-(S153+S154+S155+S156+S157+S158+S133)</f>
-        <v/>
-      </c>
-      <c r="T163" s="58">
-        <f>T161-(T153+T154+T155+T156+T157+T158+T133)</f>
-        <v/>
-      </c>
-      <c r="U163" s="58">
-        <f>U161-(U153+U154+U155+U156+U157+U158+U133)</f>
-        <v/>
-      </c>
-      <c r="V163" s="58">
-        <f>V161-(V153+V154+V155+V156+V157+V158+V133)</f>
-        <v/>
-      </c>
-      <c r="W163" s="58">
-        <f>W161-(W153+W154+W155+W156+W157+W158+W133)</f>
-        <v/>
-      </c>
-      <c r="X163" s="58">
-        <f>X161-(X153+X154+X155+X156+X157+X158+X133)</f>
-        <v/>
-      </c>
-      <c r="Y163" s="58">
-        <f>Y161-(Y153+Y154+Y155+Y156+Y157+Y158+Y133)</f>
-        <v/>
-      </c>
-      <c r="Z163" s="58">
-        <f>Z161-(Z153+Z154+Z155+Z156+Z157+Z158+Z133)</f>
-        <v/>
-      </c>
-      <c r="AA163" s="58">
-        <f>AA161-(AA153+AA154+AA155+AA156+AA157+AA158+AA133)</f>
-        <v/>
-      </c>
-      <c r="AB163" s="58">
-        <f>AB161-(AB153+AB154+AB155+AB156+AB157+AB158+AB133)</f>
-        <v/>
-      </c>
-      <c r="AC163" s="58">
-        <f>AC161-(AC153+AC154+AC155+AC156+AC157+AC158+AC133)</f>
-        <v/>
-      </c>
-      <c r="AD163" s="58">
-        <f>AD161-(AD153+AD154+AD155+AD156+AD157+AD158+AD133)</f>
-        <v/>
-      </c>
-      <c r="AE163" s="58">
-        <f>AE161-(AE153+AE154+AE155+AE156+AE157+AE158+AE133)</f>
+      <c r="C164" s="58">
+        <f>C162-(C154+C155+C156+C157+C158+C159+C133)</f>
+        <v/>
+      </c>
+      <c r="D164" s="58">
+        <f>D162-(D154+D155+D156+D157+D158+D159+D133)</f>
+        <v/>
+      </c>
+      <c r="E164" s="58">
+        <f>E162-(E154+E155+E156+E157+E158+E159+E133)</f>
+        <v/>
+      </c>
+      <c r="F164" s="58">
+        <f>F162-(F154+F155+F156+F157+F158+F159+F133)</f>
+        <v/>
+      </c>
+      <c r="G164" s="58">
+        <f>G162-(G154+G155+G156+G157+G158+G159+G133)</f>
+        <v/>
+      </c>
+      <c r="H164" s="58">
+        <f>H162-(H154+H155+H156+H157+H158+H159+H133)</f>
+        <v/>
+      </c>
+      <c r="I164" s="58">
+        <f>I162-(I154+I155+I156+I157+I158+I159+I133)</f>
+        <v/>
+      </c>
+      <c r="J164" s="58">
+        <f>J162-(J154+J155+J156+J157+J158+J159+J133)</f>
+        <v/>
+      </c>
+      <c r="K164" s="58">
+        <f>K162-(K154+K155+K156+K157+K158+K159+K133)</f>
+        <v/>
+      </c>
+      <c r="L164" s="58">
+        <f>L162-(L154+L155+L156+L157+L158+L159+L133)</f>
+        <v/>
+      </c>
+      <c r="M164" s="58">
+        <f>M162-(M154+M155+M156+M157+M158+M159+M133)</f>
+        <v/>
+      </c>
+      <c r="N164" s="58">
+        <f>N162-(N154+N155+N156+N157+N158+N159+N133)</f>
+        <v/>
+      </c>
+      <c r="O164" s="58">
+        <f>O162-(O154+O155+O156+O157+O158+O159+O133)</f>
+        <v/>
+      </c>
+      <c r="P164" s="58">
+        <f>P162-(P154+P155+P156+P157+P158+P159+P133)</f>
+        <v/>
+      </c>
+      <c r="Q164" s="58">
+        <f>Q162-(Q154+Q155+Q156+Q157+Q158+Q159+Q133)</f>
+        <v/>
+      </c>
+      <c r="R164" s="58">
+        <f>R162-(R154+R155+R156+R157+R158+R159+R133)</f>
+        <v/>
+      </c>
+      <c r="S164" s="58">
+        <f>S162-(S154+S155+S156+S157+S158+S159+S133)</f>
+        <v/>
+      </c>
+      <c r="T164" s="58">
+        <f>T162-(T154+T155+T156+T157+T158+T159+T133)</f>
+        <v/>
+      </c>
+      <c r="U164" s="58">
+        <f>U162-(U154+U155+U156+U157+U158+U159+U133)</f>
+        <v/>
+      </c>
+      <c r="V164" s="58">
+        <f>V162-(V154+V155+V156+V157+V158+V159+V133)</f>
+        <v/>
+      </c>
+      <c r="W164" s="58">
+        <f>W162-(W154+W155+W156+W157+W158+W159+W133)</f>
+        <v/>
+      </c>
+      <c r="X164" s="58">
+        <f>X162-(X154+X155+X156+X157+X158+X159+X133)</f>
+        <v/>
+      </c>
+      <c r="Y164" s="58">
+        <f>Y162-(Y154+Y155+Y156+Y157+Y158+Y159+Y133)</f>
+        <v/>
+      </c>
+      <c r="Z164" s="58">
+        <f>Z162-(Z154+Z155+Z156+Z157+Z158+Z159+Z133)</f>
+        <v/>
+      </c>
+      <c r="AA164" s="58">
+        <f>AA162-(AA154+AA155+AA156+AA157+AA158+AA159+AA133)</f>
+        <v/>
+      </c>
+      <c r="AB164" s="58">
+        <f>AB162-(AB154+AB155+AB156+AB157+AB158+AB159+AB133)</f>
+        <v/>
+      </c>
+      <c r="AC164" s="58">
+        <f>AC162-(AC154+AC155+AC156+AC157+AC158+AC159+AC133)</f>
+        <v/>
+      </c>
+      <c r="AD164" s="58">
+        <f>AD162-(AD154+AD155+AD156+AD157+AD158+AD159+AD133)</f>
+        <v/>
+      </c>
+      <c r="AE164" s="58">
+        <f>AE162-(AE154+AE155+AE156+AE157+AE158+AE159+AE133)</f>
         <v/>
       </c>
     </row>
@@ -25159,31 +25287,31 @@
         </is>
       </c>
       <c r="D11" s="61">
-        <f>SUM(Model!C161:N161)</f>
+        <f>SUM(Model!C162:N162)</f>
         <v/>
       </c>
       <c r="E11" s="61">
-        <f>SUM(Model!O161:Z161)</f>
+        <f>SUM(Model!O162:Z162)</f>
         <v/>
       </c>
       <c r="F11" s="61">
-        <f>Model!AA161</f>
+        <f>Model!AA162</f>
         <v/>
       </c>
       <c r="G11" s="61">
-        <f>Model!AB161</f>
+        <f>Model!AB162</f>
         <v/>
       </c>
       <c r="H11" s="61">
-        <f>Model!AC161</f>
+        <f>Model!AC162</f>
         <v/>
       </c>
       <c r="I11" s="61">
-        <f>Model!AD161</f>
+        <f>Model!AD162</f>
         <v/>
       </c>
       <c r="J11" s="61">
-        <f>Model!AE161</f>
+        <f>Model!AE162</f>
         <v/>
       </c>
     </row>
@@ -25207,70 +25335,70 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Stream 1a: Entry fee margin - SIP</t>
+          <t>Stream 1a: Entry fee - SIP</t>
         </is>
       </c>
       <c r="D14" s="35">
-        <f>SUM(Model!C153:N153)</f>
+        <f>SUM(Model!C154:N154)</f>
         <v/>
       </c>
       <c r="E14" s="35">
-        <f>SUM(Model!O153:Z153)</f>
+        <f>SUM(Model!O154:Z154)</f>
         <v/>
       </c>
       <c r="F14" s="35">
-        <f>Model!AA153</f>
+        <f>Model!AA154</f>
         <v/>
       </c>
       <c r="G14" s="35">
-        <f>Model!AB153</f>
+        <f>Model!AB154</f>
         <v/>
       </c>
       <c r="H14" s="35">
-        <f>Model!AC153</f>
+        <f>Model!AC154</f>
         <v/>
       </c>
       <c r="I14" s="35">
-        <f>Model!AD153</f>
+        <f>Model!AD154</f>
         <v/>
       </c>
       <c r="J14" s="35">
-        <f>Model!AE153</f>
+        <f>Model!AE154</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Stream 1b: Entry fee margin - SPOT</t>
+          <t>Stream 1b: Entry fee - SPOT</t>
         </is>
       </c>
       <c r="D15" s="35">
-        <f>SUM(Model!C154:N154)</f>
+        <f>SUM(Model!C155:N155)</f>
         <v/>
       </c>
       <c r="E15" s="35">
-        <f>SUM(Model!O154:Z154)</f>
+        <f>SUM(Model!O155:Z155)</f>
         <v/>
       </c>
       <c r="F15" s="35">
-        <f>Model!AA154</f>
+        <f>Model!AA155</f>
         <v/>
       </c>
       <c r="G15" s="35">
-        <f>Model!AB154</f>
+        <f>Model!AB155</f>
         <v/>
       </c>
       <c r="H15" s="35">
-        <f>Model!AC154</f>
+        <f>Model!AC155</f>
         <v/>
       </c>
       <c r="I15" s="35">
-        <f>Model!AD154</f>
+        <f>Model!AD155</f>
         <v/>
       </c>
       <c r="J15" s="35">
-        <f>Model!AE154</f>
+        <f>Model!AE155</f>
         <v/>
       </c>
     </row>
@@ -25281,31 +25409,31 @@
         </is>
       </c>
       <c r="D16" s="35">
-        <f>SUM(Model!C155:N155)</f>
+        <f>SUM(Model!C156:N156)</f>
         <v/>
       </c>
       <c r="E16" s="35">
-        <f>SUM(Model!O155:Z155)</f>
+        <f>SUM(Model!O156:Z156)</f>
         <v/>
       </c>
       <c r="F16" s="35">
-        <f>Model!AA155</f>
+        <f>Model!AA156</f>
         <v/>
       </c>
       <c r="G16" s="35">
-        <f>Model!AB155</f>
+        <f>Model!AB156</f>
         <v/>
       </c>
       <c r="H16" s="35">
-        <f>Model!AC155</f>
+        <f>Model!AC156</f>
         <v/>
       </c>
       <c r="I16" s="35">
-        <f>Model!AD155</f>
+        <f>Model!AD156</f>
         <v/>
       </c>
       <c r="J16" s="35">
-        <f>Model!AE155</f>
+        <f>Model!AE156</f>
         <v/>
       </c>
     </row>
@@ -25316,31 +25444,31 @@
         </is>
       </c>
       <c r="D17" s="35">
-        <f>SUM(Model!C156:N156)</f>
+        <f>SUM(Model!C157:N157)</f>
         <v/>
       </c>
       <c r="E17" s="35">
-        <f>SUM(Model!O156:Z156)</f>
+        <f>SUM(Model!O157:Z157)</f>
         <v/>
       </c>
       <c r="F17" s="35">
-        <f>Model!AA156</f>
+        <f>Model!AA157</f>
         <v/>
       </c>
       <c r="G17" s="35">
-        <f>Model!AB156</f>
+        <f>Model!AB157</f>
         <v/>
       </c>
       <c r="H17" s="35">
-        <f>Model!AC156</f>
+        <f>Model!AC157</f>
         <v/>
       </c>
       <c r="I17" s="35">
-        <f>Model!AD156</f>
+        <f>Model!AD157</f>
         <v/>
       </c>
       <c r="J17" s="35">
-        <f>Model!AE156</f>
+        <f>Model!AE157</f>
         <v/>
       </c>
     </row>
@@ -25351,31 +25479,31 @@
         </is>
       </c>
       <c r="D18" s="35">
-        <f>SUM(Model!C157:N157)</f>
+        <f>SUM(Model!C158:N158)</f>
         <v/>
       </c>
       <c r="E18" s="35">
-        <f>SUM(Model!O157:Z157)</f>
+        <f>SUM(Model!O158:Z158)</f>
         <v/>
       </c>
       <c r="F18" s="35">
-        <f>Model!AA157</f>
+        <f>Model!AA158</f>
         <v/>
       </c>
       <c r="G18" s="35">
-        <f>Model!AB157</f>
+        <f>Model!AB158</f>
         <v/>
       </c>
       <c r="H18" s="35">
-        <f>Model!AC157</f>
+        <f>Model!AC158</f>
         <v/>
       </c>
       <c r="I18" s="35">
-        <f>Model!AD157</f>
+        <f>Model!AD158</f>
         <v/>
       </c>
       <c r="J18" s="35">
-        <f>Model!AE157</f>
+        <f>Model!AE158</f>
         <v/>
       </c>
     </row>
@@ -25386,31 +25514,31 @@
         </is>
       </c>
       <c r="D19" s="35">
-        <f>SUM(Model!C158:N158)</f>
+        <f>SUM(Model!C159:N159)</f>
         <v/>
       </c>
       <c r="E19" s="35">
-        <f>SUM(Model!O158:Z158)</f>
+        <f>SUM(Model!O159:Z159)</f>
         <v/>
       </c>
       <c r="F19" s="35">
-        <f>Model!AA158</f>
+        <f>Model!AA159</f>
         <v/>
       </c>
       <c r="G19" s="35">
-        <f>Model!AB158</f>
+        <f>Model!AB159</f>
         <v/>
       </c>
       <c r="H19" s="35">
-        <f>Model!AC158</f>
+        <f>Model!AC159</f>
         <v/>
       </c>
       <c r="I19" s="35">
-        <f>Model!AD158</f>
+        <f>Model!AD159</f>
         <v/>
       </c>
       <c r="J19" s="35">
-        <f>Model!AE158</f>
+        <f>Model!AE159</f>
         <v/>
       </c>
     </row>
@@ -25456,31 +25584,31 @@
         </is>
       </c>
       <c r="D21" s="61">
-        <f>SUM(Model!C161:N161)</f>
+        <f>SUM(Model!C162:N162)</f>
         <v/>
       </c>
       <c r="E21" s="61">
-        <f>SUM(Model!O161:Z161)</f>
+        <f>SUM(Model!O162:Z162)</f>
         <v/>
       </c>
       <c r="F21" s="61">
-        <f>Model!AA161</f>
+        <f>Model!AA162</f>
         <v/>
       </c>
       <c r="G21" s="61">
-        <f>Model!AB161</f>
+        <f>Model!AB162</f>
         <v/>
       </c>
       <c r="H21" s="61">
-        <f>Model!AC161</f>
+        <f>Model!AC162</f>
         <v/>
       </c>
       <c r="I21" s="61">
-        <f>Model!AD161</f>
+        <f>Model!AD162</f>
         <v/>
       </c>
       <c r="J21" s="61">
-        <f>Model!AE161</f>
+        <f>Model!AE162</f>
         <v/>
       </c>
     </row>
@@ -26011,35 +26139,35 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>AUM</t>
+          <t>Collateral-eligible AUM</t>
         </is>
       </c>
       <c r="D40" s="61">
-        <f>Model!N143</f>
+        <f>Model!N144</f>
         <v/>
       </c>
       <c r="E40" s="61">
-        <f>Model!Z143</f>
+        <f>Model!Z144</f>
         <v/>
       </c>
       <c r="F40" s="61">
-        <f>Model!AA143</f>
+        <f>Model!AA144</f>
         <v/>
       </c>
       <c r="G40" s="61">
-        <f>Model!AB143</f>
+        <f>Model!AB144</f>
         <v/>
       </c>
       <c r="H40" s="61">
-        <f>Model!AC143</f>
+        <f>Model!AC144</f>
         <v/>
       </c>
       <c r="I40" s="61">
-        <f>Model!AD143</f>
+        <f>Model!AD144</f>
         <v/>
       </c>
       <c r="J40" s="61">
-        <f>Model!AE143</f>
+        <f>Model!AE144</f>
         <v/>
       </c>
     </row>
@@ -26050,31 +26178,31 @@
         </is>
       </c>
       <c r="D41" s="35">
-        <f>Model!N162</f>
+        <f>Model!N163</f>
         <v/>
       </c>
       <c r="E41" s="35">
-        <f>Model!Z162</f>
+        <f>Model!Z163</f>
         <v/>
       </c>
       <c r="F41" s="35">
-        <f>Model!AA162</f>
+        <f>Model!AA163</f>
         <v/>
       </c>
       <c r="G41" s="35">
-        <f>Model!AB162</f>
+        <f>Model!AB163</f>
         <v/>
       </c>
       <c r="H41" s="35">
-        <f>Model!AC162</f>
+        <f>Model!AC163</f>
         <v/>
       </c>
       <c r="I41" s="35">
-        <f>Model!AD162</f>
+        <f>Model!AD163</f>
         <v/>
       </c>
       <c r="J41" s="35">
-        <f>Model!AE162</f>
+        <f>Model!AE163</f>
         <v/>
       </c>
     </row>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
@@ -128,11 +128,11 @@
     <definedName name="sip_floor">Assumptions!$B$38</definedName>
     <definedName name="spot_attach">'Scenario Parameters'!$B$34</definedName>
     <definedName name="spot_frequency">'Scenario Parameters'!$B$36</definedName>
-    <definedName name="spot_ticket">'Scenario Parameters'!$B$35</definedName>
+    <definedName name="spot_ticket_mult">'Scenario Parameters'!$B$35</definedName>
     <definedName name="spot_to_sip">'Scenario Parameters'!$B$37</definedName>
-    <definedName name="spotmult_gulf">Assumptions!$B$33</definedName>
-    <definedName name="spotmult_india">Assumptions!$B$34</definedName>
-    <definedName name="spotmult_uae">Assumptions!$B$32</definedName>
+    <definedName name="spotticket_gulf">Assumptions!$B$33</definedName>
+    <definedName name="spotticket_india">Assumptions!$B$34</definedName>
+    <definedName name="spotticket_uae">Assumptions!$B$32</definedName>
     <definedName name="sw_lapsed_keeps_card">'Scenario Parameters'!$B$84</definedName>
     <definedName name="sw_prepaid_vs_credit">'Scenario Parameters'!$B$83</definedName>
     <definedName name="ticket_gulf">'Scenario Parameters'!$B$75</definedName>
@@ -1500,60 +1500,60 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Spot ticket multiplier - UAE</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="n">
-        <v>1.07</v>
+          <t>Spot ticket - UAE</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="n">
+        <v>190</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>x average</t>
+          <t>USD/purchase</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Derived from the regional SIP ticket relative to the book-weighted average of ~USD 31.5. Weighted across the region mix these average 1.00, so they redistribute the spot ticket without changing its level. DERIVED.</t>
+          <t>OBSERVED, PRIMARY. Botim gold: average ticket AED 700, Khaleej Times, Nov 2025 (= USD 191 at the peg). CROSS-CHECKS against the same platform's own volume disclosure - AED 100m over 128,000 trades implies AED 781. THE STRONGEST COMPARABLE IN THIS MODEL: Botim is a messaging app that became the default for Gulf expats and added gold in Aug 2025, so its users ARE Aurumix's customers - same country, same segment, same product, same period. Note 64% of its users buy under AED 500, so the mean sits above the median and this figure is, if anything, generous.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Spot ticket multiplier - Oman and Bahrain</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="n">
-        <v>0.83</v>
+          <t>Spot ticket - Oman and Bahrain</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n">
+        <v>145</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>x average</t>
+          <t>USD/purchase</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Derived from the regional SIP ticket relative to the book-weighted average of ~USD 31.5. Weighted across the region mix these average 1.00, so they redistribute the spot ticket without changing its level. DERIVED.</t>
+          <t>⚠ INFERRED - THE WEAKEST OF THE THREE. No GCC platform outside the UAE publishes an average ticket; this is a CONFIRMED NEGATIVE, not a gap in the search. Taken as the UAE figure scaled by the regional income gap (SIP 26.00/33.60 = 0.77x). Do not present this as sourced.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Spot ticket multiplier - India</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="n">
-        <v>0.95</v>
+          <t>Spot ticket - India</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="n">
+        <v>40</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>x average</t>
+          <t>USD/purchase</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Derived from the regional SIP ticket relative to the book-weighted average of ~USD 31.5. Weighted across the region mix these average 1.00, so they redistribute the spot ticket without changing its level. DERIVED.</t>
+          <t>OBSERVED, PROXY. Augmont: average festive-season purchase Rs 3,300, Times of India, Sep 2025 (= ~USD 38). Augmont is a licensed refiner and digital gold platform; a festive lump is structurally the same act as a spot purchase, which is why it is preferred to the alternatives. REJECTED: SafeGold Rs 5,000-8,000 (May 2026) - that book skews to investors, while Aurumix's Indian customer saves USD 30 a month; MMTC-PAMP Rs 800-1,200 - closer to routine micro-saving than a lump; Rs 230 industry-wide - a LinkedIn aggregate, not a citable source. ⚠ WEAKER THAN THE UAE FIGURE: right country and right behaviour, but Aurumix's Indian customer is poorer than Augmont's average buyer, so 40 may be generous.</t>
         </is>
       </c>
     </row>
@@ -3475,21 +3475,21 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Average spot ticket</t>
-        </is>
-      </c>
-      <c r="B131" s="35">
+          <t>Spot ticket scenario multiplier</t>
+        </is>
+      </c>
+      <c r="B131" s="34">
         <f>'Scenario Parameters'!$B$35</f>
         <v/>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USD/event</t>
+          <t>x the observed ticket</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>RE-ANCHORED 2026-08-20 from USD 620. Botim - a UAE gold-buying app with a 96% blue/grey collar base, and the ONLY OBSERVED SPOT FUNNEL IN THE LAUNCH MARKET - reports an average ticket of ~AED 780 (~USD 212). USD 620 sat at 2.9x the only observed figure for this demographic, which is the same population-mismatch error corrected on card spend the same day. USD 300 stays ABOVE the observed figure, on the argument that a considered purchase into an allocated-gold savings product is larger than a casual in-app buy, but no longer multiples above it. Conservative sits at USD 200, just below Botim. Scaled by region below. ASSUMPTION anchored on one observation.</t>
+          <t>REPLACED the global 'Average spot ticket' on 2026-08-21. The LEVEL is no longer a scenario input: each region now carries its own OBSERVED ticket on Assumptions (UAE 190 from Botim, India 40 from Augmont, Oman &amp; Bahrain 145 inferred). This parameter carries only the UNCERTAINTY around those observations, as a single dial. ⚠ WHY ONE DIAL AND NOT THREE: three regional triplets would be nine numbers to defend and would let a scenario silently invert the regional ordering that the sources establish. One multiplier flexes the level and PRESERVES the ordering. Aggressive 1.35 puts the UAE at ~257, still under the AED 1,000 mark; conservative 0.70 puts it at ~133, below Botim's own sub-AED-500 majority. ASSUMPTION about spread, applied to observed levels.</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>External check: Botim's 128,000 trades against ~45,000 buyers implies ~1.9/yr. INFERRED from two disclosures of different vintage - supportive, not confirmatory. ASSUMPTION.</t>
+          <t>⚠ PROVENANCE CORRECTED 2026-08-21 - THE NUMBER STANDS, ITS OLD CITATION DID NOT. The previous note read 'Botim's 128,000 trades against ~45,000 buyers implies ~1.9/yr'. THE 45,000 IS NOT A BUYER COUNT, IT IS A TRANSACTION COUNT: Khaleej Times, Nov 2025, says 775,000 users EXPLORED the feature, 'completing over 45,000 transactions'. The 128,000 is also transactions, to Feb 2026. So the old derivation divided transactions by transactions across two different windows - the result was the growth in cumulative trades, not a frequency. CONFIRMED NEGATIVE: Botim has never published a unique-buyer count, so no frequency can be derived from it, and no published frequency exists ANYWHERE for ad-hoc lump gold purchases. Comparators are 0.85/yr (Augmont, per REGISTERED user, at an average transaction of Rs 331 - micro-saving, not lumps) and 264/yr (Jar, Rs 10/day auto-roundups) - a 300x spread, neither being this product. WHAT DOES SUPPORT 1.7 is a cross-check on the COMBINED basis, attach x frequency x ticket, which is comparable: Aurumix India implies ~Rs 838/yr of gold per paying customer against Augmont's ~Rs 281/yr per registered user. 3x, and defensible - our customers are engaged SIP savers, not dormant registrations. Behaviourally 1.7 is also about right for festive lumps: Dhanteras, Akshaya Tritiya and a wedding is roughly two events. ASSUMPTION, cross-checked on the combined basis, NOT directly sourced.</t>
         </is>
       </c>
     </row>
@@ -5043,30 +5043,30 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Average spot ticket</t>
-        </is>
-      </c>
-      <c r="B35" s="41">
+          <t>Spot ticket scenario multiplier</t>
+        </is>
+      </c>
+      <c r="B35" s="40">
         <f>CHOOSE($C$6,C35,D35,E35)</f>
         <v/>
       </c>
-      <c r="C35" s="20" t="n">
-        <v>300</v>
-      </c>
-      <c r="D35" s="20" t="n">
-        <v>530</v>
-      </c>
-      <c r="E35" s="20" t="n">
-        <v>200</v>
+      <c r="C35" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.7</v>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>USD/event</t>
+          <t>x the observed ticket</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>RE-ANCHORED 2026-08-20 from USD 620. Botim - a UAE gold-buying app with a 96% blue/grey collar base, and the ONLY OBSERVED SPOT FUNNEL IN THE LAUNCH MARKET - reports an average ticket of ~AED 780 (~USD 212). USD 620 sat at 2.9x the only observed figure for this demographic, which is the same population-mismatch error corrected on card spend the same day. USD 300 stays ABOVE the observed figure, on the argument that a considered purchase into an allocated-gold savings product is larger than a casual in-app buy, but no longer multiples above it. Conservative sits at USD 200, just below Botim. Scaled by region below. ASSUMPTION anchored on one observation.</t>
+          <t>REPLACED the global 'Average spot ticket' on 2026-08-21. The LEVEL is no longer a scenario input: each region now carries its own OBSERVED ticket on Assumptions (UAE 190 from Botim, India 40 from Augmont, Oman &amp; Bahrain 145 inferred). This parameter carries only the UNCERTAINTY around those observations, as a single dial. ⚠ WHY ONE DIAL AND NOT THREE: three regional triplets would be nine numbers to defend and would let a scenario silently invert the regional ordering that the sources establish. One multiplier flexes the level and PRESERVES the ordering. Aggressive 1.35 puts the UAE at ~257, still under the AED 1,000 mark; conservative 0.70 puts it at ~133, below Botim's own sub-AED-500 majority. ASSUMPTION about spread, applied to observed levels.</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>External check: Botim's 128,000 trades against ~45,000 buyers implies ~1.9/yr. INFERRED from two disclosures of different vintage - supportive, not confirmatory. ASSUMPTION.</t>
+          <t>⚠ PROVENANCE CORRECTED 2026-08-21 - THE NUMBER STANDS, ITS OLD CITATION DID NOT. The previous note read 'Botim's 128,000 trades against ~45,000 buyers implies ~1.9/yr'. THE 45,000 IS NOT A BUYER COUNT, IT IS A TRANSACTION COUNT: Khaleej Times, Nov 2025, says 775,000 users EXPLORED the feature, 'completing over 45,000 transactions'. The 128,000 is also transactions, to Feb 2026. So the old derivation divided transactions by transactions across two different windows - the result was the growth in cumulative trades, not a frequency. CONFIRMED NEGATIVE: Botim has never published a unique-buyer count, so no frequency can be derived from it, and no published frequency exists ANYWHERE for ad-hoc lump gold purchases. Comparators are 0.85/yr (Augmont, per REGISTERED user, at an average transaction of Rs 331 - micro-saving, not lumps) and 264/yr (Jar, Rs 10/day auto-roundups) - a 300x spread, neither being this product. WHAT DOES SUPPORT 1.7 is a cross-check on the COMBINED basis, attach x frequency x ticket, which is comparable: Aurumix India implies ~Rs 838/yr of gold per paying customer against Augmont's ~Rs 281/yr per registered user. 3x, and defensible - our customers are engaged SIP savers, not dormant registrations. Behaviourally 1.7 is also about right for festive lumps: Dhanteras, Akshaya Tritiya and a wedding is roughly two events. ASSUMPTION, cross-checked on the combined basis, NOT directly sourced.</t>
         </is>
       </c>
     </row>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
@@ -37,50 +37,46 @@
     <definedName name="agentshare_gulf">Assumptions!$B$107</definedName>
     <definedName name="agentshare_india">Assumptions!$B$108</definedName>
     <definedName name="agentshare_uae">Assumptions!$B$106</definedName>
-    <definedName name="atm_a1500">'Scenario Parameters'!$B$49</definedName>
-    <definedName name="atm_a3000">'Scenario Parameters'!$B$50</definedName>
-    <definedName name="atm_a3000p">'Scenario Parameters'!$B$51</definedName>
-    <definedName name="atm_a500">'Scenario Parameters'!$B$48</definedName>
+    <definedName name="atm_a1500">'Scenario Parameters'!$B$47</definedName>
+    <definedName name="atm_a3000">'Scenario Parameters'!$B$48</definedName>
+    <definedName name="atm_a3000p">'Scenario Parameters'!$B$49</definedName>
+    <definedName name="atm_a500">'Scenario Parameters'!$B$46</definedName>
     <definedName name="atm_allowance">Assumptions!$B$18</definedName>
     <definedName name="atm_fee">Assumptions!$B$19</definedName>
-    <definedName name="atmm_a1500">'Scenario Parameters'!$B$53</definedName>
-    <definedName name="atmm_a3000">'Scenario Parameters'!$B$54</definedName>
-    <definedName name="atmm_a3000p">'Scenario Parameters'!$B$55</definedName>
-    <definedName name="atmm_a500">'Scenario Parameters'!$B$52</definedName>
-    <definedName name="aum_per_partner">'Scenario Parameters'!$B$70</definedName>
+    <definedName name="atmm_a1500">'Scenario Parameters'!$B$51</definedName>
+    <definedName name="atmm_a3000">'Scenario Parameters'!$B$52</definedName>
+    <definedName name="atmm_a3000p">'Scenario Parameters'!$B$53</definedName>
+    <definedName name="atmm_a500">'Scenario Parameters'!$B$50</definedName>
+    <definedName name="aum_per_partner">'Scenario Parameters'!$B$68</definedName>
     <definedName name="b2b_fee">Assumptions!$B$26</definedName>
     <definedName name="bar_grams">Assumptions!$B$10</definedName>
     <definedName name="cac_gulf">'Scenario Parameters'!$B$14</definedName>
     <definedName name="cac_india">'Scenario Parameters'!$B$15</definedName>
     <definedName name="cac_uae">'Scenario Parameters'!$B$13</definedName>
-    <definedName name="card_activation">'Scenario Parameters'!$B$42</definedName>
-    <definedName name="card_txns_per_draw">'Scenario Parameters'!$B$43</definedName>
-    <definedName name="card_txns_per_month">'Scenario Parameters'!$B$44</definedName>
+    <definedName name="card_activation">'Scenario Parameters'!$B$41</definedName>
+    <definedName name="card_txns_per_draw">'Scenario Parameters'!$B$42</definedName>
     <definedName name="ceil_gulf">Assumptions!$B$82</definedName>
     <definedName name="ceil_india">Assumptions!$B$83</definedName>
     <definedName name="ceil_total">Assumptions!$B$84</definedName>
     <definedName name="ceil_uae">Assumptions!$B$81</definedName>
     <definedName name="decline_uplift">Assumptions!$B$16</definedName>
-    <definedName name="draw_events">'Scenario Parameters'!$B$61</definedName>
-    <definedName name="drawn_share">'Scenario Parameters'!$B$59</definedName>
+    <definedName name="draw_events">'Scenario Parameters'!$B$59</definedName>
+    <definedName name="drawn_share">'Scenario Parameters'!$B$57</definedName>
     <definedName name="entry_fee">Assumptions!$B$8</definedName>
     <definedName name="ever_qualify">'Scenario Parameters'!$B$26</definedName>
     <definedName name="fab_premium">Assumptions!$B$9</definedName>
-    <definedName name="facility_turnover">'Scenario Parameters'!$B$60</definedName>
-    <definedName name="family_attach">'Scenario Parameters'!$B$62</definedName>
+    <definedName name="facility_turnover">'Scenario Parameters'!$B$58</definedName>
+    <definedName name="family_attach">'Scenario Parameters'!$B$60</definedName>
     <definedName name="family_price">Assumptions!$B$25</definedName>
-    <definedName name="foreign_spend_share">'Scenario Parameters'!$B$45</definedName>
+    <definedName name="foreign_spend_share">'Scenario Parameters'!$B$43</definedName>
     <definedName name="fx_margin">Assumptions!$B$17</definedName>
     <definedName name="gate_run">Assumptions!$B$39</definedName>
     <definedName name="gold_price">Assumptions!$B$6</definedName>
     <definedName name="ic_gold">Assumptions!$B$14</definedName>
-    <definedName name="issuance_events">'Scenario Parameters'!$B$46</definedName>
+    <definedName name="issuance_events">'Scenario Parameters'!$B$44</definedName>
     <definedName name="issuance_fee">Assumptions!$B$20</definedName>
     <definedName name="lapsed_redemption_mult">'Scenario Parameters'!$B$33</definedName>
     <definedName name="ltv_gold">Assumptions!$B$31</definedName>
-    <definedName name="mix_gulf">'Scenario Parameters'!$B$78</definedName>
-    <definedName name="mix_india">'Scenario Parameters'!$B$79</definedName>
-    <definedName name="mix_uae">'Scenario Parameters'!$B$77</definedName>
     <definedName name="mktg_y1">Assumptions!$B$92</definedName>
     <definedName name="mktg_y2">Assumptions!$B$93</definedName>
     <definedName name="mktg_y3">Assumptions!$B$94</definedName>
@@ -96,15 +92,15 @@
     <definedName name="organic_share">'Scenario Parameters'!$B$21</definedName>
     <definedName name="origination_gross">Assumptions!$B$27</definedName>
     <definedName name="origination_share">Assumptions!$B$28</definedName>
-    <definedName name="partners_y1">'Scenario Parameters'!$B$63</definedName>
-    <definedName name="partners_y2">'Scenario Parameters'!$B$64</definedName>
-    <definedName name="partners_y3">'Scenario Parameters'!$B$65</definedName>
-    <definedName name="partners_y4">'Scenario Parameters'!$B$66</definedName>
-    <definedName name="partners_y5">'Scenario Parameters'!$B$67</definedName>
-    <definedName name="partners_y6">'Scenario Parameters'!$B$68</definedName>
-    <definedName name="partners_y7">'Scenario Parameters'!$B$69</definedName>
+    <definedName name="partners_y1">'Scenario Parameters'!$B$61</definedName>
+    <definedName name="partners_y2">'Scenario Parameters'!$B$62</definedName>
+    <definedName name="partners_y3">'Scenario Parameters'!$B$63</definedName>
+    <definedName name="partners_y4">'Scenario Parameters'!$B$64</definedName>
+    <definedName name="partners_y5">'Scenario Parameters'!$B$65</definedName>
+    <definedName name="partners_y6">'Scenario Parameters'!$B$66</definedName>
+    <definedName name="partners_y7">'Scenario Parameters'!$B$67</definedName>
     <definedName name="persistency_m13">'Scenario Parameters'!$B$10</definedName>
-    <definedName name="pm_share">'Scenario Parameters'!$B$41</definedName>
+    <definedName name="pm_share">'Scenario Parameters'!$B$40</definedName>
     <definedName name="ramp_y1">Assumptions!$B$99</definedName>
     <definedName name="ramp_y2">Assumptions!$B$100</definedName>
     <definedName name="ramp_y3">Assumptions!$B$101</definedName>
@@ -116,7 +112,7 @@
     <definedName name="redemption_rate">'Scenario Parameters'!$B$32</definedName>
     <definedName name="referral_conversion">'Scenario Parameters'!$B$20</definedName>
     <definedName name="referral_rate">'Scenario Parameters'!$B$19</definedName>
-    <definedName name="replacement_events">'Scenario Parameters'!$B$47</definedName>
+    <definedName name="replacement_events">'Scenario Parameters'!$B$45</definedName>
     <definedName name="replacement_fee">Assumptions!$B$21</definedName>
     <definedName name="scenario_index">'Scenario Parameters'!$C$6</definedName>
     <definedName name="seas_sum_acq">Model!$C$14</definedName>
@@ -129,15 +125,14 @@
     <definedName name="spot_attach">'Scenario Parameters'!$B$34</definedName>
     <definedName name="spot_frequency">'Scenario Parameters'!$B$36</definedName>
     <definedName name="spot_ticket_mult">'Scenario Parameters'!$B$35</definedName>
-    <definedName name="spot_to_sip">'Scenario Parameters'!$B$37</definedName>
     <definedName name="spotticket_gulf">Assumptions!$B$33</definedName>
     <definedName name="spotticket_india">Assumptions!$B$34</definedName>
     <definedName name="spotticket_uae">Assumptions!$B$32</definedName>
-    <definedName name="sw_lapsed_keeps_card">'Scenario Parameters'!$B$84</definedName>
-    <definedName name="sw_prepaid_vs_credit">'Scenario Parameters'!$B$83</definedName>
-    <definedName name="ticket_gulf">'Scenario Parameters'!$B$75</definedName>
-    <definedName name="ticket_india">'Scenario Parameters'!$B$76</definedName>
-    <definedName name="ticket_uae">'Scenario Parameters'!$B$74</definedName>
+    <definedName name="sw_lapsed_keeps_card">'Scenario Parameters'!$B$79</definedName>
+    <definedName name="sw_prepaid_vs_credit">'Scenario Parameters'!$B$78</definedName>
+    <definedName name="ticket_gulf">'Scenario Parameters'!$B$73</definedName>
+    <definedName name="ticket_india">'Scenario Parameters'!$B$74</definedName>
+    <definedName name="ticket_uae">'Scenario Parameters'!$B$72</definedName>
     <definedName name="txn_fee">Assumptions!$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -967,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q169"/>
+  <dimension ref="A1:Q164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3468,7 +3463,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Load-bearing because it is MISSING, not because it is large. ASSUMPTION.</t>
+          <t>⚠ NO SOURCE. NOT DERIVED, NOT OBSERVED - CHOSEN. The v2.6 brief records it as a confirmed negative: 'S45, S46 and S47 are all Low confidence with no published source. There is no spot-attach benchmark for any comparable gold or savings product anywhere.' Load-bearing because it is MISSING, not because it is large. WHAT IT ASSERTS, in plain terms: 14% x 1.7 = 0.238 purchases per paying customer per year, i.e. the average customer makes a one-off gold purchase about once every four years. The only cross-check is Augmont's 0.85 transactions per REGISTERED user per year, which we sit at 28% of - but their average transaction is Rs 331, so they are counting micro-savings rather than lumps. It bounds this number; it does not confirm it. ⚠ KNOWN SIMPLIFICATION WITH A KNOWN DIRECTION: v2.6 applied a TENURE UPLIFT here - 'a 3-year account is ~2x as likely to buy spot as a 6-month account' - which the v3.0 simplification dropped. This rate is now flat from day one. If 14% was calibrated on a mature book, SPOT IS OVERSTATED IN THE EARLY YEARS, when nearly every account is young. Not rebuilt because spot is ~1.4% of Y7 revenue; restore the uplift in the Phase 5 simulation. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -3517,28 +3512,28 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Spot-to-SIP conversion</t>
+          <t>Programme manager share of interchange</t>
         </is>
       </c>
       <c r="B133" s="32">
-        <f>'Scenario Parameters'!$B$37</f>
+        <f>'Scenario Parameters'!$B$40</f>
         <v/>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>% of spot buyers/yr</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NO SOURCE EXISTS ANYWHERE - re-confirmed by search 2026-08-20, a CONFIRMED NEGATIVE rather than a gap in the searching. The mechanism design calls this arrow 'the growth funnel' and names spot 'the entry point for new investors'. THE STRATEGY QUESTION IN NUMERICAL FORM, and the one an experiment could answer.</t>
+          <t>SIZES THE LARGEST STREAM. No UAE/MENA figure is published. FLOOR IS 36% - take that into the sponsor conversation as the walk-away. TRIANGULATED.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Programme manager share of interchange</t>
+          <t>Facility take-up - customers who take AND use the card</t>
         </is>
       </c>
       <c r="B134" s="32">
@@ -3547,145 +3542,145 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% of gate-cleared</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>SIZES THE LARGEST STREAM. No UAE/MENA figure is published. FLOOR IS 36% - take that into the sponsor conversation as the walk-away. TRIANGULATED.</t>
+          <t>RE-BASED 2026-08-20, client decision: THE CARD IS A DRAWDOWN ON THE GOLD-COLLATERALISED FACILITY, not a salary-repaid revolving card. Aurumix has no balance sheet to lend from - it can only extend credit against collateral it holds, which is the customer's gold. Using the card IS borrowing, so card activation and credit take-up are the SAME behaviour and were previously modelled as two different populations (50% activating a card, 18% taking credit) doing what is in fact one thing. Merged onto the credit figure, which is the better-anchored of the two: Indian gold-loan penetration is under 10% at a point in time, uplifted here for pre-selection since these customers have already cleared a six-payment gate. ⚠ THE OLD 50% CAME FROM NEOBANK COMPARABLES (PULSE 68.2%, Monzo 68%) WHERE THE CARD IS THE PRODUCT - wrong in kind for a card that only lets you borrow against your own savings. DERIVED.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Facility take-up - customers who take AND use the card</t>
-        </is>
-      </c>
-      <c r="B135" s="32">
+          <t>Transactions per drawdown event</t>
+        </is>
+      </c>
+      <c r="B135" s="36">
         <f>'Scenario Parameters'!$B$42</f>
         <v/>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>% of gate-cleared</t>
+          <t>transactions/draw</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>RE-BASED 2026-08-20, client decision: THE CARD IS A DRAWDOWN ON THE GOLD-COLLATERALISED FACILITY, not a salary-repaid revolving card. Aurumix has no balance sheet to lend from - it can only extend credit against collateral it holds, which is the customer's gold. Using the card IS borrowing, so card activation and credit take-up are the SAME behaviour and were previously modelled as two different populations (50% activating a card, 18% taking credit) doing what is in fact one thing. Merged onto the credit figure, which is the better-anchored of the two: Indian gold-loan penetration is under 10% at a point in time, uplifted here for pre-selection since these customers have already cleared a six-payment gate. ⚠ THE OLD 50% CAME FROM NEOBANK COMPARABLES (PULSE 68.2%, Monzo 68%) WHERE THE CARD IS THE PRODUCT - wrong in kind for a card that only lets you borrow against your own savings. DERIVED.</t>
+          <t>RE-BASED 2026-08-20 from 12 transactions/MONTH once the card became a drawdown on the gold facility. Under that model the customer borrows a lump (limit x drawn share) a couple of times a year and spends it down, so the meaningful unit is transactions PER DRAW, not per month. At 12/month the implied ticket collapsed to ~AED 12, which is a coffee, not a reason to pledge your gold. THE AVERAGE TICKET FALLS OUT AS drawn amount / this number, and the draw events cancel - so the ticket depends only on how large a draw is and how many purchases it is spent across. ⚠ IT ALSO CHANGES WHAT THE CARD IS FOR: not daily groceries, but occasional larger needs - school fees, a medical bill, an emergency - funded by borrowing against savings rather than liquidating them. That is a materially different product story and should be put to the client in those words. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Transactions per drawdown event</t>
-        </is>
-      </c>
-      <c r="B136" s="36">
+          <t>Foreign spend share (mean)</t>
+        </is>
+      </c>
+      <c r="B136" s="32">
         <f>'Scenario Parameters'!$B$43</f>
         <v/>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>transactions/draw</t>
+          <t>% of card spend</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>RE-BASED 2026-08-20 from 12 transactions/MONTH once the card became a drawdown on the gold facility. Under that model the customer borrows a lump (limit x drawn share) a couple of times a year and spends it down, so the meaningful unit is transactions PER DRAW, not per month. At 12/month the implied ticket collapsed to ~AED 12, which is a coffee, not a reason to pledge your gold. THE AVERAGE TICKET FALLS OUT AS drawn amount / this number, and the draw events cancel - so the ticket depends only on how large a draw is and how many purchases it is spent across. ⚠ IT ALSO CHANGES WHAT THE CARD IS FOR: not daily groceries, but occasional larger needs - school fees, a medical bill, an emergency - funded by borrowing against savings rather than liquidating them. That is a materially different product story and should be put to the client in those words. ASSUMPTION.</t>
+          <t>Applied through the seasonal vector, not as a constant. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Card transactions per active card per month</t>
-        </is>
-      </c>
-      <c r="B137" s="36">
+          <t>Card issuance events</t>
+        </is>
+      </c>
+      <c r="B137" s="34">
         <f>'Scenario Parameters'!$B$44</f>
         <v/>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>transactions/month</t>
+          <t>events/card/yr</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>THE INPUT IS FREQUENCY; AVERAGE TICKET IS DERIVED FROM IT. That inversion is deliberate. Monthly spend is already pinned by income (a multiple of the SIP ticket) and capped by the gold collateral, so specifying a ticket size would over-determine the card and let it drift away from what the customer actually saves - the exact problem an absolute AED 100 ticket created. Fixing frequency instead makes the average ticket fall out as spend / frequency, which means IT SCALES WITH THE SIP CONTRIBUTION AUTOMATICALLY: a customer on a smaller monthly savings amount gets a proportionally smaller basket, in every region, with no extra input. WHY FREQUENCY IS THE BETTER THING TO ANCHOR: it has a published number and ticket size does not. Visa scheme data gives ~175 transactions per card per year for the region, about 14-15/month, and UAE low-income cash dependency fell from 84% to 69% in two years, so card usage is rising. Base is set at 12, slightly BELOW the general anchor, because this is a secondary card earned on a savings product rather than someone's main salary card. ⚠ THE UAE-WIDE AVERAGE TICKET OF ~AED 313 IS DELIBERATELY NOT USED - it spans affluent expats and corporate cards, which is the same population mismatch that put card spend at AED 6,000. NO PUBLISHED TICKET SIZE OR FREQUENCY EXISTS FOR BLUE-COLLAR GCC WORKERS SPECIFICALLY - a confirmed negative, re-checked 2026-08-20. TRIANGULATED on frequency, DERIVED on ticket.</t>
+          <t>1.00 at activation plus reissues - a tier upgrade forces a physical reissue. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Foreign spend share (mean)</t>
-        </is>
-      </c>
-      <c r="B138" s="32">
+          <t>Card replacement events</t>
+        </is>
+      </c>
+      <c r="B138" s="34">
         <f>'Scenario Parameters'!$B$45</f>
         <v/>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>% of card spend</t>
+          <t>events/card/yr</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Applied through the seasonal vector, not as a constant. ASSUMPTION.</t>
+          <t>Industry-normal loss/theft/damage is 8-15% annually. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Card issuance events</t>
-        </is>
-      </c>
-      <c r="B139" s="34">
+          <t>ATM AED 0-500 - share of cardholders</t>
+        </is>
+      </c>
+      <c r="B139" s="32">
         <f>'Scenario Parameters'!$B$46</f>
         <v/>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>events/card/yr</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>1.00 at activation plus reissues - a tier upgrade forces a physical reissue. ASSUMPTION.</t>
+          <t>KEPT AS A DISTRIBUTION DELIBERATELY. The mean draw (~AED 940) sits just BELOW the free allowance of AED 1,000 BY DESIGN, so applying the fee to the mean returns EXACTLY ZERO and stream 4 silently loses a component. The distribution returns materially more, generated almost entirely by a small high-cash tail. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Card replacement events</t>
-        </is>
-      </c>
-      <c r="B140" s="34">
+          <t>ATM AED 500-1,500 - share of cardholders</t>
+        </is>
+      </c>
+      <c r="B140" s="32">
         <f>'Scenario Parameters'!$B$47</f>
         <v/>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>events/card/yr</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Industry-normal loss/theft/damage is 8-15% annually. ASSUMPTION.</t>
+          <t>KEPT AS A DISTRIBUTION DELIBERATELY. The mean draw (~AED 940) sits just BELOW the free allowance of AED 1,000 BY DESIGN, so applying the fee to the mean returns EXACTLY ZERO and stream 4 silently loses a component. The distribution returns materially more, generated almost entirely by a small high-cash tail. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ATM AED 0-500 - share of cardholders</t>
+          <t>ATM AED 1,500-3,000 - share of cardholders</t>
         </is>
       </c>
       <c r="B141" s="32">
@@ -3706,7 +3701,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ATM AED 500-1,500 - share of cardholders</t>
+          <t>ATM AED 3,000+ - share of cardholders</t>
         </is>
       </c>
       <c r="B142" s="32">
@@ -3727,49 +3722,49 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ATM AED 1,500-3,000 - share of cardholders</t>
-        </is>
-      </c>
-      <c r="B143" s="32">
+          <t>ATM AED 0-500 - midpoint draw</t>
+        </is>
+      </c>
+      <c r="B143" s="36">
         <f>'Scenario Parameters'!$B$50</f>
         <v/>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>AED/month</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>KEPT AS A DISTRIBUTION DELIBERATELY. The mean draw (~AED 940) sits just BELOW the free allowance of AED 1,000 BY DESIGN, so applying the fee to the mean returns EXACTLY ZERO and stream 4 silently loses a component. The distribution returns materially more, generated almost entirely by a small high-cash tail. ASSUMPTION.</t>
+          <t>Raising the allowance at the top tier waives revenue from only the top ~3% of cardholders.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ATM AED 3,000+ - share of cardholders</t>
-        </is>
-      </c>
-      <c r="B144" s="32">
+          <t>ATM AED 500-1,500 - midpoint draw</t>
+        </is>
+      </c>
+      <c r="B144" s="36">
         <f>'Scenario Parameters'!$B$51</f>
         <v/>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>AED/month</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>KEPT AS A DISTRIBUTION DELIBERATELY. The mean draw (~AED 940) sits just BELOW the free allowance of AED 1,000 BY DESIGN, so applying the fee to the mean returns EXACTLY ZERO and stream 4 silently loses a component. The distribution returns materially more, generated almost entirely by a small high-cash tail. ASSUMPTION.</t>
+          <t>Raising the allowance at the top tier waives revenue from only the top ~3% of cardholders.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ATM AED 0-500 - midpoint draw</t>
+          <t>ATM AED 1,500-3,000 - midpoint draw</t>
         </is>
       </c>
       <c r="B145" s="36">
@@ -3790,7 +3785,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ATM AED 500-1,500 - midpoint draw</t>
+          <t>ATM AED 3,000+ - midpoint draw</t>
         </is>
       </c>
       <c r="B146" s="36">
@@ -3811,133 +3806,133 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ATM AED 1,500-3,000 - midpoint draw</t>
-        </is>
-      </c>
-      <c r="B147" s="36">
-        <f>'Scenario Parameters'!$B$54</f>
+          <t>Drawn as % of permitted limit</t>
+        </is>
+      </c>
+      <c r="B147" s="32">
+        <f>'Scenario Parameters'!$B$57</f>
         <v/>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AED/month</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Raising the allowance at the top tier waives revenue from only the top ~3% of cardholders.</t>
+          <t>Revolving facilities draw 40-55% of permitted. This now drives CARD SPEND as well as the loan balance, because the card is the drawdown mechanism. TRIANGULATED.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ATM AED 3,000+ - midpoint draw</t>
-        </is>
-      </c>
-      <c r="B148" s="36">
-        <f>'Scenario Parameters'!$B$55</f>
+          <t>Facility turnover, peak -&gt; average</t>
+        </is>
+      </c>
+      <c r="B148" s="34">
+        <f>'Scenario Parameters'!$B$58</f>
         <v/>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AED/month</t>
+          <t>x peak drawn</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Raising the allowance at the top tier waives revenue from only the top ~3% of cardholders.</t>
+          <t>AN ARITHMETIC CORRECTION, not a sensitivity, derived from Manappuram's 71-day realised tenor. It cuts the lending stream by 1.88x. DERIVED.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Drawn as % of permitted limit</t>
-        </is>
-      </c>
-      <c r="B149" s="32">
+          <t>Draw events per borrower per year</t>
+        </is>
+      </c>
+      <c r="B149" s="34">
         <f>'Scenario Parameters'!$B$59</f>
         <v/>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>events/yr</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Revolving facilities draw 40-55% of permitted. This now drives CARD SPEND as well as the loan balance, because the card is the drawdown mechanism. TRIANGULATED.</t>
+          <t>MOVES WITH facility turnover - do not flex independently. DERIVED.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Facility turnover, peak -&gt; average</t>
-        </is>
-      </c>
-      <c r="B150" s="34">
+          <t>Family plan attach rate</t>
+        </is>
+      </c>
+      <c r="B150" s="32">
         <f>'Scenario Parameters'!$B$60</f>
         <v/>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>x peak drawn</t>
+          <t>% of customers</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>AN ARITHMETIC CORRECTION, not a sensitivity, derived from Manappuram's 71-day realised tenor. It cuts the lending stream by 1.88x. DERIVED.</t>
+          <t>NOTHING IS STATED ANYWHERE IN THE CORPUS. Pure assumption. Scales stream 3 linearly.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Draw events per borrower per year</t>
-        </is>
-      </c>
-      <c r="B151" s="34">
+          <t>B2B partners - Y1</t>
+        </is>
+      </c>
+      <c r="B151" s="36">
         <f>'Scenario Parameters'!$B$61</f>
         <v/>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>events/yr</t>
+          <t>partners</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>MOVES WITH facility turnover - do not flex independently. DERIVED.</t>
+          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Family plan attach rate</t>
-        </is>
-      </c>
-      <c r="B152" s="32">
+          <t>B2B partners - Y2</t>
+        </is>
+      </c>
+      <c r="B152" s="36">
         <f>'Scenario Parameters'!$B$62</f>
         <v/>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>% of customers</t>
+          <t>partners</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NOTHING IS STATED ANYWHERE IN THE CORPUS. Pure assumption. Scales stream 3 linearly.</t>
+          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>B2B partners - Y1</t>
+          <t>B2B partners - Y3</t>
         </is>
       </c>
       <c r="B153" s="36">
@@ -3958,7 +3953,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>B2B partners - Y2</t>
+          <t>B2B partners - Y4</t>
         </is>
       </c>
       <c r="B154" s="36">
@@ -3979,7 +3974,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>B2B partners - Y3</t>
+          <t>B2B partners - Y5</t>
         </is>
       </c>
       <c r="B155" s="36">
@@ -4000,7 +3995,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>B2B partners - Y4</t>
+          <t>B2B partners - Y6</t>
         </is>
       </c>
       <c r="B156" s="36">
@@ -4021,7 +4016,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>B2B partners - Y5</t>
+          <t>B2B partners - Y7</t>
         </is>
       </c>
       <c r="B157" s="36">
@@ -4042,70 +4037,70 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>B2B partners - Y6</t>
-        </is>
-      </c>
-      <c r="B158" s="36">
+          <t>AUM per partner (mature)</t>
+        </is>
+      </c>
+      <c r="B158" s="35">
         <f>'Scenario Parameters'!$B$68</f>
         <v/>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>partners</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>Requires a signed partner. Partner AUM earns NO tier and consumes NO benefits - structurally the highest-margin book. DERIVED.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>B2B partners - Y7</t>
-        </is>
-      </c>
-      <c r="B159" s="36">
-        <f>'Scenario Parameters'!$B$69</f>
+          <t>Average monthly ticket - UAE</t>
+        </is>
+      </c>
+      <c r="B159" s="35">
+        <f>'Scenario Parameters'!$B$72</f>
         <v/>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>partners</t>
+          <t>USD/month</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AUM per partner (mature)</t>
+          <t>Average monthly ticket - Oman and Bahrain</t>
         </is>
       </c>
       <c r="B160" s="35">
-        <f>'Scenario Parameters'!$B$70</f>
+        <f>'Scenario Parameters'!$B$73</f>
         <v/>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>USD/month</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Requires a signed partner. Partner AUM earns NO tier and consumes NO benefits - structurally the highest-margin book. DERIVED.</t>
+          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Average monthly ticket - UAE</t>
+          <t>Average monthly ticket - India</t>
         </is>
       </c>
       <c r="B161" s="35">
@@ -4126,152 +4121,47 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Average monthly ticket - Oman and Bahrain</t>
-        </is>
-      </c>
-      <c r="B162" s="35">
-        <f>'Scenario Parameters'!$B$75</f>
+          <t>Prepaid instead of credit</t>
+        </is>
+      </c>
+      <c r="B162" s="36">
+        <f>'Scenario Parameters'!$B$78</f>
         <v/>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>USD/month</t>
+          <t>1/0 switch</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
+          <t>ON (Prepaid) caps interchange at 1.00% and removes the credit stream entirely. 'NOT A PRODUCT CHOICE, IT IS THE BUSINESS MODEL.' Worth ~USD 2.3m of Y10 revenue on the ten-year run.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Average monthly ticket - India</t>
-        </is>
-      </c>
-      <c r="B163" s="35">
-        <f>'Scenario Parameters'!$B$76</f>
+          <t>Holders keep the card</t>
+        </is>
+      </c>
+      <c r="B163" s="36">
+        <f>'Scenario Parameters'!$B$79</f>
         <v/>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>USD/month</t>
+          <t>1/0 switch</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
+          <t>NOBODY HAS DECIDED THIS. It determines whether the card streams - the majority of revenue - decay with churn or are immune to it. Worth a 42% swing in terminal revenue. Default ON because nothing in the design revokes the card; report both.</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Share of new customers - UAE</t>
-        </is>
-      </c>
-      <c r="B164" s="32">
-        <f>'Scenario Parameters'!$B$77</f>
-        <v/>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>% of new</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>DERIVED from market size: each region's share of acquisition equals its share of the addressable ceiling, so acquisition follows the opportunity. Previously these were four typed numbers with no basis, which sent 34% of acquisition to Oman and Bahrain - a market that is 16% of the opportunity - and only 8% to India, which is 26% of it. Because they are derived they sum to 1.000 by construction and cannot drift out of line with the ceilings. Shares are RENORMALISED on the Model for regions not yet open, so a region that opens later redistributes rather than vanishing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Share of new customers - Oman and Bahrain</t>
-        </is>
-      </c>
-      <c r="B165" s="32">
-        <f>'Scenario Parameters'!$B$78</f>
-        <v/>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>% of new</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>DERIVED from market size: each region's share of acquisition equals its share of the addressable ceiling, so acquisition follows the opportunity. Previously these were four typed numbers with no basis, which sent 34% of acquisition to Oman and Bahrain - a market that is 16% of the opportunity - and only 8% to India, which is 26% of it. Because they are derived they sum to 1.000 by construction and cannot drift out of line with the ceilings. Shares are RENORMALISED on the Model for regions not yet open, so a region that opens later redistributes rather than vanishing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Share of new customers - India</t>
-        </is>
-      </c>
-      <c r="B166" s="32">
-        <f>'Scenario Parameters'!$B$79</f>
-        <v/>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>% of new</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>DERIVED from market size: each region's share of acquisition equals its share of the addressable ceiling, so acquisition follows the opportunity. Previously these were four typed numbers with no basis, which sent 34% of acquisition to Oman and Bahrain - a market that is 16% of the opportunity - and only 8% to India, which is 26% of it. Because they are derived they sum to 1.000 by construction and cannot drift out of line with the ceilings. Shares are RENORMALISED on the Model for regions not yet open, so a region that opens later redistributes rather than vanishing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Prepaid instead of credit</t>
-        </is>
-      </c>
-      <c r="B167" s="36">
-        <f>'Scenario Parameters'!$B$83</f>
-        <v/>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>1/0 switch</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>ON (Prepaid) caps interchange at 1.00% and removes the credit stream entirely. 'NOT A PRODUCT CHOICE, IT IS THE BUSINESS MODEL.' Worth ~USD 2.3m of Y10 revenue on the ten-year run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Holders keep the card</t>
-        </is>
-      </c>
-      <c r="B168" s="36">
-        <f>'Scenario Parameters'!$B$84</f>
-        <v/>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>1/0 switch</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>NOBODY HAS DECIDED THIS. It determines whether the card streams - the majority of revenue - decay with churn or are immune to it. Worth a 42% swing in terminal revenue. Default ON because nothing in the design revokes the card; report both.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="9" t="inlineStr">
+      <c r="A164" s="9" t="inlineStr">
         <is>
           <t>Every row above is a GREEN link to the active value on Scenario Parameters, which is itself a CHOOSE() across the Base / Aggressive / Conservative columns. Flip the scenario selector and all of them move. The Model reads these cells and never reaches into Scenario Parameters directly, so this sheet is the complete register of every input the model uses.</t>
         </is>
@@ -4288,7 +4178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5036,7 +4926,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>Load-bearing because it is MISSING, not because it is large. ASSUMPTION.</t>
+          <t>⚠ NO SOURCE. NOT DERIVED, NOT OBSERVED - CHOSEN. The v2.6 brief records it as a confirmed negative: 'S45, S46 and S47 are all Low confidence with no published source. There is no spot-attach benchmark for any comparable gold or savings product anywhere.' Load-bearing because it is MISSING, not because it is large. WHAT IT ASSERTS, in plain terms: 14% x 1.7 = 0.238 purchases per paying customer per year, i.e. the average customer makes a one-off gold purchase about once every four years. The only cross-check is Augmont's 0.85 transactions per REGISTERED user per year, which we sit at 28% of - but their average transaction is Rs 331, so they are counting micro-savings rather than lumps. It bounds this number; it does not confirm it. ⚠ KNOWN SIMPLIFICATION WITH A KNOWN DIRECTION: v2.6 applied a TENURE UPLIFT here - 'a 3-year account is ~2x as likely to buy spot as a 6-month account' - which the v3.0 simplification dropped. This rate is now flat from day one. If 14% was calibrated on a mature book, SPOT IS OVERSTATED IN THE EARLY YEARS, when nearly every account is young. Not rebuilt because spot is ~1.4% of Y7 revenue; restore the uplift in the Phase 5 simulation. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -5100,83 +4990,83 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Spot-to-SIP conversion</t>
-        </is>
-      </c>
-      <c r="B37" s="38">
-        <f>CHOOSE($C$6,C37,D37,E37)</f>
-        <v/>
-      </c>
-      <c r="C37" s="19" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D37" s="19" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E37" s="19" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>% of spot buyers/yr</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>NO SOURCE EXISTS ANYWHERE - re-confirmed by search 2026-08-20, a CONFIRMED NEGATIVE rather than a gap in the searching. The mechanism design calls this arrow 'the growth funnel' and names spot 'the entry point for new investors'. THE STRATEGY QUESTION IN NUMERICAL FORM, and the one an experiment could answer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>GROUP D: CARD</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="13" t="n"/>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Active Value</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>Active Value</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>Unit</t>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Programme manager share of interchange</t>
+        </is>
+      </c>
+      <c r="B40" s="38">
+        <f>CHOOSE($C$6,C40,D40,E40)</f>
+        <v/>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D40" s="19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>SIZES THE LARGEST STREAM. No UAE/MENA figure is published. FLOOR IS 36% - take that into the sponsor conversation as the walk-away. TRIANGULATED.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Programme manager share of interchange</t>
+          <t>Facility take-up - customers who take AND use the card</t>
         </is>
       </c>
       <c r="B41" s="38">
@@ -5184,209 +5074,209 @@
         <v/>
       </c>
       <c r="C41" s="19" t="n">
-        <v>0.72</v>
+        <v>0.18</v>
       </c>
       <c r="D41" s="19" t="n">
-        <v>0.85</v>
+        <v>0.3</v>
       </c>
       <c r="E41" s="19" t="n">
-        <v>0.55</v>
+        <v>0.08</v>
       </c>
       <c r="F41" s="23" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>% of gate-cleared</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
-          <t>SIZES THE LARGEST STREAM. No UAE/MENA figure is published. FLOOR IS 36% - take that into the sponsor conversation as the walk-away. TRIANGULATED.</t>
+          <t>RE-BASED 2026-08-20, client decision: THE CARD IS A DRAWDOWN ON THE GOLD-COLLATERALISED FACILITY, not a salary-repaid revolving card. Aurumix has no balance sheet to lend from - it can only extend credit against collateral it holds, which is the customer's gold. Using the card IS borrowing, so card activation and credit take-up are the SAME behaviour and were previously modelled as two different populations (50% activating a card, 18% taking credit) doing what is in fact one thing. Merged onto the credit figure, which is the better-anchored of the two: Indian gold-loan penetration is under 10% at a point in time, uplifted here for pre-selection since these customers have already cleared a six-payment gate. ⚠ THE OLD 50% CAME FROM NEOBANK COMPARABLES (PULSE 68.2%, Monzo 68%) WHERE THE CARD IS THE PRODUCT - wrong in kind for a card that only lets you borrow against your own savings. DERIVED.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Facility take-up - customers who take AND use the card</t>
-        </is>
-      </c>
-      <c r="B42" s="38">
+          <t>Transactions per drawdown event</t>
+        </is>
+      </c>
+      <c r="B42" s="31">
         <f>CHOOSE($C$6,C42,D42,E42)</f>
         <v/>
       </c>
-      <c r="C42" s="19" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D42" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E42" s="19" t="n">
-        <v>0.08</v>
+      <c r="C42" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>% of gate-cleared</t>
+          <t>transactions/draw</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>RE-BASED 2026-08-20, client decision: THE CARD IS A DRAWDOWN ON THE GOLD-COLLATERALISED FACILITY, not a salary-repaid revolving card. Aurumix has no balance sheet to lend from - it can only extend credit against collateral it holds, which is the customer's gold. Using the card IS borrowing, so card activation and credit take-up are the SAME behaviour and were previously modelled as two different populations (50% activating a card, 18% taking credit) doing what is in fact one thing. Merged onto the credit figure, which is the better-anchored of the two: Indian gold-loan penetration is under 10% at a point in time, uplifted here for pre-selection since these customers have already cleared a six-payment gate. ⚠ THE OLD 50% CAME FROM NEOBANK COMPARABLES (PULSE 68.2%, Monzo 68%) WHERE THE CARD IS THE PRODUCT - wrong in kind for a card that only lets you borrow against your own savings. DERIVED.</t>
+          <t>RE-BASED 2026-08-20 from 12 transactions/MONTH once the card became a drawdown on the gold facility. Under that model the customer borrows a lump (limit x drawn share) a couple of times a year and spends it down, so the meaningful unit is transactions PER DRAW, not per month. At 12/month the implied ticket collapsed to ~AED 12, which is a coffee, not a reason to pledge your gold. THE AVERAGE TICKET FALLS OUT AS drawn amount / this number, and the draw events cancel - so the ticket depends only on how large a draw is and how many purchases it is spent across. ⚠ IT ALSO CHANGES WHAT THE CARD IS FOR: not daily groceries, but occasional larger needs - school fees, a medical bill, an emergency - funded by borrowing against savings rather than liquidating them. That is a materially different product story and should be put to the client in those words. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Transactions per drawdown event</t>
-        </is>
-      </c>
-      <c r="B43" s="31">
+          <t>Foreign spend share (mean)</t>
+        </is>
+      </c>
+      <c r="B43" s="38">
         <f>CHOOSE($C$6,C43,D43,E43)</f>
         <v/>
       </c>
-      <c r="C43" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>2</v>
+      <c r="C43" s="19" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E43" s="19" t="n">
+        <v>0.24</v>
       </c>
       <c r="F43" s="23" t="inlineStr">
         <is>
-          <t>transactions/draw</t>
+          <t>% of card spend</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>RE-BASED 2026-08-20 from 12 transactions/MONTH once the card became a drawdown on the gold facility. Under that model the customer borrows a lump (limit x drawn share) a couple of times a year and spends it down, so the meaningful unit is transactions PER DRAW, not per month. At 12/month the implied ticket collapsed to ~AED 12, which is a coffee, not a reason to pledge your gold. THE AVERAGE TICKET FALLS OUT AS drawn amount / this number, and the draw events cancel - so the ticket depends only on how large a draw is and how many purchases it is spent across. ⚠ IT ALSO CHANGES WHAT THE CARD IS FOR: not daily groceries, but occasional larger needs - school fees, a medical bill, an emergency - funded by borrowing against savings rather than liquidating them. That is a materially different product story and should be put to the client in those words. ASSUMPTION.</t>
+          <t>Applied through the seasonal vector, not as a constant. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Card transactions per active card per month</t>
-        </is>
-      </c>
-      <c r="B44" s="31">
+          <t>Card issuance events</t>
+        </is>
+      </c>
+      <c r="B44" s="40">
         <f>CHOOSE($C$6,C44,D44,E44)</f>
         <v/>
       </c>
-      <c r="C44" s="17" t="n">
-        <v>12</v>
-      </c>
-      <c r="D44" s="17" t="n">
-        <v>18</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>8</v>
+      <c r="C44" s="15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>1.1</v>
       </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
-          <t>transactions/month</t>
+          <t>events/card/yr</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>THE INPUT IS FREQUENCY; AVERAGE TICKET IS DERIVED FROM IT. That inversion is deliberate. Monthly spend is already pinned by income (a multiple of the SIP ticket) and capped by the gold collateral, so specifying a ticket size would over-determine the card and let it drift away from what the customer actually saves - the exact problem an absolute AED 100 ticket created. Fixing frequency instead makes the average ticket fall out as spend / frequency, which means IT SCALES WITH THE SIP CONTRIBUTION AUTOMATICALLY: a customer on a smaller monthly savings amount gets a proportionally smaller basket, in every region, with no extra input. WHY FREQUENCY IS THE BETTER THING TO ANCHOR: it has a published number and ticket size does not. Visa scheme data gives ~175 transactions per card per year for the region, about 14-15/month, and UAE low-income cash dependency fell from 84% to 69% in two years, so card usage is rising. Base is set at 12, slightly BELOW the general anchor, because this is a secondary card earned on a savings product rather than someone's main salary card. ⚠ THE UAE-WIDE AVERAGE TICKET OF ~AED 313 IS DELIBERATELY NOT USED - it spans affluent expats and corporate cards, which is the same population mismatch that put card spend at AED 6,000. NO PUBLISHED TICKET SIZE OR FREQUENCY EXISTS FOR BLUE-COLLAR GCC WORKERS SPECIFICALLY - a confirmed negative, re-checked 2026-08-20. TRIANGULATED on frequency, DERIVED on ticket.</t>
+          <t>1.00 at activation plus reissues - a tier upgrade forces a physical reissue. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Foreign spend share (mean)</t>
-        </is>
-      </c>
-      <c r="B45" s="38">
+          <t>Card replacement events</t>
+        </is>
+      </c>
+      <c r="B45" s="40">
         <f>CHOOSE($C$6,C45,D45,E45)</f>
         <v/>
       </c>
-      <c r="C45" s="19" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="D45" s="19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E45" s="19" t="n">
-        <v>0.24</v>
+      <c r="C45" s="15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.18</v>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>% of card spend</t>
+          <t>events/card/yr</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>Applied through the seasonal vector, not as a constant. ASSUMPTION.</t>
+          <t>Industry-normal loss/theft/damage is 8-15% annually. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Card issuance events</t>
-        </is>
-      </c>
-      <c r="B46" s="40">
+          <t>ATM AED 0-500 - share of cardholders</t>
+        </is>
+      </c>
+      <c r="B46" s="38">
         <f>CHOOSE($C$6,C46,D46,E46)</f>
         <v/>
       </c>
-      <c r="C46" s="15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="D46" s="15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>1.1</v>
+      <c r="C46" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D46" s="19" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>0.74</v>
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>events/card/yr</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>1.00 at activation plus reissues - a tier upgrade forces a physical reissue. ASSUMPTION.</t>
+          <t>KEPT AS A DISTRIBUTION DELIBERATELY. The mean draw (~AED 940) sits just BELOW the free allowance of AED 1,000 BY DESIGN, so applying the fee to the mean returns EXACTLY ZERO and stream 4 silently loses a component. The distribution returns materially more, generated almost entirely by a small high-cash tail. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Card replacement events</t>
-        </is>
-      </c>
-      <c r="B47" s="40">
+          <t>ATM AED 500-1,500 - share of cardholders</t>
+        </is>
+      </c>
+      <c r="B47" s="38">
         <f>CHOOSE($C$6,C47,D47,E47)</f>
         <v/>
       </c>
-      <c r="C47" s="15" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D47" s="15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E47" s="15" t="n">
+      <c r="C47" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D47" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E47" s="19" t="n">
         <v>0.18</v>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>events/card/yr</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
-          <t>Industry-normal loss/theft/damage is 8-15% annually. ASSUMPTION.</t>
+          <t>KEPT AS A DISTRIBUTION DELIBERATELY. The mean draw (~AED 940) sits just BELOW the free allowance of AED 1,000 BY DESIGN, so applying the fee to the mean returns EXACTLY ZERO and stream 4 silently loses a component. The distribution returns materially more, generated almost entirely by a small high-cash tail. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ATM AED 0-500 - share of cardholders</t>
+          <t>ATM AED 1,500-3,000 - share of cardholders</t>
         </is>
       </c>
       <c r="B48" s="38">
@@ -5394,13 +5284,13 @@
         <v/>
       </c>
       <c r="C48" s="19" t="n">
-        <v>0.6</v>
+        <v>0.12</v>
       </c>
       <c r="D48" s="19" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="E48" s="19" t="n">
-        <v>0.74</v>
+        <v>0.06</v>
       </c>
       <c r="F48" s="23" t="inlineStr">
         <is>
@@ -5416,7 +5306,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ATM AED 500-1,500 - share of cardholders</t>
+          <t>ATM AED 3,000+ - share of cardholders</t>
         </is>
       </c>
       <c r="B49" s="38">
@@ -5424,13 +5314,13 @@
         <v/>
       </c>
       <c r="C49" s="19" t="n">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="D49" s="19" t="n">
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="E49" s="19" t="n">
-        <v>0.18</v>
+        <v>0.02</v>
       </c>
       <c r="F49" s="23" t="inlineStr">
         <is>
@@ -5446,67 +5336,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ATM AED 1,500-3,000 - share of cardholders</t>
-        </is>
-      </c>
-      <c r="B50" s="38">
+          <t>ATM AED 0-500 - midpoint draw</t>
+        </is>
+      </c>
+      <c r="B50" s="31">
         <f>CHOOSE($C$6,C50,D50,E50)</f>
         <v/>
       </c>
-      <c r="C50" s="19" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D50" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E50" s="19" t="n">
-        <v>0.06</v>
+      <c r="C50" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>200</v>
       </c>
       <c r="F50" s="23" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>AED/month</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>KEPT AS A DISTRIBUTION DELIBERATELY. The mean draw (~AED 940) sits just BELOW the free allowance of AED 1,000 BY DESIGN, so applying the fee to the mean returns EXACTLY ZERO and stream 4 silently loses a component. The distribution returns materially more, generated almost entirely by a small high-cash tail. ASSUMPTION.</t>
+          <t>Raising the allowance at the top tier waives revenue from only the top ~3% of cardholders.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ATM AED 3,000+ - share of cardholders</t>
-        </is>
-      </c>
-      <c r="B51" s="38">
+          <t>ATM AED 500-1,500 - midpoint draw</t>
+        </is>
+      </c>
+      <c r="B51" s="31">
         <f>CHOOSE($C$6,C51,D51,E51)</f>
         <v/>
       </c>
-      <c r="C51" s="19" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D51" s="19" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E51" s="19" t="n">
-        <v>0.02</v>
+      <c r="C51" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>900</v>
       </c>
       <c r="F51" s="23" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>AED/month</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>KEPT AS A DISTRIBUTION DELIBERATELY. The mean draw (~AED 940) sits just BELOW the free allowance of AED 1,000 BY DESIGN, so applying the fee to the mean returns EXACTLY ZERO and stream 4 silently loses a component. The distribution returns materially more, generated almost entirely by a small high-cash tail. ASSUMPTION.</t>
+          <t>Raising the allowance at the top tier waives revenue from only the top ~3% of cardholders.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ATM AED 0-500 - midpoint draw</t>
+          <t>ATM AED 1,500-3,000 - midpoint draw</t>
         </is>
       </c>
       <c r="B52" s="31">
@@ -5514,13 +5404,13 @@
         <v/>
       </c>
       <c r="C52" s="17" t="n">
-        <v>250</v>
+        <v>2250</v>
       </c>
       <c r="D52" s="17" t="n">
-        <v>300</v>
+        <v>2400</v>
       </c>
       <c r="E52" s="17" t="n">
-        <v>200</v>
+        <v>2100</v>
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
@@ -5536,7 +5426,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ATM AED 500-1,500 - midpoint draw</t>
+          <t>ATM AED 3,000+ - midpoint draw</t>
         </is>
       </c>
       <c r="B53" s="31">
@@ -5544,13 +5434,13 @@
         <v/>
       </c>
       <c r="C53" s="17" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="D53" s="17" t="n">
-        <v>1100</v>
+        <v>4500</v>
       </c>
       <c r="E53" s="17" t="n">
-        <v>900</v>
+        <v>3600</v>
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
@@ -5563,233 +5453,233 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ATM AED 1,500-3,000 - midpoint draw</t>
-        </is>
-      </c>
-      <c r="B54" s="31">
-        <f>CHOOSE($C$6,C54,D54,E54)</f>
-        <v/>
-      </c>
-      <c r="C54" s="17" t="n">
-        <v>2250</v>
-      </c>
-      <c r="D54" s="17" t="n">
-        <v>2400</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>2100</v>
-      </c>
-      <c r="F54" s="23" t="inlineStr">
-        <is>
-          <t>AED/month</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>Raising the allowance at the top tier waives revenue from only the top ~3% of cardholders.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>ATM AED 3,000+ - midpoint draw</t>
-        </is>
-      </c>
-      <c r="B55" s="31">
-        <f>CHOOSE($C$6,C55,D55,E55)</f>
-        <v/>
-      </c>
-      <c r="C55" s="17" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D55" s="17" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F55" s="23" t="inlineStr">
-        <is>
-          <t>AED/month</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>Raising the allowance at the top tier waives revenue from only the top ~3% of cardholders.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>GROUP E: CREDIT, B2B AND FAMILY</t>
         </is>
       </c>
-      <c r="B57" s="13" t="n"/>
-      <c r="C57" s="13" t="n"/>
-      <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
+      <c r="B55" s="13" t="n"/>
+      <c r="C55" s="13" t="n"/>
+      <c r="D55" s="13" t="n"/>
+      <c r="E55" s="13" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Active Value</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Drawn as % of permitted limit</t>
+        </is>
+      </c>
+      <c r="B57" s="38">
+        <f>CHOOSE($C$6,C57,D57,E57)</f>
+        <v/>
+      </c>
+      <c r="C57" s="19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D57" s="19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E57" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>Revolving facilities draw 40-55% of permitted. This now drives CARD SPEND as well as the loan balance, because the card is the drawdown mechanism. TRIANGULATED.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B58" s="14" t="inlineStr">
-        <is>
-          <t>Active Value</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="F58" s="14" t="inlineStr">
-        <is>
-          <t>Unit</t>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Facility turnover, peak -&gt; average</t>
+        </is>
+      </c>
+      <c r="B58" s="40">
+        <f>CHOOSE($C$6,C58,D58,E58)</f>
+        <v/>
+      </c>
+      <c r="C58" s="15" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D58" s="15" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>x peak drawn</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>AN ARITHMETIC CORRECTION, not a sensitivity, derived from Manappuram's 71-day realised tenor. It cuts the lending stream by 1.88x. DERIVED.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Drawn as % of permitted limit</t>
-        </is>
-      </c>
-      <c r="B59" s="38">
+          <t>Draw events per borrower per year</t>
+        </is>
+      </c>
+      <c r="B59" s="40">
         <f>CHOOSE($C$6,C59,D59,E59)</f>
         <v/>
       </c>
-      <c r="C59" s="19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D59" s="19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E59" s="19" t="n">
-        <v>0.3</v>
+      <c r="C59" s="15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D59" s="15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>1.3</v>
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>events/yr</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>Revolving facilities draw 40-55% of permitted. This now drives CARD SPEND as well as the loan balance, because the card is the drawdown mechanism. TRIANGULATED.</t>
+          <t>MOVES WITH facility turnover - do not flex independently. DERIVED.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Facility turnover, peak -&gt; average</t>
-        </is>
-      </c>
-      <c r="B60" s="40">
+          <t>Family plan attach rate</t>
+        </is>
+      </c>
+      <c r="B60" s="38">
         <f>CHOOSE($C$6,C60,D60,E60)</f>
         <v/>
       </c>
-      <c r="C60" s="15" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="D60" s="15" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.3</v>
+      <c r="C60" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D60" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>0.1</v>
       </c>
       <c r="F60" s="23" t="inlineStr">
         <is>
-          <t>x peak drawn</t>
+          <t>% of customers</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>AN ARITHMETIC CORRECTION, not a sensitivity, derived from Manappuram's 71-day realised tenor. It cuts the lending stream by 1.88x. DERIVED.</t>
+          <t>NOTHING IS STATED ANYWHERE IN THE CORPUS. Pure assumption. Scales stream 3 linearly.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Draw events per borrower per year</t>
-        </is>
-      </c>
-      <c r="B61" s="40">
+          <t>B2B partners - Y1</t>
+        </is>
+      </c>
+      <c r="B61" s="31">
         <f>CHOOSE($C$6,C61,D61,E61)</f>
         <v/>
       </c>
-      <c r="C61" s="15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D61" s="15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>1.3</v>
+      <c r="C61" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="23" t="inlineStr">
         <is>
-          <t>events/yr</t>
+          <t>partners</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>MOVES WITH facility turnover - do not flex independently. DERIVED.</t>
+          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Family plan attach rate</t>
-        </is>
-      </c>
-      <c r="B62" s="38">
+          <t>B2B partners - Y2</t>
+        </is>
+      </c>
+      <c r="B62" s="31">
         <f>CHOOSE($C$6,C62,D62,E62)</f>
         <v/>
       </c>
-      <c r="C62" s="19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D62" s="19" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E62" s="19" t="n">
-        <v>0.1</v>
+      <c r="C62" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="F62" s="23" t="inlineStr">
         <is>
-          <t>% of customers</t>
+          <t>partners</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>NOTHING IS STATED ANYWHERE IN THE CORPUS. Pure assumption. Scales stream 3 linearly.</t>
+          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>B2B partners - Y1</t>
+          <t>B2B partners - Y3</t>
         </is>
       </c>
       <c r="B63" s="31">
@@ -5797,13 +5687,13 @@
         <v/>
       </c>
       <c r="C63" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63" s="17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
@@ -5819,7 +5709,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>B2B partners - Y2</t>
+          <t>B2B partners - Y4</t>
         </is>
       </c>
       <c r="B64" s="31">
@@ -5827,10 +5717,10 @@
         <v/>
       </c>
       <c r="C64" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64" s="17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>1</v>
@@ -5849,7 +5739,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>B2B partners - Y3</t>
+          <t>B2B partners - Y5</t>
         </is>
       </c>
       <c r="B65" s="31">
@@ -5857,13 +5747,13 @@
         <v/>
       </c>
       <c r="C65" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E65" s="17" t="n">
         <v>2</v>
-      </c>
-      <c r="D65" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>1</v>
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
@@ -5879,7 +5769,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>B2B partners - Y4</t>
+          <t>B2B partners - Y6</t>
         </is>
       </c>
       <c r="B66" s="31">
@@ -5887,13 +5777,13 @@
         <v/>
       </c>
       <c r="C66" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D66" s="17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="23" t="inlineStr">
         <is>
@@ -5909,7 +5799,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B2B partners - Y5</t>
+          <t>B2B partners - Y7</t>
         </is>
       </c>
       <c r="B67" s="31">
@@ -5917,10 +5807,10 @@
         <v/>
       </c>
       <c r="C67" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D67" s="17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E67" s="17" t="n">
         <v>2</v>
@@ -5939,140 +5829,140 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B2B partners - Y6</t>
-        </is>
-      </c>
-      <c r="B68" s="31">
+          <t>AUM per partner (mature)</t>
+        </is>
+      </c>
+      <c r="B68" s="41">
         <f>CHOOSE($C$6,C68,D68,E68)</f>
         <v/>
       </c>
-      <c r="C68" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D68" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="E68" s="17" t="n">
-        <v>2</v>
+      <c r="C68" s="20" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="D68" s="20" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="E68" s="20" t="n">
+        <v>22000000</v>
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>partners</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>B2B partners - Y7</t>
-        </is>
-      </c>
-      <c r="B69" s="31">
-        <f>CHOOSE($C$6,C69,D69,E69)</f>
-        <v/>
-      </c>
-      <c r="C69" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="D69" s="17" t="n">
-        <v>11</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F69" s="23" t="inlineStr">
-        <is>
-          <t>partners</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>AUM per partner (mature)</t>
-        </is>
-      </c>
-      <c r="B70" s="41">
-        <f>CHOOSE($C$6,C70,D70,E70)</f>
-        <v/>
-      </c>
-      <c r="C70" s="20" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="D70" s="20" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="E70" s="20" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="F70" s="23" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
           <t>Requires a signed partner. Partner AUM earns NO tier and consumes NO benefits - structurally the highest-margin book. DERIVED.</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="12" t="inlineStr">
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="12" t="inlineStr">
         <is>
           <t>GROUP F: REGIONS</t>
         </is>
       </c>
-      <c r="B72" s="13" t="n"/>
-      <c r="C72" s="13" t="n"/>
-      <c r="D72" s="13" t="n"/>
-      <c r="E72" s="13" t="n"/>
+      <c r="B70" s="13" t="n"/>
+      <c r="C70" s="13" t="n"/>
+      <c r="D70" s="13" t="n"/>
+      <c r="E70" s="13" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>Active Value</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Average monthly ticket - UAE</t>
+        </is>
+      </c>
+      <c r="B72" s="41">
+        <f>CHOOSE($C$6,C72,D72,E72)</f>
+        <v/>
+      </c>
+      <c r="C72" s="20" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="D72" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="E72" s="20" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F72" s="23" t="inlineStr">
+        <is>
+          <t>USD/month</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="14" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>Active Value</t>
-        </is>
-      </c>
-      <c r="C73" s="14" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="E73" s="14" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="F73" s="14" t="inlineStr">
-        <is>
-          <t>Unit</t>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Average monthly ticket - Oman and Bahrain</t>
+        </is>
+      </c>
+      <c r="B73" s="41">
+        <f>CHOOSE($C$6,C73,D73,E73)</f>
+        <v/>
+      </c>
+      <c r="C73" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="D73" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="E73" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="F73" s="23" t="inlineStr">
+        <is>
+          <t>USD/month</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Average monthly ticket - UAE</t>
+          <t>Average monthly ticket - India</t>
         </is>
       </c>
       <c r="B74" s="41">
@@ -6080,13 +5970,13 @@
         <v/>
       </c>
       <c r="C74" s="20" t="n">
-        <v>33.6</v>
+        <v>30</v>
       </c>
       <c r="D74" s="20" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E74" s="20" t="n">
-        <v>26.5</v>
+        <v>24</v>
       </c>
       <c r="F74" s="23" t="inlineStr">
         <is>
@@ -6099,209 +5989,86 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Average monthly ticket - Oman and Bahrain</t>
-        </is>
-      </c>
-      <c r="B75" s="41">
-        <f>CHOOSE($C$6,C75,D75,E75)</f>
-        <v/>
-      </c>
-      <c r="C75" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="D75" s="20" t="n">
-        <v>32</v>
-      </c>
-      <c r="E75" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="F75" s="23" t="inlineStr">
-        <is>
-          <t>USD/month</t>
-        </is>
-      </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Average monthly ticket - India</t>
-        </is>
-      </c>
-      <c r="B76" s="41">
-        <f>CHOOSE($C$6,C76,D76,E76)</f>
-        <v/>
-      </c>
-      <c r="C76" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="D76" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="E76" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="F76" s="23" t="inlineStr">
-        <is>
-          <t>USD/month</t>
-        </is>
-      </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
-        </is>
-      </c>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>STRUCTURAL SWITCHES - the two that move revenue</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="n"/>
+      <c r="C76" s="13" t="n"/>
+      <c r="D76" s="13" t="n"/>
+      <c r="E76" s="13" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Share of new customers - UAE</t>
-        </is>
-      </c>
-      <c r="B77" s="38">
-        <f>Assumptions!$B$81/(Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)</f>
-        <v/>
-      </c>
-      <c r="F77" s="23" t="inlineStr">
-        <is>
-          <t>% of new</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED from market size: each region's share of acquisition equals its share of the addressable ceiling, so acquisition follows the opportunity. Previously these were four typed numbers with no basis, which sent 34% of acquisition to Oman and Bahrain - a market that is 16% of the opportunity - and only 8% to India, which is 26% of it. Because they are derived they sum to 1.000 by construction and cannot drift out of line with the ceilings. Shares are RENORMALISED on the Model for regions not yet open, so a region that opens later redistributes rather than vanishing.</t>
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>Switch</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>Active (1/0)</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>ON value</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Share of new customers - Oman and Bahrain</t>
-        </is>
-      </c>
-      <c r="B78" s="38">
-        <f>Assumptions!$B$82/(Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)</f>
-        <v/>
-      </c>
-      <c r="F78" s="23" t="inlineStr">
-        <is>
-          <t>% of new</t>
+          <t>Prepaid instead of credit</t>
+        </is>
+      </c>
+      <c r="B78" s="31">
+        <f>IF($C$78="Prepaid",1,0)</f>
+        <v/>
+      </c>
+      <c r="C78" s="37" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="D78" s="23" t="inlineStr">
+        <is>
+          <t>Prepaid</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>DERIVED from market size: each region's share of acquisition equals its share of the addressable ceiling, so acquisition follows the opportunity. Previously these were four typed numbers with no basis, which sent 34% of acquisition to Oman and Bahrain - a market that is 16% of the opportunity - and only 8% to India, which is 26% of it. Because they are derived they sum to 1.000 by construction and cannot drift out of line with the ceilings. Shares are RENORMALISED on the Model for regions not yet open, so a region that opens later redistributes rather than vanishing.</t>
+          <t>ON (Prepaid) caps interchange at 1.00% and removes the credit stream entirely. 'NOT A PRODUCT CHOICE, IT IS THE BUSINESS MODEL.' Worth ~USD 2.3m of Y10 revenue on the ten-year run.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Share of new customers - India</t>
-        </is>
-      </c>
-      <c r="B79" s="38">
-        <f>Assumptions!$B$83/(Assumptions!$B$81+Assumptions!$B$82+Assumptions!$B$83)</f>
-        <v/>
-      </c>
-      <c r="F79" s="23" t="inlineStr">
-        <is>
-          <t>% of new</t>
+          <t>Holders keep the card</t>
+        </is>
+      </c>
+      <c r="B79" s="31">
+        <f>IF($C$79="ON",1,0)</f>
+        <v/>
+      </c>
+      <c r="C79" s="37" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D79" s="23" t="inlineStr">
+        <is>
+          <t>ON</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED from market size: each region's share of acquisition equals its share of the addressable ceiling, so acquisition follows the opportunity. Previously these were four typed numbers with no basis, which sent 34% of acquisition to Oman and Bahrain - a market that is 16% of the opportunity - and only 8% to India, which is 26% of it. Because they are derived they sum to 1.000 by construction and cannot drift out of line with the ceilings. Shares are RENORMALISED on the Model for regions not yet open, so a region that opens later redistributes rather than vanishing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>STRUCTURAL SWITCHES - the two that move revenue</t>
-        </is>
-      </c>
-      <c r="B81" s="13" t="n"/>
-      <c r="C81" s="13" t="n"/>
-      <c r="D81" s="13" t="n"/>
-      <c r="E81" s="13" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="14" t="inlineStr">
-        <is>
-          <t>Switch</t>
-        </is>
-      </c>
-      <c r="B82" s="14" t="inlineStr">
-        <is>
-          <t>Active (1/0)</t>
-        </is>
-      </c>
-      <c r="C82" s="14" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="D82" s="14" t="inlineStr">
-        <is>
-          <t>ON value</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Prepaid instead of credit</t>
-        </is>
-      </c>
-      <c r="B83" s="31">
-        <f>IF($C$83="Prepaid",1,0)</f>
-        <v/>
-      </c>
-      <c r="C83" s="37" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="D83" s="23" t="inlineStr">
-        <is>
-          <t>Prepaid</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>ON (Prepaid) caps interchange at 1.00% and removes the credit stream entirely. 'NOT A PRODUCT CHOICE, IT IS THE BUSINESS MODEL.' Worth ~USD 2.3m of Y10 revenue on the ten-year run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Holders keep the card</t>
-        </is>
-      </c>
-      <c r="B84" s="31">
-        <f>IF($C$84="ON",1,0)</f>
-        <v/>
-      </c>
-      <c r="C84" s="37" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="D84" s="23" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
-      <c r="G84" s="9" t="inlineStr">
         <is>
           <t>NOBODY HAS DECIDED THIS. It determines whether the card streams - the majority of revenue - decay with churn or are immune to it. Worth a 42% swing in terminal revenue. Default ON because nothing in the design revokes the card; report both.</t>
         </is>
@@ -6312,10 +6079,10 @@
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Base,Aggressive,Conservative"</formula1>
     </dataValidation>
-    <dataValidation sqref="C83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Credit,Prepaid"</formula1>
     </dataValidation>
-    <dataValidation sqref="C84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"ON,OFF"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7349,51 +7116,51 @@
         </is>
       </c>
       <c r="C13" s="48">
-        <f>Assumptions!$F$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f>Assumptions!$F$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v/>
       </c>
       <c r="D13" s="48">
-        <f>Assumptions!$G$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f>Assumptions!$G$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v/>
       </c>
       <c r="E13" s="48">
-        <f>Assumptions!$H$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f>Assumptions!$H$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v/>
       </c>
       <c r="F13" s="48">
-        <f>Assumptions!$I$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f>Assumptions!$I$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v/>
       </c>
       <c r="G13" s="48">
-        <f>Assumptions!$J$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f>Assumptions!$J$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v/>
       </c>
       <c r="H13" s="48">
-        <f>Assumptions!$K$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f>Assumptions!$K$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v/>
       </c>
       <c r="I13" s="48">
-        <f>Assumptions!$L$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f>Assumptions!$L$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v/>
       </c>
       <c r="J13" s="48">
-        <f>Assumptions!$M$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f>Assumptions!$M$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v/>
       </c>
       <c r="K13" s="48">
-        <f>Assumptions!$N$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f>Assumptions!$N$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v/>
       </c>
       <c r="L13" s="48">
-        <f>Assumptions!$O$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f>Assumptions!$O$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v/>
       </c>
       <c r="M13" s="48">
-        <f>Assumptions!$P$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f>Assumptions!$P$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v/>
       </c>
       <c r="N13" s="48">
-        <f>Assumptions!$Q$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$138</f>
+        <f>Assumptions!$Q$60/AVERAGE(Assumptions!$F$60:$Q$60)*Assumptions!$B$136</f>
         <v/>
       </c>
     </row>
@@ -9293,119 +9060,119 @@
         </is>
       </c>
       <c r="C33" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$44,C29*Assumptions!$B$161*C7,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$44,C29*Assumptions!$B$159*C7,0)</f>
         <v/>
       </c>
       <c r="D33" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$44,D29*Assumptions!$B$161*D7,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$44,D29*Assumptions!$B$159*D7,0)</f>
         <v/>
       </c>
       <c r="E33" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$44,E29*Assumptions!$B$161*E7,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$44,E29*Assumptions!$B$159*E7,0)</f>
         <v/>
       </c>
       <c r="F33" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$44,F29*Assumptions!$B$161*F7,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$44,F29*Assumptions!$B$159*F7,0)</f>
         <v/>
       </c>
       <c r="G33" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$44,G29*Assumptions!$B$161*G7,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$44,G29*Assumptions!$B$159*G7,0)</f>
         <v/>
       </c>
       <c r="H33" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$44,H29*Assumptions!$B$161*H7,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$44,H29*Assumptions!$B$159*H7,0)</f>
         <v/>
       </c>
       <c r="I33" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$44,I29*Assumptions!$B$161*I7,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$44,I29*Assumptions!$B$159*I7,0)</f>
         <v/>
       </c>
       <c r="J33" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$44,J29*Assumptions!$B$161*J7,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$44,J29*Assumptions!$B$159*J7,0)</f>
         <v/>
       </c>
       <c r="K33" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$44,K29*Assumptions!$B$161*K7,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$44,K29*Assumptions!$B$159*K7,0)</f>
         <v/>
       </c>
       <c r="L33" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$44,L29*Assumptions!$B$161*L7,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$44,L29*Assumptions!$B$159*L7,0)</f>
         <v/>
       </c>
       <c r="M33" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$44,M29*Assumptions!$B$161*M7,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$44,M29*Assumptions!$B$159*M7,0)</f>
         <v/>
       </c>
       <c r="N33" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$44,N29*Assumptions!$B$161*N7,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$44,N29*Assumptions!$B$159*N7,0)</f>
         <v/>
       </c>
       <c r="O33" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$44,O29*Assumptions!$B$161*O7,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$44,O29*Assumptions!$B$159*O7,0)</f>
         <v/>
       </c>
       <c r="P33" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$44,P29*Assumptions!$B$161*P7,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$44,P29*Assumptions!$B$159*P7,0)</f>
         <v/>
       </c>
       <c r="Q33" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$44,Q29*Assumptions!$B$161*Q7,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$44,Q29*Assumptions!$B$159*Q7,0)</f>
         <v/>
       </c>
       <c r="R33" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$44,R29*Assumptions!$B$161*R7,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$44,R29*Assumptions!$B$159*R7,0)</f>
         <v/>
       </c>
       <c r="S33" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$44,S29*Assumptions!$B$161*S7,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$44,S29*Assumptions!$B$159*S7,0)</f>
         <v/>
       </c>
       <c r="T33" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$44,T29*Assumptions!$B$161*T7,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$44,T29*Assumptions!$B$159*T7,0)</f>
         <v/>
       </c>
       <c r="U33" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$44,U29*Assumptions!$B$161*U7,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$44,U29*Assumptions!$B$159*U7,0)</f>
         <v/>
       </c>
       <c r="V33" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$44,V29*Assumptions!$B$161*V7,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$44,V29*Assumptions!$B$159*V7,0)</f>
         <v/>
       </c>
       <c r="W33" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$44,W29*Assumptions!$B$161*W7,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$44,W29*Assumptions!$B$159*W7,0)</f>
         <v/>
       </c>
       <c r="X33" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$44,X29*Assumptions!$B$161*X7,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$44,X29*Assumptions!$B$159*X7,0)</f>
         <v/>
       </c>
       <c r="Y33" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$44,Y29*Assumptions!$B$161*Y7,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$44,Y29*Assumptions!$B$159*Y7,0)</f>
         <v/>
       </c>
       <c r="Z33" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$44,Z29*Assumptions!$B$161*Z7,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$44,Z29*Assumptions!$B$159*Z7,0)</f>
         <v/>
       </c>
       <c r="AA33" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$44,AA29*Assumptions!$B$161*AA7,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$44,AA29*Assumptions!$B$159*AA7,0)</f>
         <v/>
       </c>
       <c r="AB33" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$44,AB29*Assumptions!$B$161*AB7,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$44,AB29*Assumptions!$B$159*AB7,0)</f>
         <v/>
       </c>
       <c r="AC33" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$44,AC29*Assumptions!$B$161*AC7,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$44,AC29*Assumptions!$B$159*AC7,0)</f>
         <v/>
       </c>
       <c r="AD33" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$44,AD29*Assumptions!$B$161*AD7,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$44,AD29*Assumptions!$B$159*AD7,0)</f>
         <v/>
       </c>
       <c r="AE33" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$44,AE29*Assumptions!$B$161*AE7,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$44,AE29*Assumptions!$B$159*AE7,0)</f>
         <v/>
       </c>
     </row>
@@ -10061,119 +9828,119 @@
         </is>
       </c>
       <c r="C39" s="53">
-        <f>C29+C31*Assumptions!$B$168</f>
+        <f>C29+C31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="D39" s="53">
-        <f>D29+D31*Assumptions!$B$168</f>
+        <f>D29+D31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="E39" s="53">
-        <f>E29+E31*Assumptions!$B$168</f>
+        <f>E29+E31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="F39" s="53">
-        <f>F29+F31*Assumptions!$B$168</f>
+        <f>F29+F31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="G39" s="53">
-        <f>G29+G31*Assumptions!$B$168</f>
+        <f>G29+G31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="H39" s="53">
-        <f>H29+H31*Assumptions!$B$168</f>
+        <f>H29+H31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="I39" s="53">
-        <f>I29+I31*Assumptions!$B$168</f>
+        <f>I29+I31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="J39" s="53">
-        <f>J29+J31*Assumptions!$B$168</f>
+        <f>J29+J31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="K39" s="53">
-        <f>K29+K31*Assumptions!$B$168</f>
+        <f>K29+K31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="L39" s="53">
-        <f>L29+L31*Assumptions!$B$168</f>
+        <f>L29+L31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="M39" s="53">
-        <f>M29+M31*Assumptions!$B$168</f>
+        <f>M29+M31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="N39" s="53">
-        <f>N29+N31*Assumptions!$B$168</f>
+        <f>N29+N31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="O39" s="53">
-        <f>O29+O31*Assumptions!$B$168</f>
+        <f>O29+O31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="P39" s="53">
-        <f>P29+P31*Assumptions!$B$168</f>
+        <f>P29+P31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="Q39" s="53">
-        <f>Q29+Q31*Assumptions!$B$168</f>
+        <f>Q29+Q31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="R39" s="53">
-        <f>R29+R31*Assumptions!$B$168</f>
+        <f>R29+R31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="S39" s="53">
-        <f>S29+S31*Assumptions!$B$168</f>
+        <f>S29+S31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="T39" s="53">
-        <f>T29+T31*Assumptions!$B$168</f>
+        <f>T29+T31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="U39" s="53">
-        <f>U29+U31*Assumptions!$B$168</f>
+        <f>U29+U31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="V39" s="53">
-        <f>V29+V31*Assumptions!$B$168</f>
+        <f>V29+V31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="W39" s="53">
-        <f>W29+W31*Assumptions!$B$168</f>
+        <f>W29+W31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="X39" s="53">
-        <f>X29+X31*Assumptions!$B$168</f>
+        <f>X29+X31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="Y39" s="53">
-        <f>Y29+Y31*Assumptions!$B$168</f>
+        <f>Y29+Y31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="Z39" s="53">
-        <f>Z29+Z31*Assumptions!$B$168</f>
+        <f>Z29+Z31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AA39" s="53">
-        <f>AA29+AA31*Assumptions!$B$168</f>
+        <f>AA29+AA31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AB39" s="53">
-        <f>AB29+AB31*Assumptions!$B$168</f>
+        <f>AB29+AB31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AC39" s="53">
-        <f>AC29+AC31*Assumptions!$B$168</f>
+        <f>AC29+AC31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AD39" s="53">
-        <f>AD29+AD31*Assumptions!$B$168</f>
+        <f>AD29+AD31*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AE39" s="53">
-        <f>AE29+AE31*Assumptions!$B$168</f>
+        <f>AE29+AE31*Assumptions!$B$163</f>
         <v/>
       </c>
     </row>
@@ -10317,119 +10084,119 @@
         </is>
       </c>
       <c r="C41" s="28">
-        <f>IF(C2&gt;=Assumptions!$B$48,C40*Assumptions!$B$135,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$48,C40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="D41" s="28">
-        <f>IF(D2&gt;=Assumptions!$B$48,D40*Assumptions!$B$135,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$48,D40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="E41" s="28">
-        <f>IF(E2&gt;=Assumptions!$B$48,E40*Assumptions!$B$135,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$48,E40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="F41" s="28">
-        <f>IF(F2&gt;=Assumptions!$B$48,F40*Assumptions!$B$135,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$48,F40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="G41" s="28">
-        <f>IF(G2&gt;=Assumptions!$B$48,G40*Assumptions!$B$135,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$48,G40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="H41" s="28">
-        <f>IF(H2&gt;=Assumptions!$B$48,H40*Assumptions!$B$135,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$48,H40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="I41" s="28">
-        <f>IF(I2&gt;=Assumptions!$B$48,I40*Assumptions!$B$135,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$48,I40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="J41" s="28">
-        <f>IF(J2&gt;=Assumptions!$B$48,J40*Assumptions!$B$135,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$48,J40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="K41" s="28">
-        <f>IF(K2&gt;=Assumptions!$B$48,K40*Assumptions!$B$135,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$48,K40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="L41" s="28">
-        <f>IF(L2&gt;=Assumptions!$B$48,L40*Assumptions!$B$135,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$48,L40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="M41" s="28">
-        <f>IF(M2&gt;=Assumptions!$B$48,M40*Assumptions!$B$135,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$48,M40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="N41" s="28">
-        <f>IF(N2&gt;=Assumptions!$B$48,N40*Assumptions!$B$135,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$48,N40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="O41" s="28">
-        <f>IF(O2&gt;=Assumptions!$B$48,O40*Assumptions!$B$135,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$48,O40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="P41" s="28">
-        <f>IF(P2&gt;=Assumptions!$B$48,P40*Assumptions!$B$135,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$48,P40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="Q41" s="28">
-        <f>IF(Q2&gt;=Assumptions!$B$48,Q40*Assumptions!$B$135,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$48,Q40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="R41" s="28">
-        <f>IF(R2&gt;=Assumptions!$B$48,R40*Assumptions!$B$135,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$48,R40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="S41" s="28">
-        <f>IF(S2&gt;=Assumptions!$B$48,S40*Assumptions!$B$135,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$48,S40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="T41" s="28">
-        <f>IF(T2&gt;=Assumptions!$B$48,T40*Assumptions!$B$135,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$48,T40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="U41" s="28">
-        <f>IF(U2&gt;=Assumptions!$B$48,U40*Assumptions!$B$135,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$48,U40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="V41" s="28">
-        <f>IF(V2&gt;=Assumptions!$B$48,V40*Assumptions!$B$135,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$48,V40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="W41" s="28">
-        <f>IF(W2&gt;=Assumptions!$B$48,W40*Assumptions!$B$135,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$48,W40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="X41" s="28">
-        <f>IF(X2&gt;=Assumptions!$B$48,X40*Assumptions!$B$135,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$48,X40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="Y41" s="28">
-        <f>IF(Y2&gt;=Assumptions!$B$48,Y40*Assumptions!$B$135,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$48,Y40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="Z41" s="28">
-        <f>IF(Z2&gt;=Assumptions!$B$48,Z40*Assumptions!$B$135,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$48,Z40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AA41" s="28">
-        <f>IF(AA2&gt;=Assumptions!$B$48,AA40*Assumptions!$B$135,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$48,AA40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AB41" s="28">
-        <f>IF(AB2&gt;=Assumptions!$B$48,AB40*Assumptions!$B$135,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$48,AB40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AC41" s="28">
-        <f>IF(AC2&gt;=Assumptions!$B$48,AC40*Assumptions!$B$135,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$48,AC40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AD41" s="28">
-        <f>IF(AD2&gt;=Assumptions!$B$48,AD40*Assumptions!$B$135,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$48,AD40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AE41" s="28">
-        <f>IF(AE2&gt;=Assumptions!$B$48,AE40*Assumptions!$B$135,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$48,AE40*Assumptions!$B$134,0)</f>
         <v/>
       </c>
     </row>
@@ -10573,119 +10340,119 @@
         </is>
       </c>
       <c r="C43" s="54">
-        <f>C42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>C42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="D43" s="54">
-        <f>D42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>D42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="E43" s="54">
-        <f>E42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>E42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="F43" s="54">
-        <f>F42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>F42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="G43" s="54">
-        <f>G42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>G42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="H43" s="54">
-        <f>H42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>H42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="I43" s="54">
-        <f>I42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>I42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="J43" s="54">
-        <f>J42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>J42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="K43" s="54">
-        <f>K42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>K42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="L43" s="54">
-        <f>L42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>L42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="M43" s="54">
-        <f>M42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>M42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="N43" s="54">
-        <f>N42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>N42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="O43" s="54">
-        <f>O42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>O42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="P43" s="54">
-        <f>P42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>P42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="Q43" s="54">
-        <f>Q42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>Q42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="R43" s="54">
-        <f>R42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>R42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="S43" s="54">
-        <f>S42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>S42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="T43" s="54">
-        <f>T42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>T42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="U43" s="54">
-        <f>U42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>U42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="V43" s="54">
-        <f>V42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>V42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="W43" s="54">
-        <f>W42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>W42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="X43" s="54">
-        <f>X42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>X42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="Y43" s="54">
-        <f>Y42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>Y42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="Z43" s="54">
-        <f>Z42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>Z42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AA43" s="54">
-        <f>AA42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AA42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AB43" s="54">
-        <f>AB42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AB42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AC43" s="54">
-        <f>AC42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AC42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AD43" s="54">
-        <f>AD42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AD42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AE43" s="54">
-        <f>AE42*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AE42*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
     </row>
@@ -11085,119 +10852,119 @@
         </is>
       </c>
       <c r="C47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,C42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,C42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="D47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,D42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,D42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="E47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,E42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,E42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="F47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,F42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,F42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="G47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,G42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,G42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="H47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,H42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,H42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="I47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,I42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,I42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="J47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,J42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,J42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="K47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,K42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,K42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="L47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,L42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,L42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="M47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,M42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,M42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="N47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,N42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,N42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="O47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,O42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,O42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="P47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,P42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,P42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="Q47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,Q42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,Q42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="R47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,R42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,R42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="S47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,S42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,S42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="T47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,T42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,T42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="U47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,U42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,U42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="V47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,V42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,V42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="W47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,W42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,W42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="X47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,X42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,X42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="Y47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,Y42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,Y42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="Z47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,Z42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,Z42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AA47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AA42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AA42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AB47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AB42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AB42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AC47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AC42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AC42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AD47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AD42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AD42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AE47" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AE42*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AE42*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
     </row>
@@ -11213,119 +10980,119 @@
         </is>
       </c>
       <c r="C48" s="44">
-        <f>C41*Assumptions!$B$151*Assumptions!$B$136*C7/12*(1+Assumptions!$B$16)</f>
+        <f>C41*Assumptions!$B$149*Assumptions!$B$135*C7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="D48" s="44">
-        <f>D41*Assumptions!$B$151*Assumptions!$B$136*D7/12*(1+Assumptions!$B$16)</f>
+        <f>D41*Assumptions!$B$149*Assumptions!$B$135*D7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="E48" s="44">
-        <f>E41*Assumptions!$B$151*Assumptions!$B$136*E7/12*(1+Assumptions!$B$16)</f>
+        <f>E41*Assumptions!$B$149*Assumptions!$B$135*E7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="F48" s="44">
-        <f>F41*Assumptions!$B$151*Assumptions!$B$136*F7/12*(1+Assumptions!$B$16)</f>
+        <f>F41*Assumptions!$B$149*Assumptions!$B$135*F7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="G48" s="44">
-        <f>G41*Assumptions!$B$151*Assumptions!$B$136*G7/12*(1+Assumptions!$B$16)</f>
+        <f>G41*Assumptions!$B$149*Assumptions!$B$135*G7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="H48" s="44">
-        <f>H41*Assumptions!$B$151*Assumptions!$B$136*H7/12*(1+Assumptions!$B$16)</f>
+        <f>H41*Assumptions!$B$149*Assumptions!$B$135*H7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="I48" s="44">
-        <f>I41*Assumptions!$B$151*Assumptions!$B$136*I7/12*(1+Assumptions!$B$16)</f>
+        <f>I41*Assumptions!$B$149*Assumptions!$B$135*I7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="J48" s="44">
-        <f>J41*Assumptions!$B$151*Assumptions!$B$136*J7/12*(1+Assumptions!$B$16)</f>
+        <f>J41*Assumptions!$B$149*Assumptions!$B$135*J7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="K48" s="44">
-        <f>K41*Assumptions!$B$151*Assumptions!$B$136*K7/12*(1+Assumptions!$B$16)</f>
+        <f>K41*Assumptions!$B$149*Assumptions!$B$135*K7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="L48" s="44">
-        <f>L41*Assumptions!$B$151*Assumptions!$B$136*L7/12*(1+Assumptions!$B$16)</f>
+        <f>L41*Assumptions!$B$149*Assumptions!$B$135*L7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="M48" s="44">
-        <f>M41*Assumptions!$B$151*Assumptions!$B$136*M7/12*(1+Assumptions!$B$16)</f>
+        <f>M41*Assumptions!$B$149*Assumptions!$B$135*M7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="N48" s="44">
-        <f>N41*Assumptions!$B$151*Assumptions!$B$136*N7/12*(1+Assumptions!$B$16)</f>
+        <f>N41*Assumptions!$B$149*Assumptions!$B$135*N7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="O48" s="44">
-        <f>O41*Assumptions!$B$151*Assumptions!$B$136*O7/12*(1+Assumptions!$B$16)</f>
+        <f>O41*Assumptions!$B$149*Assumptions!$B$135*O7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="P48" s="44">
-        <f>P41*Assumptions!$B$151*Assumptions!$B$136*P7/12*(1+Assumptions!$B$16)</f>
+        <f>P41*Assumptions!$B$149*Assumptions!$B$135*P7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="Q48" s="44">
-        <f>Q41*Assumptions!$B$151*Assumptions!$B$136*Q7/12*(1+Assumptions!$B$16)</f>
+        <f>Q41*Assumptions!$B$149*Assumptions!$B$135*Q7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="R48" s="44">
-        <f>R41*Assumptions!$B$151*Assumptions!$B$136*R7/12*(1+Assumptions!$B$16)</f>
+        <f>R41*Assumptions!$B$149*Assumptions!$B$135*R7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="S48" s="44">
-        <f>S41*Assumptions!$B$151*Assumptions!$B$136*S7/12*(1+Assumptions!$B$16)</f>
+        <f>S41*Assumptions!$B$149*Assumptions!$B$135*S7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="T48" s="44">
-        <f>T41*Assumptions!$B$151*Assumptions!$B$136*T7/12*(1+Assumptions!$B$16)</f>
+        <f>T41*Assumptions!$B$149*Assumptions!$B$135*T7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="U48" s="44">
-        <f>U41*Assumptions!$B$151*Assumptions!$B$136*U7/12*(1+Assumptions!$B$16)</f>
+        <f>U41*Assumptions!$B$149*Assumptions!$B$135*U7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="V48" s="44">
-        <f>V41*Assumptions!$B$151*Assumptions!$B$136*V7/12*(1+Assumptions!$B$16)</f>
+        <f>V41*Assumptions!$B$149*Assumptions!$B$135*V7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="W48" s="44">
-        <f>W41*Assumptions!$B$151*Assumptions!$B$136*W7/12*(1+Assumptions!$B$16)</f>
+        <f>W41*Assumptions!$B$149*Assumptions!$B$135*W7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="X48" s="44">
-        <f>X41*Assumptions!$B$151*Assumptions!$B$136*X7/12*(1+Assumptions!$B$16)</f>
+        <f>X41*Assumptions!$B$149*Assumptions!$B$135*X7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="Y48" s="44">
-        <f>Y41*Assumptions!$B$151*Assumptions!$B$136*Y7/12*(1+Assumptions!$B$16)</f>
+        <f>Y41*Assumptions!$B$149*Assumptions!$B$135*Y7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="Z48" s="44">
-        <f>Z41*Assumptions!$B$151*Assumptions!$B$136*Z7/12*(1+Assumptions!$B$16)</f>
+        <f>Z41*Assumptions!$B$149*Assumptions!$B$135*Z7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AA48" s="44">
-        <f>AA41*Assumptions!$B$151*Assumptions!$B$136*AA7/12*(1+Assumptions!$B$16)</f>
+        <f>AA41*Assumptions!$B$149*Assumptions!$B$135*AA7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AB48" s="44">
-        <f>AB41*Assumptions!$B$151*Assumptions!$B$136*AB7/12*(1+Assumptions!$B$16)</f>
+        <f>AB41*Assumptions!$B$149*Assumptions!$B$135*AB7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AC48" s="44">
-        <f>AC41*Assumptions!$B$151*Assumptions!$B$136*AC7/12*(1+Assumptions!$B$16)</f>
+        <f>AC41*Assumptions!$B$149*Assumptions!$B$135*AC7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AD48" s="44">
-        <f>AD41*Assumptions!$B$151*Assumptions!$B$136*AD7/12*(1+Assumptions!$B$16)</f>
+        <f>AD41*Assumptions!$B$149*Assumptions!$B$135*AD7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AE48" s="44">
-        <f>AE41*Assumptions!$B$151*Assumptions!$B$136*AE7/12*(1+Assumptions!$B$16)</f>
+        <f>AE41*Assumptions!$B$149*Assumptions!$B$135*AE7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
     </row>
@@ -11597,119 +11364,119 @@
         </is>
       </c>
       <c r="C51" s="54">
-        <f>C46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>C46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="D51" s="54">
-        <f>D46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>D46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="E51" s="54">
-        <f>E46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>E46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="F51" s="54">
-        <f>F46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>F46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="G51" s="54">
-        <f>G46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>G46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="H51" s="54">
-        <f>H46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>H46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="I51" s="54">
-        <f>I46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>I46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="J51" s="54">
-        <f>J46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>J46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="K51" s="54">
-        <f>K46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>K46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="L51" s="54">
-        <f>L46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>L46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="M51" s="54">
-        <f>M46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>M46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="N51" s="54">
-        <f>N46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>N46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="O51" s="54">
-        <f>O46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>O46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="P51" s="54">
-        <f>P46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>P46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="Q51" s="54">
-        <f>Q46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>Q46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="R51" s="54">
-        <f>R46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>R46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="S51" s="54">
-        <f>S46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>S46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="T51" s="54">
-        <f>T46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>T46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="U51" s="54">
-        <f>U46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>U46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="V51" s="54">
-        <f>V46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>V46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="W51" s="54">
-        <f>W46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>W46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="X51" s="54">
-        <f>X46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>X46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="Y51" s="54">
-        <f>Y46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>Y46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="Z51" s="54">
-        <f>Z46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>Z46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AA51" s="54">
-        <f>AA46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AA46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AB51" s="54">
-        <f>AB46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AB46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AC51" s="54">
-        <f>AC46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AC46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AD51" s="54">
-        <f>AD46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AD46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AE51" s="54">
-        <f>AE46*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AE46*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
     </row>
@@ -11725,119 +11492,119 @@
         </is>
       </c>
       <c r="C52" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$47,C29*Assumptions!$B$152*Assumptions!$B$25/12*C7,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$47,C29*Assumptions!$B$150*Assumptions!$B$25/12*C7,0)</f>
         <v/>
       </c>
       <c r="D52" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$47,D29*Assumptions!$B$152*Assumptions!$B$25/12*D7,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$47,D29*Assumptions!$B$150*Assumptions!$B$25/12*D7,0)</f>
         <v/>
       </c>
       <c r="E52" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$47,E29*Assumptions!$B$152*Assumptions!$B$25/12*E7,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$47,E29*Assumptions!$B$150*Assumptions!$B$25/12*E7,0)</f>
         <v/>
       </c>
       <c r="F52" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$47,F29*Assumptions!$B$152*Assumptions!$B$25/12*F7,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$47,F29*Assumptions!$B$150*Assumptions!$B$25/12*F7,0)</f>
         <v/>
       </c>
       <c r="G52" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$47,G29*Assumptions!$B$152*Assumptions!$B$25/12*G7,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$47,G29*Assumptions!$B$150*Assumptions!$B$25/12*G7,0)</f>
         <v/>
       </c>
       <c r="H52" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$47,H29*Assumptions!$B$152*Assumptions!$B$25/12*H7,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$47,H29*Assumptions!$B$150*Assumptions!$B$25/12*H7,0)</f>
         <v/>
       </c>
       <c r="I52" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$47,I29*Assumptions!$B$152*Assumptions!$B$25/12*I7,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$47,I29*Assumptions!$B$150*Assumptions!$B$25/12*I7,0)</f>
         <v/>
       </c>
       <c r="J52" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$47,J29*Assumptions!$B$152*Assumptions!$B$25/12*J7,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$47,J29*Assumptions!$B$150*Assumptions!$B$25/12*J7,0)</f>
         <v/>
       </c>
       <c r="K52" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$47,K29*Assumptions!$B$152*Assumptions!$B$25/12*K7,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$47,K29*Assumptions!$B$150*Assumptions!$B$25/12*K7,0)</f>
         <v/>
       </c>
       <c r="L52" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$47,L29*Assumptions!$B$152*Assumptions!$B$25/12*L7,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$47,L29*Assumptions!$B$150*Assumptions!$B$25/12*L7,0)</f>
         <v/>
       </c>
       <c r="M52" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$47,M29*Assumptions!$B$152*Assumptions!$B$25/12*M7,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$47,M29*Assumptions!$B$150*Assumptions!$B$25/12*M7,0)</f>
         <v/>
       </c>
       <c r="N52" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$47,N29*Assumptions!$B$152*Assumptions!$B$25/12*N7,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$47,N29*Assumptions!$B$150*Assumptions!$B$25/12*N7,0)</f>
         <v/>
       </c>
       <c r="O52" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$47,O29*Assumptions!$B$152*Assumptions!$B$25/12*O7,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$47,O29*Assumptions!$B$150*Assumptions!$B$25/12*O7,0)</f>
         <v/>
       </c>
       <c r="P52" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$47,P29*Assumptions!$B$152*Assumptions!$B$25/12*P7,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$47,P29*Assumptions!$B$150*Assumptions!$B$25/12*P7,0)</f>
         <v/>
       </c>
       <c r="Q52" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$47,Q29*Assumptions!$B$152*Assumptions!$B$25/12*Q7,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$47,Q29*Assumptions!$B$150*Assumptions!$B$25/12*Q7,0)</f>
         <v/>
       </c>
       <c r="R52" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$47,R29*Assumptions!$B$152*Assumptions!$B$25/12*R7,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$47,R29*Assumptions!$B$150*Assumptions!$B$25/12*R7,0)</f>
         <v/>
       </c>
       <c r="S52" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$47,S29*Assumptions!$B$152*Assumptions!$B$25/12*S7,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$47,S29*Assumptions!$B$150*Assumptions!$B$25/12*S7,0)</f>
         <v/>
       </c>
       <c r="T52" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$47,T29*Assumptions!$B$152*Assumptions!$B$25/12*T7,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$47,T29*Assumptions!$B$150*Assumptions!$B$25/12*T7,0)</f>
         <v/>
       </c>
       <c r="U52" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$47,U29*Assumptions!$B$152*Assumptions!$B$25/12*U7,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$47,U29*Assumptions!$B$150*Assumptions!$B$25/12*U7,0)</f>
         <v/>
       </c>
       <c r="V52" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$47,V29*Assumptions!$B$152*Assumptions!$B$25/12*V7,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$47,V29*Assumptions!$B$150*Assumptions!$B$25/12*V7,0)</f>
         <v/>
       </c>
       <c r="W52" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$47,W29*Assumptions!$B$152*Assumptions!$B$25/12*W7,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$47,W29*Assumptions!$B$150*Assumptions!$B$25/12*W7,0)</f>
         <v/>
       </c>
       <c r="X52" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$47,X29*Assumptions!$B$152*Assumptions!$B$25/12*X7,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$47,X29*Assumptions!$B$150*Assumptions!$B$25/12*X7,0)</f>
         <v/>
       </c>
       <c r="Y52" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$47,Y29*Assumptions!$B$152*Assumptions!$B$25/12*Y7,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$47,Y29*Assumptions!$B$150*Assumptions!$B$25/12*Y7,0)</f>
         <v/>
       </c>
       <c r="Z52" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$47,Z29*Assumptions!$B$152*Assumptions!$B$25/12*Z7,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$47,Z29*Assumptions!$B$150*Assumptions!$B$25/12*Z7,0)</f>
         <v/>
       </c>
       <c r="AA52" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$47,AA29*Assumptions!$B$152*Assumptions!$B$25/12*AA7,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$47,AA29*Assumptions!$B$150*Assumptions!$B$25/12*AA7,0)</f>
         <v/>
       </c>
       <c r="AB52" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$47,AB29*Assumptions!$B$152*Assumptions!$B$25/12*AB7,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$47,AB29*Assumptions!$B$150*Assumptions!$B$25/12*AB7,0)</f>
         <v/>
       </c>
       <c r="AC52" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$47,AC29*Assumptions!$B$152*Assumptions!$B$25/12*AC7,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$47,AC29*Assumptions!$B$150*Assumptions!$B$25/12*AC7,0)</f>
         <v/>
       </c>
       <c r="AD52" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$47,AD29*Assumptions!$B$152*Assumptions!$B$25/12*AD7,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$47,AD29*Assumptions!$B$150*Assumptions!$B$25/12*AD7,0)</f>
         <v/>
       </c>
       <c r="AE52" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$47,AE29*Assumptions!$B$152*Assumptions!$B$25/12*AE7,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$47,AE29*Assumptions!$B$150*Assumptions!$B$25/12*AE7,0)</f>
         <v/>
       </c>
     </row>
@@ -11853,119 +11620,119 @@
         </is>
       </c>
       <c r="C53" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$49,C46*C17*Assumptions!$B$17+C41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*C7+C41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*C7,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$49,C46*C17*Assumptions!$B$17+C41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*C7+C41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*C7,0)</f>
         <v/>
       </c>
       <c r="D53" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$49,D46*D17*Assumptions!$B$17+D41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*D7+D41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*D7,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$49,D46*D17*Assumptions!$B$17+D41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*D7+D41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*D7,0)</f>
         <v/>
       </c>
       <c r="E53" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$49,E46*E17*Assumptions!$B$17+E41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*E7+E41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*E7,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$49,E46*E17*Assumptions!$B$17+E41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*E7+E41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*E7,0)</f>
         <v/>
       </c>
       <c r="F53" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$49,F46*F17*Assumptions!$B$17+F41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*F7+F41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*F7,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$49,F46*F17*Assumptions!$B$17+F41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*F7+F41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*F7,0)</f>
         <v/>
       </c>
       <c r="G53" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$49,G46*G17*Assumptions!$B$17+G41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*G7+G41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*G7,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$49,G46*G17*Assumptions!$B$17+G41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*G7+G41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*G7,0)</f>
         <v/>
       </c>
       <c r="H53" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$49,H46*H17*Assumptions!$B$17+H41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*H7+H41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*H7,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$49,H46*H17*Assumptions!$B$17+H41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*H7+H41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*H7,0)</f>
         <v/>
       </c>
       <c r="I53" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$49,I46*I17*Assumptions!$B$17+I41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*I7+I41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*I7,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$49,I46*I17*Assumptions!$B$17+I41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*I7+I41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*I7,0)</f>
         <v/>
       </c>
       <c r="J53" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$49,J46*J17*Assumptions!$B$17+J41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*J7+J41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*J7,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$49,J46*J17*Assumptions!$B$17+J41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*J7+J41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*J7,0)</f>
         <v/>
       </c>
       <c r="K53" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$49,K46*K17*Assumptions!$B$17+K41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*K7+K41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*K7,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$49,K46*K17*Assumptions!$B$17+K41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*K7+K41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*K7,0)</f>
         <v/>
       </c>
       <c r="L53" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$49,L46*L17*Assumptions!$B$17+L41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*L7+L41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*L7,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$49,L46*L17*Assumptions!$B$17+L41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*L7+L41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*L7,0)</f>
         <v/>
       </c>
       <c r="M53" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$49,M46*M17*Assumptions!$B$17+M41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*M7+M41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*M7,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$49,M46*M17*Assumptions!$B$17+M41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*M7+M41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*M7,0)</f>
         <v/>
       </c>
       <c r="N53" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$49,N46*N17*Assumptions!$B$17+N41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*N7+N41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*N7,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$49,N46*N17*Assumptions!$B$17+N41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*N7+N41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*N7,0)</f>
         <v/>
       </c>
       <c r="O53" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$49,O46*O17*Assumptions!$B$17+O41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$49,O46*O17*Assumptions!$B$17+O41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
         <v/>
       </c>
       <c r="P53" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$49,P46*P17*Assumptions!$B$17+P41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$49,P46*P17*Assumptions!$B$17+P41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
         <v/>
       </c>
       <c r="Q53" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$49,Q46*Q17*Assumptions!$B$17+Q41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$49,Q46*Q17*Assumptions!$B$17+Q41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
         <v/>
       </c>
       <c r="R53" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$49,R46*R17*Assumptions!$B$17+R41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$49,R46*R17*Assumptions!$B$17+R41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
         <v/>
       </c>
       <c r="S53" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$49,S46*S17*Assumptions!$B$17+S41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$49,S46*S17*Assumptions!$B$17+S41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
         <v/>
       </c>
       <c r="T53" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$49,T46*T17*Assumptions!$B$17+T41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$49,T46*T17*Assumptions!$B$17+T41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
         <v/>
       </c>
       <c r="U53" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$49,U46*U17*Assumptions!$B$17+U41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$49,U46*U17*Assumptions!$B$17+U41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
         <v/>
       </c>
       <c r="V53" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$49,V46*V17*Assumptions!$B$17+V41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$49,V46*V17*Assumptions!$B$17+V41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
         <v/>
       </c>
       <c r="W53" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$49,W46*W17*Assumptions!$B$17+W41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$49,W46*W17*Assumptions!$B$17+W41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
         <v/>
       </c>
       <c r="X53" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$49,X46*X17*Assumptions!$B$17+X41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$49,X46*X17*Assumptions!$B$17+X41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
         <v/>
       </c>
       <c r="Y53" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$49,Y46*Y17*Assumptions!$B$17+Y41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$49,Y46*Y17*Assumptions!$B$17+Y41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
         <v/>
       </c>
       <c r="Z53" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$49,Z46*Z17*Assumptions!$B$17+Z41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$49,Z46*Z17*Assumptions!$B$17+Z41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
         <v/>
       </c>
       <c r="AA53" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$49,AA46*AA17*Assumptions!$B$17+AA41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$49,AA46*AA17*Assumptions!$B$17+AA41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
         <v/>
       </c>
       <c r="AB53" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$49,AB46*AB17*Assumptions!$B$17+AB41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$49,AB46*AB17*Assumptions!$B$17+AB41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
         <v/>
       </c>
       <c r="AC53" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$49,AC46*AC17*Assumptions!$B$17+AC41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$49,AC46*AC17*Assumptions!$B$17+AC41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
         <v/>
       </c>
       <c r="AD53" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$49,AD46*AD17*Assumptions!$B$17+AD41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$49,AD46*AD17*Assumptions!$B$17+AD41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
         <v/>
       </c>
       <c r="AE53" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$49,AE46*AE17*Assumptions!$B$17+AE41*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE41*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$49,AE46*AE17*Assumptions!$B$17+AE41*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE41*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
         <v/>
       </c>
     </row>
@@ -11981,119 +11748,119 @@
         </is>
       </c>
       <c r="C54" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$50,C41*C42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$50,C41*C42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="D54" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$50,D41*D42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$50,D41*D42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="E54" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$50,E41*E42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$50,E41*E42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="F54" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$50,F41*F42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$50,F41*F42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="G54" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$50,G41*G42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$50,G41*G42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="H54" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$50,H41*H42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$50,H41*H42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="I54" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$50,I41*I42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$50,I41*I42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="J54" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$50,J41*J42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$50,J41*J42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="K54" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$50,K41*K42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$50,K41*K42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="L54" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$50,L41*L42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$50,L41*L42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="M54" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$50,M41*M42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$50,M41*M42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="N54" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$50,N41*N42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$50,N41*N42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="O54" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$50,O41*O42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$50,O41*O42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="P54" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$50,P41*P42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$50,P41*P42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="Q54" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$50,Q41*Q42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$50,Q41*Q42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="R54" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$50,R41*R42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$50,R41*R42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="S54" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$50,S41*S42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$50,S41*S42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="T54" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$50,T41*T42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$50,T41*T42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="U54" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$50,U41*U42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$50,U41*U42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="V54" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$50,V41*V42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$50,V41*V42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="W54" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$50,W41*W42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$50,W41*W42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="X54" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$50,X41*X42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$50,X41*X42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="Y54" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$50,Y41*Y42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$50,Y41*Y42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="Z54" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$50,Z41*Z42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$50,Z41*Z42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AA54" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$50,AA41*AA42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$50,AA41*AA42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AB54" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$50,AB41*AB42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$50,AB41*AB42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AC54" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$50,AC41*AC42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$50,AC41*AC42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AD54" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$50,AD41*AD42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$50,AD41*AD42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AE54" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$50,AE41*AE42*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$50,AE41*AE42*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
     </row>
@@ -12109,119 +11876,119 @@
         </is>
       </c>
       <c r="C55" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$50,(C54*Assumptions!$B$29*Assumptions!$B$30+C41*C43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$50,(C54*Assumptions!$B$29*Assumptions!$B$30+C41*C43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
         <v/>
       </c>
       <c r="D55" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$50,(D54*Assumptions!$B$29*Assumptions!$B$30+D41*D43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$50,(D54*Assumptions!$B$29*Assumptions!$B$30+D41*D43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
         <v/>
       </c>
       <c r="E55" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$50,(E54*Assumptions!$B$29*Assumptions!$B$30+E41*E43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$50,(E54*Assumptions!$B$29*Assumptions!$B$30+E41*E43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
         <v/>
       </c>
       <c r="F55" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$50,(F54*Assumptions!$B$29*Assumptions!$B$30+F41*F43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$50,(F54*Assumptions!$B$29*Assumptions!$B$30+F41*F43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
         <v/>
       </c>
       <c r="G55" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$50,(G54*Assumptions!$B$29*Assumptions!$B$30+G41*G43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$50,(G54*Assumptions!$B$29*Assumptions!$B$30+G41*G43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
         <v/>
       </c>
       <c r="H55" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$50,(H54*Assumptions!$B$29*Assumptions!$B$30+H41*H43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$50,(H54*Assumptions!$B$29*Assumptions!$B$30+H41*H43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
         <v/>
       </c>
       <c r="I55" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$50,(I54*Assumptions!$B$29*Assumptions!$B$30+I41*I43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$50,(I54*Assumptions!$B$29*Assumptions!$B$30+I41*I43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
         <v/>
       </c>
       <c r="J55" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$50,(J54*Assumptions!$B$29*Assumptions!$B$30+J41*J43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$50,(J54*Assumptions!$B$29*Assumptions!$B$30+J41*J43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
         <v/>
       </c>
       <c r="K55" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$50,(K54*Assumptions!$B$29*Assumptions!$B$30+K41*K43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$50,(K54*Assumptions!$B$29*Assumptions!$B$30+K41*K43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
         <v/>
       </c>
       <c r="L55" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$50,(L54*Assumptions!$B$29*Assumptions!$B$30+L41*L43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$50,(L54*Assumptions!$B$29*Assumptions!$B$30+L41*L43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
         <v/>
       </c>
       <c r="M55" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$50,(M54*Assumptions!$B$29*Assumptions!$B$30+M41*M43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$50,(M54*Assumptions!$B$29*Assumptions!$B$30+M41*M43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
         <v/>
       </c>
       <c r="N55" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$50,(N54*Assumptions!$B$29*Assumptions!$B$30+N41*N43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$50,(N54*Assumptions!$B$29*Assumptions!$B$30+N41*N43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
         <v/>
       </c>
       <c r="O55" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$50,(O54*Assumptions!$B$29*Assumptions!$B$30+O41*O43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$50,(O54*Assumptions!$B$29*Assumptions!$B$30+O41*O43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
         <v/>
       </c>
       <c r="P55" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$50,(P54*Assumptions!$B$29*Assumptions!$B$30+P41*P43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$50,(P54*Assumptions!$B$29*Assumptions!$B$30+P41*P43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
         <v/>
       </c>
       <c r="Q55" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$50,(Q54*Assumptions!$B$29*Assumptions!$B$30+Q41*Q43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$50,(Q54*Assumptions!$B$29*Assumptions!$B$30+Q41*Q43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
         <v/>
       </c>
       <c r="R55" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$50,(R54*Assumptions!$B$29*Assumptions!$B$30+R41*R43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$50,(R54*Assumptions!$B$29*Assumptions!$B$30+R41*R43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
         <v/>
       </c>
       <c r="S55" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$50,(S54*Assumptions!$B$29*Assumptions!$B$30+S41*S43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$50,(S54*Assumptions!$B$29*Assumptions!$B$30+S41*S43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
         <v/>
       </c>
       <c r="T55" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$50,(T54*Assumptions!$B$29*Assumptions!$B$30+T41*T43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$50,(T54*Assumptions!$B$29*Assumptions!$B$30+T41*T43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
         <v/>
       </c>
       <c r="U55" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$50,(U54*Assumptions!$B$29*Assumptions!$B$30+U41*U43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$50,(U54*Assumptions!$B$29*Assumptions!$B$30+U41*U43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
         <v/>
       </c>
       <c r="V55" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$50,(V54*Assumptions!$B$29*Assumptions!$B$30+V41*V43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$50,(V54*Assumptions!$B$29*Assumptions!$B$30+V41*V43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
         <v/>
       </c>
       <c r="W55" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$50,(W54*Assumptions!$B$29*Assumptions!$B$30+W41*W43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$50,(W54*Assumptions!$B$29*Assumptions!$B$30+W41*W43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
         <v/>
       </c>
       <c r="X55" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$50,(X54*Assumptions!$B$29*Assumptions!$B$30+X41*X43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$50,(X54*Assumptions!$B$29*Assumptions!$B$30+X41*X43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
         <v/>
       </c>
       <c r="Y55" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$50,(Y54*Assumptions!$B$29*Assumptions!$B$30+Y41*Y43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$50,(Y54*Assumptions!$B$29*Assumptions!$B$30+Y41*Y43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
         <v/>
       </c>
       <c r="Z55" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$50,(Z54*Assumptions!$B$29*Assumptions!$B$30+Z41*Z43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$50,(Z54*Assumptions!$B$29*Assumptions!$B$30+Z41*Z43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
         <v/>
       </c>
       <c r="AA55" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$50,(AA54*Assumptions!$B$29*Assumptions!$B$30+AA41*AA43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$50,(AA54*Assumptions!$B$29*Assumptions!$B$30+AA41*AA43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
         <v/>
       </c>
       <c r="AB55" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$50,(AB54*Assumptions!$B$29*Assumptions!$B$30+AB41*AB43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$50,(AB54*Assumptions!$B$29*Assumptions!$B$30+AB41*AB43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
         <v/>
       </c>
       <c r="AC55" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$50,(AC54*Assumptions!$B$29*Assumptions!$B$30+AC41*AC43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$50,(AC54*Assumptions!$B$29*Assumptions!$B$30+AC41*AC43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
         <v/>
       </c>
       <c r="AD55" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$50,(AD54*Assumptions!$B$29*Assumptions!$B$30+AD41*AD43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$50,(AD54*Assumptions!$B$29*Assumptions!$B$30+AD41*AD43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
         <v/>
       </c>
       <c r="AE55" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$50,(AE54*Assumptions!$B$29*Assumptions!$B$30+AE41*AE43*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$50,(AE54*Assumptions!$B$29*Assumptions!$B$30+AE41*AE43*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
         <v/>
       </c>
     </row>
@@ -13680,119 +13447,119 @@
         </is>
       </c>
       <c r="C69" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$44,C65*Assumptions!$B$162*C7,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$44,C65*Assumptions!$B$160*C7,0)</f>
         <v/>
       </c>
       <c r="D69" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$44,D65*Assumptions!$B$162*D7,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$44,D65*Assumptions!$B$160*D7,0)</f>
         <v/>
       </c>
       <c r="E69" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$44,E65*Assumptions!$B$162*E7,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$44,E65*Assumptions!$B$160*E7,0)</f>
         <v/>
       </c>
       <c r="F69" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$44,F65*Assumptions!$B$162*F7,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$44,F65*Assumptions!$B$160*F7,0)</f>
         <v/>
       </c>
       <c r="G69" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$44,G65*Assumptions!$B$162*G7,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$44,G65*Assumptions!$B$160*G7,0)</f>
         <v/>
       </c>
       <c r="H69" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$44,H65*Assumptions!$B$162*H7,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$44,H65*Assumptions!$B$160*H7,0)</f>
         <v/>
       </c>
       <c r="I69" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$44,I65*Assumptions!$B$162*I7,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$44,I65*Assumptions!$B$160*I7,0)</f>
         <v/>
       </c>
       <c r="J69" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$44,J65*Assumptions!$B$162*J7,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$44,J65*Assumptions!$B$160*J7,0)</f>
         <v/>
       </c>
       <c r="K69" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$44,K65*Assumptions!$B$162*K7,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$44,K65*Assumptions!$B$160*K7,0)</f>
         <v/>
       </c>
       <c r="L69" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$44,L65*Assumptions!$B$162*L7,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$44,L65*Assumptions!$B$160*L7,0)</f>
         <v/>
       </c>
       <c r="M69" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$44,M65*Assumptions!$B$162*M7,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$44,M65*Assumptions!$B$160*M7,0)</f>
         <v/>
       </c>
       <c r="N69" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$44,N65*Assumptions!$B$162*N7,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$44,N65*Assumptions!$B$160*N7,0)</f>
         <v/>
       </c>
       <c r="O69" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$44,O65*Assumptions!$B$162*O7,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$44,O65*Assumptions!$B$160*O7,0)</f>
         <v/>
       </c>
       <c r="P69" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$44,P65*Assumptions!$B$162*P7,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$44,P65*Assumptions!$B$160*P7,0)</f>
         <v/>
       </c>
       <c r="Q69" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$44,Q65*Assumptions!$B$162*Q7,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$44,Q65*Assumptions!$B$160*Q7,0)</f>
         <v/>
       </c>
       <c r="R69" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$44,R65*Assumptions!$B$162*R7,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$44,R65*Assumptions!$B$160*R7,0)</f>
         <v/>
       </c>
       <c r="S69" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$44,S65*Assumptions!$B$162*S7,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$44,S65*Assumptions!$B$160*S7,0)</f>
         <v/>
       </c>
       <c r="T69" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$44,T65*Assumptions!$B$162*T7,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$44,T65*Assumptions!$B$160*T7,0)</f>
         <v/>
       </c>
       <c r="U69" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$44,U65*Assumptions!$B$162*U7,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$44,U65*Assumptions!$B$160*U7,0)</f>
         <v/>
       </c>
       <c r="V69" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$44,V65*Assumptions!$B$162*V7,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$44,V65*Assumptions!$B$160*V7,0)</f>
         <v/>
       </c>
       <c r="W69" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$44,W65*Assumptions!$B$162*W7,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$44,W65*Assumptions!$B$160*W7,0)</f>
         <v/>
       </c>
       <c r="X69" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$44,X65*Assumptions!$B$162*X7,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$44,X65*Assumptions!$B$160*X7,0)</f>
         <v/>
       </c>
       <c r="Y69" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$44,Y65*Assumptions!$B$162*Y7,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$44,Y65*Assumptions!$B$160*Y7,0)</f>
         <v/>
       </c>
       <c r="Z69" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$44,Z65*Assumptions!$B$162*Z7,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$44,Z65*Assumptions!$B$160*Z7,0)</f>
         <v/>
       </c>
       <c r="AA69" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$44,AA65*Assumptions!$B$162*AA7,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$44,AA65*Assumptions!$B$160*AA7,0)</f>
         <v/>
       </c>
       <c r="AB69" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$44,AB65*Assumptions!$B$162*AB7,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$44,AB65*Assumptions!$B$160*AB7,0)</f>
         <v/>
       </c>
       <c r="AC69" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$44,AC65*Assumptions!$B$162*AC7,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$44,AC65*Assumptions!$B$160*AC7,0)</f>
         <v/>
       </c>
       <c r="AD69" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$44,AD65*Assumptions!$B$162*AD7,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$44,AD65*Assumptions!$B$160*AD7,0)</f>
         <v/>
       </c>
       <c r="AE69" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$44,AE65*Assumptions!$B$162*AE7,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$44,AE65*Assumptions!$B$160*AE7,0)</f>
         <v/>
       </c>
     </row>
@@ -14448,119 +14215,119 @@
         </is>
       </c>
       <c r="C75" s="53">
-        <f>C65+C67*Assumptions!$B$168</f>
+        <f>C65+C67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="D75" s="53">
-        <f>D65+D67*Assumptions!$B$168</f>
+        <f>D65+D67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="E75" s="53">
-        <f>E65+E67*Assumptions!$B$168</f>
+        <f>E65+E67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="F75" s="53">
-        <f>F65+F67*Assumptions!$B$168</f>
+        <f>F65+F67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="G75" s="53">
-        <f>G65+G67*Assumptions!$B$168</f>
+        <f>G65+G67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="H75" s="53">
-        <f>H65+H67*Assumptions!$B$168</f>
+        <f>H65+H67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="I75" s="53">
-        <f>I65+I67*Assumptions!$B$168</f>
+        <f>I65+I67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="J75" s="53">
-        <f>J65+J67*Assumptions!$B$168</f>
+        <f>J65+J67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="K75" s="53">
-        <f>K65+K67*Assumptions!$B$168</f>
+        <f>K65+K67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="L75" s="53">
-        <f>L65+L67*Assumptions!$B$168</f>
+        <f>L65+L67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="M75" s="53">
-        <f>M65+M67*Assumptions!$B$168</f>
+        <f>M65+M67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="N75" s="53">
-        <f>N65+N67*Assumptions!$B$168</f>
+        <f>N65+N67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="O75" s="53">
-        <f>O65+O67*Assumptions!$B$168</f>
+        <f>O65+O67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="P75" s="53">
-        <f>P65+P67*Assumptions!$B$168</f>
+        <f>P65+P67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="Q75" s="53">
-        <f>Q65+Q67*Assumptions!$B$168</f>
+        <f>Q65+Q67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="R75" s="53">
-        <f>R65+R67*Assumptions!$B$168</f>
+        <f>R65+R67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="S75" s="53">
-        <f>S65+S67*Assumptions!$B$168</f>
+        <f>S65+S67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="T75" s="53">
-        <f>T65+T67*Assumptions!$B$168</f>
+        <f>T65+T67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="U75" s="53">
-        <f>U65+U67*Assumptions!$B$168</f>
+        <f>U65+U67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="V75" s="53">
-        <f>V65+V67*Assumptions!$B$168</f>
+        <f>V65+V67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="W75" s="53">
-        <f>W65+W67*Assumptions!$B$168</f>
+        <f>W65+W67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="X75" s="53">
-        <f>X65+X67*Assumptions!$B$168</f>
+        <f>X65+X67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="Y75" s="53">
-        <f>Y65+Y67*Assumptions!$B$168</f>
+        <f>Y65+Y67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="Z75" s="53">
-        <f>Z65+Z67*Assumptions!$B$168</f>
+        <f>Z65+Z67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AA75" s="53">
-        <f>AA65+AA67*Assumptions!$B$168</f>
+        <f>AA65+AA67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AB75" s="53">
-        <f>AB65+AB67*Assumptions!$B$168</f>
+        <f>AB65+AB67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AC75" s="53">
-        <f>AC65+AC67*Assumptions!$B$168</f>
+        <f>AC65+AC67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AD75" s="53">
-        <f>AD65+AD67*Assumptions!$B$168</f>
+        <f>AD65+AD67*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AE75" s="53">
-        <f>AE65+AE67*Assumptions!$B$168</f>
+        <f>AE65+AE67*Assumptions!$B$163</f>
         <v/>
       </c>
     </row>
@@ -14704,119 +14471,119 @@
         </is>
       </c>
       <c r="C77" s="28">
-        <f>IF(C2&gt;=Assumptions!$B$48,C76*Assumptions!$B$135,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$48,C76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="D77" s="28">
-        <f>IF(D2&gt;=Assumptions!$B$48,D76*Assumptions!$B$135,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$48,D76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="E77" s="28">
-        <f>IF(E2&gt;=Assumptions!$B$48,E76*Assumptions!$B$135,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$48,E76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="F77" s="28">
-        <f>IF(F2&gt;=Assumptions!$B$48,F76*Assumptions!$B$135,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$48,F76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="G77" s="28">
-        <f>IF(G2&gt;=Assumptions!$B$48,G76*Assumptions!$B$135,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$48,G76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="H77" s="28">
-        <f>IF(H2&gt;=Assumptions!$B$48,H76*Assumptions!$B$135,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$48,H76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="I77" s="28">
-        <f>IF(I2&gt;=Assumptions!$B$48,I76*Assumptions!$B$135,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$48,I76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="J77" s="28">
-        <f>IF(J2&gt;=Assumptions!$B$48,J76*Assumptions!$B$135,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$48,J76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="K77" s="28">
-        <f>IF(K2&gt;=Assumptions!$B$48,K76*Assumptions!$B$135,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$48,K76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="L77" s="28">
-        <f>IF(L2&gt;=Assumptions!$B$48,L76*Assumptions!$B$135,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$48,L76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="M77" s="28">
-        <f>IF(M2&gt;=Assumptions!$B$48,M76*Assumptions!$B$135,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$48,M76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="N77" s="28">
-        <f>IF(N2&gt;=Assumptions!$B$48,N76*Assumptions!$B$135,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$48,N76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="O77" s="28">
-        <f>IF(O2&gt;=Assumptions!$B$48,O76*Assumptions!$B$135,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$48,O76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="P77" s="28">
-        <f>IF(P2&gt;=Assumptions!$B$48,P76*Assumptions!$B$135,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$48,P76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="Q77" s="28">
-        <f>IF(Q2&gt;=Assumptions!$B$48,Q76*Assumptions!$B$135,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$48,Q76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="R77" s="28">
-        <f>IF(R2&gt;=Assumptions!$B$48,R76*Assumptions!$B$135,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$48,R76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="S77" s="28">
-        <f>IF(S2&gt;=Assumptions!$B$48,S76*Assumptions!$B$135,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$48,S76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="T77" s="28">
-        <f>IF(T2&gt;=Assumptions!$B$48,T76*Assumptions!$B$135,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$48,T76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="U77" s="28">
-        <f>IF(U2&gt;=Assumptions!$B$48,U76*Assumptions!$B$135,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$48,U76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="V77" s="28">
-        <f>IF(V2&gt;=Assumptions!$B$48,V76*Assumptions!$B$135,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$48,V76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="W77" s="28">
-        <f>IF(W2&gt;=Assumptions!$B$48,W76*Assumptions!$B$135,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$48,W76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="X77" s="28">
-        <f>IF(X2&gt;=Assumptions!$B$48,X76*Assumptions!$B$135,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$48,X76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="Y77" s="28">
-        <f>IF(Y2&gt;=Assumptions!$B$48,Y76*Assumptions!$B$135,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$48,Y76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="Z77" s="28">
-        <f>IF(Z2&gt;=Assumptions!$B$48,Z76*Assumptions!$B$135,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$48,Z76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AA77" s="28">
-        <f>IF(AA2&gt;=Assumptions!$B$48,AA76*Assumptions!$B$135,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$48,AA76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AB77" s="28">
-        <f>IF(AB2&gt;=Assumptions!$B$48,AB76*Assumptions!$B$135,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$48,AB76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AC77" s="28">
-        <f>IF(AC2&gt;=Assumptions!$B$48,AC76*Assumptions!$B$135,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$48,AC76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AD77" s="28">
-        <f>IF(AD2&gt;=Assumptions!$B$48,AD76*Assumptions!$B$135,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$48,AD76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AE77" s="28">
-        <f>IF(AE2&gt;=Assumptions!$B$48,AE76*Assumptions!$B$135,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$48,AE76*Assumptions!$B$134,0)</f>
         <v/>
       </c>
     </row>
@@ -14960,119 +14727,119 @@
         </is>
       </c>
       <c r="C79" s="54">
-        <f>C78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>C78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="D79" s="54">
-        <f>D78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>D78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="E79" s="54">
-        <f>E78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>E78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="F79" s="54">
-        <f>F78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>F78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="G79" s="54">
-        <f>G78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>G78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="H79" s="54">
-        <f>H78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>H78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="I79" s="54">
-        <f>I78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>I78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="J79" s="54">
-        <f>J78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>J78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="K79" s="54">
-        <f>K78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>K78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="L79" s="54">
-        <f>L78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>L78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="M79" s="54">
-        <f>M78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>M78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="N79" s="54">
-        <f>N78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>N78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="O79" s="54">
-        <f>O78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>O78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="P79" s="54">
-        <f>P78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>P78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="Q79" s="54">
-        <f>Q78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>Q78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="R79" s="54">
-        <f>R78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>R78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="S79" s="54">
-        <f>S78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>S78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="T79" s="54">
-        <f>T78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>T78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="U79" s="54">
-        <f>U78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>U78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="V79" s="54">
-        <f>V78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>V78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="W79" s="54">
-        <f>W78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>W78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="X79" s="54">
-        <f>X78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>X78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="Y79" s="54">
-        <f>Y78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>Y78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="Z79" s="54">
-        <f>Z78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>Z78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AA79" s="54">
-        <f>AA78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AA78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AB79" s="54">
-        <f>AB78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AB78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AC79" s="54">
-        <f>AC78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AC78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AD79" s="54">
-        <f>AD78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AD78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AE79" s="54">
-        <f>AE78*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AE78*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
     </row>
@@ -15472,119 +15239,119 @@
         </is>
       </c>
       <c r="C83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,C78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,C78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="D83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,D78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,D78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="E83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,E78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,E78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="F83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,F78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,F78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="G83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,G78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,G78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="H83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,H78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,H78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="I83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,I78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,I78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="J83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,J78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,J78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="K83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,K78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,K78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="L83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,L78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,L78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="M83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,M78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,M78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="N83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,N78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,N78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="O83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,O78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,O78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="P83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,P78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,P78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="Q83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,Q78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,Q78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="R83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,R78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,R78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="S83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,S78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,S78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="T83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,T78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,T78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="U83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,U78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,U78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="V83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,V78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,V78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="W83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,W78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,W78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="X83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,X78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,X78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="Y83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,Y78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,Y78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="Z83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,Z78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,Z78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AA83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AA78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AA78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AB83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AB78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AB78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AC83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AC78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AC78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AD83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AD78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AD78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AE83" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AE78*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AE78*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
     </row>
@@ -15600,119 +15367,119 @@
         </is>
       </c>
       <c r="C84" s="44">
-        <f>C77*Assumptions!$B$151*Assumptions!$B$136*C7/12*(1+Assumptions!$B$16)</f>
+        <f>C77*Assumptions!$B$149*Assumptions!$B$135*C7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="D84" s="44">
-        <f>D77*Assumptions!$B$151*Assumptions!$B$136*D7/12*(1+Assumptions!$B$16)</f>
+        <f>D77*Assumptions!$B$149*Assumptions!$B$135*D7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="E84" s="44">
-        <f>E77*Assumptions!$B$151*Assumptions!$B$136*E7/12*(1+Assumptions!$B$16)</f>
+        <f>E77*Assumptions!$B$149*Assumptions!$B$135*E7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="F84" s="44">
-        <f>F77*Assumptions!$B$151*Assumptions!$B$136*F7/12*(1+Assumptions!$B$16)</f>
+        <f>F77*Assumptions!$B$149*Assumptions!$B$135*F7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="G84" s="44">
-        <f>G77*Assumptions!$B$151*Assumptions!$B$136*G7/12*(1+Assumptions!$B$16)</f>
+        <f>G77*Assumptions!$B$149*Assumptions!$B$135*G7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="H84" s="44">
-        <f>H77*Assumptions!$B$151*Assumptions!$B$136*H7/12*(1+Assumptions!$B$16)</f>
+        <f>H77*Assumptions!$B$149*Assumptions!$B$135*H7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="I84" s="44">
-        <f>I77*Assumptions!$B$151*Assumptions!$B$136*I7/12*(1+Assumptions!$B$16)</f>
+        <f>I77*Assumptions!$B$149*Assumptions!$B$135*I7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="J84" s="44">
-        <f>J77*Assumptions!$B$151*Assumptions!$B$136*J7/12*(1+Assumptions!$B$16)</f>
+        <f>J77*Assumptions!$B$149*Assumptions!$B$135*J7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="K84" s="44">
-        <f>K77*Assumptions!$B$151*Assumptions!$B$136*K7/12*(1+Assumptions!$B$16)</f>
+        <f>K77*Assumptions!$B$149*Assumptions!$B$135*K7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="L84" s="44">
-        <f>L77*Assumptions!$B$151*Assumptions!$B$136*L7/12*(1+Assumptions!$B$16)</f>
+        <f>L77*Assumptions!$B$149*Assumptions!$B$135*L7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="M84" s="44">
-        <f>M77*Assumptions!$B$151*Assumptions!$B$136*M7/12*(1+Assumptions!$B$16)</f>
+        <f>M77*Assumptions!$B$149*Assumptions!$B$135*M7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="N84" s="44">
-        <f>N77*Assumptions!$B$151*Assumptions!$B$136*N7/12*(1+Assumptions!$B$16)</f>
+        <f>N77*Assumptions!$B$149*Assumptions!$B$135*N7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="O84" s="44">
-        <f>O77*Assumptions!$B$151*Assumptions!$B$136*O7/12*(1+Assumptions!$B$16)</f>
+        <f>O77*Assumptions!$B$149*Assumptions!$B$135*O7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="P84" s="44">
-        <f>P77*Assumptions!$B$151*Assumptions!$B$136*P7/12*(1+Assumptions!$B$16)</f>
+        <f>P77*Assumptions!$B$149*Assumptions!$B$135*P7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="Q84" s="44">
-        <f>Q77*Assumptions!$B$151*Assumptions!$B$136*Q7/12*(1+Assumptions!$B$16)</f>
+        <f>Q77*Assumptions!$B$149*Assumptions!$B$135*Q7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="R84" s="44">
-        <f>R77*Assumptions!$B$151*Assumptions!$B$136*R7/12*(1+Assumptions!$B$16)</f>
+        <f>R77*Assumptions!$B$149*Assumptions!$B$135*R7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="S84" s="44">
-        <f>S77*Assumptions!$B$151*Assumptions!$B$136*S7/12*(1+Assumptions!$B$16)</f>
+        <f>S77*Assumptions!$B$149*Assumptions!$B$135*S7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="T84" s="44">
-        <f>T77*Assumptions!$B$151*Assumptions!$B$136*T7/12*(1+Assumptions!$B$16)</f>
+        <f>T77*Assumptions!$B$149*Assumptions!$B$135*T7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="U84" s="44">
-        <f>U77*Assumptions!$B$151*Assumptions!$B$136*U7/12*(1+Assumptions!$B$16)</f>
+        <f>U77*Assumptions!$B$149*Assumptions!$B$135*U7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="V84" s="44">
-        <f>V77*Assumptions!$B$151*Assumptions!$B$136*V7/12*(1+Assumptions!$B$16)</f>
+        <f>V77*Assumptions!$B$149*Assumptions!$B$135*V7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="W84" s="44">
-        <f>W77*Assumptions!$B$151*Assumptions!$B$136*W7/12*(1+Assumptions!$B$16)</f>
+        <f>W77*Assumptions!$B$149*Assumptions!$B$135*W7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="X84" s="44">
-        <f>X77*Assumptions!$B$151*Assumptions!$B$136*X7/12*(1+Assumptions!$B$16)</f>
+        <f>X77*Assumptions!$B$149*Assumptions!$B$135*X7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="Y84" s="44">
-        <f>Y77*Assumptions!$B$151*Assumptions!$B$136*Y7/12*(1+Assumptions!$B$16)</f>
+        <f>Y77*Assumptions!$B$149*Assumptions!$B$135*Y7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="Z84" s="44">
-        <f>Z77*Assumptions!$B$151*Assumptions!$B$136*Z7/12*(1+Assumptions!$B$16)</f>
+        <f>Z77*Assumptions!$B$149*Assumptions!$B$135*Z7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AA84" s="44">
-        <f>AA77*Assumptions!$B$151*Assumptions!$B$136*AA7/12*(1+Assumptions!$B$16)</f>
+        <f>AA77*Assumptions!$B$149*Assumptions!$B$135*AA7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AB84" s="44">
-        <f>AB77*Assumptions!$B$151*Assumptions!$B$136*AB7/12*(1+Assumptions!$B$16)</f>
+        <f>AB77*Assumptions!$B$149*Assumptions!$B$135*AB7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AC84" s="44">
-        <f>AC77*Assumptions!$B$151*Assumptions!$B$136*AC7/12*(1+Assumptions!$B$16)</f>
+        <f>AC77*Assumptions!$B$149*Assumptions!$B$135*AC7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AD84" s="44">
-        <f>AD77*Assumptions!$B$151*Assumptions!$B$136*AD7/12*(1+Assumptions!$B$16)</f>
+        <f>AD77*Assumptions!$B$149*Assumptions!$B$135*AD7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AE84" s="44">
-        <f>AE77*Assumptions!$B$151*Assumptions!$B$136*AE7/12*(1+Assumptions!$B$16)</f>
+        <f>AE77*Assumptions!$B$149*Assumptions!$B$135*AE7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
     </row>
@@ -15984,119 +15751,119 @@
         </is>
       </c>
       <c r="C87" s="54">
-        <f>C82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>C82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="D87" s="54">
-        <f>D82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>D82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="E87" s="54">
-        <f>E82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>E82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="F87" s="54">
-        <f>F82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>F82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="G87" s="54">
-        <f>G82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>G82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="H87" s="54">
-        <f>H82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>H82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="I87" s="54">
-        <f>I82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>I82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="J87" s="54">
-        <f>J82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>J82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="K87" s="54">
-        <f>K82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>K82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="L87" s="54">
-        <f>L82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>L82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="M87" s="54">
-        <f>M82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>M82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="N87" s="54">
-        <f>N82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>N82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="O87" s="54">
-        <f>O82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>O82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="P87" s="54">
-        <f>P82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>P82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="Q87" s="54">
-        <f>Q82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>Q82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="R87" s="54">
-        <f>R82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>R82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="S87" s="54">
-        <f>S82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>S82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="T87" s="54">
-        <f>T82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>T82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="U87" s="54">
-        <f>U82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>U82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="V87" s="54">
-        <f>V82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>V82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="W87" s="54">
-        <f>W82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>W82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="X87" s="54">
-        <f>X82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>X82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="Y87" s="54">
-        <f>Y82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>Y82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="Z87" s="54">
-        <f>Z82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>Z82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AA87" s="54">
-        <f>AA82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AA82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AB87" s="54">
-        <f>AB82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AB82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AC87" s="54">
-        <f>AC82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AC82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AD87" s="54">
-        <f>AD82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AD82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AE87" s="54">
-        <f>AE82*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AE82*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
     </row>
@@ -16112,119 +15879,119 @@
         </is>
       </c>
       <c r="C88" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$47,C65*Assumptions!$B$152*Assumptions!$B$25/12*C7,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$47,C65*Assumptions!$B$150*Assumptions!$B$25/12*C7,0)</f>
         <v/>
       </c>
       <c r="D88" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$47,D65*Assumptions!$B$152*Assumptions!$B$25/12*D7,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$47,D65*Assumptions!$B$150*Assumptions!$B$25/12*D7,0)</f>
         <v/>
       </c>
       <c r="E88" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$47,E65*Assumptions!$B$152*Assumptions!$B$25/12*E7,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$47,E65*Assumptions!$B$150*Assumptions!$B$25/12*E7,0)</f>
         <v/>
       </c>
       <c r="F88" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$47,F65*Assumptions!$B$152*Assumptions!$B$25/12*F7,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$47,F65*Assumptions!$B$150*Assumptions!$B$25/12*F7,0)</f>
         <v/>
       </c>
       <c r="G88" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$47,G65*Assumptions!$B$152*Assumptions!$B$25/12*G7,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$47,G65*Assumptions!$B$150*Assumptions!$B$25/12*G7,0)</f>
         <v/>
       </c>
       <c r="H88" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$47,H65*Assumptions!$B$152*Assumptions!$B$25/12*H7,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$47,H65*Assumptions!$B$150*Assumptions!$B$25/12*H7,0)</f>
         <v/>
       </c>
       <c r="I88" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$47,I65*Assumptions!$B$152*Assumptions!$B$25/12*I7,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$47,I65*Assumptions!$B$150*Assumptions!$B$25/12*I7,0)</f>
         <v/>
       </c>
       <c r="J88" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$47,J65*Assumptions!$B$152*Assumptions!$B$25/12*J7,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$47,J65*Assumptions!$B$150*Assumptions!$B$25/12*J7,0)</f>
         <v/>
       </c>
       <c r="K88" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$47,K65*Assumptions!$B$152*Assumptions!$B$25/12*K7,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$47,K65*Assumptions!$B$150*Assumptions!$B$25/12*K7,0)</f>
         <v/>
       </c>
       <c r="L88" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$47,L65*Assumptions!$B$152*Assumptions!$B$25/12*L7,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$47,L65*Assumptions!$B$150*Assumptions!$B$25/12*L7,0)</f>
         <v/>
       </c>
       <c r="M88" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$47,M65*Assumptions!$B$152*Assumptions!$B$25/12*M7,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$47,M65*Assumptions!$B$150*Assumptions!$B$25/12*M7,0)</f>
         <v/>
       </c>
       <c r="N88" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$47,N65*Assumptions!$B$152*Assumptions!$B$25/12*N7,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$47,N65*Assumptions!$B$150*Assumptions!$B$25/12*N7,0)</f>
         <v/>
       </c>
       <c r="O88" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$47,O65*Assumptions!$B$152*Assumptions!$B$25/12*O7,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$47,O65*Assumptions!$B$150*Assumptions!$B$25/12*O7,0)</f>
         <v/>
       </c>
       <c r="P88" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$47,P65*Assumptions!$B$152*Assumptions!$B$25/12*P7,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$47,P65*Assumptions!$B$150*Assumptions!$B$25/12*P7,0)</f>
         <v/>
       </c>
       <c r="Q88" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$47,Q65*Assumptions!$B$152*Assumptions!$B$25/12*Q7,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$47,Q65*Assumptions!$B$150*Assumptions!$B$25/12*Q7,0)</f>
         <v/>
       </c>
       <c r="R88" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$47,R65*Assumptions!$B$152*Assumptions!$B$25/12*R7,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$47,R65*Assumptions!$B$150*Assumptions!$B$25/12*R7,0)</f>
         <v/>
       </c>
       <c r="S88" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$47,S65*Assumptions!$B$152*Assumptions!$B$25/12*S7,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$47,S65*Assumptions!$B$150*Assumptions!$B$25/12*S7,0)</f>
         <v/>
       </c>
       <c r="T88" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$47,T65*Assumptions!$B$152*Assumptions!$B$25/12*T7,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$47,T65*Assumptions!$B$150*Assumptions!$B$25/12*T7,0)</f>
         <v/>
       </c>
       <c r="U88" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$47,U65*Assumptions!$B$152*Assumptions!$B$25/12*U7,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$47,U65*Assumptions!$B$150*Assumptions!$B$25/12*U7,0)</f>
         <v/>
       </c>
       <c r="V88" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$47,V65*Assumptions!$B$152*Assumptions!$B$25/12*V7,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$47,V65*Assumptions!$B$150*Assumptions!$B$25/12*V7,0)</f>
         <v/>
       </c>
       <c r="W88" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$47,W65*Assumptions!$B$152*Assumptions!$B$25/12*W7,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$47,W65*Assumptions!$B$150*Assumptions!$B$25/12*W7,0)</f>
         <v/>
       </c>
       <c r="X88" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$47,X65*Assumptions!$B$152*Assumptions!$B$25/12*X7,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$47,X65*Assumptions!$B$150*Assumptions!$B$25/12*X7,0)</f>
         <v/>
       </c>
       <c r="Y88" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$47,Y65*Assumptions!$B$152*Assumptions!$B$25/12*Y7,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$47,Y65*Assumptions!$B$150*Assumptions!$B$25/12*Y7,0)</f>
         <v/>
       </c>
       <c r="Z88" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$47,Z65*Assumptions!$B$152*Assumptions!$B$25/12*Z7,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$47,Z65*Assumptions!$B$150*Assumptions!$B$25/12*Z7,0)</f>
         <v/>
       </c>
       <c r="AA88" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$47,AA65*Assumptions!$B$152*Assumptions!$B$25/12*AA7,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$47,AA65*Assumptions!$B$150*Assumptions!$B$25/12*AA7,0)</f>
         <v/>
       </c>
       <c r="AB88" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$47,AB65*Assumptions!$B$152*Assumptions!$B$25/12*AB7,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$47,AB65*Assumptions!$B$150*Assumptions!$B$25/12*AB7,0)</f>
         <v/>
       </c>
       <c r="AC88" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$47,AC65*Assumptions!$B$152*Assumptions!$B$25/12*AC7,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$47,AC65*Assumptions!$B$150*Assumptions!$B$25/12*AC7,0)</f>
         <v/>
       </c>
       <c r="AD88" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$47,AD65*Assumptions!$B$152*Assumptions!$B$25/12*AD7,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$47,AD65*Assumptions!$B$150*Assumptions!$B$25/12*AD7,0)</f>
         <v/>
       </c>
       <c r="AE88" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$47,AE65*Assumptions!$B$152*Assumptions!$B$25/12*AE7,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$47,AE65*Assumptions!$B$150*Assumptions!$B$25/12*AE7,0)</f>
         <v/>
       </c>
     </row>
@@ -16240,119 +16007,119 @@
         </is>
       </c>
       <c r="C89" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$49,C82*C17*Assumptions!$B$17+C77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*C7+C77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*C7,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$49,C82*C17*Assumptions!$B$17+C77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*C7+C77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*C7,0)</f>
         <v/>
       </c>
       <c r="D89" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$49,D82*D17*Assumptions!$B$17+D77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*D7+D77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*D7,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$49,D82*D17*Assumptions!$B$17+D77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*D7+D77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*D7,0)</f>
         <v/>
       </c>
       <c r="E89" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$49,E82*E17*Assumptions!$B$17+E77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*E7+E77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*E7,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$49,E82*E17*Assumptions!$B$17+E77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*E7+E77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*E7,0)</f>
         <v/>
       </c>
       <c r="F89" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$49,F82*F17*Assumptions!$B$17+F77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*F7+F77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*F7,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$49,F82*F17*Assumptions!$B$17+F77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*F7+F77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*F7,0)</f>
         <v/>
       </c>
       <c r="G89" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$49,G82*G17*Assumptions!$B$17+G77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*G7+G77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*G7,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$49,G82*G17*Assumptions!$B$17+G77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*G7+G77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*G7,0)</f>
         <v/>
       </c>
       <c r="H89" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$49,H82*H17*Assumptions!$B$17+H77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*H7+H77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*H7,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$49,H82*H17*Assumptions!$B$17+H77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*H7+H77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*H7,0)</f>
         <v/>
       </c>
       <c r="I89" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$49,I82*I17*Assumptions!$B$17+I77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*I7+I77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*I7,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$49,I82*I17*Assumptions!$B$17+I77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*I7+I77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*I7,0)</f>
         <v/>
       </c>
       <c r="J89" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$49,J82*J17*Assumptions!$B$17+J77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*J7+J77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*J7,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$49,J82*J17*Assumptions!$B$17+J77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*J7+J77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*J7,0)</f>
         <v/>
       </c>
       <c r="K89" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$49,K82*K17*Assumptions!$B$17+K77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*K7+K77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*K7,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$49,K82*K17*Assumptions!$B$17+K77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*K7+K77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*K7,0)</f>
         <v/>
       </c>
       <c r="L89" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$49,L82*L17*Assumptions!$B$17+L77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*L7+L77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*L7,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$49,L82*L17*Assumptions!$B$17+L77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*L7+L77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*L7,0)</f>
         <v/>
       </c>
       <c r="M89" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$49,M82*M17*Assumptions!$B$17+M77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*M7+M77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*M7,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$49,M82*M17*Assumptions!$B$17+M77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*M7+M77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*M7,0)</f>
         <v/>
       </c>
       <c r="N89" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$49,N82*N17*Assumptions!$B$17+N77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*N7+N77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*N7,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$49,N82*N17*Assumptions!$B$17+N77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*N7+N77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*N7,0)</f>
         <v/>
       </c>
       <c r="O89" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$49,O82*O17*Assumptions!$B$17+O77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$49,O82*O17*Assumptions!$B$17+O77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
         <v/>
       </c>
       <c r="P89" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$49,P82*P17*Assumptions!$B$17+P77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$49,P82*P17*Assumptions!$B$17+P77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
         <v/>
       </c>
       <c r="Q89" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$49,Q82*Q17*Assumptions!$B$17+Q77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$49,Q82*Q17*Assumptions!$B$17+Q77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
         <v/>
       </c>
       <c r="R89" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$49,R82*R17*Assumptions!$B$17+R77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$49,R82*R17*Assumptions!$B$17+R77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
         <v/>
       </c>
       <c r="S89" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$49,S82*S17*Assumptions!$B$17+S77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$49,S82*S17*Assumptions!$B$17+S77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
         <v/>
       </c>
       <c r="T89" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$49,T82*T17*Assumptions!$B$17+T77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$49,T82*T17*Assumptions!$B$17+T77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
         <v/>
       </c>
       <c r="U89" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$49,U82*U17*Assumptions!$B$17+U77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$49,U82*U17*Assumptions!$B$17+U77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
         <v/>
       </c>
       <c r="V89" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$49,V82*V17*Assumptions!$B$17+V77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$49,V82*V17*Assumptions!$B$17+V77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
         <v/>
       </c>
       <c r="W89" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$49,W82*W17*Assumptions!$B$17+W77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$49,W82*W17*Assumptions!$B$17+W77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
         <v/>
       </c>
       <c r="X89" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$49,X82*X17*Assumptions!$B$17+X77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$49,X82*X17*Assumptions!$B$17+X77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
         <v/>
       </c>
       <c r="Y89" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$49,Y82*Y17*Assumptions!$B$17+Y77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$49,Y82*Y17*Assumptions!$B$17+Y77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
         <v/>
       </c>
       <c r="Z89" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$49,Z82*Z17*Assumptions!$B$17+Z77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$49,Z82*Z17*Assumptions!$B$17+Z77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
         <v/>
       </c>
       <c r="AA89" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$49,AA82*AA17*Assumptions!$B$17+AA77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$49,AA82*AA17*Assumptions!$B$17+AA77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
         <v/>
       </c>
       <c r="AB89" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$49,AB82*AB17*Assumptions!$B$17+AB77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$49,AB82*AB17*Assumptions!$B$17+AB77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
         <v/>
       </c>
       <c r="AC89" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$49,AC82*AC17*Assumptions!$B$17+AC77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$49,AC82*AC17*Assumptions!$B$17+AC77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
         <v/>
       </c>
       <c r="AD89" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$49,AD82*AD17*Assumptions!$B$17+AD77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$49,AD82*AD17*Assumptions!$B$17+AD77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
         <v/>
       </c>
       <c r="AE89" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$49,AE82*AE17*Assumptions!$B$17+AE77*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE77*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$49,AE82*AE17*Assumptions!$B$17+AE77*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE77*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
         <v/>
       </c>
     </row>
@@ -16368,119 +16135,119 @@
         </is>
       </c>
       <c r="C90" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$50,C77*C78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$50,C77*C78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="D90" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$50,D77*D78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$50,D77*D78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="E90" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$50,E77*E78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$50,E77*E78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="F90" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$50,F77*F78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$50,F77*F78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="G90" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$50,G77*G78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$50,G77*G78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="H90" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$50,H77*H78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$50,H77*H78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="I90" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$50,I77*I78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$50,I77*I78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="J90" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$50,J77*J78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$50,J77*J78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="K90" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$50,K77*K78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$50,K77*K78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="L90" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$50,L77*L78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$50,L77*L78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="M90" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$50,M77*M78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$50,M77*M78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="N90" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$50,N77*N78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$50,N77*N78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="O90" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$50,O77*O78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$50,O77*O78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="P90" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$50,P77*P78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$50,P77*P78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="Q90" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$50,Q77*Q78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$50,Q77*Q78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="R90" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$50,R77*R78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$50,R77*R78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="S90" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$50,S77*S78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$50,S77*S78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="T90" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$50,T77*T78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$50,T77*T78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="U90" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$50,U77*U78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$50,U77*U78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="V90" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$50,V77*V78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$50,V77*V78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="W90" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$50,W77*W78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$50,W77*W78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="X90" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$50,X77*X78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$50,X77*X78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="Y90" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$50,Y77*Y78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$50,Y77*Y78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="Z90" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$50,Z77*Z78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$50,Z77*Z78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AA90" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$50,AA77*AA78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$50,AA77*AA78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AB90" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$50,AB77*AB78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$50,AB77*AB78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AC90" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$50,AC77*AC78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$50,AC77*AC78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AD90" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$50,AD77*AD78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$50,AD77*AD78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AE90" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$50,AE77*AE78*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$50,AE77*AE78*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
     </row>
@@ -16496,119 +16263,119 @@
         </is>
       </c>
       <c r="C91" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$50,(C90*Assumptions!$B$29*Assumptions!$B$30+C77*C79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$50,(C90*Assumptions!$B$29*Assumptions!$B$30+C77*C79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
         <v/>
       </c>
       <c r="D91" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$50,(D90*Assumptions!$B$29*Assumptions!$B$30+D77*D79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$50,(D90*Assumptions!$B$29*Assumptions!$B$30+D77*D79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
         <v/>
       </c>
       <c r="E91" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$50,(E90*Assumptions!$B$29*Assumptions!$B$30+E77*E79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$50,(E90*Assumptions!$B$29*Assumptions!$B$30+E77*E79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
         <v/>
       </c>
       <c r="F91" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$50,(F90*Assumptions!$B$29*Assumptions!$B$30+F77*F79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$50,(F90*Assumptions!$B$29*Assumptions!$B$30+F77*F79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
         <v/>
       </c>
       <c r="G91" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$50,(G90*Assumptions!$B$29*Assumptions!$B$30+G77*G79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$50,(G90*Assumptions!$B$29*Assumptions!$B$30+G77*G79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
         <v/>
       </c>
       <c r="H91" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$50,(H90*Assumptions!$B$29*Assumptions!$B$30+H77*H79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$50,(H90*Assumptions!$B$29*Assumptions!$B$30+H77*H79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
         <v/>
       </c>
       <c r="I91" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$50,(I90*Assumptions!$B$29*Assumptions!$B$30+I77*I79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$50,(I90*Assumptions!$B$29*Assumptions!$B$30+I77*I79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
         <v/>
       </c>
       <c r="J91" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$50,(J90*Assumptions!$B$29*Assumptions!$B$30+J77*J79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$50,(J90*Assumptions!$B$29*Assumptions!$B$30+J77*J79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
         <v/>
       </c>
       <c r="K91" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$50,(K90*Assumptions!$B$29*Assumptions!$B$30+K77*K79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$50,(K90*Assumptions!$B$29*Assumptions!$B$30+K77*K79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
         <v/>
       </c>
       <c r="L91" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$50,(L90*Assumptions!$B$29*Assumptions!$B$30+L77*L79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$50,(L90*Assumptions!$B$29*Assumptions!$B$30+L77*L79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
         <v/>
       </c>
       <c r="M91" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$50,(M90*Assumptions!$B$29*Assumptions!$B$30+M77*M79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$50,(M90*Assumptions!$B$29*Assumptions!$B$30+M77*M79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
         <v/>
       </c>
       <c r="N91" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$50,(N90*Assumptions!$B$29*Assumptions!$B$30+N77*N79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$50,(N90*Assumptions!$B$29*Assumptions!$B$30+N77*N79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
         <v/>
       </c>
       <c r="O91" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$50,(O90*Assumptions!$B$29*Assumptions!$B$30+O77*O79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$50,(O90*Assumptions!$B$29*Assumptions!$B$30+O77*O79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
         <v/>
       </c>
       <c r="P91" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$50,(P90*Assumptions!$B$29*Assumptions!$B$30+P77*P79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$50,(P90*Assumptions!$B$29*Assumptions!$B$30+P77*P79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
         <v/>
       </c>
       <c r="Q91" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$50,(Q90*Assumptions!$B$29*Assumptions!$B$30+Q77*Q79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$50,(Q90*Assumptions!$B$29*Assumptions!$B$30+Q77*Q79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
         <v/>
       </c>
       <c r="R91" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$50,(R90*Assumptions!$B$29*Assumptions!$B$30+R77*R79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$50,(R90*Assumptions!$B$29*Assumptions!$B$30+R77*R79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
         <v/>
       </c>
       <c r="S91" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$50,(S90*Assumptions!$B$29*Assumptions!$B$30+S77*S79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$50,(S90*Assumptions!$B$29*Assumptions!$B$30+S77*S79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
         <v/>
       </c>
       <c r="T91" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$50,(T90*Assumptions!$B$29*Assumptions!$B$30+T77*T79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$50,(T90*Assumptions!$B$29*Assumptions!$B$30+T77*T79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
         <v/>
       </c>
       <c r="U91" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$50,(U90*Assumptions!$B$29*Assumptions!$B$30+U77*U79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$50,(U90*Assumptions!$B$29*Assumptions!$B$30+U77*U79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
         <v/>
       </c>
       <c r="V91" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$50,(V90*Assumptions!$B$29*Assumptions!$B$30+V77*V79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$50,(V90*Assumptions!$B$29*Assumptions!$B$30+V77*V79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
         <v/>
       </c>
       <c r="W91" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$50,(W90*Assumptions!$B$29*Assumptions!$B$30+W77*W79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$50,(W90*Assumptions!$B$29*Assumptions!$B$30+W77*W79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
         <v/>
       </c>
       <c r="X91" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$50,(X90*Assumptions!$B$29*Assumptions!$B$30+X77*X79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$50,(X90*Assumptions!$B$29*Assumptions!$B$30+X77*X79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
         <v/>
       </c>
       <c r="Y91" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$50,(Y90*Assumptions!$B$29*Assumptions!$B$30+Y77*Y79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$50,(Y90*Assumptions!$B$29*Assumptions!$B$30+Y77*Y79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
         <v/>
       </c>
       <c r="Z91" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$50,(Z90*Assumptions!$B$29*Assumptions!$B$30+Z77*Z79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$50,(Z90*Assumptions!$B$29*Assumptions!$B$30+Z77*Z79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
         <v/>
       </c>
       <c r="AA91" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$50,(AA90*Assumptions!$B$29*Assumptions!$B$30+AA77*AA79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$50,(AA90*Assumptions!$B$29*Assumptions!$B$30+AA77*AA79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
         <v/>
       </c>
       <c r="AB91" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$50,(AB90*Assumptions!$B$29*Assumptions!$B$30+AB77*AB79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$50,(AB90*Assumptions!$B$29*Assumptions!$B$30+AB77*AB79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
         <v/>
       </c>
       <c r="AC91" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$50,(AC90*Assumptions!$B$29*Assumptions!$B$30+AC77*AC79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$50,(AC90*Assumptions!$B$29*Assumptions!$B$30+AC77*AC79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
         <v/>
       </c>
       <c r="AD91" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$50,(AD90*Assumptions!$B$29*Assumptions!$B$30+AD77*AD79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$50,(AD90*Assumptions!$B$29*Assumptions!$B$30+AD77*AD79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
         <v/>
       </c>
       <c r="AE91" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$50,(AE90*Assumptions!$B$29*Assumptions!$B$30+AE77*AE79*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$50,(AE90*Assumptions!$B$29*Assumptions!$B$30+AE77*AE79*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
         <v/>
       </c>
     </row>
@@ -18067,119 +17834,119 @@
         </is>
       </c>
       <c r="C105" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$44,C101*Assumptions!$B$163*C7,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$44,C101*Assumptions!$B$161*C7,0)</f>
         <v/>
       </c>
       <c r="D105" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$44,D101*Assumptions!$B$163*D7,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$44,D101*Assumptions!$B$161*D7,0)</f>
         <v/>
       </c>
       <c r="E105" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$44,E101*Assumptions!$B$163*E7,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$44,E101*Assumptions!$B$161*E7,0)</f>
         <v/>
       </c>
       <c r="F105" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$44,F101*Assumptions!$B$163*F7,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$44,F101*Assumptions!$B$161*F7,0)</f>
         <v/>
       </c>
       <c r="G105" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$44,G101*Assumptions!$B$163*G7,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$44,G101*Assumptions!$B$161*G7,0)</f>
         <v/>
       </c>
       <c r="H105" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$44,H101*Assumptions!$B$163*H7,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$44,H101*Assumptions!$B$161*H7,0)</f>
         <v/>
       </c>
       <c r="I105" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$44,I101*Assumptions!$B$163*I7,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$44,I101*Assumptions!$B$161*I7,0)</f>
         <v/>
       </c>
       <c r="J105" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$44,J101*Assumptions!$B$163*J7,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$44,J101*Assumptions!$B$161*J7,0)</f>
         <v/>
       </c>
       <c r="K105" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$44,K101*Assumptions!$B$163*K7,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$44,K101*Assumptions!$B$161*K7,0)</f>
         <v/>
       </c>
       <c r="L105" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$44,L101*Assumptions!$B$163*L7,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$44,L101*Assumptions!$B$161*L7,0)</f>
         <v/>
       </c>
       <c r="M105" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$44,M101*Assumptions!$B$163*M7,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$44,M101*Assumptions!$B$161*M7,0)</f>
         <v/>
       </c>
       <c r="N105" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$44,N101*Assumptions!$B$163*N7,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$44,N101*Assumptions!$B$161*N7,0)</f>
         <v/>
       </c>
       <c r="O105" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$44,O101*Assumptions!$B$163*O7,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$44,O101*Assumptions!$B$161*O7,0)</f>
         <v/>
       </c>
       <c r="P105" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$44,P101*Assumptions!$B$163*P7,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$44,P101*Assumptions!$B$161*P7,0)</f>
         <v/>
       </c>
       <c r="Q105" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$44,Q101*Assumptions!$B$163*Q7,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$44,Q101*Assumptions!$B$161*Q7,0)</f>
         <v/>
       </c>
       <c r="R105" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$44,R101*Assumptions!$B$163*R7,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$44,R101*Assumptions!$B$161*R7,0)</f>
         <v/>
       </c>
       <c r="S105" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$44,S101*Assumptions!$B$163*S7,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$44,S101*Assumptions!$B$161*S7,0)</f>
         <v/>
       </c>
       <c r="T105" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$44,T101*Assumptions!$B$163*T7,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$44,T101*Assumptions!$B$161*T7,0)</f>
         <v/>
       </c>
       <c r="U105" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$44,U101*Assumptions!$B$163*U7,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$44,U101*Assumptions!$B$161*U7,0)</f>
         <v/>
       </c>
       <c r="V105" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$44,V101*Assumptions!$B$163*V7,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$44,V101*Assumptions!$B$161*V7,0)</f>
         <v/>
       </c>
       <c r="W105" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$44,W101*Assumptions!$B$163*W7,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$44,W101*Assumptions!$B$161*W7,0)</f>
         <v/>
       </c>
       <c r="X105" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$44,X101*Assumptions!$B$163*X7,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$44,X101*Assumptions!$B$161*X7,0)</f>
         <v/>
       </c>
       <c r="Y105" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$44,Y101*Assumptions!$B$163*Y7,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$44,Y101*Assumptions!$B$161*Y7,0)</f>
         <v/>
       </c>
       <c r="Z105" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$44,Z101*Assumptions!$B$163*Z7,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$44,Z101*Assumptions!$B$161*Z7,0)</f>
         <v/>
       </c>
       <c r="AA105" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$44,AA101*Assumptions!$B$163*AA7,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$44,AA101*Assumptions!$B$161*AA7,0)</f>
         <v/>
       </c>
       <c r="AB105" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$44,AB101*Assumptions!$B$163*AB7,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$44,AB101*Assumptions!$B$161*AB7,0)</f>
         <v/>
       </c>
       <c r="AC105" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$44,AC101*Assumptions!$B$163*AC7,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$44,AC101*Assumptions!$B$161*AC7,0)</f>
         <v/>
       </c>
       <c r="AD105" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$44,AD101*Assumptions!$B$163*AD7,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$44,AD101*Assumptions!$B$161*AD7,0)</f>
         <v/>
       </c>
       <c r="AE105" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$44,AE101*Assumptions!$B$163*AE7,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$44,AE101*Assumptions!$B$161*AE7,0)</f>
         <v/>
       </c>
     </row>
@@ -18835,119 +18602,119 @@
         </is>
       </c>
       <c r="C111" s="53">
-        <f>C101+C103*Assumptions!$B$168</f>
+        <f>C101+C103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="D111" s="53">
-        <f>D101+D103*Assumptions!$B$168</f>
+        <f>D101+D103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="E111" s="53">
-        <f>E101+E103*Assumptions!$B$168</f>
+        <f>E101+E103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="F111" s="53">
-        <f>F101+F103*Assumptions!$B$168</f>
+        <f>F101+F103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="G111" s="53">
-        <f>G101+G103*Assumptions!$B$168</f>
+        <f>G101+G103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="H111" s="53">
-        <f>H101+H103*Assumptions!$B$168</f>
+        <f>H101+H103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="I111" s="53">
-        <f>I101+I103*Assumptions!$B$168</f>
+        <f>I101+I103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="J111" s="53">
-        <f>J101+J103*Assumptions!$B$168</f>
+        <f>J101+J103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="K111" s="53">
-        <f>K101+K103*Assumptions!$B$168</f>
+        <f>K101+K103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="L111" s="53">
-        <f>L101+L103*Assumptions!$B$168</f>
+        <f>L101+L103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="M111" s="53">
-        <f>M101+M103*Assumptions!$B$168</f>
+        <f>M101+M103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="N111" s="53">
-        <f>N101+N103*Assumptions!$B$168</f>
+        <f>N101+N103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="O111" s="53">
-        <f>O101+O103*Assumptions!$B$168</f>
+        <f>O101+O103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="P111" s="53">
-        <f>P101+P103*Assumptions!$B$168</f>
+        <f>P101+P103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="Q111" s="53">
-        <f>Q101+Q103*Assumptions!$B$168</f>
+        <f>Q101+Q103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="R111" s="53">
-        <f>R101+R103*Assumptions!$B$168</f>
+        <f>R101+R103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="S111" s="53">
-        <f>S101+S103*Assumptions!$B$168</f>
+        <f>S101+S103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="T111" s="53">
-        <f>T101+T103*Assumptions!$B$168</f>
+        <f>T101+T103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="U111" s="53">
-        <f>U101+U103*Assumptions!$B$168</f>
+        <f>U101+U103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="V111" s="53">
-        <f>V101+V103*Assumptions!$B$168</f>
+        <f>V101+V103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="W111" s="53">
-        <f>W101+W103*Assumptions!$B$168</f>
+        <f>W101+W103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="X111" s="53">
-        <f>X101+X103*Assumptions!$B$168</f>
+        <f>X101+X103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="Y111" s="53">
-        <f>Y101+Y103*Assumptions!$B$168</f>
+        <f>Y101+Y103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="Z111" s="53">
-        <f>Z101+Z103*Assumptions!$B$168</f>
+        <f>Z101+Z103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AA111" s="53">
-        <f>AA101+AA103*Assumptions!$B$168</f>
+        <f>AA101+AA103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AB111" s="53">
-        <f>AB101+AB103*Assumptions!$B$168</f>
+        <f>AB101+AB103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AC111" s="53">
-        <f>AC101+AC103*Assumptions!$B$168</f>
+        <f>AC101+AC103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AD111" s="53">
-        <f>AD101+AD103*Assumptions!$B$168</f>
+        <f>AD101+AD103*Assumptions!$B$163</f>
         <v/>
       </c>
       <c r="AE111" s="53">
-        <f>AE101+AE103*Assumptions!$B$168</f>
+        <f>AE101+AE103*Assumptions!$B$163</f>
         <v/>
       </c>
     </row>
@@ -19091,119 +18858,119 @@
         </is>
       </c>
       <c r="C113" s="28">
-        <f>IF(C2&gt;=Assumptions!$B$48,C112*Assumptions!$B$135,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$48,C112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="D113" s="28">
-        <f>IF(D2&gt;=Assumptions!$B$48,D112*Assumptions!$B$135,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$48,D112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="E113" s="28">
-        <f>IF(E2&gt;=Assumptions!$B$48,E112*Assumptions!$B$135,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$48,E112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="F113" s="28">
-        <f>IF(F2&gt;=Assumptions!$B$48,F112*Assumptions!$B$135,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$48,F112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="G113" s="28">
-        <f>IF(G2&gt;=Assumptions!$B$48,G112*Assumptions!$B$135,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$48,G112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="H113" s="28">
-        <f>IF(H2&gt;=Assumptions!$B$48,H112*Assumptions!$B$135,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$48,H112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="I113" s="28">
-        <f>IF(I2&gt;=Assumptions!$B$48,I112*Assumptions!$B$135,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$48,I112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="J113" s="28">
-        <f>IF(J2&gt;=Assumptions!$B$48,J112*Assumptions!$B$135,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$48,J112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="K113" s="28">
-        <f>IF(K2&gt;=Assumptions!$B$48,K112*Assumptions!$B$135,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$48,K112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="L113" s="28">
-        <f>IF(L2&gt;=Assumptions!$B$48,L112*Assumptions!$B$135,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$48,L112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="M113" s="28">
-        <f>IF(M2&gt;=Assumptions!$B$48,M112*Assumptions!$B$135,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$48,M112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="N113" s="28">
-        <f>IF(N2&gt;=Assumptions!$B$48,N112*Assumptions!$B$135,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$48,N112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="O113" s="28">
-        <f>IF(O2&gt;=Assumptions!$B$48,O112*Assumptions!$B$135,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$48,O112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="P113" s="28">
-        <f>IF(P2&gt;=Assumptions!$B$48,P112*Assumptions!$B$135,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$48,P112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="Q113" s="28">
-        <f>IF(Q2&gt;=Assumptions!$B$48,Q112*Assumptions!$B$135,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$48,Q112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="R113" s="28">
-        <f>IF(R2&gt;=Assumptions!$B$48,R112*Assumptions!$B$135,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$48,R112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="S113" s="28">
-        <f>IF(S2&gt;=Assumptions!$B$48,S112*Assumptions!$B$135,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$48,S112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="T113" s="28">
-        <f>IF(T2&gt;=Assumptions!$B$48,T112*Assumptions!$B$135,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$48,T112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="U113" s="28">
-        <f>IF(U2&gt;=Assumptions!$B$48,U112*Assumptions!$B$135,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$48,U112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="V113" s="28">
-        <f>IF(V2&gt;=Assumptions!$B$48,V112*Assumptions!$B$135,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$48,V112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="W113" s="28">
-        <f>IF(W2&gt;=Assumptions!$B$48,W112*Assumptions!$B$135,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$48,W112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="X113" s="28">
-        <f>IF(X2&gt;=Assumptions!$B$48,X112*Assumptions!$B$135,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$48,X112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="Y113" s="28">
-        <f>IF(Y2&gt;=Assumptions!$B$48,Y112*Assumptions!$B$135,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$48,Y112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="Z113" s="28">
-        <f>IF(Z2&gt;=Assumptions!$B$48,Z112*Assumptions!$B$135,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$48,Z112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AA113" s="28">
-        <f>IF(AA2&gt;=Assumptions!$B$48,AA112*Assumptions!$B$135,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$48,AA112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AB113" s="28">
-        <f>IF(AB2&gt;=Assumptions!$B$48,AB112*Assumptions!$B$135,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$48,AB112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AC113" s="28">
-        <f>IF(AC2&gt;=Assumptions!$B$48,AC112*Assumptions!$B$135,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$48,AC112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AD113" s="28">
-        <f>IF(AD2&gt;=Assumptions!$B$48,AD112*Assumptions!$B$135,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$48,AD112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
       <c r="AE113" s="28">
-        <f>IF(AE2&gt;=Assumptions!$B$48,AE112*Assumptions!$B$135,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$48,AE112*Assumptions!$B$134,0)</f>
         <v/>
       </c>
     </row>
@@ -19347,119 +19114,119 @@
         </is>
       </c>
       <c r="C115" s="54">
-        <f>C114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>C114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="D115" s="54">
-        <f>D114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>D114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="E115" s="54">
-        <f>E114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>E114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="F115" s="54">
-        <f>F114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>F114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="G115" s="54">
-        <f>G114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>G114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="H115" s="54">
-        <f>H114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>H114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="I115" s="54">
-        <f>I114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>I114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="J115" s="54">
-        <f>J114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>J114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="K115" s="54">
-        <f>K114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>K114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="L115" s="54">
-        <f>L114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>L114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="M115" s="54">
-        <f>M114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>M114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="N115" s="54">
-        <f>N114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>N114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="O115" s="54">
-        <f>O114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>O114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="P115" s="54">
-        <f>P114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>P114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="Q115" s="54">
-        <f>Q114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>Q114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="R115" s="54">
-        <f>R114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>R114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="S115" s="54">
-        <f>S114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>S114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="T115" s="54">
-        <f>T114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>T114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="U115" s="54">
-        <f>U114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>U114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="V115" s="54">
-        <f>V114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>V114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="W115" s="54">
-        <f>W114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>W114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="X115" s="54">
-        <f>X114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>X114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="Y115" s="54">
-        <f>Y114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>Y114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="Z115" s="54">
-        <f>Z114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>Z114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AA115" s="54">
-        <f>AA114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AA114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AB115" s="54">
-        <f>AB114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AB114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AC115" s="54">
-        <f>AC114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AC114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AD115" s="54">
-        <f>AD114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AD114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="AE115" s="54">
-        <f>AE114*Assumptions!$B$149*Assumptions!$B$151</f>
+        <f>AE114*Assumptions!$B$147*Assumptions!$B$149</f>
         <v/>
       </c>
     </row>
@@ -19859,119 +19626,119 @@
         </is>
       </c>
       <c r="C119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,C114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,C114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="D119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,D114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,D114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="E119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,E114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,E114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="F119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,F114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,F114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="G119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,G114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,G114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="H119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,H114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,H114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="I119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,I114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,I114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="J119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,J114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,J114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="K119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,K114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,K114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="L119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,L114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,L114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="M119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,M114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,M114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="N119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,N114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,N114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="O119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,O114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,O114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="P119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,P114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,P114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="Q119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,Q114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,Q114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="R119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,R114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,R114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="S119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,S114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,S114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="T119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,T114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,T114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="U119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,U114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,U114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="V119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,V114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,V114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="W119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,W114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,W114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="X119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,X114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,X114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="Y119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,Y114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,Y114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="Z119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,Z114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,Z114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AA119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AA114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AA114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AB119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AB114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AB114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AC119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AC114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AC114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AD119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AD114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AD114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
       <c r="AE119" s="44">
-        <f>IF(Assumptions!$B$136=0,0,AE114*Assumptions!$B$149*Assumptions!$B$7/Assumptions!$B$136)</f>
+        <f>IF(Assumptions!$B$135=0,0,AE114*Assumptions!$B$147*Assumptions!$B$7/Assumptions!$B$135)</f>
         <v/>
       </c>
     </row>
@@ -19987,119 +19754,119 @@
         </is>
       </c>
       <c r="C120" s="44">
-        <f>C113*Assumptions!$B$151*Assumptions!$B$136*C7/12*(1+Assumptions!$B$16)</f>
+        <f>C113*Assumptions!$B$149*Assumptions!$B$135*C7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="D120" s="44">
-        <f>D113*Assumptions!$B$151*Assumptions!$B$136*D7/12*(1+Assumptions!$B$16)</f>
+        <f>D113*Assumptions!$B$149*Assumptions!$B$135*D7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="E120" s="44">
-        <f>E113*Assumptions!$B$151*Assumptions!$B$136*E7/12*(1+Assumptions!$B$16)</f>
+        <f>E113*Assumptions!$B$149*Assumptions!$B$135*E7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="F120" s="44">
-        <f>F113*Assumptions!$B$151*Assumptions!$B$136*F7/12*(1+Assumptions!$B$16)</f>
+        <f>F113*Assumptions!$B$149*Assumptions!$B$135*F7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="G120" s="44">
-        <f>G113*Assumptions!$B$151*Assumptions!$B$136*G7/12*(1+Assumptions!$B$16)</f>
+        <f>G113*Assumptions!$B$149*Assumptions!$B$135*G7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="H120" s="44">
-        <f>H113*Assumptions!$B$151*Assumptions!$B$136*H7/12*(1+Assumptions!$B$16)</f>
+        <f>H113*Assumptions!$B$149*Assumptions!$B$135*H7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="I120" s="44">
-        <f>I113*Assumptions!$B$151*Assumptions!$B$136*I7/12*(1+Assumptions!$B$16)</f>
+        <f>I113*Assumptions!$B$149*Assumptions!$B$135*I7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="J120" s="44">
-        <f>J113*Assumptions!$B$151*Assumptions!$B$136*J7/12*(1+Assumptions!$B$16)</f>
+        <f>J113*Assumptions!$B$149*Assumptions!$B$135*J7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="K120" s="44">
-        <f>K113*Assumptions!$B$151*Assumptions!$B$136*K7/12*(1+Assumptions!$B$16)</f>
+        <f>K113*Assumptions!$B$149*Assumptions!$B$135*K7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="L120" s="44">
-        <f>L113*Assumptions!$B$151*Assumptions!$B$136*L7/12*(1+Assumptions!$B$16)</f>
+        <f>L113*Assumptions!$B$149*Assumptions!$B$135*L7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="M120" s="44">
-        <f>M113*Assumptions!$B$151*Assumptions!$B$136*M7/12*(1+Assumptions!$B$16)</f>
+        <f>M113*Assumptions!$B$149*Assumptions!$B$135*M7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="N120" s="44">
-        <f>N113*Assumptions!$B$151*Assumptions!$B$136*N7/12*(1+Assumptions!$B$16)</f>
+        <f>N113*Assumptions!$B$149*Assumptions!$B$135*N7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="O120" s="44">
-        <f>O113*Assumptions!$B$151*Assumptions!$B$136*O7/12*(1+Assumptions!$B$16)</f>
+        <f>O113*Assumptions!$B$149*Assumptions!$B$135*O7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="P120" s="44">
-        <f>P113*Assumptions!$B$151*Assumptions!$B$136*P7/12*(1+Assumptions!$B$16)</f>
+        <f>P113*Assumptions!$B$149*Assumptions!$B$135*P7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="Q120" s="44">
-        <f>Q113*Assumptions!$B$151*Assumptions!$B$136*Q7/12*(1+Assumptions!$B$16)</f>
+        <f>Q113*Assumptions!$B$149*Assumptions!$B$135*Q7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="R120" s="44">
-        <f>R113*Assumptions!$B$151*Assumptions!$B$136*R7/12*(1+Assumptions!$B$16)</f>
+        <f>R113*Assumptions!$B$149*Assumptions!$B$135*R7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="S120" s="44">
-        <f>S113*Assumptions!$B$151*Assumptions!$B$136*S7/12*(1+Assumptions!$B$16)</f>
+        <f>S113*Assumptions!$B$149*Assumptions!$B$135*S7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="T120" s="44">
-        <f>T113*Assumptions!$B$151*Assumptions!$B$136*T7/12*(1+Assumptions!$B$16)</f>
+        <f>T113*Assumptions!$B$149*Assumptions!$B$135*T7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="U120" s="44">
-        <f>U113*Assumptions!$B$151*Assumptions!$B$136*U7/12*(1+Assumptions!$B$16)</f>
+        <f>U113*Assumptions!$B$149*Assumptions!$B$135*U7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="V120" s="44">
-        <f>V113*Assumptions!$B$151*Assumptions!$B$136*V7/12*(1+Assumptions!$B$16)</f>
+        <f>V113*Assumptions!$B$149*Assumptions!$B$135*V7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="W120" s="44">
-        <f>W113*Assumptions!$B$151*Assumptions!$B$136*W7/12*(1+Assumptions!$B$16)</f>
+        <f>W113*Assumptions!$B$149*Assumptions!$B$135*W7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="X120" s="44">
-        <f>X113*Assumptions!$B$151*Assumptions!$B$136*X7/12*(1+Assumptions!$B$16)</f>
+        <f>X113*Assumptions!$B$149*Assumptions!$B$135*X7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="Y120" s="44">
-        <f>Y113*Assumptions!$B$151*Assumptions!$B$136*Y7/12*(1+Assumptions!$B$16)</f>
+        <f>Y113*Assumptions!$B$149*Assumptions!$B$135*Y7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="Z120" s="44">
-        <f>Z113*Assumptions!$B$151*Assumptions!$B$136*Z7/12*(1+Assumptions!$B$16)</f>
+        <f>Z113*Assumptions!$B$149*Assumptions!$B$135*Z7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AA120" s="44">
-        <f>AA113*Assumptions!$B$151*Assumptions!$B$136*AA7/12*(1+Assumptions!$B$16)</f>
+        <f>AA113*Assumptions!$B$149*Assumptions!$B$135*AA7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AB120" s="44">
-        <f>AB113*Assumptions!$B$151*Assumptions!$B$136*AB7/12*(1+Assumptions!$B$16)</f>
+        <f>AB113*Assumptions!$B$149*Assumptions!$B$135*AB7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AC120" s="44">
-        <f>AC113*Assumptions!$B$151*Assumptions!$B$136*AC7/12*(1+Assumptions!$B$16)</f>
+        <f>AC113*Assumptions!$B$149*Assumptions!$B$135*AC7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AD120" s="44">
-        <f>AD113*Assumptions!$B$151*Assumptions!$B$136*AD7/12*(1+Assumptions!$B$16)</f>
+        <f>AD113*Assumptions!$B$149*Assumptions!$B$135*AD7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
       <c r="AE120" s="44">
-        <f>AE113*Assumptions!$B$151*Assumptions!$B$136*AE7/12*(1+Assumptions!$B$16)</f>
+        <f>AE113*Assumptions!$B$149*Assumptions!$B$135*AE7/12*(1+Assumptions!$B$16)</f>
         <v/>
       </c>
     </row>
@@ -20371,119 +20138,119 @@
         </is>
       </c>
       <c r="C123" s="54">
-        <f>C118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>C118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="D123" s="54">
-        <f>D118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>D118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="E123" s="54">
-        <f>E118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>E118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="F123" s="54">
-        <f>F118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>F118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="G123" s="54">
-        <f>G118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>G118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="H123" s="54">
-        <f>H118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>H118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="I123" s="54">
-        <f>I118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>I118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="J123" s="54">
-        <f>J118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>J118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="K123" s="54">
-        <f>K118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>K118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="L123" s="54">
-        <f>L118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>L118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="M123" s="54">
-        <f>M118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>M118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="N123" s="54">
-        <f>N118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>N118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="O123" s="54">
-        <f>O118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>O118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="P123" s="54">
-        <f>P118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>P118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="Q123" s="54">
-        <f>Q118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>Q118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="R123" s="54">
-        <f>R118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>R118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="S123" s="54">
-        <f>S118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>S118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="T123" s="54">
-        <f>T118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>T118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="U123" s="54">
-        <f>U118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>U118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="V123" s="54">
-        <f>V118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>V118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="W123" s="54">
-        <f>W118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>W118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="X123" s="54">
-        <f>X118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>X118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="Y123" s="54">
-        <f>Y118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>Y118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="Z123" s="54">
-        <f>Z118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>Z118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AA123" s="54">
-        <f>AA118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AA118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AB123" s="54">
-        <f>AB118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AB118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AC123" s="54">
-        <f>AC118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AC118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AD123" s="54">
-        <f>AD118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AD118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
       <c r="AE123" s="54">
-        <f>AE118*IF(Assumptions!$B$167=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$134)</f>
+        <f>AE118*IF(Assumptions!$B$162=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$133)</f>
         <v/>
       </c>
     </row>
@@ -20499,119 +20266,119 @@
         </is>
       </c>
       <c r="C124" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$47,C101*Assumptions!$B$152*Assumptions!$B$25/12*C7,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$47,C101*Assumptions!$B$150*Assumptions!$B$25/12*C7,0)</f>
         <v/>
       </c>
       <c r="D124" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$47,D101*Assumptions!$B$152*Assumptions!$B$25/12*D7,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$47,D101*Assumptions!$B$150*Assumptions!$B$25/12*D7,0)</f>
         <v/>
       </c>
       <c r="E124" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$47,E101*Assumptions!$B$152*Assumptions!$B$25/12*E7,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$47,E101*Assumptions!$B$150*Assumptions!$B$25/12*E7,0)</f>
         <v/>
       </c>
       <c r="F124" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$47,F101*Assumptions!$B$152*Assumptions!$B$25/12*F7,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$47,F101*Assumptions!$B$150*Assumptions!$B$25/12*F7,0)</f>
         <v/>
       </c>
       <c r="G124" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$47,G101*Assumptions!$B$152*Assumptions!$B$25/12*G7,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$47,G101*Assumptions!$B$150*Assumptions!$B$25/12*G7,0)</f>
         <v/>
       </c>
       <c r="H124" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$47,H101*Assumptions!$B$152*Assumptions!$B$25/12*H7,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$47,H101*Assumptions!$B$150*Assumptions!$B$25/12*H7,0)</f>
         <v/>
       </c>
       <c r="I124" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$47,I101*Assumptions!$B$152*Assumptions!$B$25/12*I7,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$47,I101*Assumptions!$B$150*Assumptions!$B$25/12*I7,0)</f>
         <v/>
       </c>
       <c r="J124" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$47,J101*Assumptions!$B$152*Assumptions!$B$25/12*J7,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$47,J101*Assumptions!$B$150*Assumptions!$B$25/12*J7,0)</f>
         <v/>
       </c>
       <c r="K124" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$47,K101*Assumptions!$B$152*Assumptions!$B$25/12*K7,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$47,K101*Assumptions!$B$150*Assumptions!$B$25/12*K7,0)</f>
         <v/>
       </c>
       <c r="L124" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$47,L101*Assumptions!$B$152*Assumptions!$B$25/12*L7,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$47,L101*Assumptions!$B$150*Assumptions!$B$25/12*L7,0)</f>
         <v/>
       </c>
       <c r="M124" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$47,M101*Assumptions!$B$152*Assumptions!$B$25/12*M7,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$47,M101*Assumptions!$B$150*Assumptions!$B$25/12*M7,0)</f>
         <v/>
       </c>
       <c r="N124" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$47,N101*Assumptions!$B$152*Assumptions!$B$25/12*N7,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$47,N101*Assumptions!$B$150*Assumptions!$B$25/12*N7,0)</f>
         <v/>
       </c>
       <c r="O124" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$47,O101*Assumptions!$B$152*Assumptions!$B$25/12*O7,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$47,O101*Assumptions!$B$150*Assumptions!$B$25/12*O7,0)</f>
         <v/>
       </c>
       <c r="P124" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$47,P101*Assumptions!$B$152*Assumptions!$B$25/12*P7,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$47,P101*Assumptions!$B$150*Assumptions!$B$25/12*P7,0)</f>
         <v/>
       </c>
       <c r="Q124" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$47,Q101*Assumptions!$B$152*Assumptions!$B$25/12*Q7,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$47,Q101*Assumptions!$B$150*Assumptions!$B$25/12*Q7,0)</f>
         <v/>
       </c>
       <c r="R124" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$47,R101*Assumptions!$B$152*Assumptions!$B$25/12*R7,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$47,R101*Assumptions!$B$150*Assumptions!$B$25/12*R7,0)</f>
         <v/>
       </c>
       <c r="S124" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$47,S101*Assumptions!$B$152*Assumptions!$B$25/12*S7,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$47,S101*Assumptions!$B$150*Assumptions!$B$25/12*S7,0)</f>
         <v/>
       </c>
       <c r="T124" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$47,T101*Assumptions!$B$152*Assumptions!$B$25/12*T7,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$47,T101*Assumptions!$B$150*Assumptions!$B$25/12*T7,0)</f>
         <v/>
       </c>
       <c r="U124" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$47,U101*Assumptions!$B$152*Assumptions!$B$25/12*U7,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$47,U101*Assumptions!$B$150*Assumptions!$B$25/12*U7,0)</f>
         <v/>
       </c>
       <c r="V124" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$47,V101*Assumptions!$B$152*Assumptions!$B$25/12*V7,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$47,V101*Assumptions!$B$150*Assumptions!$B$25/12*V7,0)</f>
         <v/>
       </c>
       <c r="W124" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$47,W101*Assumptions!$B$152*Assumptions!$B$25/12*W7,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$47,W101*Assumptions!$B$150*Assumptions!$B$25/12*W7,0)</f>
         <v/>
       </c>
       <c r="X124" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$47,X101*Assumptions!$B$152*Assumptions!$B$25/12*X7,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$47,X101*Assumptions!$B$150*Assumptions!$B$25/12*X7,0)</f>
         <v/>
       </c>
       <c r="Y124" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$47,Y101*Assumptions!$B$152*Assumptions!$B$25/12*Y7,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$47,Y101*Assumptions!$B$150*Assumptions!$B$25/12*Y7,0)</f>
         <v/>
       </c>
       <c r="Z124" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$47,Z101*Assumptions!$B$152*Assumptions!$B$25/12*Z7,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$47,Z101*Assumptions!$B$150*Assumptions!$B$25/12*Z7,0)</f>
         <v/>
       </c>
       <c r="AA124" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$47,AA101*Assumptions!$B$152*Assumptions!$B$25/12*AA7,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$47,AA101*Assumptions!$B$150*Assumptions!$B$25/12*AA7,0)</f>
         <v/>
       </c>
       <c r="AB124" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$47,AB101*Assumptions!$B$152*Assumptions!$B$25/12*AB7,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$47,AB101*Assumptions!$B$150*Assumptions!$B$25/12*AB7,0)</f>
         <v/>
       </c>
       <c r="AC124" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$47,AC101*Assumptions!$B$152*Assumptions!$B$25/12*AC7,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$47,AC101*Assumptions!$B$150*Assumptions!$B$25/12*AC7,0)</f>
         <v/>
       </c>
       <c r="AD124" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$47,AD101*Assumptions!$B$152*Assumptions!$B$25/12*AD7,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$47,AD101*Assumptions!$B$150*Assumptions!$B$25/12*AD7,0)</f>
         <v/>
       </c>
       <c r="AE124" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$47,AE101*Assumptions!$B$152*Assumptions!$B$25/12*AE7,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$47,AE101*Assumptions!$B$150*Assumptions!$B$25/12*AE7,0)</f>
         <v/>
       </c>
     </row>
@@ -20627,119 +20394,119 @@
         </is>
       </c>
       <c r="C125" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$49,C118*C17*Assumptions!$B$17+C113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*C7+C113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*C7,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$49,C118*C17*Assumptions!$B$17+C113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*C7+C113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*C7,0)</f>
         <v/>
       </c>
       <c r="D125" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$49,D118*D17*Assumptions!$B$17+D113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*D7+D113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*D7,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$49,D118*D17*Assumptions!$B$17+D113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*D7+D113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*D7,0)</f>
         <v/>
       </c>
       <c r="E125" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$49,E118*E17*Assumptions!$B$17+E113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*E7+E113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*E7,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$49,E118*E17*Assumptions!$B$17+E113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*E7+E113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*E7,0)</f>
         <v/>
       </c>
       <c r="F125" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$49,F118*F17*Assumptions!$B$17+F113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*F7+F113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*F7,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$49,F118*F17*Assumptions!$B$17+F113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*F7+F113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*F7,0)</f>
         <v/>
       </c>
       <c r="G125" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$49,G118*G17*Assumptions!$B$17+G113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*G7+G113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*G7,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$49,G118*G17*Assumptions!$B$17+G113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*G7+G113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*G7,0)</f>
         <v/>
       </c>
       <c r="H125" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$49,H118*H17*Assumptions!$B$17+H113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*H7+H113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*H7,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$49,H118*H17*Assumptions!$B$17+H113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*H7+H113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*H7,0)</f>
         <v/>
       </c>
       <c r="I125" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$49,I118*I17*Assumptions!$B$17+I113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*I7+I113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*I7,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$49,I118*I17*Assumptions!$B$17+I113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*I7+I113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*I7,0)</f>
         <v/>
       </c>
       <c r="J125" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$49,J118*J17*Assumptions!$B$17+J113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*J7+J113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*J7,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$49,J118*J17*Assumptions!$B$17+J113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*J7+J113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*J7,0)</f>
         <v/>
       </c>
       <c r="K125" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$49,K118*K17*Assumptions!$B$17+K113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*K7+K113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*K7,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$49,K118*K17*Assumptions!$B$17+K113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*K7+K113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*K7,0)</f>
         <v/>
       </c>
       <c r="L125" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$49,L118*L17*Assumptions!$B$17+L113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*L7+L113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*L7,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$49,L118*L17*Assumptions!$B$17+L113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*L7+L113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*L7,0)</f>
         <v/>
       </c>
       <c r="M125" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$49,M118*M17*Assumptions!$B$17+M113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*M7+M113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*M7,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$49,M118*M17*Assumptions!$B$17+M113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*M7+M113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*M7,0)</f>
         <v/>
       </c>
       <c r="N125" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$49,N118*N17*Assumptions!$B$17+N113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*N7+N113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*N7,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$49,N118*N17*Assumptions!$B$17+N113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*N7+N113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*N7,0)</f>
         <v/>
       </c>
       <c r="O125" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$49,O118*O17*Assumptions!$B$17+O113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$49,O118*O17*Assumptions!$B$17+O113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*O7+O113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*O7,0)</f>
         <v/>
       </c>
       <c r="P125" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$49,P118*P17*Assumptions!$B$17+P113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$49,P118*P17*Assumptions!$B$17+P113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*P7+P113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*P7,0)</f>
         <v/>
       </c>
       <c r="Q125" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$49,Q118*Q17*Assumptions!$B$17+Q113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$49,Q118*Q17*Assumptions!$B$17+Q113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Q7+Q113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Q7,0)</f>
         <v/>
       </c>
       <c r="R125" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$49,R118*R17*Assumptions!$B$17+R113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$49,R118*R17*Assumptions!$B$17+R113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*R7+R113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*R7,0)</f>
         <v/>
       </c>
       <c r="S125" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$49,S118*S17*Assumptions!$B$17+S113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$49,S118*S17*Assumptions!$B$17+S113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*S7+S113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*S7,0)</f>
         <v/>
       </c>
       <c r="T125" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$49,T118*T17*Assumptions!$B$17+T113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$49,T118*T17*Assumptions!$B$17+T113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*T7+T113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*T7,0)</f>
         <v/>
       </c>
       <c r="U125" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$49,U118*U17*Assumptions!$B$17+U113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$49,U118*U17*Assumptions!$B$17+U113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*U7+U113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*U7,0)</f>
         <v/>
       </c>
       <c r="V125" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$49,V118*V17*Assumptions!$B$17+V113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$49,V118*V17*Assumptions!$B$17+V113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*V7+V113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*V7,0)</f>
         <v/>
       </c>
       <c r="W125" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$49,W118*W17*Assumptions!$B$17+W113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$49,W118*W17*Assumptions!$B$17+W113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*W7+W113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*W7,0)</f>
         <v/>
       </c>
       <c r="X125" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$49,X118*X17*Assumptions!$B$17+X113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$49,X118*X17*Assumptions!$B$17+X113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*X7+X113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*X7,0)</f>
         <v/>
       </c>
       <c r="Y125" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$49,Y118*Y17*Assumptions!$B$17+Y113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$49,Y118*Y17*Assumptions!$B$17+Y113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Y7+Y113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Y7,0)</f>
         <v/>
       </c>
       <c r="Z125" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$49,Z118*Z17*Assumptions!$B$17+Z113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$49,Z118*Z17*Assumptions!$B$17+Z113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*Z7+Z113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*Z7,0)</f>
         <v/>
       </c>
       <c r="AA125" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$49,AA118*AA17*Assumptions!$B$17+AA113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$49,AA118*AA17*Assumptions!$B$17+AA113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AA7+AA113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AA7,0)</f>
         <v/>
       </c>
       <c r="AB125" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$49,AB118*AB17*Assumptions!$B$17+AB113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$49,AB118*AB17*Assumptions!$B$17+AB113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AB7+AB113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AB7,0)</f>
         <v/>
       </c>
       <c r="AC125" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$49,AC118*AC17*Assumptions!$B$17+AC113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$49,AC118*AC17*Assumptions!$B$17+AC113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AC7+AC113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AC7,0)</f>
         <v/>
       </c>
       <c r="AD125" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$49,AD118*AD17*Assumptions!$B$17+AD113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$49,AD118*AD17*Assumptions!$B$17+AD113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AD7+AD113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AD7,0)</f>
         <v/>
       </c>
       <c r="AE125" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$49,AE118*AE17*Assumptions!$B$17+AE113*(Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18)+Assumptions!$B$143*MAX(0,Assumptions!$B$147-Assumptions!$B$18)+Assumptions!$B$144*MAX(0,Assumptions!$B$148-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE113*(Assumptions!$B$139*Assumptions!$B$20+Assumptions!$B$140*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$49,AE118*AE17*Assumptions!$B$17+AE113*(Assumptions!$B$139*MAX(0,Assumptions!$B$143-Assumptions!$B$18)+Assumptions!$B$140*MAX(0,Assumptions!$B$144-Assumptions!$B$18)+Assumptions!$B$141*MAX(0,Assumptions!$B$145-Assumptions!$B$18)+Assumptions!$B$142*MAX(0,Assumptions!$B$146-Assumptions!$B$18))*Assumptions!$B$19/Assumptions!$B$7*AE7+AE113*(Assumptions!$B$137*Assumptions!$B$20+Assumptions!$B$138*Assumptions!$B$21)/12/Assumptions!$B$7*AE7,0)</f>
         <v/>
       </c>
     </row>
@@ -20755,119 +20522,119 @@
         </is>
       </c>
       <c r="C126" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$50,C113*C114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$50,C113*C114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="D126" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$50,D113*D114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$50,D113*D114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="E126" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$50,E113*E114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$50,E113*E114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="F126" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$50,F113*F114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$50,F113*F114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="G126" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$50,G113*G114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$50,G113*G114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="H126" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$50,H113*H114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$50,H113*H114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="I126" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$50,I113*I114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$50,I113*I114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="J126" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$50,J113*J114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$50,J113*J114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="K126" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$50,K113*K114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$50,K113*K114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="L126" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$50,L113*L114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$50,L113*L114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="M126" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$50,M113*M114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$50,M113*M114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="N126" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$50,N113*N114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$50,N113*N114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="O126" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$50,O113*O114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$50,O113*O114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="P126" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$50,P113*P114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$50,P113*P114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="Q126" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$50,Q113*Q114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$50,Q113*Q114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="R126" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$50,R113*R114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$50,R113*R114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="S126" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$50,S113*S114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$50,S113*S114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="T126" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$50,T113*T114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$50,T113*T114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="U126" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$50,U113*U114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$50,U113*U114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="V126" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$50,V113*V114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$50,V113*V114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="W126" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$50,W113*W114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$50,W113*W114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="X126" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$50,X113*X114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$50,X113*X114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="Y126" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$50,Y113*Y114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$50,Y113*Y114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="Z126" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$50,Z113*Z114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$50,Z113*Z114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AA126" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$50,AA113*AA114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$50,AA113*AA114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AB126" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$50,AB113*AB114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$50,AB113*AB114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AC126" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$50,AC113*AC114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$50,AC113*AC114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AD126" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$50,AD113*AD114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$50,AD113*AD114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
       <c r="AE126" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$50,AE113*AE114*(1-Assumptions!$B$167)*Assumptions!$B$149*Assumptions!$B$150,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$50,AE113*AE114*(1-Assumptions!$B$162)*Assumptions!$B$147*Assumptions!$B$148,0)</f>
         <v/>
       </c>
     </row>
@@ -20883,119 +20650,119 @@
         </is>
       </c>
       <c r="C127" s="54">
-        <f>IF(C2&gt;=Assumptions!$B$50,(C126*Assumptions!$B$29*Assumptions!$B$30+C113*C115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$50,(C126*Assumptions!$B$29*Assumptions!$B$30+C113*C115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
         <v/>
       </c>
       <c r="D127" s="54">
-        <f>IF(D2&gt;=Assumptions!$B$50,(D126*Assumptions!$B$29*Assumptions!$B$30+D113*D115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$50,(D126*Assumptions!$B$29*Assumptions!$B$30+D113*D115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
         <v/>
       </c>
       <c r="E127" s="54">
-        <f>IF(E2&gt;=Assumptions!$B$50,(E126*Assumptions!$B$29*Assumptions!$B$30+E113*E115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$50,(E126*Assumptions!$B$29*Assumptions!$B$30+E113*E115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
         <v/>
       </c>
       <c r="F127" s="54">
-        <f>IF(F2&gt;=Assumptions!$B$50,(F126*Assumptions!$B$29*Assumptions!$B$30+F113*F115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$50,(F126*Assumptions!$B$29*Assumptions!$B$30+F113*F115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
         <v/>
       </c>
       <c r="G127" s="54">
-        <f>IF(G2&gt;=Assumptions!$B$50,(G126*Assumptions!$B$29*Assumptions!$B$30+G113*G115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$50,(G126*Assumptions!$B$29*Assumptions!$B$30+G113*G115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
         <v/>
       </c>
       <c r="H127" s="54">
-        <f>IF(H2&gt;=Assumptions!$B$50,(H126*Assumptions!$B$29*Assumptions!$B$30+H113*H115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$50,(H126*Assumptions!$B$29*Assumptions!$B$30+H113*H115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
         <v/>
       </c>
       <c r="I127" s="54">
-        <f>IF(I2&gt;=Assumptions!$B$50,(I126*Assumptions!$B$29*Assumptions!$B$30+I113*I115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$50,(I126*Assumptions!$B$29*Assumptions!$B$30+I113*I115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
         <v/>
       </c>
       <c r="J127" s="54">
-        <f>IF(J2&gt;=Assumptions!$B$50,(J126*Assumptions!$B$29*Assumptions!$B$30+J113*J115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$50,(J126*Assumptions!$B$29*Assumptions!$B$30+J113*J115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
         <v/>
       </c>
       <c r="K127" s="54">
-        <f>IF(K2&gt;=Assumptions!$B$50,(K126*Assumptions!$B$29*Assumptions!$B$30+K113*K115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$50,(K126*Assumptions!$B$29*Assumptions!$B$30+K113*K115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
         <v/>
       </c>
       <c r="L127" s="54">
-        <f>IF(L2&gt;=Assumptions!$B$50,(L126*Assumptions!$B$29*Assumptions!$B$30+L113*L115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$50,(L126*Assumptions!$B$29*Assumptions!$B$30+L113*L115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
         <v/>
       </c>
       <c r="M127" s="54">
-        <f>IF(M2&gt;=Assumptions!$B$50,(M126*Assumptions!$B$29*Assumptions!$B$30+M113*M115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$50,(M126*Assumptions!$B$29*Assumptions!$B$30+M113*M115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
         <v/>
       </c>
       <c r="N127" s="54">
-        <f>IF(N2&gt;=Assumptions!$B$50,(N126*Assumptions!$B$29*Assumptions!$B$30+N113*N115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$50,(N126*Assumptions!$B$29*Assumptions!$B$30+N113*N115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
         <v/>
       </c>
       <c r="O127" s="54">
-        <f>IF(O2&gt;=Assumptions!$B$50,(O126*Assumptions!$B$29*Assumptions!$B$30+O113*O115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$50,(O126*Assumptions!$B$29*Assumptions!$B$30+O113*O115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
         <v/>
       </c>
       <c r="P127" s="54">
-        <f>IF(P2&gt;=Assumptions!$B$50,(P126*Assumptions!$B$29*Assumptions!$B$30+P113*P115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$50,(P126*Assumptions!$B$29*Assumptions!$B$30+P113*P115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
         <v/>
       </c>
       <c r="Q127" s="54">
-        <f>IF(Q2&gt;=Assumptions!$B$50,(Q126*Assumptions!$B$29*Assumptions!$B$30+Q113*Q115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$50,(Q126*Assumptions!$B$29*Assumptions!$B$30+Q113*Q115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
         <v/>
       </c>
       <c r="R127" s="54">
-        <f>IF(R2&gt;=Assumptions!$B$50,(R126*Assumptions!$B$29*Assumptions!$B$30+R113*R115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$50,(R126*Assumptions!$B$29*Assumptions!$B$30+R113*R115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
         <v/>
       </c>
       <c r="S127" s="54">
-        <f>IF(S2&gt;=Assumptions!$B$50,(S126*Assumptions!$B$29*Assumptions!$B$30+S113*S115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$50,(S126*Assumptions!$B$29*Assumptions!$B$30+S113*S115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
         <v/>
       </c>
       <c r="T127" s="54">
-        <f>IF(T2&gt;=Assumptions!$B$50,(T126*Assumptions!$B$29*Assumptions!$B$30+T113*T115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$50,(T126*Assumptions!$B$29*Assumptions!$B$30+T113*T115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
         <v/>
       </c>
       <c r="U127" s="54">
-        <f>IF(U2&gt;=Assumptions!$B$50,(U126*Assumptions!$B$29*Assumptions!$B$30+U113*U115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$50,(U126*Assumptions!$B$29*Assumptions!$B$30+U113*U115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
         <v/>
       </c>
       <c r="V127" s="54">
-        <f>IF(V2&gt;=Assumptions!$B$50,(V126*Assumptions!$B$29*Assumptions!$B$30+V113*V115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$50,(V126*Assumptions!$B$29*Assumptions!$B$30+V113*V115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
         <v/>
       </c>
       <c r="W127" s="54">
-        <f>IF(W2&gt;=Assumptions!$B$50,(W126*Assumptions!$B$29*Assumptions!$B$30+W113*W115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$50,(W126*Assumptions!$B$29*Assumptions!$B$30+W113*W115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
         <v/>
       </c>
       <c r="X127" s="54">
-        <f>IF(X2&gt;=Assumptions!$B$50,(X126*Assumptions!$B$29*Assumptions!$B$30+X113*X115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$50,(X126*Assumptions!$B$29*Assumptions!$B$30+X113*X115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
         <v/>
       </c>
       <c r="Y127" s="54">
-        <f>IF(Y2&gt;=Assumptions!$B$50,(Y126*Assumptions!$B$29*Assumptions!$B$30+Y113*Y115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$50,(Y126*Assumptions!$B$29*Assumptions!$B$30+Y113*Y115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
         <v/>
       </c>
       <c r="Z127" s="54">
-        <f>IF(Z2&gt;=Assumptions!$B$50,(Z126*Assumptions!$B$29*Assumptions!$B$30+Z113*Z115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$50,(Z126*Assumptions!$B$29*Assumptions!$B$30+Z113*Z115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
         <v/>
       </c>
       <c r="AA127" s="54">
-        <f>IF(AA2&gt;=Assumptions!$B$50,(AA126*Assumptions!$B$29*Assumptions!$B$30+AA113*AA115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$50,(AA126*Assumptions!$B$29*Assumptions!$B$30+AA113*AA115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
         <v/>
       </c>
       <c r="AB127" s="54">
-        <f>IF(AB2&gt;=Assumptions!$B$50,(AB126*Assumptions!$B$29*Assumptions!$B$30+AB113*AB115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$50,(AB126*Assumptions!$B$29*Assumptions!$B$30+AB113*AB115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
         <v/>
       </c>
       <c r="AC127" s="54">
-        <f>IF(AC2&gt;=Assumptions!$B$50,(AC126*Assumptions!$B$29*Assumptions!$B$30+AC113*AC115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$50,(AC126*Assumptions!$B$29*Assumptions!$B$30+AC113*AC115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
         <v/>
       </c>
       <c r="AD127" s="54">
-        <f>IF(AD2&gt;=Assumptions!$B$50,(AD126*Assumptions!$B$29*Assumptions!$B$30+AD113*AD115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$50,(AD126*Assumptions!$B$29*Assumptions!$B$30+AD113*AD115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
         <v/>
       </c>
       <c r="AE127" s="54">
-        <f>IF(AE2&gt;=Assumptions!$B$50,(AE126*Assumptions!$B$29*Assumptions!$B$30+AE113*AE115*(1-Assumptions!$B$167)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$50,(AE126*Assumptions!$B$29*Assumptions!$B$30+AE113*AE115*(1-Assumptions!$B$162)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
         <v/>
       </c>
     </row>
@@ -21304,119 +21071,119 @@
         </is>
       </c>
       <c r="C132" s="57">
-        <f>IF(C2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,C5)*Assumptions!$B$160,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,C5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="D132" s="57">
-        <f>IF(D2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,D5)*Assumptions!$B$160,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,D5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="E132" s="57">
-        <f>IF(E2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,E5)*Assumptions!$B$160,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,E5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="F132" s="57">
-        <f>IF(F2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,F5)*Assumptions!$B$160,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,F5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="G132" s="57">
-        <f>IF(G2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,G5)*Assumptions!$B$160,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,G5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="H132" s="57">
-        <f>IF(H2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,H5)*Assumptions!$B$160,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,H5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="I132" s="57">
-        <f>IF(I2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,I5)*Assumptions!$B$160,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,I5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="J132" s="57">
-        <f>IF(J2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,J5)*Assumptions!$B$160,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,J5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="K132" s="57">
-        <f>IF(K2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,K5)*Assumptions!$B$160,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,K5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="L132" s="57">
-        <f>IF(L2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,L5)*Assumptions!$B$160,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,L5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="M132" s="57">
-        <f>IF(M2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,M5)*Assumptions!$B$160,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,M5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="N132" s="57">
-        <f>IF(N2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,N5)*Assumptions!$B$160,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,N5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="O132" s="57">
-        <f>IF(O2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,O5)*Assumptions!$B$160,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,O5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="P132" s="57">
-        <f>IF(P2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,P5)*Assumptions!$B$160,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,P5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="Q132" s="57">
-        <f>IF(Q2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,Q5)*Assumptions!$B$160,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,Q5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="R132" s="57">
-        <f>IF(R2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,R5)*Assumptions!$B$160,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,R5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="S132" s="57">
-        <f>IF(S2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,S5)*Assumptions!$B$160,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,S5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="T132" s="57">
-        <f>IF(T2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,T5)*Assumptions!$B$160,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,T5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="U132" s="57">
-        <f>IF(U2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,U5)*Assumptions!$B$160,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,U5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="V132" s="57">
-        <f>IF(V2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,V5)*Assumptions!$B$160,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,V5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="W132" s="57">
-        <f>IF(W2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,W5)*Assumptions!$B$160,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,W5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="X132" s="57">
-        <f>IF(X2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,X5)*Assumptions!$B$160,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,X5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="Y132" s="57">
-        <f>IF(Y2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,Y5)*Assumptions!$B$160,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,Y5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="Z132" s="57">
-        <f>IF(Z2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,Z5)*Assumptions!$B$160,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,Z5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="AA132" s="57">
-        <f>IF(AA2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,AA5)*Assumptions!$B$160,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,AA5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="AB132" s="57">
-        <f>IF(AB2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,AB5)*Assumptions!$B$160,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,AB5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="AC132" s="57">
-        <f>IF(AC2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,AC5)*Assumptions!$B$160,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,AC5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="AD132" s="57">
-        <f>IF(AD2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,AD5)*Assumptions!$B$160,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,AD5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
       <c r="AE132" s="57">
-        <f>IF(AE2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$153:$B$159,AE5)*Assumptions!$B$160,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$51,INDEX(Assumptions!$B$151:$B$157,AE5)*Assumptions!$B$158,0)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B37" s="19" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="B93" s="17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>A STOCK, not a flow: at 45% attrition, holding 200 active needs ~90 recruits a year. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="B94" s="17" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>A STOCK, not a flow: at 45% attrition, holding 200 active needs ~90 recruits a year. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="B95" s="17" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>A STOCK, not a flow: at 45% attrition, holding 200 active needs ~90 recruits a year. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="B96" s="17" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>A STOCK, not a flow: at 45% attrition, holding 200 active needs ~90 recruits a year. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="B97" s="17" t="n">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>A STOCK, not a flow: at 45% attrition, holding 200 active needs ~90 recruits a year. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="B98" s="17" t="n">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>A STOCK, not a flow: at 45% attrition, holding 200 active needs ~90 recruits a year. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="B99" s="17" t="n">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>A STOCK, not a flow: at 45% attrition, holding 200 active needs ~90 recruits a year. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B100" s="20" t="n">
-        <v>60000</v>
+        <v>90000</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>A DECISION VARIABLE and an input to acquisition, not an output of a cost table.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="B101" s="20" t="n">
-        <v>180000</v>
+        <v>270000</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>A DECISION VARIABLE and an input to acquisition, not an output of a cost table.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="B102" s="20" t="n">
-        <v>250000</v>
+        <v>375000</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>A DECISION VARIABLE and an input to acquisition, not an output of a cost table.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="B103" s="20" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>A DECISION VARIABLE and an input to acquisition, not an output of a cost table.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="B104" s="20" t="n">
-        <v>600000</v>
+        <v>900000</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>A DECISION VARIABLE and an input to acquisition, not an output of a cost table.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="B105" s="20" t="n">
-        <v>850000</v>
+        <v>1275000</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>A DECISION VARIABLE and an input to acquisition, not an output of a cost table.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="B106" s="20" t="n">
-        <v>1100000</v>
+        <v>1650000</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>A DECISION VARIABLE and an input to acquisition, not an output of a cost table.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Insurance agency comparator. TRIANGULATED.</t>
+          <t>RAISED 2026-08-21 from 4, client instruction. The insurance agency comparator that produced 4 is for agents selling a COMPLEX UNDERWRITTEN PRODUCT with medical questions and multi-page forms; a gold SIP signup is a fraction of that work, so the comparator was conservative for this product. ⚠ COMPOUNDS WITH THE AGENT HEADCOUNT, which was raised 50% the same day - together they are 2.25x the agent output the model carried this morning. Both are execution assumptions with no external anchor at the new level; if either disappoints, the other does not compensate. TRIANGULATED at 4, ASSUMPTION at 6.</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cap removed deliberately, so the distribution is right-skewed. MODEL THE MEAN, NOT THE MEDIAN. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21 from 0.45, client instruction. Cap removed deliberately, so the distribution is right-skewed - MODEL THE MEAN, NOT THE MEDIAN. 0.60 means the average customer produces roughly three referrals every five years; the mean is pulled up by a small number of highly social referrers, which is the normal shape for a trust-based product inside a tight diaspora community. ⚠ IT IS STILL AN ASSUMPTION WITH NO EXTERNAL ANCHOR, and it compounds: referrals feed the paying base, which feeds more referrals. That loop is the reason this parameter is more load-bearing than its size suggests. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Kept separate so the CAC never applies to it. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21 from 0.12, client instruction. Kept separate from CAC deliberately, so the acquisition cost never applies to it - THAT IS ALSO WHY IT IS AN ATTRACTIVE NUMBER TO RAISE, and why it deserves scepticism. 0.25 says a quarter of paid-driven signups arrive again for free through word of mouth, app store discovery and community effects. Defensible for a product sold inside a dense diaspora network where the paid campaign and the community overlap almost completely. ⚠ NO EXTERNAL ANCHOR AT EITHER LEVEL, and it is arithmetically identical to a 12% CAC reduction - so raising this AND cutting CAC in the same pass is close to taking the same benefit twice. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>RELABELLED 2026-08-21 after the client correctly objected to the old name, 'self-custody leakage'. THE GOLD DOES NOT LEAVE THE VAULT: a token moving to a customer's own wallet sells nothing and burns nothing, so calling it an AUM decrease was wrong. What it does leave is Aurumix's COLLATERAL-ELIGIBLE base - Aurumix cannot foreclose on a token sitting in a private wallet, so that gold can no longer back a credit limit. In this model AUM has exactly ONE consumer, the card credit limit, so the arithmetic was always right and only the label was misleading. ⚠ THAT ONE-CONSUMER PROPERTY IS WHAT MAKES THIS SAFE: if a later build points anything else at AUM - a custody fee, a reported-AUM headline - this row must be split in two first. Contrast the redemption line, which IS gold genuinely gone. ASSUMPTION.</t>
+          <t>HALVED 2026-08-21 from 0.12, client instruction. ⚠ NOTE IT HAS ZERO EFFECT ON GOLD UNDER CUSTODY - measured, not asserted - because self-custodied metal never left the vault and was never in that measure. It moves ONLY the collateral-eligible base and therefore the card credit limit, worth ~0.2% of Y7 revenue. RELABELLED earlier the same day after the client correctly objected to the old name, 'self-custody leakage'. THE GOLD DOES NOT LEAVE THE VAULT: a token moving to a customer's own wallet sells nothing and burns nothing, so calling it an AUM decrease was wrong. What it does leave is Aurumix's COLLATERAL-ELIGIBLE base - Aurumix cannot foreclose on a token sitting in a private wallet, so that gold can no longer back a credit limit. In this model AUM has exactly ONE consumer, the card credit limit, so the arithmetic was always right and only the label was misleading. ⚠ THAT ONE-CONSUMER PROPERTY IS WHAT MAKES THIS SAFE: if a later build points anything else at AUM - a custody fee, a reported-AUM headline - this row must be split in two first. Contrast the redemption line, which IS gold genuinely gone. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>A DIFFERENT EVENT from self-custody and a separate line. PAXG turnover of 5.9% is the only comparator. VARA forbids charging any fee on it. ASSUMPTION.</t>
+          <t>LOWERED 2026-08-21 from 0.08, client instruction - AND THIS ONE MOVES TOWARDS THE EVIDENCE, not away from it. PAXG turnover of 5.9% is the only comparator that exists, and 8% sat above it for no stated reason; 6% sits essentially on it. A DIFFERENT EVENT from gold moving out of Aurumix's control, and a separate line: this is metal actually sold and tokens burned. VARA forbids charging any fee on it. ASSUMPTION, now aligned to the single available comparator.</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Customers who stopped paying redeem FASTER - they have no accruing benefit left to protect. Because holders become the majority of the book by Y4, this is the DOMINANT AUM DECAY TERM from roughly Y4. ASSUMPTION.</t>
+          <t>LOWERED 2026-08-21 from 2.2, client instruction. ⚠ THIS IS THE WEAKEST OF THE THREE DECAY CHANGES. The LOGIC behind a multiplier above 1.0 is untouched and still holds: customers who stopped paying redeem faster, because they have no accruing benefit left to protect. Lowering it to 1.6 weakens that argument without new evidence for the smaller number - it says lapsed customers are stickier than previously assumed, which is the convenient direction. Because holders become the majority of the book by Y4, this remains the DOMINANT AUM DECAY TERM from roughly Y4, so the change is not cosmetic. ASSUMPTION, and the first one to revisit if AUM is challenged.</t>
         </is>
       </c>
     </row>
@@ -4575,13 +4575,13 @@
         <v/>
       </c>
       <c r="C16" s="15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>Insurance agency comparator. TRIANGULATED.</t>
+          <t>RAISED 2026-08-21 from 4, client instruction. The insurance agency comparator that produced 4 is for agents selling a COMPLEX UNDERWRITTEN PRODUCT with medical questions and multi-page forms; a gold SIP signup is a fraction of that work, so the comparator was conservative for this product. ⚠ COMPOUNDS WITH THE AGENT HEADCOUNT, which was raised 50% the same day - together they are 2.25x the agent output the model carried this morning. Both are execution assumptions with no external anchor at the new level; if either disappoints, the other does not compensate. TRIANGULATED at 4, ASSUMPTION at 6.</t>
         </is>
       </c>
     </row>
@@ -4605,13 +4605,13 @@
         <v/>
       </c>
       <c r="C17" s="20" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="D17" s="20" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
@@ -4635,13 +4635,13 @@
         <v/>
       </c>
       <c r="C18" s="20" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D18" s="20" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E18" s="20" t="n">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
@@ -4665,13 +4665,13 @@
         <v/>
       </c>
       <c r="C19" s="20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D19" s="20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
@@ -4785,13 +4785,13 @@
         <v/>
       </c>
       <c r="C23" s="15" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Cap removed deliberately, so the distribution is right-skewed. MODEL THE MEAN, NOT THE MEDIAN. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21 from 0.45, client instruction. Cap removed deliberately, so the distribution is right-skewed - MODEL THE MEAN, NOT THE MEDIAN. 0.60 means the average customer produces roughly three referrals every five years; the mean is pulled up by a small number of highly social referrers, which is the normal shape for a trust-based product inside a tight diaspora community. ⚠ IT IS STILL AN ASSUMPTION WITH NO EXTERNAL ANCHOR, and it compounds: referrals feed the paying base, which feeds more referrals. That loop is the reason this parameter is more load-bearing than its size suggests. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -4845,13 +4845,13 @@
         <v/>
       </c>
       <c r="C25" s="19" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E25" s="19" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Kept separate so the CAC never applies to it. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21 from 0.12, client instruction. Kept separate from CAC deliberately, so the acquisition cost never applies to it - THAT IS ALSO WHY IT IS AN ATTRACTIVE NUMBER TO RAISE, and why it deserves scepticism. 0.25 says a quarter of paid-driven signups arrive again for free through word of mouth, app store discovery and community effects. Defensible for a product sold inside a dense diaspora network where the paid campaign and the community overlap almost completely. ⚠ NO EXTERNAL ANCHOR AT EITHER LEVEL, and it is arithmetically identical to a 12% CAC reduction - so raising this AND cutting CAC in the same pass is close to taking the same benefit twice. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -5051,13 +5051,13 @@
         <v/>
       </c>
       <c r="C35" s="19" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="D35" s="19" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>RELABELLED 2026-08-21 after the client correctly objected to the old name, 'self-custody leakage'. THE GOLD DOES NOT LEAVE THE VAULT: a token moving to a customer's own wallet sells nothing and burns nothing, so calling it an AUM decrease was wrong. What it does leave is Aurumix's COLLATERAL-ELIGIBLE base - Aurumix cannot foreclose on a token sitting in a private wallet, so that gold can no longer back a credit limit. In this model AUM has exactly ONE consumer, the card credit limit, so the arithmetic was always right and only the label was misleading. ⚠ THAT ONE-CONSUMER PROPERTY IS WHAT MAKES THIS SAFE: if a later build points anything else at AUM - a custody fee, a reported-AUM headline - this row must be split in two first. Contrast the redemption line, which IS gold genuinely gone. ASSUMPTION.</t>
+          <t>HALVED 2026-08-21 from 0.12, client instruction. ⚠ NOTE IT HAS ZERO EFFECT ON GOLD UNDER CUSTODY - measured, not asserted - because self-custodied metal never left the vault and was never in that measure. It moves ONLY the collateral-eligible base and therefore the card credit limit, worth ~0.2% of Y7 revenue. RELABELLED earlier the same day after the client correctly objected to the old name, 'self-custody leakage'. THE GOLD DOES NOT LEAVE THE VAULT: a token moving to a customer's own wallet sells nothing and burns nothing, so calling it an AUM decrease was wrong. What it does leave is Aurumix's COLLATERAL-ELIGIBLE base - Aurumix cannot foreclose on a token sitting in a private wallet, so that gold can no longer back a credit limit. In this model AUM has exactly ONE consumer, the card credit limit, so the arithmetic was always right and only the label was misleading. ⚠ THAT ONE-CONSUMER PROPERTY IS WHAT MAKES THIS SAFE: if a later build points anything else at AUM - a custody fee, a reported-AUM headline - this row must be split in two first. Contrast the redemption line, which IS gold genuinely gone. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -5081,13 +5081,13 @@
         <v/>
       </c>
       <c r="C36" s="19" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D36" s="19" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>A DIFFERENT EVENT from self-custody and a separate line. PAXG turnover of 5.9% is the only comparator. VARA forbids charging any fee on it. ASSUMPTION.</t>
+          <t>LOWERED 2026-08-21 from 0.08, client instruction - AND THIS ONE MOVES TOWARDS THE EVIDENCE, not away from it. PAXG turnover of 5.9% is the only comparator that exists, and 8% sat above it for no stated reason; 6% sits essentially on it. A DIFFERENT EVENT from gold moving out of Aurumix's control, and a separate line: this is metal actually sold and tokens burned. VARA forbids charging any fee on it. ASSUMPTION, now aligned to the single available comparator.</t>
         </is>
       </c>
     </row>
@@ -5111,13 +5111,13 @@
         <v/>
       </c>
       <c r="C37" s="15" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="F37" s="23" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>Customers who stopped paying redeem FASTER - they have no accruing benefit left to protect. Because holders become the majority of the book by Y4, this is the DOMINANT AUM DECAY TERM from roughly Y4. ASSUMPTION.</t>
+          <t>LOWERED 2026-08-21 from 2.2, client instruction. ⚠ THIS IS THE WEAKEST OF THE THREE DECAY CHANGES. The LOGIC behind a multiplier above 1.0 is untouched and still holds: customers who stopped paying redeem faster, because they have no accruing benefit left to protect. Lowering it to 1.6 weakens that argument without new evidence for the smaller number - it says lapsed customers are stickier than previously assumed, which is the convenient direction. Because holders become the majority of the book by Y4, this remains the DOMINANT AUM DECAY TERM from roughly Y4, so the change is not cosmetic. ASSUMPTION, and the first one to revisit if AUM is challenged.</t>
         </is>
       </c>
     </row>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
@@ -47,7 +47,8 @@
     <definedName name="atmm_a3000">'Scenario Parameters'!$B$56</definedName>
     <definedName name="atmm_a3000p">'Scenario Parameters'!$B$57</definedName>
     <definedName name="atmm_a500">'Scenario Parameters'!$B$54</definedName>
-    <definedName name="aum_per_partner">'Scenario Parameters'!$B$72</definedName>
+    <definedName name="aum_per_partner">'Scenario Parameters'!$B$75</definedName>
+    <definedName name="aum_per_partner_user">'Scenario Parameters'!$B$74</definedName>
     <definedName name="b2b_fee">Assumptions!$B$26</definedName>
     <definedName name="bar_grams">Assumptions!$B$10</definedName>
     <definedName name="cac_gulf">'Scenario Parameters'!$B$18</definedName>
@@ -93,6 +94,8 @@
     <definedName name="organic_share">'Scenario Parameters'!$B$25</definedName>
     <definedName name="origination_gross">Assumptions!$B$27</definedName>
     <definedName name="origination_share">Assumptions!$B$28</definedName>
+    <definedName name="partner_adoption">'Scenario Parameters'!$B$73</definedName>
+    <definedName name="partner_users">'Scenario Parameters'!$B$72</definedName>
     <definedName name="partners_y1">'Scenario Parameters'!$B$65</definedName>
     <definedName name="partners_y2">'Scenario Parameters'!$B$66</definedName>
     <definedName name="partners_y3">'Scenario Parameters'!$B$67</definedName>
@@ -132,11 +135,11 @@
     <definedName name="spotticket_gulf">Assumptions!$B$33</definedName>
     <definedName name="spotticket_india">Assumptions!$B$34</definedName>
     <definedName name="spotticket_uae">Assumptions!$B$32</definedName>
-    <definedName name="sw_lapsed_keeps_card">'Scenario Parameters'!$B$83</definedName>
-    <definedName name="sw_prepaid_vs_credit">'Scenario Parameters'!$B$82</definedName>
-    <definedName name="ticket_gulf">'Scenario Parameters'!$B$77</definedName>
-    <definedName name="ticket_india">'Scenario Parameters'!$B$78</definedName>
-    <definedName name="ticket_uae">'Scenario Parameters'!$B$76</definedName>
+    <definedName name="sw_lapsed_keeps_card">'Scenario Parameters'!$B$86</definedName>
+    <definedName name="sw_prepaid_vs_credit">'Scenario Parameters'!$B$85</definedName>
+    <definedName name="ticket_gulf">'Scenario Parameters'!$B$80</definedName>
+    <definedName name="ticket_india">'Scenario Parameters'!$B$81</definedName>
+    <definedName name="ticket_uae">'Scenario Parameters'!$B$79</definedName>
     <definedName name="txn_fee">Assumptions!$B$15</definedName>
     <definedName name="xchk_uae_obs">Assumptions!$B$89</definedName>
   </definedNames>
@@ -968,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q173"/>
+  <dimension ref="A1:Q176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4061,7 +4064,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4085,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4106,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4127,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4148,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4169,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4187,138 +4190,201 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>AUM per partner (mature)</t>
-        </is>
-      </c>
-      <c r="B167" s="36">
+          <t>Average partner user base</t>
+        </is>
+      </c>
+      <c r="B167" s="37">
         <f>'Scenario Parameters'!$B$72</f>
         <v/>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>active users</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Requires a signed partner. Partner AUM earns NO tier and consumes NO benefits - structurally the highest-margin book. DERIVED.</t>
+          <t>THE MIX, NOT THE BIGGEST. A realistic six-partner Gulf book is roughly one Botim-scale (1.7m ACTIVE fintech users, of 8.2-8.5m app users), two at e&amp; money scale (~1.5m subscribers), and three small wallets at a few hundred thousand - which averages near 900k. ⚠ USE ACTIVE USERS, NOT REGISTERED: Botim's own numbers separate 8.5m app users, 3m KYC'd and 1.7m active fintech users, and adopting the headline would overstate this by 5x. CITED for the two largest, ASSUMPTION for the tail.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Average monthly ticket - UAE</t>
-        </is>
-      </c>
-      <c r="B168" s="36">
-        <f>'Scenario Parameters'!$B$76</f>
+          <t>Partner users adopting gold (mature)</t>
+        </is>
+      </c>
+      <c r="B168" s="34">
+        <f>'Scenario Parameters'!$B$73</f>
         <v/>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>USD/month</t>
+          <t>% of partner users</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
+          <t>OBSERVED ANCHOR: O Gold reports 75,000 ACTIVE users against Botim's 1.7m active fintech users - 4.4% - and 775,000 who merely explored the feature. Base is set at 6%, ABOVE the observed 4.4%, because that figure is roughly six months after the gold feature launched and adoption should mature; 6% is a 1.4x maturation, not a doubling. ⚠ THE 4.4% IS THE ONLY OBSERVED GOLD-ADOPTION RATE FOR A GULF WALLET THAT EXISTS. TRIANGULATED.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Average monthly ticket - Oman and Bahrain</t>
+          <t>AUM per adopting partner user</t>
         </is>
       </c>
       <c r="B169" s="36">
-        <f>'Scenario Parameters'!$B$77</f>
+        <f>'Scenario Parameters'!$B$74</f>
         <v/>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>USD/month</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
+          <t>DERIVED FROM BOTIM'S OWN DISCLOSURES AND CROSS-CHECKED AGAINST OUR OWN BOOK - two independent routes to nearly the same number, which is why this is the firmest input in the B2B block. Botim: AED 100m+ of gold across 128,000 trades since Aug 2025, against 75,000 active O Gold users, implies ~USD 363 per active user. Aurumix's own direct book runs at ~USD 302 of gold per customer. A partner's users are buying the same product with the same wallets. DERIVED.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Average monthly ticket - India</t>
+          <t>AUM per partner (derived)</t>
         </is>
       </c>
       <c r="B170" s="36">
-        <f>'Scenario Parameters'!$B$78</f>
+        <f>'Scenario Parameters'!$B$75</f>
         <v/>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>USD/month</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
+          <t>NO LONGER A TYPED NUMBER. Was a flat USD 32m asserted as 'mature AUM per partner' with no derivation. Now users x adoption x AUM per adopting user, every term of which has an external anchor. THE POINT OF THE CHANGE: the only remaining argument is the PARTNER COUNT, which rests on a nameable candidate list and is the argument that can actually be won. DERIVED.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Prepaid instead of credit</t>
-        </is>
-      </c>
-      <c r="B171" s="37">
-        <f>'Scenario Parameters'!$B$82</f>
+          <t>Average monthly ticket - UAE</t>
+        </is>
+      </c>
+      <c r="B171" s="36">
+        <f>'Scenario Parameters'!$B$79</f>
         <v/>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>1/0 switch</t>
+          <t>USD/month</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ON (Prepaid) caps interchange at 1.00% and removes the credit stream entirely. 'NOT A PRODUCT CHOICE, IT IS THE BUSINESS MODEL.' Worth ~USD 2.3m of Y10 revenue on the ten-year run.</t>
+          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>Average monthly ticket - Oman and Bahrain</t>
+        </is>
+      </c>
+      <c r="B172" s="36">
+        <f>'Scenario Parameters'!$B$80</f>
+        <v/>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>USD/month</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Average monthly ticket - India</t>
+        </is>
+      </c>
+      <c r="B173" s="36">
+        <f>'Scenario Parameters'!$B$81</f>
+        <v/>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>USD/month</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Prepaid instead of credit</t>
+        </is>
+      </c>
+      <c r="B174" s="37">
+        <f>'Scenario Parameters'!$B$85</f>
+        <v/>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>1/0 switch</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>ON (Prepaid) caps interchange at 1.00% and removes the credit stream entirely. 'NOT A PRODUCT CHOICE, IT IS THE BUSINESS MODEL.' Worth ~USD 2.3m of Y10 revenue on the ten-year run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
           <t>Holders keep the card</t>
         </is>
       </c>
-      <c r="B172" s="37">
-        <f>'Scenario Parameters'!$B$83</f>
-        <v/>
-      </c>
-      <c r="C172" t="inlineStr">
+      <c r="B175" s="37">
+        <f>'Scenario Parameters'!$B$86</f>
+        <v/>
+      </c>
+      <c r="C175" t="inlineStr">
         <is>
           <t>1/0 switch</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>NOBODY HAS DECIDED THIS. It determines whether the card streams - the majority of revenue - decay with churn or are immune to it. Worth a 42% swing in terminal revenue. Default ON because nothing in the design revokes the card; report both.</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="9" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="9" t="inlineStr">
         <is>
           <t>Every row above is a GREEN link to the active value on Scenario Parameters, which is itself a CHOOSE() across the Base / Aggressive / Conservative columns. Flip the scenario selector and all of them move. The Model reads these cells and never reaches into Scenario Parameters directly, so this sheet is the complete register of every input the model uses.</t>
         </is>
@@ -4335,7 +4401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5872,7 +5938,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="17" t="n">
         <v>1</v>
@@ -5902,7 +5968,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -5917,10 +5983,10 @@
         <v/>
       </c>
       <c r="C67" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E67" s="17" t="n">
         <v>1</v>
@@ -5932,7 +5998,7 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -5947,13 +6013,13 @@
         <v/>
       </c>
       <c r="C68" s="17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D68" s="17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E68" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
@@ -5962,7 +6028,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -5977,13 +6043,13 @@
         <v/>
       </c>
       <c r="C69" s="17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D69" s="17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E69" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
@@ -5992,7 +6058,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -6007,13 +6073,13 @@
         <v/>
       </c>
       <c r="C70" s="17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D70" s="17" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E70" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F70" s="23" t="inlineStr">
         <is>
@@ -6022,7 +6088,7 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -6037,13 +6103,13 @@
         <v/>
       </c>
       <c r="C71" s="17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D71" s="17" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E71" s="17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F71" s="23" t="inlineStr">
         <is>
@@ -6052,253 +6118,334 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>Enterprise cadence for a pre-revenue infrastructure vendor. Partner 1 signs in Y2, matching the M13 B2B go-live - the schedule previously started at Y3 and had to move with it, or stream 6 would have activated with no partner to earn on. TERMINAL COUNTS ARE UNCHANGED, so the pipeline accelerates by a year without inflating the addressable partner market. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AUM per partner (mature)</t>
-        </is>
-      </c>
-      <c r="B72" s="42">
+          <t>Average partner user base</t>
+        </is>
+      </c>
+      <c r="B72" s="31">
         <f>CHOOSE($C$6,C72,D72,E72)</f>
         <v/>
       </c>
-      <c r="C72" s="20" t="n">
-        <v>32000000</v>
-      </c>
-      <c r="D72" s="20" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="E72" s="20" t="n">
-        <v>22000000</v>
+      <c r="C72" s="17" t="n">
+        <v>900000</v>
+      </c>
+      <c r="D72" s="17" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>500000</v>
       </c>
       <c r="F72" s="23" t="inlineStr">
         <is>
+          <t>active users</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>THE MIX, NOT THE BIGGEST. A realistic six-partner Gulf book is roughly one Botim-scale (1.7m ACTIVE fintech users, of 8.2-8.5m app users), two at e&amp; money scale (~1.5m subscribers), and three small wallets at a few hundred thousand - which averages near 900k. ⚠ USE ACTIVE USERS, NOT REGISTERED: Botim's own numbers separate 8.5m app users, 3m KYC'd and 1.7m active fintech users, and adopting the headline would overstate this by 5x. CITED for the two largest, ASSUMPTION for the tail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Partner users adopting gold (mature)</t>
+        </is>
+      </c>
+      <c r="B73" s="40">
+        <f>CHOOSE($C$6,C73,D73,E73)</f>
+        <v/>
+      </c>
+      <c r="C73" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D73" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E73" s="19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F73" s="23" t="inlineStr">
+        <is>
+          <t>% of partner users</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>OBSERVED ANCHOR: O Gold reports 75,000 ACTIVE users against Botim's 1.7m active fintech users - 4.4% - and 775,000 who merely explored the feature. Base is set at 6%, ABOVE the observed 4.4%, because that figure is roughly six months after the gold feature launched and adoption should mature; 6% is a 1.4x maturation, not a doubling. ⚠ THE 4.4% IS THE ONLY OBSERVED GOLD-ADOPTION RATE FOR A GULF WALLET THAT EXISTS. TRIANGULATED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AUM per adopting partner user</t>
+        </is>
+      </c>
+      <c r="B74" s="42">
+        <f>CHOOSE($C$6,C74,D74,E74)</f>
+        <v/>
+      </c>
+      <c r="C74" s="20" t="n">
+        <v>350</v>
+      </c>
+      <c r="D74" s="20" t="n">
+        <v>500</v>
+      </c>
+      <c r="E74" s="20" t="n">
+        <v>220</v>
+      </c>
+      <c r="F74" s="23" t="inlineStr">
+        <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>Requires a signed partner. Partner AUM earns NO tier and consumes NO benefits - structurally the highest-margin book. DERIVED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="A74" s="12" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>DERIVED FROM BOTIM'S OWN DISCLOSURES AND CROSS-CHECKED AGAINST OUR OWN BOOK - two independent routes to nearly the same number, which is why this is the firmest input in the B2B block. Botim: AED 100m+ of gold across 128,000 trades since Aug 2025, against 75,000 active O Gold users, implies ~USD 363 per active user. Aurumix's own direct book runs at ~USD 302 of gold per customer. A partner's users are buying the same product with the same wallets. DERIVED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AUM per partner (derived)</t>
+        </is>
+      </c>
+      <c r="B75" s="42">
+        <f>'Scenario Parameters'!$B$72*'Scenario Parameters'!$B$73*'Scenario Parameters'!$B$74</f>
+        <v/>
+      </c>
+      <c r="F75" s="23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>NO LONGER A TYPED NUMBER. Was a flat USD 32m asserted as 'mature AUM per partner' with no derivation. Now users x adoption x AUM per adopting user, every term of which has an external anchor. THE POINT OF THE CHANGE: the only remaining argument is the PARTNER COUNT, which rests on a nameable candidate list and is the argument that can actually be won. DERIVED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="12" t="inlineStr">
         <is>
           <t>GROUP F: REGIONS</t>
         </is>
       </c>
-      <c r="B74" s="13" t="n"/>
-      <c r="C74" s="13" t="n"/>
-      <c r="D74" s="13" t="n"/>
-      <c r="E74" s="13" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="14" t="inlineStr">
+      <c r="B77" s="13" t="n"/>
+      <c r="C77" s="13" t="n"/>
+      <c r="D77" s="13" t="n"/>
+      <c r="E77" s="13" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B78" s="14" t="inlineStr">
         <is>
           <t>Active Value</t>
         </is>
       </c>
-      <c r="C75" s="14" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D75" s="14" t="inlineStr">
+      <c r="D78" s="14" t="inlineStr">
         <is>
           <t>Aggressive</t>
         </is>
       </c>
-      <c r="E75" s="14" t="inlineStr">
+      <c r="E78" s="14" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
       </c>
-      <c r="F75" s="14" t="inlineStr">
+      <c r="F78" s="14" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Average monthly ticket - UAE</t>
         </is>
       </c>
-      <c r="B76" s="42">
-        <f>CHOOSE($C$6,C76,D76,E76)</f>
-        <v/>
-      </c>
-      <c r="C76" s="20" t="n">
+      <c r="B79" s="42">
+        <f>CHOOSE($C$6,C79,D79,E79)</f>
+        <v/>
+      </c>
+      <c r="C79" s="20" t="n">
         <v>33.6</v>
       </c>
-      <c r="D76" s="20" t="n">
+      <c r="D79" s="20" t="n">
         <v>41</v>
       </c>
-      <c r="E76" s="20" t="n">
+      <c r="E79" s="20" t="n">
         <v>26.5</v>
       </c>
-      <c r="F76" s="23" t="inlineStr">
+      <c r="F79" s="23" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr">
         <is>
           <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>Average monthly ticket - Oman and Bahrain</t>
         </is>
       </c>
-      <c r="B77" s="42">
-        <f>CHOOSE($C$6,C77,D77,E77)</f>
-        <v/>
-      </c>
-      <c r="C77" s="20" t="n">
+      <c r="B80" s="42">
+        <f>CHOOSE($C$6,C80,D80,E80)</f>
+        <v/>
+      </c>
+      <c r="C80" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="D77" s="20" t="n">
+      <c r="D80" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="E77" s="20" t="n">
+      <c r="E80" s="20" t="n">
         <v>21</v>
       </c>
-      <c r="F77" s="23" t="inlineStr">
+      <c r="F80" s="23" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
+      <c r="G80" s="9" t="inlineStr">
         <is>
           <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Average monthly ticket - India</t>
         </is>
       </c>
-      <c r="B78" s="42">
-        <f>CHOOSE($C$6,C78,D78,E78)</f>
-        <v/>
-      </c>
-      <c r="C78" s="20" t="n">
+      <c r="B81" s="42">
+        <f>CHOOSE($C$6,C81,D81,E81)</f>
+        <v/>
+      </c>
+      <c r="C81" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="D78" s="20" t="n">
+      <c r="D81" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="E78" s="20" t="n">
+      <c r="E81" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="F78" s="23" t="inlineStr">
+      <c r="F81" s="23" t="inlineStr">
         <is>
           <t>USD/month</t>
         </is>
       </c>
-      <c r="G78" s="9" t="inlineStr">
+      <c r="G81" s="9" t="inlineStr">
         <is>
           <t>THE SIP AMOUNT - the recurring monthly gold contribution. SAVINGS-CAPACITY anchored, not remittance anchored, because remittance is a committed obligation rather than discretionary money; a recurring gold debit realistically captures 10-15% of monthly savings capacity. Anchors: Joyalukkas has PRICE-DISCOVERED AED 100 (USD 27) as the viable mass-market monthly instalment for this exact demographic, and Malabar sits at AED 200. The blend lands BELOW AMFI's USD 34 Indian retail SIP average (Rs 31,961 crore over 10.63 crore accounts, current at July 2026), which is the correct direction since AMFI reflects domestic urban investors with more discretionary income than a Gulf blue-collar book - it is an upper bound, not a proxy. UAE is the ceiling-weighted blend of the former Indian (USD 38) and other South Asian (USD 26) rows. Book-weighted average ~USD 31.45. TRIANGULATED.</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="A80" s="12" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="12" t="inlineStr">
         <is>
           <t>STRUCTURAL SWITCHES - the two that move revenue</t>
         </is>
       </c>
-      <c r="B80" s="13" t="n"/>
-      <c r="C80" s="13" t="n"/>
-      <c r="D80" s="13" t="n"/>
-      <c r="E80" s="13" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="14" t="inlineStr">
+      <c r="B83" s="13" t="n"/>
+      <c r="C83" s="13" t="n"/>
+      <c r="D83" s="13" t="n"/>
+      <c r="E83" s="13" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
         <is>
           <t>Switch</t>
         </is>
       </c>
-      <c r="B81" s="14" t="inlineStr">
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>Active (1/0)</t>
         </is>
       </c>
-      <c r="C81" s="14" t="inlineStr">
+      <c r="C84" s="14" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="D81" s="14" t="inlineStr">
+      <c r="D84" s="14" t="inlineStr">
         <is>
           <t>ON value</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Prepaid instead of credit</t>
         </is>
       </c>
-      <c r="B82" s="31">
-        <f>IF($C$82="Prepaid",1,0)</f>
-        <v/>
-      </c>
-      <c r="C82" s="38" t="inlineStr">
+      <c r="B85" s="31">
+        <f>IF($C$85="Prepaid",1,0)</f>
+        <v/>
+      </c>
+      <c r="C85" s="38" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="D82" s="23" t="inlineStr">
+      <c r="D85" s="23" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr">
+      <c r="G85" s="9" t="inlineStr">
         <is>
           <t>ON (Prepaid) caps interchange at 1.00% and removes the credit stream entirely. 'NOT A PRODUCT CHOICE, IT IS THE BUSINESS MODEL.' Worth ~USD 2.3m of Y10 revenue on the ten-year run.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Holders keep the card</t>
         </is>
       </c>
-      <c r="B83" s="31">
-        <f>IF($C$83="ON",1,0)</f>
-        <v/>
-      </c>
-      <c r="C83" s="38" t="inlineStr">
+      <c r="B86" s="31">
+        <f>IF($C$86="ON",1,0)</f>
+        <v/>
+      </c>
+      <c r="C86" s="38" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="D83" s="23" t="inlineStr">
+      <c r="D86" s="23" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="G83" s="9" t="inlineStr">
+      <c r="G86" s="9" t="inlineStr">
         <is>
           <t>NOBODY HAS DECIDED THIS. It determines whether the card streams - the majority of revenue - decay with churn or are immune to it. Worth a 42% swing in terminal revenue. Default ON because nothing in the design revokes the card; report both.</t>
         </is>
@@ -6309,10 +6456,10 @@
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Base,Aggressive,Conservative"</formula1>
     </dataValidation>
-    <dataValidation sqref="C82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Credit,Prepaid"</formula1>
     </dataValidation>
-    <dataValidation sqref="C83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="C86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"ON,OFF"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9425,119 +9572,119 @@
         </is>
       </c>
       <c r="C35" s="55">
-        <f>IF(C2&gt;=Assumptions!$B$47,C31*Assumptions!$B$168*C7,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$47,C31*Assumptions!$B$171*C7,0)</f>
         <v/>
       </c>
       <c r="D35" s="55">
-        <f>IF(D2&gt;=Assumptions!$B$47,D31*Assumptions!$B$168*D7,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$47,D31*Assumptions!$B$171*D7,0)</f>
         <v/>
       </c>
       <c r="E35" s="55">
-        <f>IF(E2&gt;=Assumptions!$B$47,E31*Assumptions!$B$168*E7,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$47,E31*Assumptions!$B$171*E7,0)</f>
         <v/>
       </c>
       <c r="F35" s="55">
-        <f>IF(F2&gt;=Assumptions!$B$47,F31*Assumptions!$B$168*F7,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$47,F31*Assumptions!$B$171*F7,0)</f>
         <v/>
       </c>
       <c r="G35" s="55">
-        <f>IF(G2&gt;=Assumptions!$B$47,G31*Assumptions!$B$168*G7,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$47,G31*Assumptions!$B$171*G7,0)</f>
         <v/>
       </c>
       <c r="H35" s="55">
-        <f>IF(H2&gt;=Assumptions!$B$47,H31*Assumptions!$B$168*H7,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$47,H31*Assumptions!$B$171*H7,0)</f>
         <v/>
       </c>
       <c r="I35" s="55">
-        <f>IF(I2&gt;=Assumptions!$B$47,I31*Assumptions!$B$168*I7,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$47,I31*Assumptions!$B$171*I7,0)</f>
         <v/>
       </c>
       <c r="J35" s="55">
-        <f>IF(J2&gt;=Assumptions!$B$47,J31*Assumptions!$B$168*J7,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$47,J31*Assumptions!$B$171*J7,0)</f>
         <v/>
       </c>
       <c r="K35" s="55">
-        <f>IF(K2&gt;=Assumptions!$B$47,K31*Assumptions!$B$168*K7,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$47,K31*Assumptions!$B$171*K7,0)</f>
         <v/>
       </c>
       <c r="L35" s="55">
-        <f>IF(L2&gt;=Assumptions!$B$47,L31*Assumptions!$B$168*L7,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$47,L31*Assumptions!$B$171*L7,0)</f>
         <v/>
       </c>
       <c r="M35" s="55">
-        <f>IF(M2&gt;=Assumptions!$B$47,M31*Assumptions!$B$168*M7,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$47,M31*Assumptions!$B$171*M7,0)</f>
         <v/>
       </c>
       <c r="N35" s="55">
-        <f>IF(N2&gt;=Assumptions!$B$47,N31*Assumptions!$B$168*N7,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$47,N31*Assumptions!$B$171*N7,0)</f>
         <v/>
       </c>
       <c r="O35" s="55">
-        <f>IF(O2&gt;=Assumptions!$B$47,O31*Assumptions!$B$168*O7,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$47,O31*Assumptions!$B$171*O7,0)</f>
         <v/>
       </c>
       <c r="P35" s="55">
-        <f>IF(P2&gt;=Assumptions!$B$47,P31*Assumptions!$B$168*P7,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$47,P31*Assumptions!$B$171*P7,0)</f>
         <v/>
       </c>
       <c r="Q35" s="55">
-        <f>IF(Q2&gt;=Assumptions!$B$47,Q31*Assumptions!$B$168*Q7,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$47,Q31*Assumptions!$B$171*Q7,0)</f>
         <v/>
       </c>
       <c r="R35" s="55">
-        <f>IF(R2&gt;=Assumptions!$B$47,R31*Assumptions!$B$168*R7,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$47,R31*Assumptions!$B$171*R7,0)</f>
         <v/>
       </c>
       <c r="S35" s="55">
-        <f>IF(S2&gt;=Assumptions!$B$47,S31*Assumptions!$B$168*S7,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$47,S31*Assumptions!$B$171*S7,0)</f>
         <v/>
       </c>
       <c r="T35" s="55">
-        <f>IF(T2&gt;=Assumptions!$B$47,T31*Assumptions!$B$168*T7,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$47,T31*Assumptions!$B$171*T7,0)</f>
         <v/>
       </c>
       <c r="U35" s="55">
-        <f>IF(U2&gt;=Assumptions!$B$47,U31*Assumptions!$B$168*U7,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$47,U31*Assumptions!$B$171*U7,0)</f>
         <v/>
       </c>
       <c r="V35" s="55">
-        <f>IF(V2&gt;=Assumptions!$B$47,V31*Assumptions!$B$168*V7,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$47,V31*Assumptions!$B$171*V7,0)</f>
         <v/>
       </c>
       <c r="W35" s="55">
-        <f>IF(W2&gt;=Assumptions!$B$47,W31*Assumptions!$B$168*W7,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$47,W31*Assumptions!$B$171*W7,0)</f>
         <v/>
       </c>
       <c r="X35" s="55">
-        <f>IF(X2&gt;=Assumptions!$B$47,X31*Assumptions!$B$168*X7,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$47,X31*Assumptions!$B$171*X7,0)</f>
         <v/>
       </c>
       <c r="Y35" s="55">
-        <f>IF(Y2&gt;=Assumptions!$B$47,Y31*Assumptions!$B$168*Y7,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$47,Y31*Assumptions!$B$171*Y7,0)</f>
         <v/>
       </c>
       <c r="Z35" s="55">
-        <f>IF(Z2&gt;=Assumptions!$B$47,Z31*Assumptions!$B$168*Z7,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$47,Z31*Assumptions!$B$171*Z7,0)</f>
         <v/>
       </c>
       <c r="AA35" s="55">
-        <f>IF(AA2&gt;=Assumptions!$B$47,AA31*Assumptions!$B$168*AA7,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$47,AA31*Assumptions!$B$171*AA7,0)</f>
         <v/>
       </c>
       <c r="AB35" s="55">
-        <f>IF(AB2&gt;=Assumptions!$B$47,AB31*Assumptions!$B$168*AB7,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$47,AB31*Assumptions!$B$171*AB7,0)</f>
         <v/>
       </c>
       <c r="AC35" s="55">
-        <f>IF(AC2&gt;=Assumptions!$B$47,AC31*Assumptions!$B$168*AC7,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$47,AC31*Assumptions!$B$171*AC7,0)</f>
         <v/>
       </c>
       <c r="AD35" s="55">
-        <f>IF(AD2&gt;=Assumptions!$B$47,AD31*Assumptions!$B$168*AD7,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$47,AD31*Assumptions!$B$171*AD7,0)</f>
         <v/>
       </c>
       <c r="AE35" s="55">
-        <f>IF(AE2&gt;=Assumptions!$B$47,AE31*Assumptions!$B$168*AE7,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$47,AE31*Assumptions!$B$171*AE7,0)</f>
         <v/>
       </c>
     </row>
@@ -10449,119 +10596,119 @@
         </is>
       </c>
       <c r="C43" s="54">
-        <f>C31+C33*Assumptions!$B$172</f>
+        <f>C31+C33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="D43" s="54">
-        <f>D31+D33*Assumptions!$B$172</f>
+        <f>D31+D33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="E43" s="54">
-        <f>E31+E33*Assumptions!$B$172</f>
+        <f>E31+E33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="F43" s="54">
-        <f>F31+F33*Assumptions!$B$172</f>
+        <f>F31+F33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="G43" s="54">
-        <f>G31+G33*Assumptions!$B$172</f>
+        <f>G31+G33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="H43" s="54">
-        <f>H31+H33*Assumptions!$B$172</f>
+        <f>H31+H33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="I43" s="54">
-        <f>I31+I33*Assumptions!$B$172</f>
+        <f>I31+I33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="J43" s="54">
-        <f>J31+J33*Assumptions!$B$172</f>
+        <f>J31+J33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="K43" s="54">
-        <f>K31+K33*Assumptions!$B$172</f>
+        <f>K31+K33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="L43" s="54">
-        <f>L31+L33*Assumptions!$B$172</f>
+        <f>L31+L33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="M43" s="54">
-        <f>M31+M33*Assumptions!$B$172</f>
+        <f>M31+M33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="N43" s="54">
-        <f>N31+N33*Assumptions!$B$172</f>
+        <f>N31+N33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="O43" s="54">
-        <f>O31+O33*Assumptions!$B$172</f>
+        <f>O31+O33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="P43" s="54">
-        <f>P31+P33*Assumptions!$B$172</f>
+        <f>P31+P33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="Q43" s="54">
-        <f>Q31+Q33*Assumptions!$B$172</f>
+        <f>Q31+Q33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="R43" s="54">
-        <f>R31+R33*Assumptions!$B$172</f>
+        <f>R31+R33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="S43" s="54">
-        <f>S31+S33*Assumptions!$B$172</f>
+        <f>S31+S33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="T43" s="54">
-        <f>T31+T33*Assumptions!$B$172</f>
+        <f>T31+T33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="U43" s="54">
-        <f>U31+U33*Assumptions!$B$172</f>
+        <f>U31+U33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="V43" s="54">
-        <f>V31+V33*Assumptions!$B$172</f>
+        <f>V31+V33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="W43" s="54">
-        <f>W31+W33*Assumptions!$B$172</f>
+        <f>W31+W33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="X43" s="54">
-        <f>X31+X33*Assumptions!$B$172</f>
+        <f>X31+X33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="Y43" s="54">
-        <f>Y31+Y33*Assumptions!$B$172</f>
+        <f>Y31+Y33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="Z43" s="54">
-        <f>Z31+Z33*Assumptions!$B$172</f>
+        <f>Z31+Z33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AA43" s="54">
-        <f>AA31+AA33*Assumptions!$B$172</f>
+        <f>AA31+AA33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AB43" s="54">
-        <f>AB31+AB33*Assumptions!$B$172</f>
+        <f>AB31+AB33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AC43" s="54">
-        <f>AC31+AC33*Assumptions!$B$172</f>
+        <f>AC31+AC33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AD43" s="54">
-        <f>AD31+AD33*Assumptions!$B$172</f>
+        <f>AD31+AD33*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AE43" s="54">
-        <f>AE31+AE33*Assumptions!$B$172</f>
+        <f>AE31+AE33*Assumptions!$B$175</f>
         <v/>
       </c>
     </row>
@@ -11985,119 +12132,119 @@
         </is>
       </c>
       <c r="C55" s="55">
-        <f>C50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>C50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="D55" s="55">
-        <f>D50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>D50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="E55" s="55">
-        <f>E50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>E50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="F55" s="55">
-        <f>F50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>F50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="G55" s="55">
-        <f>G50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>G50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="H55" s="55">
-        <f>H50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>H50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="I55" s="55">
-        <f>I50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>I50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="J55" s="55">
-        <f>J50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>J50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="K55" s="55">
-        <f>K50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>K50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="L55" s="55">
-        <f>L50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>L50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="M55" s="55">
-        <f>M50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>M50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="N55" s="55">
-        <f>N50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>N50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="O55" s="55">
-        <f>O50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>O50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="P55" s="55">
-        <f>P50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>P50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="Q55" s="55">
-        <f>Q50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>Q50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="R55" s="55">
-        <f>R50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>R50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="S55" s="55">
-        <f>S50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>S50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="T55" s="55">
-        <f>T50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>T50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="U55" s="55">
-        <f>U50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>U50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="V55" s="55">
-        <f>V50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>V50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="W55" s="55">
-        <f>W50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>W50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="X55" s="55">
-        <f>X50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>X50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="Y55" s="55">
-        <f>Y50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>Y50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="Z55" s="55">
-        <f>Z50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>Z50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AA55" s="55">
-        <f>AA50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AA50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AB55" s="55">
-        <f>AB50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AB50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AC55" s="55">
-        <f>AC50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AC50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AD55" s="55">
-        <f>AD50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AD50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AE55" s="55">
-        <f>AE50*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AE50*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
     </row>
@@ -12369,119 +12516,119 @@
         </is>
       </c>
       <c r="C58" s="55">
-        <f>IF(C2&gt;=Assumptions!$B$53,C45*C46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$53,C45*C46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="D58" s="55">
-        <f>IF(D2&gt;=Assumptions!$B$53,D45*D46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$53,D45*D46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="E58" s="55">
-        <f>IF(E2&gt;=Assumptions!$B$53,E45*E46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$53,E45*E46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="F58" s="55">
-        <f>IF(F2&gt;=Assumptions!$B$53,F45*F46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$53,F45*F46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="G58" s="55">
-        <f>IF(G2&gt;=Assumptions!$B$53,G45*G46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$53,G45*G46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="H58" s="55">
-        <f>IF(H2&gt;=Assumptions!$B$53,H45*H46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$53,H45*H46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="I58" s="55">
-        <f>IF(I2&gt;=Assumptions!$B$53,I45*I46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$53,I45*I46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="J58" s="55">
-        <f>IF(J2&gt;=Assumptions!$B$53,J45*J46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$53,J45*J46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="K58" s="55">
-        <f>IF(K2&gt;=Assumptions!$B$53,K45*K46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$53,K45*K46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="L58" s="55">
-        <f>IF(L2&gt;=Assumptions!$B$53,L45*L46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$53,L45*L46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="M58" s="55">
-        <f>IF(M2&gt;=Assumptions!$B$53,M45*M46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$53,M45*M46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="N58" s="55">
-        <f>IF(N2&gt;=Assumptions!$B$53,N45*N46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$53,N45*N46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="O58" s="55">
-        <f>IF(O2&gt;=Assumptions!$B$53,O45*O46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$53,O45*O46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="P58" s="55">
-        <f>IF(P2&gt;=Assumptions!$B$53,P45*P46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$53,P45*P46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="Q58" s="55">
-        <f>IF(Q2&gt;=Assumptions!$B$53,Q45*Q46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$53,Q45*Q46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="R58" s="55">
-        <f>IF(R2&gt;=Assumptions!$B$53,R45*R46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$53,R45*R46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="S58" s="55">
-        <f>IF(S2&gt;=Assumptions!$B$53,S45*S46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$53,S45*S46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="T58" s="55">
-        <f>IF(T2&gt;=Assumptions!$B$53,T45*T46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$53,T45*T46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="U58" s="55">
-        <f>IF(U2&gt;=Assumptions!$B$53,U45*U46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$53,U45*U46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="V58" s="55">
-        <f>IF(V2&gt;=Assumptions!$B$53,V45*V46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$53,V45*V46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="W58" s="55">
-        <f>IF(W2&gt;=Assumptions!$B$53,W45*W46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$53,W45*W46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="X58" s="55">
-        <f>IF(X2&gt;=Assumptions!$B$53,X45*X46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$53,X45*X46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="Y58" s="55">
-        <f>IF(Y2&gt;=Assumptions!$B$53,Y45*Y46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$53,Y45*Y46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="Z58" s="55">
-        <f>IF(Z2&gt;=Assumptions!$B$53,Z45*Z46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$53,Z45*Z46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AA58" s="55">
-        <f>IF(AA2&gt;=Assumptions!$B$53,AA45*AA46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$53,AA45*AA46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AB58" s="55">
-        <f>IF(AB2&gt;=Assumptions!$B$53,AB45*AB46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$53,AB45*AB46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AC58" s="55">
-        <f>IF(AC2&gt;=Assumptions!$B$53,AC45*AC46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$53,AC45*AC46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AD58" s="55">
-        <f>IF(AD2&gt;=Assumptions!$B$53,AD45*AD46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$53,AD45*AD46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AE58" s="55">
-        <f>IF(AE2&gt;=Assumptions!$B$53,AE45*AE46*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$53,AE45*AE46*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
     </row>
@@ -12497,119 +12644,119 @@
         </is>
       </c>
       <c r="C59" s="55">
-        <f>IF(C2&gt;=Assumptions!$B$53,(C58*Assumptions!$B$29*Assumptions!$B$30+C45*C47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$53,(C58*Assumptions!$B$29*Assumptions!$B$30+C45*C47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
         <v/>
       </c>
       <c r="D59" s="55">
-        <f>IF(D2&gt;=Assumptions!$B$53,(D58*Assumptions!$B$29*Assumptions!$B$30+D45*D47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$53,(D58*Assumptions!$B$29*Assumptions!$B$30+D45*D47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
         <v/>
       </c>
       <c r="E59" s="55">
-        <f>IF(E2&gt;=Assumptions!$B$53,(E58*Assumptions!$B$29*Assumptions!$B$30+E45*E47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$53,(E58*Assumptions!$B$29*Assumptions!$B$30+E45*E47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
         <v/>
       </c>
       <c r="F59" s="55">
-        <f>IF(F2&gt;=Assumptions!$B$53,(F58*Assumptions!$B$29*Assumptions!$B$30+F45*F47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$53,(F58*Assumptions!$B$29*Assumptions!$B$30+F45*F47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
         <v/>
       </c>
       <c r="G59" s="55">
-        <f>IF(G2&gt;=Assumptions!$B$53,(G58*Assumptions!$B$29*Assumptions!$B$30+G45*G47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$53,(G58*Assumptions!$B$29*Assumptions!$B$30+G45*G47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
         <v/>
       </c>
       <c r="H59" s="55">
-        <f>IF(H2&gt;=Assumptions!$B$53,(H58*Assumptions!$B$29*Assumptions!$B$30+H45*H47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$53,(H58*Assumptions!$B$29*Assumptions!$B$30+H45*H47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
         <v/>
       </c>
       <c r="I59" s="55">
-        <f>IF(I2&gt;=Assumptions!$B$53,(I58*Assumptions!$B$29*Assumptions!$B$30+I45*I47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$53,(I58*Assumptions!$B$29*Assumptions!$B$30+I45*I47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
         <v/>
       </c>
       <c r="J59" s="55">
-        <f>IF(J2&gt;=Assumptions!$B$53,(J58*Assumptions!$B$29*Assumptions!$B$30+J45*J47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$53,(J58*Assumptions!$B$29*Assumptions!$B$30+J45*J47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
         <v/>
       </c>
       <c r="K59" s="55">
-        <f>IF(K2&gt;=Assumptions!$B$53,(K58*Assumptions!$B$29*Assumptions!$B$30+K45*K47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$53,(K58*Assumptions!$B$29*Assumptions!$B$30+K45*K47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
         <v/>
       </c>
       <c r="L59" s="55">
-        <f>IF(L2&gt;=Assumptions!$B$53,(L58*Assumptions!$B$29*Assumptions!$B$30+L45*L47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$53,(L58*Assumptions!$B$29*Assumptions!$B$30+L45*L47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
         <v/>
       </c>
       <c r="M59" s="55">
-        <f>IF(M2&gt;=Assumptions!$B$53,(M58*Assumptions!$B$29*Assumptions!$B$30+M45*M47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$53,(M58*Assumptions!$B$29*Assumptions!$B$30+M45*M47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
         <v/>
       </c>
       <c r="N59" s="55">
-        <f>IF(N2&gt;=Assumptions!$B$53,(N58*Assumptions!$B$29*Assumptions!$B$30+N45*N47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$53,(N58*Assumptions!$B$29*Assumptions!$B$30+N45*N47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
         <v/>
       </c>
       <c r="O59" s="55">
-        <f>IF(O2&gt;=Assumptions!$B$53,(O58*Assumptions!$B$29*Assumptions!$B$30+O45*O47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$53,(O58*Assumptions!$B$29*Assumptions!$B$30+O45*O47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
         <v/>
       </c>
       <c r="P59" s="55">
-        <f>IF(P2&gt;=Assumptions!$B$53,(P58*Assumptions!$B$29*Assumptions!$B$30+P45*P47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$53,(P58*Assumptions!$B$29*Assumptions!$B$30+P45*P47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
         <v/>
       </c>
       <c r="Q59" s="55">
-        <f>IF(Q2&gt;=Assumptions!$B$53,(Q58*Assumptions!$B$29*Assumptions!$B$30+Q45*Q47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$53,(Q58*Assumptions!$B$29*Assumptions!$B$30+Q45*Q47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
         <v/>
       </c>
       <c r="R59" s="55">
-        <f>IF(R2&gt;=Assumptions!$B$53,(R58*Assumptions!$B$29*Assumptions!$B$30+R45*R47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$53,(R58*Assumptions!$B$29*Assumptions!$B$30+R45*R47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
         <v/>
       </c>
       <c r="S59" s="55">
-        <f>IF(S2&gt;=Assumptions!$B$53,(S58*Assumptions!$B$29*Assumptions!$B$30+S45*S47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$53,(S58*Assumptions!$B$29*Assumptions!$B$30+S45*S47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
         <v/>
       </c>
       <c r="T59" s="55">
-        <f>IF(T2&gt;=Assumptions!$B$53,(T58*Assumptions!$B$29*Assumptions!$B$30+T45*T47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$53,(T58*Assumptions!$B$29*Assumptions!$B$30+T45*T47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
         <v/>
       </c>
       <c r="U59" s="55">
-        <f>IF(U2&gt;=Assumptions!$B$53,(U58*Assumptions!$B$29*Assumptions!$B$30+U45*U47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$53,(U58*Assumptions!$B$29*Assumptions!$B$30+U45*U47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
         <v/>
       </c>
       <c r="V59" s="55">
-        <f>IF(V2&gt;=Assumptions!$B$53,(V58*Assumptions!$B$29*Assumptions!$B$30+V45*V47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$53,(V58*Assumptions!$B$29*Assumptions!$B$30+V45*V47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
         <v/>
       </c>
       <c r="W59" s="55">
-        <f>IF(W2&gt;=Assumptions!$B$53,(W58*Assumptions!$B$29*Assumptions!$B$30+W45*W47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$53,(W58*Assumptions!$B$29*Assumptions!$B$30+W45*W47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
         <v/>
       </c>
       <c r="X59" s="55">
-        <f>IF(X2&gt;=Assumptions!$B$53,(X58*Assumptions!$B$29*Assumptions!$B$30+X45*X47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$53,(X58*Assumptions!$B$29*Assumptions!$B$30+X45*X47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
         <v/>
       </c>
       <c r="Y59" s="55">
-        <f>IF(Y2&gt;=Assumptions!$B$53,(Y58*Assumptions!$B$29*Assumptions!$B$30+Y45*Y47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$53,(Y58*Assumptions!$B$29*Assumptions!$B$30+Y45*Y47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
         <v/>
       </c>
       <c r="Z59" s="55">
-        <f>IF(Z2&gt;=Assumptions!$B$53,(Z58*Assumptions!$B$29*Assumptions!$B$30+Z45*Z47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$53,(Z58*Assumptions!$B$29*Assumptions!$B$30+Z45*Z47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
         <v/>
       </c>
       <c r="AA59" s="55">
-        <f>IF(AA2&gt;=Assumptions!$B$53,(AA58*Assumptions!$B$29*Assumptions!$B$30+AA45*AA47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$53,(AA58*Assumptions!$B$29*Assumptions!$B$30+AA45*AA47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
         <v/>
       </c>
       <c r="AB59" s="55">
-        <f>IF(AB2&gt;=Assumptions!$B$53,(AB58*Assumptions!$B$29*Assumptions!$B$30+AB45*AB47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$53,(AB58*Assumptions!$B$29*Assumptions!$B$30+AB45*AB47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
         <v/>
       </c>
       <c r="AC59" s="55">
-        <f>IF(AC2&gt;=Assumptions!$B$53,(AC58*Assumptions!$B$29*Assumptions!$B$30+AC45*AC47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$53,(AC58*Assumptions!$B$29*Assumptions!$B$30+AC45*AC47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
         <v/>
       </c>
       <c r="AD59" s="55">
-        <f>IF(AD2&gt;=Assumptions!$B$53,(AD58*Assumptions!$B$29*Assumptions!$B$30+AD45*AD47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$53,(AD58*Assumptions!$B$29*Assumptions!$B$30+AD45*AD47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
         <v/>
       </c>
       <c r="AE59" s="55">
-        <f>IF(AE2&gt;=Assumptions!$B$53,(AE58*Assumptions!$B$29*Assumptions!$B$30+AE45*AE47*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$53,(AE58*Assumptions!$B$29*Assumptions!$B$30+AE45*AE47*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
         <v/>
       </c>
     </row>
@@ -14068,119 +14215,119 @@
         </is>
       </c>
       <c r="C73" s="55">
-        <f>IF(C2&gt;=Assumptions!$B$47,C69*Assumptions!$B$169*C7,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$47,C69*Assumptions!$B$172*C7,0)</f>
         <v/>
       </c>
       <c r="D73" s="55">
-        <f>IF(D2&gt;=Assumptions!$B$47,D69*Assumptions!$B$169*D7,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$47,D69*Assumptions!$B$172*D7,0)</f>
         <v/>
       </c>
       <c r="E73" s="55">
-        <f>IF(E2&gt;=Assumptions!$B$47,E69*Assumptions!$B$169*E7,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$47,E69*Assumptions!$B$172*E7,0)</f>
         <v/>
       </c>
       <c r="F73" s="55">
-        <f>IF(F2&gt;=Assumptions!$B$47,F69*Assumptions!$B$169*F7,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$47,F69*Assumptions!$B$172*F7,0)</f>
         <v/>
       </c>
       <c r="G73" s="55">
-        <f>IF(G2&gt;=Assumptions!$B$47,G69*Assumptions!$B$169*G7,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$47,G69*Assumptions!$B$172*G7,0)</f>
         <v/>
       </c>
       <c r="H73" s="55">
-        <f>IF(H2&gt;=Assumptions!$B$47,H69*Assumptions!$B$169*H7,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$47,H69*Assumptions!$B$172*H7,0)</f>
         <v/>
       </c>
       <c r="I73" s="55">
-        <f>IF(I2&gt;=Assumptions!$B$47,I69*Assumptions!$B$169*I7,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$47,I69*Assumptions!$B$172*I7,0)</f>
         <v/>
       </c>
       <c r="J73" s="55">
-        <f>IF(J2&gt;=Assumptions!$B$47,J69*Assumptions!$B$169*J7,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$47,J69*Assumptions!$B$172*J7,0)</f>
         <v/>
       </c>
       <c r="K73" s="55">
-        <f>IF(K2&gt;=Assumptions!$B$47,K69*Assumptions!$B$169*K7,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$47,K69*Assumptions!$B$172*K7,0)</f>
         <v/>
       </c>
       <c r="L73" s="55">
-        <f>IF(L2&gt;=Assumptions!$B$47,L69*Assumptions!$B$169*L7,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$47,L69*Assumptions!$B$172*L7,0)</f>
         <v/>
       </c>
       <c r="M73" s="55">
-        <f>IF(M2&gt;=Assumptions!$B$47,M69*Assumptions!$B$169*M7,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$47,M69*Assumptions!$B$172*M7,0)</f>
         <v/>
       </c>
       <c r="N73" s="55">
-        <f>IF(N2&gt;=Assumptions!$B$47,N69*Assumptions!$B$169*N7,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$47,N69*Assumptions!$B$172*N7,0)</f>
         <v/>
       </c>
       <c r="O73" s="55">
-        <f>IF(O2&gt;=Assumptions!$B$47,O69*Assumptions!$B$169*O7,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$47,O69*Assumptions!$B$172*O7,0)</f>
         <v/>
       </c>
       <c r="P73" s="55">
-        <f>IF(P2&gt;=Assumptions!$B$47,P69*Assumptions!$B$169*P7,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$47,P69*Assumptions!$B$172*P7,0)</f>
         <v/>
       </c>
       <c r="Q73" s="55">
-        <f>IF(Q2&gt;=Assumptions!$B$47,Q69*Assumptions!$B$169*Q7,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$47,Q69*Assumptions!$B$172*Q7,0)</f>
         <v/>
       </c>
       <c r="R73" s="55">
-        <f>IF(R2&gt;=Assumptions!$B$47,R69*Assumptions!$B$169*R7,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$47,R69*Assumptions!$B$172*R7,0)</f>
         <v/>
       </c>
       <c r="S73" s="55">
-        <f>IF(S2&gt;=Assumptions!$B$47,S69*Assumptions!$B$169*S7,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$47,S69*Assumptions!$B$172*S7,0)</f>
         <v/>
       </c>
       <c r="T73" s="55">
-        <f>IF(T2&gt;=Assumptions!$B$47,T69*Assumptions!$B$169*T7,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$47,T69*Assumptions!$B$172*T7,0)</f>
         <v/>
       </c>
       <c r="U73" s="55">
-        <f>IF(U2&gt;=Assumptions!$B$47,U69*Assumptions!$B$169*U7,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$47,U69*Assumptions!$B$172*U7,0)</f>
         <v/>
       </c>
       <c r="V73" s="55">
-        <f>IF(V2&gt;=Assumptions!$B$47,V69*Assumptions!$B$169*V7,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$47,V69*Assumptions!$B$172*V7,0)</f>
         <v/>
       </c>
       <c r="W73" s="55">
-        <f>IF(W2&gt;=Assumptions!$B$47,W69*Assumptions!$B$169*W7,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$47,W69*Assumptions!$B$172*W7,0)</f>
         <v/>
       </c>
       <c r="X73" s="55">
-        <f>IF(X2&gt;=Assumptions!$B$47,X69*Assumptions!$B$169*X7,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$47,X69*Assumptions!$B$172*X7,0)</f>
         <v/>
       </c>
       <c r="Y73" s="55">
-        <f>IF(Y2&gt;=Assumptions!$B$47,Y69*Assumptions!$B$169*Y7,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$47,Y69*Assumptions!$B$172*Y7,0)</f>
         <v/>
       </c>
       <c r="Z73" s="55">
-        <f>IF(Z2&gt;=Assumptions!$B$47,Z69*Assumptions!$B$169*Z7,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$47,Z69*Assumptions!$B$172*Z7,0)</f>
         <v/>
       </c>
       <c r="AA73" s="55">
-        <f>IF(AA2&gt;=Assumptions!$B$47,AA69*Assumptions!$B$169*AA7,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$47,AA69*Assumptions!$B$172*AA7,0)</f>
         <v/>
       </c>
       <c r="AB73" s="55">
-        <f>IF(AB2&gt;=Assumptions!$B$47,AB69*Assumptions!$B$169*AB7,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$47,AB69*Assumptions!$B$172*AB7,0)</f>
         <v/>
       </c>
       <c r="AC73" s="55">
-        <f>IF(AC2&gt;=Assumptions!$B$47,AC69*Assumptions!$B$169*AC7,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$47,AC69*Assumptions!$B$172*AC7,0)</f>
         <v/>
       </c>
       <c r="AD73" s="55">
-        <f>IF(AD2&gt;=Assumptions!$B$47,AD69*Assumptions!$B$169*AD7,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$47,AD69*Assumptions!$B$172*AD7,0)</f>
         <v/>
       </c>
       <c r="AE73" s="55">
-        <f>IF(AE2&gt;=Assumptions!$B$47,AE69*Assumptions!$B$169*AE7,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$47,AE69*Assumptions!$B$172*AE7,0)</f>
         <v/>
       </c>
     </row>
@@ -15092,119 +15239,119 @@
         </is>
       </c>
       <c r="C81" s="54">
-        <f>C69+C71*Assumptions!$B$172</f>
+        <f>C69+C71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="D81" s="54">
-        <f>D69+D71*Assumptions!$B$172</f>
+        <f>D69+D71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="E81" s="54">
-        <f>E69+E71*Assumptions!$B$172</f>
+        <f>E69+E71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="F81" s="54">
-        <f>F69+F71*Assumptions!$B$172</f>
+        <f>F69+F71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="G81" s="54">
-        <f>G69+G71*Assumptions!$B$172</f>
+        <f>G69+G71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="H81" s="54">
-        <f>H69+H71*Assumptions!$B$172</f>
+        <f>H69+H71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="I81" s="54">
-        <f>I69+I71*Assumptions!$B$172</f>
+        <f>I69+I71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="J81" s="54">
-        <f>J69+J71*Assumptions!$B$172</f>
+        <f>J69+J71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="K81" s="54">
-        <f>K69+K71*Assumptions!$B$172</f>
+        <f>K69+K71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="L81" s="54">
-        <f>L69+L71*Assumptions!$B$172</f>
+        <f>L69+L71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="M81" s="54">
-        <f>M69+M71*Assumptions!$B$172</f>
+        <f>M69+M71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="N81" s="54">
-        <f>N69+N71*Assumptions!$B$172</f>
+        <f>N69+N71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="O81" s="54">
-        <f>O69+O71*Assumptions!$B$172</f>
+        <f>O69+O71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="P81" s="54">
-        <f>P69+P71*Assumptions!$B$172</f>
+        <f>P69+P71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="Q81" s="54">
-        <f>Q69+Q71*Assumptions!$B$172</f>
+        <f>Q69+Q71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="R81" s="54">
-        <f>R69+R71*Assumptions!$B$172</f>
+        <f>R69+R71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="S81" s="54">
-        <f>S69+S71*Assumptions!$B$172</f>
+        <f>S69+S71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="T81" s="54">
-        <f>T69+T71*Assumptions!$B$172</f>
+        <f>T69+T71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="U81" s="54">
-        <f>U69+U71*Assumptions!$B$172</f>
+        <f>U69+U71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="V81" s="54">
-        <f>V69+V71*Assumptions!$B$172</f>
+        <f>V69+V71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="W81" s="54">
-        <f>W69+W71*Assumptions!$B$172</f>
+        <f>W69+W71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="X81" s="54">
-        <f>X69+X71*Assumptions!$B$172</f>
+        <f>X69+X71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="Y81" s="54">
-        <f>Y69+Y71*Assumptions!$B$172</f>
+        <f>Y69+Y71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="Z81" s="54">
-        <f>Z69+Z71*Assumptions!$B$172</f>
+        <f>Z69+Z71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AA81" s="54">
-        <f>AA69+AA71*Assumptions!$B$172</f>
+        <f>AA69+AA71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AB81" s="54">
-        <f>AB69+AB71*Assumptions!$B$172</f>
+        <f>AB69+AB71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AC81" s="54">
-        <f>AC69+AC71*Assumptions!$B$172</f>
+        <f>AC69+AC71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AD81" s="54">
-        <f>AD69+AD71*Assumptions!$B$172</f>
+        <f>AD69+AD71*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AE81" s="54">
-        <f>AE69+AE71*Assumptions!$B$172</f>
+        <f>AE69+AE71*Assumptions!$B$175</f>
         <v/>
       </c>
     </row>
@@ -16628,119 +16775,119 @@
         </is>
       </c>
       <c r="C93" s="55">
-        <f>C88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>C88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="D93" s="55">
-        <f>D88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>D88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="E93" s="55">
-        <f>E88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>E88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="F93" s="55">
-        <f>F88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>F88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="G93" s="55">
-        <f>G88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>G88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="H93" s="55">
-        <f>H88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>H88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="I93" s="55">
-        <f>I88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>I88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="J93" s="55">
-        <f>J88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>J88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="K93" s="55">
-        <f>K88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>K88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="L93" s="55">
-        <f>L88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>L88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="M93" s="55">
-        <f>M88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>M88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="N93" s="55">
-        <f>N88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>N88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="O93" s="55">
-        <f>O88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>O88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="P93" s="55">
-        <f>P88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>P88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="Q93" s="55">
-        <f>Q88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>Q88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="R93" s="55">
-        <f>R88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>R88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="S93" s="55">
-        <f>S88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>S88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="T93" s="55">
-        <f>T88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>T88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="U93" s="55">
-        <f>U88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>U88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="V93" s="55">
-        <f>V88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>V88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="W93" s="55">
-        <f>W88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>W88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="X93" s="55">
-        <f>X88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>X88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="Y93" s="55">
-        <f>Y88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>Y88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="Z93" s="55">
-        <f>Z88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>Z88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AA93" s="55">
-        <f>AA88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AA88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AB93" s="55">
-        <f>AB88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AB88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AC93" s="55">
-        <f>AC88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AC88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AD93" s="55">
-        <f>AD88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AD88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AE93" s="55">
-        <f>AE88*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AE88*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
     </row>
@@ -17012,119 +17159,119 @@
         </is>
       </c>
       <c r="C96" s="55">
-        <f>IF(C2&gt;=Assumptions!$B$53,C83*C84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$53,C83*C84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="D96" s="55">
-        <f>IF(D2&gt;=Assumptions!$B$53,D83*D84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$53,D83*D84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="E96" s="55">
-        <f>IF(E2&gt;=Assumptions!$B$53,E83*E84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$53,E83*E84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="F96" s="55">
-        <f>IF(F2&gt;=Assumptions!$B$53,F83*F84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$53,F83*F84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="G96" s="55">
-        <f>IF(G2&gt;=Assumptions!$B$53,G83*G84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$53,G83*G84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="H96" s="55">
-        <f>IF(H2&gt;=Assumptions!$B$53,H83*H84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$53,H83*H84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="I96" s="55">
-        <f>IF(I2&gt;=Assumptions!$B$53,I83*I84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$53,I83*I84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="J96" s="55">
-        <f>IF(J2&gt;=Assumptions!$B$53,J83*J84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$53,J83*J84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="K96" s="55">
-        <f>IF(K2&gt;=Assumptions!$B$53,K83*K84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$53,K83*K84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="L96" s="55">
-        <f>IF(L2&gt;=Assumptions!$B$53,L83*L84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$53,L83*L84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="M96" s="55">
-        <f>IF(M2&gt;=Assumptions!$B$53,M83*M84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$53,M83*M84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="N96" s="55">
-        <f>IF(N2&gt;=Assumptions!$B$53,N83*N84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$53,N83*N84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="O96" s="55">
-        <f>IF(O2&gt;=Assumptions!$B$53,O83*O84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$53,O83*O84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="P96" s="55">
-        <f>IF(P2&gt;=Assumptions!$B$53,P83*P84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$53,P83*P84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="Q96" s="55">
-        <f>IF(Q2&gt;=Assumptions!$B$53,Q83*Q84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$53,Q83*Q84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="R96" s="55">
-        <f>IF(R2&gt;=Assumptions!$B$53,R83*R84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$53,R83*R84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="S96" s="55">
-        <f>IF(S2&gt;=Assumptions!$B$53,S83*S84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$53,S83*S84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="T96" s="55">
-        <f>IF(T2&gt;=Assumptions!$B$53,T83*T84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$53,T83*T84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="U96" s="55">
-        <f>IF(U2&gt;=Assumptions!$B$53,U83*U84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$53,U83*U84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="V96" s="55">
-        <f>IF(V2&gt;=Assumptions!$B$53,V83*V84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$53,V83*V84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="W96" s="55">
-        <f>IF(W2&gt;=Assumptions!$B$53,W83*W84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$53,W83*W84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="X96" s="55">
-        <f>IF(X2&gt;=Assumptions!$B$53,X83*X84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$53,X83*X84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="Y96" s="55">
-        <f>IF(Y2&gt;=Assumptions!$B$53,Y83*Y84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$53,Y83*Y84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="Z96" s="55">
-        <f>IF(Z2&gt;=Assumptions!$B$53,Z83*Z84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$53,Z83*Z84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AA96" s="55">
-        <f>IF(AA2&gt;=Assumptions!$B$53,AA83*AA84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$53,AA83*AA84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AB96" s="55">
-        <f>IF(AB2&gt;=Assumptions!$B$53,AB83*AB84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$53,AB83*AB84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AC96" s="55">
-        <f>IF(AC2&gt;=Assumptions!$B$53,AC83*AC84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$53,AC83*AC84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AD96" s="55">
-        <f>IF(AD2&gt;=Assumptions!$B$53,AD83*AD84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$53,AD83*AD84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AE96" s="55">
-        <f>IF(AE2&gt;=Assumptions!$B$53,AE83*AE84*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$53,AE83*AE84*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
     </row>
@@ -17140,119 +17287,119 @@
         </is>
       </c>
       <c r="C97" s="55">
-        <f>IF(C2&gt;=Assumptions!$B$53,(C96*Assumptions!$B$29*Assumptions!$B$30+C83*C85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$53,(C96*Assumptions!$B$29*Assumptions!$B$30+C83*C85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
         <v/>
       </c>
       <c r="D97" s="55">
-        <f>IF(D2&gt;=Assumptions!$B$53,(D96*Assumptions!$B$29*Assumptions!$B$30+D83*D85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$53,(D96*Assumptions!$B$29*Assumptions!$B$30+D83*D85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
         <v/>
       </c>
       <c r="E97" s="55">
-        <f>IF(E2&gt;=Assumptions!$B$53,(E96*Assumptions!$B$29*Assumptions!$B$30+E83*E85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$53,(E96*Assumptions!$B$29*Assumptions!$B$30+E83*E85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
         <v/>
       </c>
       <c r="F97" s="55">
-        <f>IF(F2&gt;=Assumptions!$B$53,(F96*Assumptions!$B$29*Assumptions!$B$30+F83*F85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$53,(F96*Assumptions!$B$29*Assumptions!$B$30+F83*F85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
         <v/>
       </c>
       <c r="G97" s="55">
-        <f>IF(G2&gt;=Assumptions!$B$53,(G96*Assumptions!$B$29*Assumptions!$B$30+G83*G85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$53,(G96*Assumptions!$B$29*Assumptions!$B$30+G83*G85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
         <v/>
       </c>
       <c r="H97" s="55">
-        <f>IF(H2&gt;=Assumptions!$B$53,(H96*Assumptions!$B$29*Assumptions!$B$30+H83*H85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$53,(H96*Assumptions!$B$29*Assumptions!$B$30+H83*H85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
         <v/>
       </c>
       <c r="I97" s="55">
-        <f>IF(I2&gt;=Assumptions!$B$53,(I96*Assumptions!$B$29*Assumptions!$B$30+I83*I85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$53,(I96*Assumptions!$B$29*Assumptions!$B$30+I83*I85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
         <v/>
       </c>
       <c r="J97" s="55">
-        <f>IF(J2&gt;=Assumptions!$B$53,(J96*Assumptions!$B$29*Assumptions!$B$30+J83*J85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$53,(J96*Assumptions!$B$29*Assumptions!$B$30+J83*J85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
         <v/>
       </c>
       <c r="K97" s="55">
-        <f>IF(K2&gt;=Assumptions!$B$53,(K96*Assumptions!$B$29*Assumptions!$B$30+K83*K85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$53,(K96*Assumptions!$B$29*Assumptions!$B$30+K83*K85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
         <v/>
       </c>
       <c r="L97" s="55">
-        <f>IF(L2&gt;=Assumptions!$B$53,(L96*Assumptions!$B$29*Assumptions!$B$30+L83*L85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$53,(L96*Assumptions!$B$29*Assumptions!$B$30+L83*L85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
         <v/>
       </c>
       <c r="M97" s="55">
-        <f>IF(M2&gt;=Assumptions!$B$53,(M96*Assumptions!$B$29*Assumptions!$B$30+M83*M85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$53,(M96*Assumptions!$B$29*Assumptions!$B$30+M83*M85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
         <v/>
       </c>
       <c r="N97" s="55">
-        <f>IF(N2&gt;=Assumptions!$B$53,(N96*Assumptions!$B$29*Assumptions!$B$30+N83*N85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$53,(N96*Assumptions!$B$29*Assumptions!$B$30+N83*N85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
         <v/>
       </c>
       <c r="O97" s="55">
-        <f>IF(O2&gt;=Assumptions!$B$53,(O96*Assumptions!$B$29*Assumptions!$B$30+O83*O85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$53,(O96*Assumptions!$B$29*Assumptions!$B$30+O83*O85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
         <v/>
       </c>
       <c r="P97" s="55">
-        <f>IF(P2&gt;=Assumptions!$B$53,(P96*Assumptions!$B$29*Assumptions!$B$30+P83*P85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$53,(P96*Assumptions!$B$29*Assumptions!$B$30+P83*P85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
         <v/>
       </c>
       <c r="Q97" s="55">
-        <f>IF(Q2&gt;=Assumptions!$B$53,(Q96*Assumptions!$B$29*Assumptions!$B$30+Q83*Q85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$53,(Q96*Assumptions!$B$29*Assumptions!$B$30+Q83*Q85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
         <v/>
       </c>
       <c r="R97" s="55">
-        <f>IF(R2&gt;=Assumptions!$B$53,(R96*Assumptions!$B$29*Assumptions!$B$30+R83*R85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$53,(R96*Assumptions!$B$29*Assumptions!$B$30+R83*R85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
         <v/>
       </c>
       <c r="S97" s="55">
-        <f>IF(S2&gt;=Assumptions!$B$53,(S96*Assumptions!$B$29*Assumptions!$B$30+S83*S85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$53,(S96*Assumptions!$B$29*Assumptions!$B$30+S83*S85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
         <v/>
       </c>
       <c r="T97" s="55">
-        <f>IF(T2&gt;=Assumptions!$B$53,(T96*Assumptions!$B$29*Assumptions!$B$30+T83*T85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$53,(T96*Assumptions!$B$29*Assumptions!$B$30+T83*T85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
         <v/>
       </c>
       <c r="U97" s="55">
-        <f>IF(U2&gt;=Assumptions!$B$53,(U96*Assumptions!$B$29*Assumptions!$B$30+U83*U85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$53,(U96*Assumptions!$B$29*Assumptions!$B$30+U83*U85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
         <v/>
       </c>
       <c r="V97" s="55">
-        <f>IF(V2&gt;=Assumptions!$B$53,(V96*Assumptions!$B$29*Assumptions!$B$30+V83*V85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$53,(V96*Assumptions!$B$29*Assumptions!$B$30+V83*V85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
         <v/>
       </c>
       <c r="W97" s="55">
-        <f>IF(W2&gt;=Assumptions!$B$53,(W96*Assumptions!$B$29*Assumptions!$B$30+W83*W85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$53,(W96*Assumptions!$B$29*Assumptions!$B$30+W83*W85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
         <v/>
       </c>
       <c r="X97" s="55">
-        <f>IF(X2&gt;=Assumptions!$B$53,(X96*Assumptions!$B$29*Assumptions!$B$30+X83*X85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$53,(X96*Assumptions!$B$29*Assumptions!$B$30+X83*X85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
         <v/>
       </c>
       <c r="Y97" s="55">
-        <f>IF(Y2&gt;=Assumptions!$B$53,(Y96*Assumptions!$B$29*Assumptions!$B$30+Y83*Y85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$53,(Y96*Assumptions!$B$29*Assumptions!$B$30+Y83*Y85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
         <v/>
       </c>
       <c r="Z97" s="55">
-        <f>IF(Z2&gt;=Assumptions!$B$53,(Z96*Assumptions!$B$29*Assumptions!$B$30+Z83*Z85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$53,(Z96*Assumptions!$B$29*Assumptions!$B$30+Z83*Z85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
         <v/>
       </c>
       <c r="AA97" s="55">
-        <f>IF(AA2&gt;=Assumptions!$B$53,(AA96*Assumptions!$B$29*Assumptions!$B$30+AA83*AA85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$53,(AA96*Assumptions!$B$29*Assumptions!$B$30+AA83*AA85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
         <v/>
       </c>
       <c r="AB97" s="55">
-        <f>IF(AB2&gt;=Assumptions!$B$53,(AB96*Assumptions!$B$29*Assumptions!$B$30+AB83*AB85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$53,(AB96*Assumptions!$B$29*Assumptions!$B$30+AB83*AB85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
         <v/>
       </c>
       <c r="AC97" s="55">
-        <f>IF(AC2&gt;=Assumptions!$B$53,(AC96*Assumptions!$B$29*Assumptions!$B$30+AC83*AC85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$53,(AC96*Assumptions!$B$29*Assumptions!$B$30+AC83*AC85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
         <v/>
       </c>
       <c r="AD97" s="55">
-        <f>IF(AD2&gt;=Assumptions!$B$53,(AD96*Assumptions!$B$29*Assumptions!$B$30+AD83*AD85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$53,(AD96*Assumptions!$B$29*Assumptions!$B$30+AD83*AD85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
         <v/>
       </c>
       <c r="AE97" s="55">
-        <f>IF(AE2&gt;=Assumptions!$B$53,(AE96*Assumptions!$B$29*Assumptions!$B$30+AE83*AE85*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$53,(AE96*Assumptions!$B$29*Assumptions!$B$30+AE83*AE85*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
         <v/>
       </c>
     </row>
@@ -18711,119 +18858,119 @@
         </is>
       </c>
       <c r="C111" s="55">
-        <f>IF(C2&gt;=Assumptions!$B$47,C107*Assumptions!$B$170*C7,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$47,C107*Assumptions!$B$173*C7,0)</f>
         <v/>
       </c>
       <c r="D111" s="55">
-        <f>IF(D2&gt;=Assumptions!$B$47,D107*Assumptions!$B$170*D7,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$47,D107*Assumptions!$B$173*D7,0)</f>
         <v/>
       </c>
       <c r="E111" s="55">
-        <f>IF(E2&gt;=Assumptions!$B$47,E107*Assumptions!$B$170*E7,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$47,E107*Assumptions!$B$173*E7,0)</f>
         <v/>
       </c>
       <c r="F111" s="55">
-        <f>IF(F2&gt;=Assumptions!$B$47,F107*Assumptions!$B$170*F7,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$47,F107*Assumptions!$B$173*F7,0)</f>
         <v/>
       </c>
       <c r="G111" s="55">
-        <f>IF(G2&gt;=Assumptions!$B$47,G107*Assumptions!$B$170*G7,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$47,G107*Assumptions!$B$173*G7,0)</f>
         <v/>
       </c>
       <c r="H111" s="55">
-        <f>IF(H2&gt;=Assumptions!$B$47,H107*Assumptions!$B$170*H7,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$47,H107*Assumptions!$B$173*H7,0)</f>
         <v/>
       </c>
       <c r="I111" s="55">
-        <f>IF(I2&gt;=Assumptions!$B$47,I107*Assumptions!$B$170*I7,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$47,I107*Assumptions!$B$173*I7,0)</f>
         <v/>
       </c>
       <c r="J111" s="55">
-        <f>IF(J2&gt;=Assumptions!$B$47,J107*Assumptions!$B$170*J7,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$47,J107*Assumptions!$B$173*J7,0)</f>
         <v/>
       </c>
       <c r="K111" s="55">
-        <f>IF(K2&gt;=Assumptions!$B$47,K107*Assumptions!$B$170*K7,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$47,K107*Assumptions!$B$173*K7,0)</f>
         <v/>
       </c>
       <c r="L111" s="55">
-        <f>IF(L2&gt;=Assumptions!$B$47,L107*Assumptions!$B$170*L7,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$47,L107*Assumptions!$B$173*L7,0)</f>
         <v/>
       </c>
       <c r="M111" s="55">
-        <f>IF(M2&gt;=Assumptions!$B$47,M107*Assumptions!$B$170*M7,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$47,M107*Assumptions!$B$173*M7,0)</f>
         <v/>
       </c>
       <c r="N111" s="55">
-        <f>IF(N2&gt;=Assumptions!$B$47,N107*Assumptions!$B$170*N7,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$47,N107*Assumptions!$B$173*N7,0)</f>
         <v/>
       </c>
       <c r="O111" s="55">
-        <f>IF(O2&gt;=Assumptions!$B$47,O107*Assumptions!$B$170*O7,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$47,O107*Assumptions!$B$173*O7,0)</f>
         <v/>
       </c>
       <c r="P111" s="55">
-        <f>IF(P2&gt;=Assumptions!$B$47,P107*Assumptions!$B$170*P7,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$47,P107*Assumptions!$B$173*P7,0)</f>
         <v/>
       </c>
       <c r="Q111" s="55">
-        <f>IF(Q2&gt;=Assumptions!$B$47,Q107*Assumptions!$B$170*Q7,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$47,Q107*Assumptions!$B$173*Q7,0)</f>
         <v/>
       </c>
       <c r="R111" s="55">
-        <f>IF(R2&gt;=Assumptions!$B$47,R107*Assumptions!$B$170*R7,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$47,R107*Assumptions!$B$173*R7,0)</f>
         <v/>
       </c>
       <c r="S111" s="55">
-        <f>IF(S2&gt;=Assumptions!$B$47,S107*Assumptions!$B$170*S7,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$47,S107*Assumptions!$B$173*S7,0)</f>
         <v/>
       </c>
       <c r="T111" s="55">
-        <f>IF(T2&gt;=Assumptions!$B$47,T107*Assumptions!$B$170*T7,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$47,T107*Assumptions!$B$173*T7,0)</f>
         <v/>
       </c>
       <c r="U111" s="55">
-        <f>IF(U2&gt;=Assumptions!$B$47,U107*Assumptions!$B$170*U7,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$47,U107*Assumptions!$B$173*U7,0)</f>
         <v/>
       </c>
       <c r="V111" s="55">
-        <f>IF(V2&gt;=Assumptions!$B$47,V107*Assumptions!$B$170*V7,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$47,V107*Assumptions!$B$173*V7,0)</f>
         <v/>
       </c>
       <c r="W111" s="55">
-        <f>IF(W2&gt;=Assumptions!$B$47,W107*Assumptions!$B$170*W7,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$47,W107*Assumptions!$B$173*W7,0)</f>
         <v/>
       </c>
       <c r="X111" s="55">
-        <f>IF(X2&gt;=Assumptions!$B$47,X107*Assumptions!$B$170*X7,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$47,X107*Assumptions!$B$173*X7,0)</f>
         <v/>
       </c>
       <c r="Y111" s="55">
-        <f>IF(Y2&gt;=Assumptions!$B$47,Y107*Assumptions!$B$170*Y7,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$47,Y107*Assumptions!$B$173*Y7,0)</f>
         <v/>
       </c>
       <c r="Z111" s="55">
-        <f>IF(Z2&gt;=Assumptions!$B$47,Z107*Assumptions!$B$170*Z7,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$47,Z107*Assumptions!$B$173*Z7,0)</f>
         <v/>
       </c>
       <c r="AA111" s="55">
-        <f>IF(AA2&gt;=Assumptions!$B$47,AA107*Assumptions!$B$170*AA7,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$47,AA107*Assumptions!$B$173*AA7,0)</f>
         <v/>
       </c>
       <c r="AB111" s="55">
-        <f>IF(AB2&gt;=Assumptions!$B$47,AB107*Assumptions!$B$170*AB7,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$47,AB107*Assumptions!$B$173*AB7,0)</f>
         <v/>
       </c>
       <c r="AC111" s="55">
-        <f>IF(AC2&gt;=Assumptions!$B$47,AC107*Assumptions!$B$170*AC7,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$47,AC107*Assumptions!$B$173*AC7,0)</f>
         <v/>
       </c>
       <c r="AD111" s="55">
-        <f>IF(AD2&gt;=Assumptions!$B$47,AD107*Assumptions!$B$170*AD7,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$47,AD107*Assumptions!$B$173*AD7,0)</f>
         <v/>
       </c>
       <c r="AE111" s="55">
-        <f>IF(AE2&gt;=Assumptions!$B$47,AE107*Assumptions!$B$170*AE7,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$47,AE107*Assumptions!$B$173*AE7,0)</f>
         <v/>
       </c>
     </row>
@@ -19735,119 +19882,119 @@
         </is>
       </c>
       <c r="C119" s="54">
-        <f>C107+C109*Assumptions!$B$172</f>
+        <f>C107+C109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="D119" s="54">
-        <f>D107+D109*Assumptions!$B$172</f>
+        <f>D107+D109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="E119" s="54">
-        <f>E107+E109*Assumptions!$B$172</f>
+        <f>E107+E109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="F119" s="54">
-        <f>F107+F109*Assumptions!$B$172</f>
+        <f>F107+F109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="G119" s="54">
-        <f>G107+G109*Assumptions!$B$172</f>
+        <f>G107+G109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="H119" s="54">
-        <f>H107+H109*Assumptions!$B$172</f>
+        <f>H107+H109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="I119" s="54">
-        <f>I107+I109*Assumptions!$B$172</f>
+        <f>I107+I109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="J119" s="54">
-        <f>J107+J109*Assumptions!$B$172</f>
+        <f>J107+J109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="K119" s="54">
-        <f>K107+K109*Assumptions!$B$172</f>
+        <f>K107+K109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="L119" s="54">
-        <f>L107+L109*Assumptions!$B$172</f>
+        <f>L107+L109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="M119" s="54">
-        <f>M107+M109*Assumptions!$B$172</f>
+        <f>M107+M109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="N119" s="54">
-        <f>N107+N109*Assumptions!$B$172</f>
+        <f>N107+N109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="O119" s="54">
-        <f>O107+O109*Assumptions!$B$172</f>
+        <f>O107+O109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="P119" s="54">
-        <f>P107+P109*Assumptions!$B$172</f>
+        <f>P107+P109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="Q119" s="54">
-        <f>Q107+Q109*Assumptions!$B$172</f>
+        <f>Q107+Q109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="R119" s="54">
-        <f>R107+R109*Assumptions!$B$172</f>
+        <f>R107+R109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="S119" s="54">
-        <f>S107+S109*Assumptions!$B$172</f>
+        <f>S107+S109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="T119" s="54">
-        <f>T107+T109*Assumptions!$B$172</f>
+        <f>T107+T109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="U119" s="54">
-        <f>U107+U109*Assumptions!$B$172</f>
+        <f>U107+U109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="V119" s="54">
-        <f>V107+V109*Assumptions!$B$172</f>
+        <f>V107+V109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="W119" s="54">
-        <f>W107+W109*Assumptions!$B$172</f>
+        <f>W107+W109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="X119" s="54">
-        <f>X107+X109*Assumptions!$B$172</f>
+        <f>X107+X109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="Y119" s="54">
-        <f>Y107+Y109*Assumptions!$B$172</f>
+        <f>Y107+Y109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="Z119" s="54">
-        <f>Z107+Z109*Assumptions!$B$172</f>
+        <f>Z107+Z109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AA119" s="54">
-        <f>AA107+AA109*Assumptions!$B$172</f>
+        <f>AA107+AA109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AB119" s="54">
-        <f>AB107+AB109*Assumptions!$B$172</f>
+        <f>AB107+AB109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AC119" s="54">
-        <f>AC107+AC109*Assumptions!$B$172</f>
+        <f>AC107+AC109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AD119" s="54">
-        <f>AD107+AD109*Assumptions!$B$172</f>
+        <f>AD107+AD109*Assumptions!$B$175</f>
         <v/>
       </c>
       <c r="AE119" s="54">
-        <f>AE107+AE109*Assumptions!$B$172</f>
+        <f>AE107+AE109*Assumptions!$B$175</f>
         <v/>
       </c>
     </row>
@@ -21271,119 +21418,119 @@
         </is>
       </c>
       <c r="C131" s="55">
-        <f>C126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>C126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="D131" s="55">
-        <f>D126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>D126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="E131" s="55">
-        <f>E126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>E126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="F131" s="55">
-        <f>F126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>F126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="G131" s="55">
-        <f>G126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>G126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="H131" s="55">
-        <f>H126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>H126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="I131" s="55">
-        <f>I126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>I126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="J131" s="55">
-        <f>J126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>J126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="K131" s="55">
-        <f>K126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>K126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="L131" s="55">
-        <f>L126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>L126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="M131" s="55">
-        <f>M126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>M126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="N131" s="55">
-        <f>N126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>N126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="O131" s="55">
-        <f>O126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>O126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="P131" s="55">
-        <f>P126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>P126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="Q131" s="55">
-        <f>Q126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>Q126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="R131" s="55">
-        <f>R126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>R126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="S131" s="55">
-        <f>S126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>S126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="T131" s="55">
-        <f>T126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>T126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="U131" s="55">
-        <f>U126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>U126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="V131" s="55">
-        <f>V126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>V126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="W131" s="55">
-        <f>W126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>W126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="X131" s="55">
-        <f>X126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>X126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="Y131" s="55">
-        <f>Y126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>Y126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="Z131" s="55">
-        <f>Z126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>Z126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AA131" s="55">
-        <f>AA126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AA126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AB131" s="55">
-        <f>AB126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AB126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AC131" s="55">
-        <f>AC126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AC126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AD131" s="55">
-        <f>AD126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AD126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
       <c r="AE131" s="55">
-        <f>AE126*IF(Assumptions!$B$171=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
+        <f>AE126*IF(Assumptions!$B$174=1,MIN(Assumptions!$B$14,1%),Assumptions!$B$14)*(1-Assumptions!$B$142)</f>
         <v/>
       </c>
     </row>
@@ -21655,119 +21802,119 @@
         </is>
       </c>
       <c r="C134" s="55">
-        <f>IF(C2&gt;=Assumptions!$B$53,C121*C122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$53,C121*C122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="D134" s="55">
-        <f>IF(D2&gt;=Assumptions!$B$53,D121*D122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$53,D121*D122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="E134" s="55">
-        <f>IF(E2&gt;=Assumptions!$B$53,E121*E122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$53,E121*E122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="F134" s="55">
-        <f>IF(F2&gt;=Assumptions!$B$53,F121*F122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$53,F121*F122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="G134" s="55">
-        <f>IF(G2&gt;=Assumptions!$B$53,G121*G122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$53,G121*G122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="H134" s="55">
-        <f>IF(H2&gt;=Assumptions!$B$53,H121*H122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$53,H121*H122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="I134" s="55">
-        <f>IF(I2&gt;=Assumptions!$B$53,I121*I122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$53,I121*I122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="J134" s="55">
-        <f>IF(J2&gt;=Assumptions!$B$53,J121*J122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$53,J121*J122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="K134" s="55">
-        <f>IF(K2&gt;=Assumptions!$B$53,K121*K122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$53,K121*K122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="L134" s="55">
-        <f>IF(L2&gt;=Assumptions!$B$53,L121*L122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$53,L121*L122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="M134" s="55">
-        <f>IF(M2&gt;=Assumptions!$B$53,M121*M122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$53,M121*M122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="N134" s="55">
-        <f>IF(N2&gt;=Assumptions!$B$53,N121*N122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$53,N121*N122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="O134" s="55">
-        <f>IF(O2&gt;=Assumptions!$B$53,O121*O122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$53,O121*O122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="P134" s="55">
-        <f>IF(P2&gt;=Assumptions!$B$53,P121*P122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$53,P121*P122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="Q134" s="55">
-        <f>IF(Q2&gt;=Assumptions!$B$53,Q121*Q122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$53,Q121*Q122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="R134" s="55">
-        <f>IF(R2&gt;=Assumptions!$B$53,R121*R122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$53,R121*R122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="S134" s="55">
-        <f>IF(S2&gt;=Assumptions!$B$53,S121*S122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$53,S121*S122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="T134" s="55">
-        <f>IF(T2&gt;=Assumptions!$B$53,T121*T122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$53,T121*T122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="U134" s="55">
-        <f>IF(U2&gt;=Assumptions!$B$53,U121*U122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$53,U121*U122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="V134" s="55">
-        <f>IF(V2&gt;=Assumptions!$B$53,V121*V122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$53,V121*V122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="W134" s="55">
-        <f>IF(W2&gt;=Assumptions!$B$53,W121*W122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$53,W121*W122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="X134" s="55">
-        <f>IF(X2&gt;=Assumptions!$B$53,X121*X122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$53,X121*X122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="Y134" s="55">
-        <f>IF(Y2&gt;=Assumptions!$B$53,Y121*Y122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$53,Y121*Y122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="Z134" s="55">
-        <f>IF(Z2&gt;=Assumptions!$B$53,Z121*Z122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$53,Z121*Z122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AA134" s="55">
-        <f>IF(AA2&gt;=Assumptions!$B$53,AA121*AA122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$53,AA121*AA122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AB134" s="55">
-        <f>IF(AB2&gt;=Assumptions!$B$53,AB121*AB122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$53,AB121*AB122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AC134" s="55">
-        <f>IF(AC2&gt;=Assumptions!$B$53,AC121*AC122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$53,AC121*AC122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AD134" s="55">
-        <f>IF(AD2&gt;=Assumptions!$B$53,AD121*AD122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$53,AD121*AD122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
       <c r="AE134" s="55">
-        <f>IF(AE2&gt;=Assumptions!$B$53,AE121*AE122*(1-Assumptions!$B$171)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$53,AE121*AE122*(1-Assumptions!$B$174)*Assumptions!$B$156*Assumptions!$B$157,0)</f>
         <v/>
       </c>
     </row>
@@ -21783,119 +21930,119 @@
         </is>
       </c>
       <c r="C135" s="55">
-        <f>IF(C2&gt;=Assumptions!$B$53,(C134*Assumptions!$B$29*Assumptions!$B$30+C121*C123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$53,(C134*Assumptions!$B$29*Assumptions!$B$30+C121*C123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*C7/12,0)</f>
         <v/>
       </c>
       <c r="D135" s="55">
-        <f>IF(D2&gt;=Assumptions!$B$53,(D134*Assumptions!$B$29*Assumptions!$B$30+D121*D123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$53,(D134*Assumptions!$B$29*Assumptions!$B$30+D121*D123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*D7/12,0)</f>
         <v/>
       </c>
       <c r="E135" s="55">
-        <f>IF(E2&gt;=Assumptions!$B$53,(E134*Assumptions!$B$29*Assumptions!$B$30+E121*E123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$53,(E134*Assumptions!$B$29*Assumptions!$B$30+E121*E123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*E7/12,0)</f>
         <v/>
       </c>
       <c r="F135" s="55">
-        <f>IF(F2&gt;=Assumptions!$B$53,(F134*Assumptions!$B$29*Assumptions!$B$30+F121*F123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$53,(F134*Assumptions!$B$29*Assumptions!$B$30+F121*F123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*F7/12,0)</f>
         <v/>
       </c>
       <c r="G135" s="55">
-        <f>IF(G2&gt;=Assumptions!$B$53,(G134*Assumptions!$B$29*Assumptions!$B$30+G121*G123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$53,(G134*Assumptions!$B$29*Assumptions!$B$30+G121*G123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*G7/12,0)</f>
         <v/>
       </c>
       <c r="H135" s="55">
-        <f>IF(H2&gt;=Assumptions!$B$53,(H134*Assumptions!$B$29*Assumptions!$B$30+H121*H123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$53,(H134*Assumptions!$B$29*Assumptions!$B$30+H121*H123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*H7/12,0)</f>
         <v/>
       </c>
       <c r="I135" s="55">
-        <f>IF(I2&gt;=Assumptions!$B$53,(I134*Assumptions!$B$29*Assumptions!$B$30+I121*I123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$53,(I134*Assumptions!$B$29*Assumptions!$B$30+I121*I123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*I7/12,0)</f>
         <v/>
       </c>
       <c r="J135" s="55">
-        <f>IF(J2&gt;=Assumptions!$B$53,(J134*Assumptions!$B$29*Assumptions!$B$30+J121*J123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$53,(J134*Assumptions!$B$29*Assumptions!$B$30+J121*J123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*J7/12,0)</f>
         <v/>
       </c>
       <c r="K135" s="55">
-        <f>IF(K2&gt;=Assumptions!$B$53,(K134*Assumptions!$B$29*Assumptions!$B$30+K121*K123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$53,(K134*Assumptions!$B$29*Assumptions!$B$30+K121*K123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*K7/12,0)</f>
         <v/>
       </c>
       <c r="L135" s="55">
-        <f>IF(L2&gt;=Assumptions!$B$53,(L134*Assumptions!$B$29*Assumptions!$B$30+L121*L123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$53,(L134*Assumptions!$B$29*Assumptions!$B$30+L121*L123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*L7/12,0)</f>
         <v/>
       </c>
       <c r="M135" s="55">
-        <f>IF(M2&gt;=Assumptions!$B$53,(M134*Assumptions!$B$29*Assumptions!$B$30+M121*M123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$53,(M134*Assumptions!$B$29*Assumptions!$B$30+M121*M123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*M7/12,0)</f>
         <v/>
       </c>
       <c r="N135" s="55">
-        <f>IF(N2&gt;=Assumptions!$B$53,(N134*Assumptions!$B$29*Assumptions!$B$30+N121*N123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$53,(N134*Assumptions!$B$29*Assumptions!$B$30+N121*N123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*N7/12,0)</f>
         <v/>
       </c>
       <c r="O135" s="55">
-        <f>IF(O2&gt;=Assumptions!$B$53,(O134*Assumptions!$B$29*Assumptions!$B$30+O121*O123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$53,(O134*Assumptions!$B$29*Assumptions!$B$30+O121*O123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*O7/12,0)</f>
         <v/>
       </c>
       <c r="P135" s="55">
-        <f>IF(P2&gt;=Assumptions!$B$53,(P134*Assumptions!$B$29*Assumptions!$B$30+P121*P123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$53,(P134*Assumptions!$B$29*Assumptions!$B$30+P121*P123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*P7/12,0)</f>
         <v/>
       </c>
       <c r="Q135" s="55">
-        <f>IF(Q2&gt;=Assumptions!$B$53,(Q134*Assumptions!$B$29*Assumptions!$B$30+Q121*Q123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$53,(Q134*Assumptions!$B$29*Assumptions!$B$30+Q121*Q123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Q7/12,0)</f>
         <v/>
       </c>
       <c r="R135" s="55">
-        <f>IF(R2&gt;=Assumptions!$B$53,(R134*Assumptions!$B$29*Assumptions!$B$30+R121*R123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$53,(R134*Assumptions!$B$29*Assumptions!$B$30+R121*R123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*R7/12,0)</f>
         <v/>
       </c>
       <c r="S135" s="55">
-        <f>IF(S2&gt;=Assumptions!$B$53,(S134*Assumptions!$B$29*Assumptions!$B$30+S121*S123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$53,(S134*Assumptions!$B$29*Assumptions!$B$30+S121*S123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*S7/12,0)</f>
         <v/>
       </c>
       <c r="T135" s="55">
-        <f>IF(T2&gt;=Assumptions!$B$53,(T134*Assumptions!$B$29*Assumptions!$B$30+T121*T123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$53,(T134*Assumptions!$B$29*Assumptions!$B$30+T121*T123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*T7/12,0)</f>
         <v/>
       </c>
       <c r="U135" s="55">
-        <f>IF(U2&gt;=Assumptions!$B$53,(U134*Assumptions!$B$29*Assumptions!$B$30+U121*U123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$53,(U134*Assumptions!$B$29*Assumptions!$B$30+U121*U123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*U7/12,0)</f>
         <v/>
       </c>
       <c r="V135" s="55">
-        <f>IF(V2&gt;=Assumptions!$B$53,(V134*Assumptions!$B$29*Assumptions!$B$30+V121*V123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$53,(V134*Assumptions!$B$29*Assumptions!$B$30+V121*V123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*V7/12,0)</f>
         <v/>
       </c>
       <c r="W135" s="55">
-        <f>IF(W2&gt;=Assumptions!$B$53,(W134*Assumptions!$B$29*Assumptions!$B$30+W121*W123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$53,(W134*Assumptions!$B$29*Assumptions!$B$30+W121*W123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*W7/12,0)</f>
         <v/>
       </c>
       <c r="X135" s="55">
-        <f>IF(X2&gt;=Assumptions!$B$53,(X134*Assumptions!$B$29*Assumptions!$B$30+X121*X123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$53,(X134*Assumptions!$B$29*Assumptions!$B$30+X121*X123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*X7/12,0)</f>
         <v/>
       </c>
       <c r="Y135" s="55">
-        <f>IF(Y2&gt;=Assumptions!$B$53,(Y134*Assumptions!$B$29*Assumptions!$B$30+Y121*Y123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$53,(Y134*Assumptions!$B$29*Assumptions!$B$30+Y121*Y123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Y7/12,0)</f>
         <v/>
       </c>
       <c r="Z135" s="55">
-        <f>IF(Z2&gt;=Assumptions!$B$53,(Z134*Assumptions!$B$29*Assumptions!$B$30+Z121*Z123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$53,(Z134*Assumptions!$B$29*Assumptions!$B$30+Z121*Z123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*Z7/12,0)</f>
         <v/>
       </c>
       <c r="AA135" s="55">
-        <f>IF(AA2&gt;=Assumptions!$B$53,(AA134*Assumptions!$B$29*Assumptions!$B$30+AA121*AA123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$53,(AA134*Assumptions!$B$29*Assumptions!$B$30+AA121*AA123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AA7/12,0)</f>
         <v/>
       </c>
       <c r="AB135" s="55">
-        <f>IF(AB2&gt;=Assumptions!$B$53,(AB134*Assumptions!$B$29*Assumptions!$B$30+AB121*AB123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$53,(AB134*Assumptions!$B$29*Assumptions!$B$30+AB121*AB123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AB7/12,0)</f>
         <v/>
       </c>
       <c r="AC135" s="55">
-        <f>IF(AC2&gt;=Assumptions!$B$53,(AC134*Assumptions!$B$29*Assumptions!$B$30+AC121*AC123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$53,(AC134*Assumptions!$B$29*Assumptions!$B$30+AC121*AC123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AC7/12,0)</f>
         <v/>
       </c>
       <c r="AD135" s="55">
-        <f>IF(AD2&gt;=Assumptions!$B$53,(AD134*Assumptions!$B$29*Assumptions!$B$30+AD121*AD123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$53,(AD134*Assumptions!$B$29*Assumptions!$B$30+AD121*AD123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AD7/12,0)</f>
         <v/>
       </c>
       <c r="AE135" s="55">
-        <f>IF(AE2&gt;=Assumptions!$B$53,(AE134*Assumptions!$B$29*Assumptions!$B$30+AE121*AE123*(1-Assumptions!$B$171)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$53,(AE134*Assumptions!$B$29*Assumptions!$B$30+AE121*AE123*(1-Assumptions!$B$174)*Assumptions!$B$27*Assumptions!$B$28)*AE7/12,0)</f>
         <v/>
       </c>
     </row>
@@ -22204,119 +22351,119 @@
         </is>
       </c>
       <c r="C140" s="58">
-        <f>IF(C2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,C5)*Assumptions!$B$167,0)</f>
+        <f>IF(C2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,C5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="D140" s="58">
-        <f>IF(D2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,D5)*Assumptions!$B$167,0)</f>
+        <f>IF(D2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,D5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="E140" s="58">
-        <f>IF(E2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,E5)*Assumptions!$B$167,0)</f>
+        <f>IF(E2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,E5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="F140" s="58">
-        <f>IF(F2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,F5)*Assumptions!$B$167,0)</f>
+        <f>IF(F2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,F5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="G140" s="58">
-        <f>IF(G2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,G5)*Assumptions!$B$167,0)</f>
+        <f>IF(G2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,G5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="H140" s="58">
-        <f>IF(H2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,H5)*Assumptions!$B$167,0)</f>
+        <f>IF(H2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,H5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="I140" s="58">
-        <f>IF(I2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,I5)*Assumptions!$B$167,0)</f>
+        <f>IF(I2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,I5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="J140" s="58">
-        <f>IF(J2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,J5)*Assumptions!$B$167,0)</f>
+        <f>IF(J2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,J5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="K140" s="58">
-        <f>IF(K2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,K5)*Assumptions!$B$167,0)</f>
+        <f>IF(K2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,K5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="L140" s="58">
-        <f>IF(L2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,L5)*Assumptions!$B$167,0)</f>
+        <f>IF(L2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,L5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="M140" s="58">
-        <f>IF(M2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,M5)*Assumptions!$B$167,0)</f>
+        <f>IF(M2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,M5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="N140" s="58">
-        <f>IF(N2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,N5)*Assumptions!$B$167,0)</f>
+        <f>IF(N2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,N5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="O140" s="58">
-        <f>IF(O2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,O5)*Assumptions!$B$167,0)</f>
+        <f>IF(O2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,O5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="P140" s="58">
-        <f>IF(P2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,P5)*Assumptions!$B$167,0)</f>
+        <f>IF(P2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,P5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="Q140" s="58">
-        <f>IF(Q2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,Q5)*Assumptions!$B$167,0)</f>
+        <f>IF(Q2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,Q5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="R140" s="58">
-        <f>IF(R2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,R5)*Assumptions!$B$167,0)</f>
+        <f>IF(R2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,R5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="S140" s="58">
-        <f>IF(S2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,S5)*Assumptions!$B$167,0)</f>
+        <f>IF(S2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,S5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="T140" s="58">
-        <f>IF(T2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,T5)*Assumptions!$B$167,0)</f>
+        <f>IF(T2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,T5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="U140" s="58">
-        <f>IF(U2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,U5)*Assumptions!$B$167,0)</f>
+        <f>IF(U2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,U5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="V140" s="58">
-        <f>IF(V2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,V5)*Assumptions!$B$167,0)</f>
+        <f>IF(V2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,V5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="W140" s="58">
-        <f>IF(W2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,W5)*Assumptions!$B$167,0)</f>
+        <f>IF(W2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,W5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="X140" s="58">
-        <f>IF(X2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,X5)*Assumptions!$B$167,0)</f>
+        <f>IF(X2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,X5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="Y140" s="58">
-        <f>IF(Y2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,Y5)*Assumptions!$B$167,0)</f>
+        <f>IF(Y2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,Y5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="Z140" s="58">
-        <f>IF(Z2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,Z5)*Assumptions!$B$167,0)</f>
+        <f>IF(Z2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,Z5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="AA140" s="58">
-        <f>IF(AA2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AA5)*Assumptions!$B$167,0)</f>
+        <f>IF(AA2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AA5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="AB140" s="58">
-        <f>IF(AB2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AB5)*Assumptions!$B$167,0)</f>
+        <f>IF(AB2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AB5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="AC140" s="58">
-        <f>IF(AC2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AC5)*Assumptions!$B$167,0)</f>
+        <f>IF(AC2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AC5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="AD140" s="58">
-        <f>IF(AD2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AD5)*Assumptions!$B$167,0)</f>
+        <f>IF(AD2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AD5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
       <c r="AE140" s="58">
-        <f>IF(AE2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AE5)*Assumptions!$B$167,0)</f>
+        <f>IF(AE2&gt;=Assumptions!$B$54,INDEX(Assumptions!$B$160:$B$166,AE5)*Assumptions!$B$170,0)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LOWERED 2026-08-21 from 0.20. ⚠ THE UNIT ALSO CHANGED, AND THAT MATTERS: it is now the share of NEW customers who take the plan when they join, feeding a SUBSCRIBER BALANCE that then churns - not a standing share of the whole book that could never fall. The steady-state share of paying customers holding a plan therefore lands BELOW this number. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on; 20% was high for an OPTIONAL PAID extra on a savings product, where low single digits to low teens is the normal range. ASSUMPTION.</t>
+          <t>SET AT 0.15 on 2026-08-21, client instruction - the same day it came DOWN from 0.20 to 0.08, so it has landed close to where it started. What has genuinely changed is not the number but the STRUCTURE. ⚠ THE UNIT ALSO CHANGED, AND THAT MATTERS: it is now the share of NEW customers who take the plan when they join, feeding a SUBSCRIBER BALANCE that then churns - not a standing share of the whole book that could never fall. The steady-state share of paying customers holding a plan therefore lands BELOW this number. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on; 20% is at the top of the normal range for an OPTIONAL PAID extra on a savings product, which is low single digits to low teens. ⚠ IT IS NOT EQUIVALENT TO THE OLD 20% AND SHOULD NOT BE READ AS A PARTIAL REVERSAL: 20% was a permanent share of the whole book that could never decay, while 15% applies once, on joining, to a balance that then churns at ~7.1% a month. The standing share of paying customers holding a plan settles near 10.5%, not 15%. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -5980,14 +5980,14 @@
         <v/>
       </c>
       <c r="C64" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D64" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E64" s="19" t="n">
         <v>0.08</v>
       </c>
-      <c r="D64" s="19" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E64" s="19" t="n">
-        <v>0.04</v>
-      </c>
       <c r="F64" s="23" t="inlineStr">
         <is>
           <t>% of NEW customers</t>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>LOWERED 2026-08-21 from 0.20. ⚠ THE UNIT ALSO CHANGED, AND THAT MATTERS: it is now the share of NEW customers who take the plan when they join, feeding a SUBSCRIBER BALANCE that then churns - not a standing share of the whole book that could never fall. The steady-state share of paying customers holding a plan therefore lands BELOW this number. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on; 20% was high for an OPTIONAL PAID extra on a savings product, where low single digits to low teens is the normal range. ASSUMPTION.</t>
+          <t>SET AT 0.15 on 2026-08-21, client instruction - the same day it came DOWN from 0.20 to 0.08, so it has landed close to where it started. What has genuinely changed is not the number but the STRUCTURE. ⚠ THE UNIT ALSO CHANGED, AND THAT MATTERS: it is now the share of NEW customers who take the plan when they join, feeding a SUBSCRIBER BALANCE that then churns - not a standing share of the whole book that could never fall. The steady-state share of paying customers holding a plan therefore lands BELOW this number. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on; 20% is at the top of the normal range for an OPTIONAL PAID extra on a savings product, which is low single digits to low teens. ⚠ IT IS NOT EQUIVALENT TO THE OLD 20% AND SHOULD NOT BE READ AS A PARTIAL REVERSAL: 20% was a permanent share of the whole book that could never decay, while 15% applies once, on joining, to a balance that then churns at ~7.1% a month. The standing share of paying customers holding a plan settles near 10.5%, not 15%. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on. ASSUMPTION.</t>
         </is>
       </c>
     </row>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
@@ -1381,7 +1381,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>RE-PRICED 2026-08-21 from USD 120/yr. THE OLD PRICE WAS ABOVE TRUST &amp; WILL'S PREMIUM US MEMBERSHIP (USD 49/yr) AND WAS 33% OF EVERYTHING THE CUSTOMER SAVES IN A YEAR - a USD 30/month saver puts away USD 360, and we were charging 120 of it. THE INDUSTRY MODEL IS A ONE-OFF FEE PLUS A SMALL ANNUAL UPDATE LAYER, and it is the annual layer this row represents: Trust &amp; Will USD 199 one-off + USD 49/yr; Farewill GBP 100 + GBP 10/yr; Epilogue C$139 with NO subscription at all; other platforms renew updates at ~C$4.50/yr. Formal UAE will registration is a different product entirely and one-off - DIFC AED 10,000 single / 15,000 mirror, Abu Dhabi Civil Court AED 950 as the cheapest formal route. Indian online wills run INR 500-4,000 basic. Family add-ons on finance apps are usually BUNDLED FREE; where charged it is USD 5-15/month for a WHOLE HOUSEHOLD (Monarch 99.99/yr, Zeta 59.99/yr, Greenlight 5.99/mo). SET AT USD 50/yr, client instruction 2026-08-21. That is essentially TRUST &amp; WILL'S USD 49/yr MEMBERSHIP - a defensible anchor in that it matches the best-known product in the category, but ⚠ NOTE WHOSE PRODUCT IT IS: Trust &amp; Will sells to US customers who paid 199-599 up front for an estate plan, not to a migrant worker saving USD 30 a month. At 50 the plan is 14% OF EVERYTHING THE CUSTOMER SAVES IN A YEAR, against 10% at 36 and 33% at the original 120. It is no longer absurd, but it is priced at a developed-market benchmark for an emerging-market customer, and that is the line an adviser would push on. ⚠ A ONE-OFF SETUP FEE IS NOT MODELLED - if the client wants the full industry structure, that is a second row, not a bigger number here. CITED comparators, ASSUMPTION on the point in the range.</t>
+          <t>RE-PRICED 2026-08-21 from USD 120/yr. THE OLD PRICE WAS ABOVE TRUST &amp; WILL'S PREMIUM US MEMBERSHIP (USD 49/yr) AND WAS 33% OF EVERYTHING THE CUSTOMER SAVES IN A YEAR - a USD 30/month saver puts away USD 360, and we were charging 120 of it. THE INDUSTRY MODEL IS A ONE-OFF FEE PLUS A SMALL ANNUAL UPDATE LAYER, and it is the annual layer this row represents: Trust &amp; Will USD 199 one-off + USD 49/yr; Farewill GBP 100 + GBP 10/yr; Epilogue C$139 with NO subscription at all; other platforms renew updates at ~C$4.50/yr. Formal UAE will registration is a different product entirely and one-off - DIFC AED 10,000 single / 15,000 mirror, Abu Dhabi Civil Court AED 950 as the cheapest formal route. Indian online wills run INR 500-4,000 basic. Family add-ons on finance apps are usually BUNDLED FREE; where charged it is USD 5-15/month for a WHOLE HOUSEHOLD (Monarch 99.99/yr, Zeta 59.99/yr, Greenlight 5.99/mo). SET AT USD 50/yr, client instruction 2026-08-21. That is essentially TRUST &amp; WILL'S USD 49/yr MEMBERSHIP - a defensible anchor in that it matches the best-known product in the category, but NOTE WHOSE PRODUCT IT IS: Trust &amp; Will sells to US customers who paid 199-599 up front for an estate plan, not to a migrant worker saving USD 30 a month. At 50 the plan is 14% OF EVERYTHING THE CUSTOMER SAVES IN A YEAR, against 10% at 36 and 33% at the original 120. It is no longer absurd, but it is priced at a developed-market benchmark for an emerging-market customer, and that is the line an adviser would push on. A ONE-OFF SETUP FEE IS NOT MODELLED - if the client wants the full industry structure, that is a second row, not a bigger number here. CITED comparators, ASSUMPTION on the point in the range.</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ADDED 2026-08-21, client instruction. Charged per named beneficiary BEYOND THE FIRST, which the plan includes - the standard shape for this kind of add-on, and the reason the formula carries a MAX(0, n-1) rather than charging every beneficiary. ⚠ NO COMPARABLE EXISTS: will services price PER WILL, not per beneficiary. DIFC charges more for a MIRROR will (two people) and more again for guardianship, but nobody publishes a per-beneficiary tariff. So this is priced on COST RECOVERY, which is the defensible basis available: every named beneficiary needs identity capture and AML screening, and Sumsub screening already sits in this model at ~USD 1.85 per check in the redemption cost memo. USD 6/yr covers that with margin without becoming a second subscription. DELIBERATELY SMALL. At 1.5 chargeable beneficiaries it adds USD 9/yr to a USD 50 plan - an 18% uplift on a stream worth ~3.5% of revenue, so it cannot move the model and should not be tuned to try. ASSUMPTION on a cost-recovery basis.</t>
+          <t>ADDED 2026-08-21, client instruction. Charged per named beneficiary BEYOND THE FIRST, which the plan includes - the standard shape for this kind of add-on, and the reason the formula carries a MAX(0, n-1) rather than charging every beneficiary. NO COMPARABLE EXISTS: will services price PER WILL, not per beneficiary. DIFC charges more for a MIRROR will (two people) and more again for guardianship, but nobody publishes a per-beneficiary tariff. So this is priced on COST RECOVERY, which is the defensible basis available: every named beneficiary needs identity capture and AML screening, and Sumsub screening already sits in this model at ~USD 1.85 per check in the redemption cost memo. USD 6/yr covers that with margin without becoming a second subscription. DELIBERATELY SMALL. At 1.5 chargeable beneficiaries it adds USD 9/yr to a USD 50 plan - an 18% uplift on a stream worth ~3.5% of revenue, so it cannot move the model and should not be tuned to try. ASSUMPTION on a cost-recovery basis.</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>⚠ INFERRED - THE WEAKEST OF THE THREE. No GCC platform outside the UAE publishes an average ticket; this is a CONFIRMED NEGATIVE, not a gap in the search. Taken as the UAE figure scaled by the regional income gap (SIP 26.00/33.60 = 0.77x). Do not present this as sourced.</t>
+          <t>INFERRED - THE WEAKEST OF THE THREE. No GCC platform outside the UAE publishes an average ticket; this is a CONFIRMED NEGATIVE, not a gap in the search. Taken as the UAE figure scaled by the regional income gap (SIP 26.00/33.60 = 0.77x). Do not present this as sourced.</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OBSERVED, PROXY. Augmont: average festive-season purchase Rs 3,300, Times of India, Sep 2025 (= ~USD 38). Augmont is a licensed refiner and digital gold platform; a festive lump is structurally the same act as a spot purchase, which is why it is preferred to the alternatives. REJECTED: SafeGold Rs 5,000-8,000 (May 2026) - that book skews to investors, while Aurumix's Indian customer saves USD 30 a month; MMTC-PAMP Rs 800-1,200 - closer to routine micro-saving than a lump; Rs 230 industry-wide - a LinkedIn aggregate, not a citable source. ⚠ WEAKER THAN THE UAE FIGURE: right country and right behaviour, but Aurumix's Indian customer is poorer than Augmont's average buyer, so 40 may be generous.</t>
+          <t>OBSERVED, PROXY. Augmont: average festive-season purchase Rs 3,300, Times of India, Sep 2025 (= ~USD 38). Augmont is a licensed refiner and digital gold platform; a festive lump is structurally the same act as a spot purchase, which is why it is preferred to the alternatives. REJECTED: SafeGold Rs 5,000-8,000 (May 2026) - that book skews to investors, while Aurumix's Indian customer saves USD 30 a month; MMTC-PAMP Rs 800-1,200 - closer to routine micro-saving than a lump; Rs 230 industry-wide - a LinkedIn aggregate, not a citable source. WEAKER THAN THE UAE FIGURE: right country and right behaviour, but Aurumix's Indian customer is poorer than Augmont's average buyer, so 40 may be generous.</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Share of paying customers who make ANY spot purchase in a year - NOT a monthly rate, and NOT how often a buyer buys (that is the separate frequency input). Set on the affordability ratio above: the spot ticket as a multiple of the same customer's monthly SIP. ⚠ NO PUBLISHED BENCHMARK EXISTS - confirmed negative. ⚠ KNOWN SIMPLIFICATION: v2.6 applied a TENURE UPLIFT here ('a 3-year account is ~2x as likely to buy spot as a 6-month account') which v3.0 dropped, so this is flat from day one and OVERSTATES SPOT IN THE EARLY YEARS, when nearly every account is young. Restore the uplift in the Phase 5 simulation. ASSUMPTION, structured on an observable driver.</t>
+          <t>Share of paying customers who make ANY spot purchase in a year - NOT a monthly rate, and NOT how often a buyer buys (that is the separate frequency input). Set on the affordability ratio above: the spot ticket as a multiple of the same customer's monthly SIP. NO PUBLISHED BENCHMARK EXISTS - confirmed negative. KNOWN SIMPLIFICATION: v2.6 applied a TENURE UPLIFT here ('a 3-year account is ~2x as likely to buy spot as a 6-month account') which v3.0 dropped, so this is flat from day one and OVERSTATES SPOT IN THE EARLY YEARS, when nearly every account is young. Restore the uplift in the Phase 5 simulation. ASSUMPTION, structured on an observable driver.</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Share of paying customers who make ANY spot purchase in a year - NOT a monthly rate, and NOT how often a buyer buys (that is the separate frequency input). Set on the affordability ratio above: the spot ticket as a multiple of the same customer's monthly SIP. ⚠ NO PUBLISHED BENCHMARK EXISTS - confirmed negative. ⚠ KNOWN SIMPLIFICATION: v2.6 applied a TENURE UPLIFT here ('a 3-year account is ~2x as likely to buy spot as a 6-month account') which v3.0 dropped, so this is flat from day one and OVERSTATES SPOT IN THE EARLY YEARS, when nearly every account is young. Restore the uplift in the Phase 5 simulation. ASSUMPTION, structured on an observable driver.</t>
+          <t>Share of paying customers who make ANY spot purchase in a year - NOT a monthly rate, and NOT how often a buyer buys (that is the separate frequency input). Set on the affordability ratio above: the spot ticket as a multiple of the same customer's monthly SIP. NO PUBLISHED BENCHMARK EXISTS - confirmed negative. KNOWN SIMPLIFICATION: v2.6 applied a TENURE UPLIFT here ('a 3-year account is ~2x as likely to buy spot as a 6-month account') which v3.0 dropped, so this is flat from day one and OVERSTATES SPOT IN THE EARLY YEARS, when nearly every account is young. Restore the uplift in the Phase 5 simulation. ASSUMPTION, structured on an observable driver.</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Share of paying customers who make ANY spot purchase in a year - NOT a monthly rate, and NOT how often a buyer buys (that is the separate frequency input). Set on the affordability ratio above: the spot ticket as a multiple of the same customer's monthly SIP. ⚠ NO PUBLISHED BENCHMARK EXISTS - confirmed negative. ⚠ KNOWN SIMPLIFICATION: v2.6 applied a TENURE UPLIFT here ('a 3-year account is ~2x as likely to buy spot as a 6-month account') which v3.0 dropped, so this is flat from day one and OVERSTATES SPOT IN THE EARLY YEARS, when nearly every account is young. Restore the uplift in the Phase 5 simulation. ASSUMPTION, structured on an observable driver.</t>
+          <t>Share of paying customers who make ANY spot purchase in a year - NOT a monthly rate, and NOT how often a buyer buys (that is the separate frequency input). Set on the affordability ratio above: the spot ticket as a multiple of the same customer's monthly SIP. NO PUBLISHED BENCHMARK EXISTS - confirmed negative. KNOWN SIMPLIFICATION: v2.6 applied a TENURE UPLIFT here ('a 3-year account is ~2x as likely to buy spot as a 6-month account') which v3.0 dropped, so this is flat from day one and OVERSTATES SPOT IN THE EARLY YEARS, when nearly every account is young. Restore the uplift in the Phase 5 simulation. ASSUMPTION, structured on an observable driver.</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>RE-CUT 2026-08-20 from 4.20: the outbound bank transfer fee (USD 1.00-2.50) is REMOVED - that is the customer's cost to bear, not Aurumix's. What remains is Sumsub AML re-screening at 1.85 plus operational handling at ~1.35, both of which Aurumix genuinely pays. ⚠ NOT IN THE REVENUE MODEL: redemption is a COST and arrives with the cost build. This row is carried so the driver is documented and the unit rate already agreed. THE FINDING IT CARRIES IS UNCHANGED AND IS THE POINT - VARA Annex 2 III.E.4 forbids charging ANY fee on redemption, verified verbatim at primary source, so the cost is 100% absorbed, no offsetting revenue exists or can exist, and THERE CAN NEVER BE AN EXIT FEE. DERIVED.</t>
+          <t>RE-CUT 2026-08-20 from 4.20: the outbound bank transfer fee (USD 1.00-2.50) is REMOVED - that is the customer's cost to bear, not Aurumix's. What remains is Sumsub AML re-screening at 1.85 plus operational handling at ~1.35, both of which Aurumix genuinely pays. NOT IN THE REVENUE MODEL: redemption is a COST and arrives with the cost build. This row is carried so the driver is documented and the unit rate already agreed. THE FINDING IT CARRIES IS UNCHANGED AND IS THE POINT - VARA Annex 2 III.E.4 forbids charging ANY fee on redemption, verified verbatim at primary source, so the cost is 100% absorbed, no offsetting revenue exists or can exist, and THERE CAN NEVER BE AN EXIT FEE. DERIVED.</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>M1 (client decision 2026-08-20, moved earlier from M13). The India payment route is ASSUMED SOLVED in this model. ⚠ That is a live assumption, not a settled fact - if the route is not solved, this region does not open at all and roughly a quarter of terminal revenue goes with it.</t>
+          <t>M1 (client decision 2026-08-20, moved earlier from M13). The India payment route is ASSUMED SOLVED in this model. That is a live assumption, not a settled fact - if the route is not solved, this region does not open at all and roughly a quarter of terminal revenue goes with it.</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>UPDATED 2026-08-20. UAE-Indian is 4.36m - the Indian consulate's official count at December 2024, also given as 4.3m by the Embassy of India. The brief carried 3.5m, which is roughly a 2021-22 vintage: the community was 3.89m at December 2023 and 4.36m a year later, having doubled from 2.2m over the decade. UAE-other South Asian is 3.46m, the sum of Pakistani 1.90m, Bangladeshi 0.84m, Nepali 0.36m and Sri Lankan 0.36m - the brief's 3.4m was already correct. These are TOTAL RESIDENT NATIONALS including dependants, which is why the economically-active filter below applies. Oman and Bahrain is an expatriate WORKER count. INDIA IS NOT A DEMOGRAPHIC BASE - it is sized BEHAVIOURALLY from gold ETF folios intersected with active digital-gold holders, so its filters are 100%. ⚠ HELD STATIC over the horizon, which is conservative: the UAE Indian community grew ~12% in the single year to Dec 2024.</t>
+          <t>UPDATED 2026-08-20. UAE-Indian is 4.36m - the Indian consulate's official count at December 2024, also given as 4.3m by the Embassy of India. The brief carried 3.5m, which is roughly a 2021-22 vintage: the community was 3.89m at December 2023 and 4.36m a year later, having doubled from 2.2m over the decade. UAE-other South Asian is 3.46m, the sum of Pakistani 1.90m, Bangladeshi 0.84m, Nepali 0.36m and Sri Lankan 0.36m - the brief's 3.4m was already correct. These are TOTAL RESIDENT NATIONALS including dependants, which is why the economically-active filter below applies. Oman and Bahrain is an expatriate WORKER count. INDIA IS NOT A DEMOGRAPHIC BASE - it is sized BEHAVIOURALLY from gold ETF folios intersected with active digital-gold holders, so its filters are 100%. HELD STATIC over the horizon, which is conservative: the UAE Indian community grew ~12% in the single year to Dec 2024.</t>
         </is>
       </c>
       <c r="F74" s="26" t="n">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>~181,150, against the brief's 165,750. ⚠ THE BRIEF'S 'base x ceiling is the invariant' RULE IS DELIBERATELY BROKEN HERE, and the distinction matters: that rule guards against a METHODOLOGICAL re-cut quietly inflating the market by re-tuning filters, which proves nothing. This is not that - it is a DATA CORRECTION. The UAE Indian population really is 4.36m rather than 3.5m, so the addressable market really is larger. Holding the invariant would mean asserting that penetration falls exactly as population rises, which has no basis. The penetration ceilings are untouched.</t>
+          <t>~181,150, against the brief's 165,750. THE BRIEF'S 'base x ceiling is the invariant' RULE IS DELIBERATELY BROKEN HERE, and the distinction matters: that rule guards against a METHODOLOGICAL re-cut quietly inflating the market by re-tuning filters, which proves nothing. This is not that - it is a DATA CORRECTION. The UAE Indian population really is 4.36m rather than 3.5m, so the addressable market really is larger. Holding the invariant would mean asserting that penetration falls exactly as population rises, which has no basis. The penetration ceilings are untouched.</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>⚠ LIVE, SO IT MOVES IF ANYONE RAISES A CEILING - which is the point. Two INDEPENDENT methods landing within ~2x is the strongest defence of the funnel in this model: the funnel says the UAE can reach ~113,000 SIP accounts, and a real UAE gold app in the same segment has ~75,000 active users today. Our addressable base of ~1.43m sits against 775,000 who explored that product - same order again. If this multiple drifts far above ~2x, the ceiling has stopped being defensible by evidence and is being set by the answer someone wanted. DERIVED from a cited observation.</t>
+          <t>LIVE, SO IT MOVES IF ANYONE RAISES A CEILING - which is the point. Two INDEPENDENT methods landing within ~2x is the strongest defence of the funnel in this model: the funnel says the UAE can reach ~113,000 SIP accounts, and a real UAE gold app in the same segment has ~75,000 active users today. Our addressable base of ~1.43m sits against 775,000 who explored that product - same order again. If this multiple drifts far above ~2x, the ceiling has stopped being defensible by evidence and is being set by the answer someone wanted. DERIVED from a cited observation.</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CONFIRMED NEGATIVE, recorded so it is not re-searched. No GCC platform outside the UAE publishes a user count. India publishes only REGISTERED counts (Jar 35m, Augmont 42m) which cannot be deduplicated or converted to active users, so no comparable cross-check can be built. ⚠ NOTE THAT INDIA'S OWN BASE IS ALREADY user-derived - its 12.5m is 'holds a gold ETF folio or actively buys digital gold', which is why its three filters all sit at 1.00 - AND IT IS THE LEAST TRACEABLE BASE IN THE MODEL. That is the evidence that a user-based method does not automatically produce a better-sourced number.</t>
+          <t>CONFIRMED NEGATIVE, recorded so it is not re-searched. No GCC platform outside the UAE publishes a user count. India publishes only REGISTERED counts (Jar 35m, Augmont 42m) which cannot be deduplicated or converted to active users, so no comparable cross-check can be built. NOTE THAT INDIA'S OWN BASE IS ALREADY user-derived - its 12.5m is 'holds a gold ETF folio or actively buys digital gold', which is why its three filters all sit at 1.00 - AND IT IS THE LEAST TRACEABLE BASE IN THE MODEL. That is the evidence that a user-based method does not automatically produce a better-sourced number.</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. ⚠ COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. ⚠ AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
+          <t>RAISED 50% on 2026-08-21. A STOCK, NOT A FLOW: at 45% attrition, holding 186 active needs ~84 recruits a year just to stand still, and reaching 186 from 8 means recruiting and training several hundred people over seven years. COMPOUNDS WITH AGENT PRODUCTIVITY, raised from 4 to 6 the same day - together they are 2.25x the agent output the model carried this morning. AND IT IS A COST THIS MODEL CANNOT SEE: agents are paid, and the salesforce is now 45% UAE / 10% Oman &amp; Bahrain / 45% India, where a Dubai salesperson and an Indian commission agent are not remotely the same expense. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. 🔴 THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. ⚠ IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
+          <t>RAISED 50% on 2026-08-21, client instruction. A DECISION VARIABLE and an input to acquisition, not an output of a cost table. THE SINGLE LARGEST LEVER IN THE MODEL AND THE ONLY ONE THAT IS PURELY A SPENDING CHOICE: measured sensitivity puts +50% here at +28.5% customers and +29.3% gold. IT IS ALSO THE ONE THE REVENUE-ONLY SCOPE FLATTERS MOST. This model has no cost side yet, so an extra USD 1.9m of marketing across the horizon appears here as pure upside. It is not - it is USD 1.9m of spend, and whether it is worth making is a question only the cost build can answer. DO NOT PRESENT THE UPLIFT FROM THIS ROW AS PROFIT.</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>REVISED 2026-08-20. An earlier cut put 100% in India, which left the UAE - the licensed home market - with no people selling at all. There will be a salesforce outside India; it is simply SALARIED rather than commission-only. FOR REVENUE THE DISTINCTION DOES NOT MATTER: both are people acquiring customers at some productivity. ⚠ IT MATTERS ENORMOUSLY FOR COST - a Dubai salesperson and an Indian commission agent are not remotely the same expense, and this split MUST be cost-weighted when the cost build lands. India stays high because a large agent pool is cheapest to build there; UAE is weighted for being the core licensed market. ⚠ NOT the same thing as stream 6: that is B2B, partners white-labelling the platform onto their own customer books, and is not a consumer sales channel at all. Must sum to 100%. CLIENT INPUT.</t>
+          <t>REVISED 2026-08-20. An earlier cut put 100% in India, which left the UAE - the licensed home market - with no people selling at all. There will be a salesforce outside India; it is simply SALARIED rather than commission-only. FOR REVENUE THE DISTINCTION DOES NOT MATTER: both are people acquiring customers at some productivity. IT MATTERS ENORMOUSLY FOR COST - a Dubai salesperson and an Indian commission agent are not remotely the same expense, and this split MUST be cost-weighted when the cost build lands. India stays high because a large agent pool is cheapest to build there; UAE is weighted for being the core licensed market. NOT the same thing as stream 6: that is B2B, partners white-labelling the platform onto their own customer books, and is not a consumer sales channel at all. Must sum to 100%. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>REVISED 2026-08-20. An earlier cut put 100% in India, which left the UAE - the licensed home market - with no people selling at all. There will be a salesforce outside India; it is simply SALARIED rather than commission-only. FOR REVENUE THE DISTINCTION DOES NOT MATTER: both are people acquiring customers at some productivity. ⚠ IT MATTERS ENORMOUSLY FOR COST - a Dubai salesperson and an Indian commission agent are not remotely the same expense, and this split MUST be cost-weighted when the cost build lands. India stays high because a large agent pool is cheapest to build there; UAE is weighted for being the core licensed market. ⚠ NOT the same thing as stream 6: that is B2B, partners white-labelling the platform onto their own customer books, and is not a consumer sales channel at all. Must sum to 100%. CLIENT INPUT.</t>
+          <t>REVISED 2026-08-20. An earlier cut put 100% in India, which left the UAE - the licensed home market - with no people selling at all. There will be a salesforce outside India; it is simply SALARIED rather than commission-only. FOR REVENUE THE DISTINCTION DOES NOT MATTER: both are people acquiring customers at some productivity. IT MATTERS ENORMOUSLY FOR COST - a Dubai salesperson and an Indian commission agent are not remotely the same expense, and this split MUST be cost-weighted when the cost build lands. India stays high because a large agent pool is cheapest to build there; UAE is weighted for being the core licensed market. NOT the same thing as stream 6: that is B2B, partners white-labelling the platform onto their own customer books, and is not a consumer sales channel at all. Must sum to 100%. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>REVISED 2026-08-20. An earlier cut put 100% in India, which left the UAE - the licensed home market - with no people selling at all. There will be a salesforce outside India; it is simply SALARIED rather than commission-only. FOR REVENUE THE DISTINCTION DOES NOT MATTER: both are people acquiring customers at some productivity. ⚠ IT MATTERS ENORMOUSLY FOR COST - a Dubai salesperson and an Indian commission agent are not remotely the same expense, and this split MUST be cost-weighted when the cost build lands. India stays high because a large agent pool is cheapest to build there; UAE is weighted for being the core licensed market. ⚠ NOT the same thing as stream 6: that is B2B, partners white-labelling the platform onto their own customer books, and is not a consumer sales channel at all. Must sum to 100%. CLIENT INPUT.</t>
+          <t>REVISED 2026-08-20. An earlier cut put 100% in India, which left the UAE - the licensed home market - with no people selling at all. There will be a salesforce outside India; it is simply SALARIED rather than commission-only. FOR REVENUE THE DISTINCTION DOES NOT MATTER: both are people acquiring customers at some productivity. IT MATTERS ENORMOUSLY FOR COST - a Dubai salesperson and an Indian commission agent are not remotely the same expense, and this split MUST be cost-weighted when the cost build lands. India stays high because a large agent pool is cheapest to build there; UAE is weighted for being the core licensed market. NOT the same thing as stream 6: that is B2B, partners white-labelling the platform onto their own customer books, and is not a consumer sales channel at all. Must sum to 100%. CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ADDED 2026-08-21, client instruction, replacing a flat price. 8.1% is the COMPOUND ANNUAL GROWTH RATE SINCE 1971, the end of the gold standard - chosen because it is the LONGEST window and therefore the least cherry-picked. The shorter the window the better gold looks: ~8.6% over 50 years, ~9-10% over 20, ~13-14% over 10, and over 20% over the last 5. Taking the recent decade would have flattered the model on a rally. CITED. ⚠ THIS IS A NOMINAL RATE AND NOTHING ELSE IN THE MODEL INFLATES. SIP tickets, spot tickets, CAC, card fees and the B2B fee are all frozen in 2027 dollars. There is NO CONSENSUS POSITIVE LONG-RUN REAL RETURN for gold - it is generally treated as a store of value with a near-zero real yield - so most of this 8.1% IS INFLATION. Applying it to the metal while freezing everything else quietly asserts that gold outruns wages, prices and costs by 8% a year for seven years, which is not a claim anyone would defend out loud. The Model therefore also carries AUM AT THE CONSTANT M1 PRICE, and that is the honest series for judging whether the BUSINESS grew. Conservative is set at 0.0% deliberately: it restores the original flat-price design, under which every revenue change is attributable to the business rather than the metal.</t>
+          <t>ADDED 2026-08-21, client instruction, replacing a flat price. 8.1% is the COMPOUND ANNUAL GROWTH RATE SINCE 1971, the end of the gold standard - chosen because it is the LONGEST window and therefore the least cherry-picked. The shorter the window the better gold looks: ~8.6% over 50 years, ~9-10% over 20, ~13-14% over 10, and over 20% over the last 5. Taking the recent decade would have flattered the model on a rally. CITED. THIS IS A NOMINAL RATE AND NOTHING ELSE IN THE MODEL INFLATES. SIP tickets, spot tickets, CAC, card fees and the B2B fee are all frozen in 2027 dollars. There is NO CONSENSUS POSITIVE LONG-RUN REAL RETURN for gold - it is generally treated as a store of value with a near-zero real yield - so most of this 8.1% IS INFLATION. Applying it to the metal while freezing everything else quietly asserts that gold outruns wages, prices and costs by 8% a year for seven years, which is not a claim anyone would defend out loud. The Model therefore also carries AUM AT THE CONSTANT M1 PRICE, and that is the honest series for judging whether the BUSINESS grew. Conservative is set at 0.0% deliberately: it restores the original flat-price design, under which every revenue change is attributable to the business rather than the metal.</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21 from 4, client instruction. The insurance agency comparator that produced 4 is for agents selling a COMPLEX UNDERWRITTEN PRODUCT with medical questions and multi-page forms; a gold SIP signup is a fraction of that work, so the comparator was conservative for this product. ⚠ COMPOUNDS WITH THE AGENT HEADCOUNT, which was raised 50% the same day - together they are 2.25x the agent output the model carried this morning. Both are execution assumptions with no external anchor at the new level; if either disappoints, the other does not compensate. TRIANGULATED at 4, ASSUMPTION at 6.</t>
+          <t>RAISED 2026-08-21 from 4, client instruction. The insurance agency comparator that produced 4 is for agents selling a COMPLEX UNDERWRITTEN PRODUCT with medical questions and multi-page forms; a gold SIP signup is a fraction of that work, so the comparator was conservative for this product. COMPOUNDS WITH THE AGENT HEADCOUNT, which was raised 50% the same day - together they are 2.25x the agent output the model carried this morning. Both are execution assumptions with no external anchor at the new level; if either disappoints, the other does not compensate. TRIANGULATED at 4, ASSUMPTION at 6.</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; ⚠ note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
+          <t>REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; ⚠ note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
+          <t>REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; ⚠ note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
+          <t>REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21 from 0.45, client instruction. Cap removed deliberately, so the distribution is right-skewed - MODEL THE MEAN, NOT THE MEDIAN. 0.60 means the average customer produces roughly three referrals every five years; the mean is pulled up by a small number of highly social referrers, which is the normal shape for a trust-based product inside a tight diaspora community. ⚠ IT IS STILL AN ASSUMPTION WITH NO EXTERNAL ANCHOR, and it compounds: referrals feed the paying base, which feeds more referrals. That loop is the reason this parameter is more load-bearing than its size suggests. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21 from 0.45, client instruction. Cap removed deliberately, so the distribution is right-skewed - MODEL THE MEAN, NOT THE MEDIAN. 0.60 means the average customer produces roughly three referrals every five years; the mean is pulled up by a small number of highly social referrers, which is the normal shape for a trust-based product inside a tight diaspora community. IT IS STILL AN ASSUMPTION WITH NO EXTERNAL ANCHOR, and it compounds: referrals feed the paying base, which feeds more referrals. That loop is the reason this parameter is more load-bearing than its size suggests. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21 from 0.12, client instruction. Kept separate from CAC deliberately, so the acquisition cost never applies to it - THAT IS ALSO WHY IT IS AN ATTRACTIVE NUMBER TO RAISE, and why it deserves scepticism. 0.25 says a quarter of paid-driven signups arrive again for free through word of mouth, app store discovery and community effects. Defensible for a product sold inside a dense diaspora network where the paid campaign and the community overlap almost completely. ⚠ NO EXTERNAL ANCHOR AT EITHER LEVEL, and it is arithmetically identical to a 12% CAC reduction - so raising this AND cutting CAC in the same pass is close to taking the same benefit twice. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21 from 0.12, client instruction. Kept separate from CAC deliberately, so the acquisition cost never applies to it - THAT IS ALSO WHY IT IS AN ATTRACTIVE NUMBER TO RAISE, and why it deserves scepticism. 0.25 says a quarter of paid-driven signups arrive again for free through word of mouth, app store discovery and community effects. Defensible for a product sold inside a dense diaspora network where the paid campaign and the community overlap almost completely. NO EXTERNAL ANCHOR AT EITHER LEVEL, and it is arithmetically identical to a 12% CAC reduction - so raising this AND cutting CAC in the same pass is close to taking the same benefit twice. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>HALVED 2026-08-21 from 0.12, client instruction. ⚠ NOTE IT HAS ZERO EFFECT ON GOLD UNDER CUSTODY - measured, not asserted - because self-custodied metal never left the vault and was never in that measure. It moves ONLY the collateral-eligible base and therefore the card credit limit, worth ~0.2% of Y7 revenue. RELABELLED earlier the same day after the client correctly objected to the old name, 'self-custody leakage'. THE GOLD DOES NOT LEAVE THE VAULT: a token moving to a customer's own wallet sells nothing and burns nothing, so calling it an AUM decrease was wrong. What it does leave is Aurumix's COLLATERAL-ELIGIBLE base - Aurumix cannot foreclose on a token sitting in a private wallet, so that gold can no longer back a credit limit. In this model AUM has exactly ONE consumer, the card credit limit, so the arithmetic was always right and only the label was misleading. ⚠ THAT ONE-CONSUMER PROPERTY IS WHAT MAKES THIS SAFE: if a later build points anything else at AUM - a custody fee, a reported-AUM headline - this row must be split in two first. Contrast the redemption line, which IS gold genuinely gone. ASSUMPTION.</t>
+          <t>HALVED 2026-08-21 from 0.12, client instruction. NOTE IT HAS ZERO EFFECT ON GOLD UNDER CUSTODY - measured, not asserted - because self-custodied metal never left the vault and was never in that measure. It moves ONLY the collateral-eligible base and therefore the card credit limit, worth ~0.2% of Y7 revenue. RELABELLED earlier the same day after the client correctly objected to the old name, 'self-custody leakage'. THE GOLD DOES NOT LEAVE THE VAULT: a token moving to a customer's own wallet sells nothing and burns nothing, so calling it an AUM decrease was wrong. What it does leave is Aurumix's COLLATERAL-ELIGIBLE base - Aurumix cannot foreclose on a token sitting in a private wallet, so that gold can no longer back a credit limit. In this model AUM has exactly ONE consumer, the card credit limit, so the arithmetic was always right and only the label was misleading. THAT ONE-CONSUMER PROPERTY IS WHAT MAKES THIS SAFE: if a later build points anything else at AUM - a custody fee, a reported-AUM headline - this row must be split in two first. Contrast the redemption line, which IS gold genuinely gone. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LOWERED 2026-08-21 from 2.2, client instruction. ⚠ THIS IS THE WEAKEST OF THE THREE DECAY CHANGES. The LOGIC behind a multiplier above 1.0 is untouched and still holds: customers who stopped paying redeem faster, because they have no accruing benefit left to protect. Lowering it to 1.6 weakens that argument without new evidence for the smaller number - it says lapsed customers are stickier than previously assumed, which is the convenient direction. Because holders become the majority of the book by Y4, this remains the DOMINANT AUM DECAY TERM from roughly Y4, so the change is not cosmetic. ASSUMPTION, and the first one to revisit if AUM is challenged.</t>
+          <t>LOWERED 2026-08-21 from 2.2, client instruction. THIS IS THE WEAKEST OF THE THREE DECAY CHANGES. The LOGIC behind a multiplier above 1.0 is untouched and still holds: customers who stopped paying redeem faster, because they have no accruing benefit left to protect. Lowering it to 1.6 weakens that argument without new evidence for the smaller number - it says lapsed customers are stickier than previously assumed, which is the convenient direction. Because holders become the majority of the book by Y4, this remains the DOMINANT AUM DECAY TERM from roughly Y4, so the change is not cosmetic. ASSUMPTION, and the first one to revisit if AUM is challenged.</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>REPLACED the global 'Average spot ticket' on 2026-08-21. The LEVEL is no longer a scenario input: each region now carries its own OBSERVED ticket on Assumptions (UAE 190 from Botim, India 40 from Augmont, Oman &amp; Bahrain 145 inferred). This parameter carries only the UNCERTAINTY around those observations, as a single dial. ⚠ WHY ONE DIAL AND NOT THREE: three regional triplets would be nine numbers to defend and would let a scenario silently invert the regional ordering that the sources establish. One multiplier flexes the level and PRESERVES the ordering. Aggressive 1.35 puts the UAE at ~257, still under the AED 1,000 mark; conservative 0.70 puts it at ~133, below Botim's own sub-AED-500 majority. ASSUMPTION about spread, applied to observed levels.</t>
+          <t>REPLACED the global 'Average spot ticket' on 2026-08-21. The LEVEL is no longer a scenario input: each region now carries its own OBSERVED ticket on Assumptions (UAE 190 from Botim, India 40 from Augmont, Oman &amp; Bahrain 145 inferred). This parameter carries only the UNCERTAINTY around those observations, as a single dial. WHY ONE DIAL AND NOT THREE: three regional triplets would be nine numbers to defend and would let a scenario silently invert the regional ordering that the sources establish. One multiplier flexes the level and PRESERVES the ordering. Aggressive 1.35 puts the UAE at ~257, still under the AED 1,000 mark; conservative 0.70 puts it at ~133, below Botim's own sub-AED-500 majority. ASSUMPTION about spread, applied to observed levels.</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>⚠ PROVENANCE CORRECTED 2026-08-21 - THE NUMBER STANDS, ITS OLD CITATION DID NOT. The previous note read 'Botim's 128,000 trades against ~45,000 buyers implies ~1.9/yr'. THE 45,000 IS NOT A BUYER COUNT, IT IS A TRANSACTION COUNT: Khaleej Times, Nov 2025, says 775,000 users EXPLORED the feature, 'completing over 45,000 transactions'. The 128,000 is also transactions, to Feb 2026. So the old derivation divided transactions by transactions across two different windows - the result was the growth in cumulative trades, not a frequency. CONFIRMED NEGATIVE: Botim has never published a unique-buyer count, so no frequency can be derived from it, and no published frequency exists ANYWHERE for ad-hoc lump gold purchases. Comparators are 0.85/yr (Augmont, per REGISTERED user, at an average transaction of Rs 331 - micro-saving, not lumps) and 264/yr (Jar, Rs 10/day auto-roundups) - a 300x spread, neither being this product. WHAT DOES SUPPORT 1.7 is a cross-check on the COMBINED basis, attach x frequency x ticket, which is comparable: Aurumix India implies ~Rs 838/yr of gold per paying customer against Augmont's ~Rs 281/yr per registered user. 3x, and defensible - our customers are engaged SIP savers, not dormant registrations. Behaviourally 1.7 is also about right for festive lumps: Dhanteras, Akshaya Tritiya and a wedding is roughly two events. ASSUMPTION, cross-checked on the combined basis, NOT directly sourced.</t>
+          <t>PROVENANCE CORRECTED 2026-08-21 - THE NUMBER STANDS, ITS OLD CITATION DID NOT. The previous note read 'Botim's 128,000 trades against ~45,000 buyers implies ~1.9/yr'. THE 45,000 IS NOT A BUYER COUNT, IT IS A TRANSACTION COUNT: Khaleej Times, Nov 2025, says 775,000 users EXPLORED the feature, 'completing over 45,000 transactions'. The 128,000 is also transactions, to Feb 2026. So the old derivation divided transactions by transactions across two different windows - the result was the growth in cumulative trades, not a frequency. CONFIRMED NEGATIVE: Botim has never published a unique-buyer count, so no frequency can be derived from it, and no published frequency exists ANYWHERE for ad-hoc lump gold purchases. Comparators are 0.85/yr (Augmont, per REGISTERED user, at an average transaction of Rs 331 - micro-saving, not lumps) and 264/yr (Jar, Rs 10/day auto-roundups) - a 300x spread, neither being this product. WHAT DOES SUPPORT 1.7 is a cross-check on the COMBINED basis, attach x frequency x ticket, which is comparable: Aurumix India implies ~Rs 838/yr of gold per paying customer against Augmont's ~Rs 281/yr per registered user. 3x, and defensible - our customers are engaged SIP savers, not dormant registrations. Behaviourally 1.7 is also about right for festive lumps: Dhanteras, Akshaya Tritiya and a wedding is roughly two events. ASSUMPTION, cross-checked on the combined basis, NOT directly sourced.</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>RE-BASED 2026-08-20, client decision: THE CARD IS A DRAWDOWN ON THE GOLD-COLLATERALISED FACILITY, not a salary-repaid revolving card. Aurumix has no balance sheet to lend from - it can only extend credit against collateral it holds, which is the customer's gold. Using the card IS borrowing, so card activation and credit take-up are the SAME behaviour and were previously modelled as two different populations (50% activating a card, 18% taking credit) doing what is in fact one thing. Merged onto the credit figure, which is the better-anchored of the two: Indian gold-loan penetration is under 10% at a point in time, uplifted here for pre-selection since these customers have already cleared a six-payment gate. ⚠ THE OLD 50% CAME FROM NEOBANK COMPARABLES (PULSE 68.2%, Monzo 68%) WHERE THE CARD IS THE PRODUCT - wrong in kind for a card that only lets you borrow against your own savings. DERIVED.</t>
+          <t>RE-BASED 2026-08-20, client decision: THE CARD IS A DRAWDOWN ON THE GOLD-COLLATERALISED FACILITY, not a salary-repaid revolving card. Aurumix has no balance sheet to lend from - it can only extend credit against collateral it holds, which is the customer's gold. Using the card IS borrowing, so card activation and credit take-up are the SAME behaviour and were previously modelled as two different populations (50% activating a card, 18% taking credit) doing what is in fact one thing. Merged onto the credit figure, which is the better-anchored of the two: Indian gold-loan penetration is under 10% at a point in time, uplifted here for pre-selection since these customers have already cleared a six-payment gate. THE OLD 50% CAME FROM NEOBANK COMPARABLES (PULSE 68.2%, Monzo 68%) WHERE THE CARD IS THE PRODUCT - wrong in kind for a card that only lets you borrow against your own savings. DERIVED.</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>RE-BASED 2026-08-20 from 12 transactions/MONTH once the card became a drawdown on the gold facility. Under that model the customer borrows a lump (limit x drawn share) a couple of times a year and spends it down, so the meaningful unit is transactions PER DRAW, not per month. At 12/month the implied ticket collapsed to ~AED 12, which is a coffee, not a reason to pledge your gold. THE AVERAGE TICKET FALLS OUT AS drawn amount / this number, and the draw events cancel - so the ticket depends only on how large a draw is and how many purchases it is spent across. ⚠ IT ALSO CHANGES WHAT THE CARD IS FOR: not daily groceries, but occasional larger needs - school fees, a medical bill, an emergency - funded by borrowing against savings rather than liquidating them. That is a materially different product story and should be put to the client in those words. ASSUMPTION.</t>
+          <t>RE-BASED 2026-08-20 from 12 transactions/MONTH once the card became a drawdown on the gold facility. Under that model the customer borrows a lump (limit x drawn share) a couple of times a year and spends it down, so the meaningful unit is transactions PER DRAW, not per month. At 12/month the implied ticket collapsed to ~AED 12, which is a coffee, not a reason to pledge your gold. THE AVERAGE TICKET FALLS OUT AS drawn amount / this number, and the draw events cancel - so the ticket depends only on how large a draw is and how many purchases it is spent across. IT ALSO CHANGES WHAT THE CARD IS FOR: not daily groceries, but occasional larger needs - school fees, a medical bill, an emergency - funded by borrowing against savings rather than liquidating them. That is a materially different product story and should be put to the client in those words. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>SET AT 0.15 on 2026-08-21, client instruction - the same day it came DOWN from 0.20 to 0.08, so it has landed close to where it started. What has genuinely changed is not the number but the STRUCTURE. ⚠ THE UNIT ALSO CHANGED, AND THAT MATTERS: it is now the share of NEW customers who take the plan when they join, feeding a SUBSCRIBER BALANCE that then churns - not a standing share of the whole book that could never fall. The steady-state share of paying customers holding a plan therefore lands BELOW this number. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on; 20% is at the top of the normal range for an OPTIONAL PAID extra on a savings product, which is low single digits to low teens. ⚠ IT IS NOT EQUIVALENT TO THE OLD 20% AND SHOULD NOT BE READ AS A PARTIAL REVERSAL: 20% was a permanent share of the whole book that could never decay, while 15% applies once, on joining, to a balance that then churns at ~7.1% a month. The standing share of paying customers holding a plan settles near 10.5%, not 15%. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on. ASSUMPTION.</t>
+          <t>SET AT 0.15 on 2026-08-21, client instruction - the same day it came DOWN from 0.20 to 0.08, so it has landed close to where it started. What has genuinely changed is not the number but the STRUCTURE. THE UNIT ALSO CHANGED, AND THAT MATTERS: it is now the share of NEW customers who take the plan when they join, feeding a SUBSCRIBER BALANCE that then churns - not a standing share of the whole book that could never fall. The steady-state share of paying customers holding a plan therefore lands BELOW this number. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on; 20% is at the top of the normal range for an OPTIONAL PAID extra on a savings product, which is low single digits to low teens. IT IS NOT EQUIVALENT TO THE OLD 20% AND SHOULD NOT BE READ AS A PARTIAL REVERSAL: 20% was a permanent share of the whole book that could never decay, while 15% applies once, on joining, to a balance that then churns at ~7.1% a month. The standing share of paying customers holding a plan settles near 10.5%, not 15%. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>ADDED 2026-08-21. THE FIRST IS INCLUDED IN THE PLAN PRICE, so only the excess over 1.0 is charged - at 2.5 that is 1.5 chargeable. No platform publishes beneficiaries-per-will. What anchors it is who these customers are: South Asian migrant workers who remit ~80% of income to families at home, typically supporting a spouse, children and parents. Household sizes in the source countries run ~4.4 in India, ~4.5 in Bangladesh and ~6.8 in Pakistan, so naming 2-3 beneficiaries is conservative against the family they actually support. ⚠ NOT THE SAME AS HOUSEHOLD SIZE - a beneficiary is a named, identity-verified person on a legal instrument, and people name fewer than they support. ASSUMPTION anchored on demographics.</t>
+          <t>ADDED 2026-08-21. THE FIRST IS INCLUDED IN THE PLAN PRICE, so only the excess over 1.0 is charged - at 2.5 that is 1.5 chargeable. No platform publishes beneficiaries-per-will. What anchors it is who these customers are: South Asian migrant workers who remit ~80% of income to families at home, typically supporting a spouse, children and parents. Household sizes in the source countries run ~4.4 in India, ~4.5 in Bangladesh and ~6.8 in Pakistan, so naming 2-3 beneficiaries is conservative against the family they actually support. NOT THE SAME AS HOUSEHOLD SIZE - a beneficiary is a named, identity-verified person on a legal instrument, and people name fewer than they support. ASSUMPTION anchored on demographics.</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>THE MIX, NOT THE BIGGEST. A realistic six-partner Gulf book is roughly one Botim-scale (1.7m ACTIVE fintech users, of 8.2-8.5m app users), two at e&amp; money scale (~1.5m subscribers), and three small wallets at a few hundred thousand - which averages near 900k. ⚠ USE ACTIVE USERS, NOT REGISTERED: Botim's own numbers separate 8.5m app users, 3m KYC'd and 1.7m active fintech users, and adopting the headline would overstate this by 5x. CITED for the two largest, ASSUMPTION for the tail.</t>
+          <t>THE MIX, NOT THE BIGGEST. A realistic six-partner Gulf book is roughly one Botim-scale (1.7m ACTIVE fintech users, of 8.2-8.5m app users), two at e&amp; money scale (~1.5m subscribers), and three small wallets at a few hundred thousand - which averages near 900k. USE ACTIVE USERS, NOT REGISTERED: Botim's own numbers separate 8.5m app users, 3m KYC'd and 1.7m active fintech users, and adopting the headline would overstate this by 5x. CITED for the two largest, ASSUMPTION for the tail.</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>OBSERVED ANCHOR: O Gold reports 75,000 ACTIVE users against Botim's 1.7m active fintech users - 4.4% - and 775,000 who merely explored the feature. Base is set at 6%, ABOVE the observed 4.4%, because that figure is roughly six months after the gold feature launched and adoption should mature; 6% is a 1.4x maturation, not a doubling. ⚠ THE 4.4% IS THE ONLY OBSERVED GOLD-ADOPTION RATE FOR A GULF WALLET THAT EXISTS. TRIANGULATED.</t>
+          <t>OBSERVED ANCHOR: O Gold reports 75,000 ACTIVE users against Botim's 1.7m active fintech users - 4.4% - and 775,000 who merely explored the feature. Base is set at 6%, ABOVE the observed 4.4%, because that figure is roughly six months after the gold feature launched and adoption should mature; 6% is a 1.4x maturation, not a doubling. THE 4.4% IS THE ONLY OBSERVED GOLD-ADOPTION RATE FOR A GULF WALLET THAT EXISTS. TRIANGULATED.</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>ADDED 2026-08-21, client instruction, replacing a flat price. 8.1% is the COMPOUND ANNUAL GROWTH RATE SINCE 1971, the end of the gold standard - chosen because it is the LONGEST window and therefore the least cherry-picked. The shorter the window the better gold looks: ~8.6% over 50 years, ~9-10% over 20, ~13-14% over 10, and over 20% over the last 5. Taking the recent decade would have flattered the model on a rally. CITED. ⚠ THIS IS A NOMINAL RATE AND NOTHING ELSE IN THE MODEL INFLATES. SIP tickets, spot tickets, CAC, card fees and the B2B fee are all frozen in 2027 dollars. There is NO CONSENSUS POSITIVE LONG-RUN REAL RETURN for gold - it is generally treated as a store of value with a near-zero real yield - so most of this 8.1% IS INFLATION. Applying it to the metal while freezing everything else quietly asserts that gold outruns wages, prices and costs by 8% a year for seven years, which is not a claim anyone would defend out loud. The Model therefore also carries AUM AT THE CONSTANT M1 PRICE, and that is the honest series for judging whether the BUSINESS grew. Conservative is set at 0.0% deliberately: it restores the original flat-price design, under which every revenue change is attributable to the business rather than the metal.</t>
+          <t>ADDED 2026-08-21, client instruction, replacing a flat price. 8.1% is the COMPOUND ANNUAL GROWTH RATE SINCE 1971, the end of the gold standard - chosen because it is the LONGEST window and therefore the least cherry-picked. The shorter the window the better gold looks: ~8.6% over 50 years, ~9-10% over 20, ~13-14% over 10, and over 20% over the last 5. Taking the recent decade would have flattered the model on a rally. CITED. THIS IS A NOMINAL RATE AND NOTHING ELSE IN THE MODEL INFLATES. SIP tickets, spot tickets, CAC, card fees and the B2B fee are all frozen in 2027 dollars. There is NO CONSENSUS POSITIVE LONG-RUN REAL RETURN for gold - it is generally treated as a store of value with a near-zero real yield - so most of this 8.1% IS INFLATION. Applying it to the metal while freezing everything else quietly asserts that gold outruns wages, prices and costs by 8% a year for seven years, which is not a claim anyone would defend out loud. The Model therefore also carries AUM AT THE CONSTANT M1 PRICE, and that is the honest series for judging whether the BUSINESS grew. Conservative is set at 0.0% deliberately: it restores the original flat-price design, under which every revenue change is attributable to the business rather than the metal.</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21 from 4, client instruction. The insurance agency comparator that produced 4 is for agents selling a COMPLEX UNDERWRITTEN PRODUCT with medical questions and multi-page forms; a gold SIP signup is a fraction of that work, so the comparator was conservative for this product. ⚠ COMPOUNDS WITH THE AGENT HEADCOUNT, which was raised 50% the same day - together they are 2.25x the agent output the model carried this morning. Both are execution assumptions with no external anchor at the new level; if either disappoints, the other does not compensate. TRIANGULATED at 4, ASSUMPTION at 6.</t>
+          <t>RAISED 2026-08-21 from 4, client instruction. The insurance agency comparator that produced 4 is for agents selling a COMPLEX UNDERWRITTEN PRODUCT with medical questions and multi-page forms; a gold SIP signup is a fraction of that work, so the comparator was conservative for this product. COMPOUNDS WITH THE AGENT HEADCOUNT, which was raised 50% the same day - together they are 2.25x the agent output the model carried this morning. Both are execution assumptions with no external anchor at the new level; if either disappoints, the other does not compensate. TRIANGULATED at 4, ASSUMPTION at 6.</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; ⚠ note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
+          <t>REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; ⚠ note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
+          <t>REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; ⚠ note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
+          <t>REGIONALISED 2026-08-20. A single global USD 120 was applied everywhere, which is roughly right for the UAE and badly wrong for India. PUBLISHED BENCHMARKS: Dubai consumer fintech USD 65-220; retail neobank account paid-only USD 35-70; GCC wealthtech funded accounts USD 80-220; 'true' fully-loaded CAC per ACTIVATED customer USD 85-350 against USD 50-100 reported, once KYC, onboarding and non-activating signups are counted. INDIA IS A DIFFERENT MARKET ENTIRELY: consumer fintech INR 500-1,500 (~USD 6-18), neobank savings activation INR 1,100-1,800, wealth and broking apps INR 2,500-5,500 (~USD 30-65); Jupiter reports a USD 5-6 paid CAC. USD 120 is ~INR 10,500 - some 7-20x the Indian mass-market benchmark and still 2-4x its premium wealth apps. UAE is held at 120 as a FULLY-LOADED figure; note it sits at the top of the range for a LOW-TICKET product, and the published low-ticket band is USD 4-70. TRIANGULATED.</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21 from 0.45, client instruction. Cap removed deliberately, so the distribution is right-skewed - MODEL THE MEAN, NOT THE MEDIAN. 0.60 means the average customer produces roughly three referrals every five years; the mean is pulled up by a small number of highly social referrers, which is the normal shape for a trust-based product inside a tight diaspora community. ⚠ IT IS STILL AN ASSUMPTION WITH NO EXTERNAL ANCHOR, and it compounds: referrals feed the paying base, which feeds more referrals. That loop is the reason this parameter is more load-bearing than its size suggests. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21 from 0.45, client instruction. Cap removed deliberately, so the distribution is right-skewed - MODEL THE MEAN, NOT THE MEDIAN. 0.60 means the average customer produces roughly three referrals every five years; the mean is pulled up by a small number of highly social referrers, which is the normal shape for a trust-based product inside a tight diaspora community. IT IS STILL AN ASSUMPTION WITH NO EXTERNAL ANCHOR, and it compounds: referrals feed the paying base, which feeds more referrals. That loop is the reason this parameter is more load-bearing than its size suggests. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21 from 0.12, client instruction. Kept separate from CAC deliberately, so the acquisition cost never applies to it - THAT IS ALSO WHY IT IS AN ATTRACTIVE NUMBER TO RAISE, and why it deserves scepticism. 0.25 says a quarter of paid-driven signups arrive again for free through word of mouth, app store discovery and community effects. Defensible for a product sold inside a dense diaspora network where the paid campaign and the community overlap almost completely. ⚠ NO EXTERNAL ANCHOR AT EITHER LEVEL, and it is arithmetically identical to a 12% CAC reduction - so raising this AND cutting CAC in the same pass is close to taking the same benefit twice. ASSUMPTION.</t>
+          <t>RAISED 2026-08-21 from 0.12, client instruction. Kept separate from CAC deliberately, so the acquisition cost never applies to it - THAT IS ALSO WHY IT IS AN ATTRACTIVE NUMBER TO RAISE, and why it deserves scepticism. 0.25 says a quarter of paid-driven signups arrive again for free through word of mouth, app store discovery and community effects. Defensible for a product sold inside a dense diaspora network where the paid campaign and the community overlap almost completely. NO EXTERNAL ANCHOR AT EITHER LEVEL, and it is arithmetically identical to a 12% CAC reduction - so raising this AND cutting CAC in the same pass is close to taking the same benefit twice. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>HALVED 2026-08-21 from 0.12, client instruction. ⚠ NOTE IT HAS ZERO EFFECT ON GOLD UNDER CUSTODY - measured, not asserted - because self-custodied metal never left the vault and was never in that measure. It moves ONLY the collateral-eligible base and therefore the card credit limit, worth ~0.2% of Y7 revenue. RELABELLED earlier the same day after the client correctly objected to the old name, 'self-custody leakage'. THE GOLD DOES NOT LEAVE THE VAULT: a token moving to a customer's own wallet sells nothing and burns nothing, so calling it an AUM decrease was wrong. What it does leave is Aurumix's COLLATERAL-ELIGIBLE base - Aurumix cannot foreclose on a token sitting in a private wallet, so that gold can no longer back a credit limit. In this model AUM has exactly ONE consumer, the card credit limit, so the arithmetic was always right and only the label was misleading. ⚠ THAT ONE-CONSUMER PROPERTY IS WHAT MAKES THIS SAFE: if a later build points anything else at AUM - a custody fee, a reported-AUM headline - this row must be split in two first. Contrast the redemption line, which IS gold genuinely gone. ASSUMPTION.</t>
+          <t>HALVED 2026-08-21 from 0.12, client instruction. NOTE IT HAS ZERO EFFECT ON GOLD UNDER CUSTODY - measured, not asserted - because self-custodied metal never left the vault and was never in that measure. It moves ONLY the collateral-eligible base and therefore the card credit limit, worth ~0.2% of Y7 revenue. RELABELLED earlier the same day after the client correctly objected to the old name, 'self-custody leakage'. THE GOLD DOES NOT LEAVE THE VAULT: a token moving to a customer's own wallet sells nothing and burns nothing, so calling it an AUM decrease was wrong. What it does leave is Aurumix's COLLATERAL-ELIGIBLE base - Aurumix cannot foreclose on a token sitting in a private wallet, so that gold can no longer back a credit limit. In this model AUM has exactly ONE consumer, the card credit limit, so the arithmetic was always right and only the label was misleading. THAT ONE-CONSUMER PROPERTY IS WHAT MAKES THIS SAFE: if a later build points anything else at AUM - a custody fee, a reported-AUM headline - this row must be split in two first. Contrast the redemption line, which IS gold genuinely gone. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>LOWERED 2026-08-21 from 2.2, client instruction. ⚠ THIS IS THE WEAKEST OF THE THREE DECAY CHANGES. The LOGIC behind a multiplier above 1.0 is untouched and still holds: customers who stopped paying redeem faster, because they have no accruing benefit left to protect. Lowering it to 1.6 weakens that argument without new evidence for the smaller number - it says lapsed customers are stickier than previously assumed, which is the convenient direction. Because holders become the majority of the book by Y4, this remains the DOMINANT AUM DECAY TERM from roughly Y4, so the change is not cosmetic. ASSUMPTION, and the first one to revisit if AUM is challenged.</t>
+          <t>LOWERED 2026-08-21 from 2.2, client instruction. THIS IS THE WEAKEST OF THE THREE DECAY CHANGES. The LOGIC behind a multiplier above 1.0 is untouched and still holds: customers who stopped paying redeem faster, because they have no accruing benefit left to protect. Lowering it to 1.6 weakens that argument without new evidence for the smaller number - it says lapsed customers are stickier than previously assumed, which is the convenient direction. Because holders become the majority of the book by Y4, this remains the DOMINANT AUM DECAY TERM from roughly Y4, so the change is not cosmetic. ASSUMPTION, and the first one to revisit if AUM is challenged.</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>REPLACED the global 'Average spot ticket' on 2026-08-21. The LEVEL is no longer a scenario input: each region now carries its own OBSERVED ticket on Assumptions (UAE 190 from Botim, India 40 from Augmont, Oman &amp; Bahrain 145 inferred). This parameter carries only the UNCERTAINTY around those observations, as a single dial. ⚠ WHY ONE DIAL AND NOT THREE: three regional triplets would be nine numbers to defend and would let a scenario silently invert the regional ordering that the sources establish. One multiplier flexes the level and PRESERVES the ordering. Aggressive 1.35 puts the UAE at ~257, still under the AED 1,000 mark; conservative 0.70 puts it at ~133, below Botim's own sub-AED-500 majority. ASSUMPTION about spread, applied to observed levels.</t>
+          <t>REPLACED the global 'Average spot ticket' on 2026-08-21. The LEVEL is no longer a scenario input: each region now carries its own OBSERVED ticket on Assumptions (UAE 190 from Botim, India 40 from Augmont, Oman &amp; Bahrain 145 inferred). This parameter carries only the UNCERTAINTY around those observations, as a single dial. WHY ONE DIAL AND NOT THREE: three regional triplets would be nine numbers to defend and would let a scenario silently invert the regional ordering that the sources establish. One multiplier flexes the level and PRESERVES the ordering. Aggressive 1.35 puts the UAE at ~257, still under the AED 1,000 mark; conservative 0.70 puts it at ~133, below Botim's own sub-AED-500 majority. ASSUMPTION about spread, applied to observed levels.</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>⚠ PROVENANCE CORRECTED 2026-08-21 - THE NUMBER STANDS, ITS OLD CITATION DID NOT. The previous note read 'Botim's 128,000 trades against ~45,000 buyers implies ~1.9/yr'. THE 45,000 IS NOT A BUYER COUNT, IT IS A TRANSACTION COUNT: Khaleej Times, Nov 2025, says 775,000 users EXPLORED the feature, 'completing over 45,000 transactions'. The 128,000 is also transactions, to Feb 2026. So the old derivation divided transactions by transactions across two different windows - the result was the growth in cumulative trades, not a frequency. CONFIRMED NEGATIVE: Botim has never published a unique-buyer count, so no frequency can be derived from it, and no published frequency exists ANYWHERE for ad-hoc lump gold purchases. Comparators are 0.85/yr (Augmont, per REGISTERED user, at an average transaction of Rs 331 - micro-saving, not lumps) and 264/yr (Jar, Rs 10/day auto-roundups) - a 300x spread, neither being this product. WHAT DOES SUPPORT 1.7 is a cross-check on the COMBINED basis, attach x frequency x ticket, which is comparable: Aurumix India implies ~Rs 838/yr of gold per paying customer against Augmont's ~Rs 281/yr per registered user. 3x, and defensible - our customers are engaged SIP savers, not dormant registrations. Behaviourally 1.7 is also about right for festive lumps: Dhanteras, Akshaya Tritiya and a wedding is roughly two events. ASSUMPTION, cross-checked on the combined basis, NOT directly sourced.</t>
+          <t>PROVENANCE CORRECTED 2026-08-21 - THE NUMBER STANDS, ITS OLD CITATION DID NOT. The previous note read 'Botim's 128,000 trades against ~45,000 buyers implies ~1.9/yr'. THE 45,000 IS NOT A BUYER COUNT, IT IS A TRANSACTION COUNT: Khaleej Times, Nov 2025, says 775,000 users EXPLORED the feature, 'completing over 45,000 transactions'. The 128,000 is also transactions, to Feb 2026. So the old derivation divided transactions by transactions across two different windows - the result was the growth in cumulative trades, not a frequency. CONFIRMED NEGATIVE: Botim has never published a unique-buyer count, so no frequency can be derived from it, and no published frequency exists ANYWHERE for ad-hoc lump gold purchases. Comparators are 0.85/yr (Augmont, per REGISTERED user, at an average transaction of Rs 331 - micro-saving, not lumps) and 264/yr (Jar, Rs 10/day auto-roundups) - a 300x spread, neither being this product. WHAT DOES SUPPORT 1.7 is a cross-check on the COMBINED basis, attach x frequency x ticket, which is comparable: Aurumix India implies ~Rs 838/yr of gold per paying customer against Augmont's ~Rs 281/yr per registered user. 3x, and defensible - our customers are engaged SIP savers, not dormant registrations. Behaviourally 1.7 is also about right for festive lumps: Dhanteras, Akshaya Tritiya and a wedding is roughly two events. ASSUMPTION, cross-checked on the combined basis, NOT directly sourced.</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>RE-BASED 2026-08-20, client decision: THE CARD IS A DRAWDOWN ON THE GOLD-COLLATERALISED FACILITY, not a salary-repaid revolving card. Aurumix has no balance sheet to lend from - it can only extend credit against collateral it holds, which is the customer's gold. Using the card IS borrowing, so card activation and credit take-up are the SAME behaviour and were previously modelled as two different populations (50% activating a card, 18% taking credit) doing what is in fact one thing. Merged onto the credit figure, which is the better-anchored of the two: Indian gold-loan penetration is under 10% at a point in time, uplifted here for pre-selection since these customers have already cleared a six-payment gate. ⚠ THE OLD 50% CAME FROM NEOBANK COMPARABLES (PULSE 68.2%, Monzo 68%) WHERE THE CARD IS THE PRODUCT - wrong in kind for a card that only lets you borrow against your own savings. DERIVED.</t>
+          <t>RE-BASED 2026-08-20, client decision: THE CARD IS A DRAWDOWN ON THE GOLD-COLLATERALISED FACILITY, not a salary-repaid revolving card. Aurumix has no balance sheet to lend from - it can only extend credit against collateral it holds, which is the customer's gold. Using the card IS borrowing, so card activation and credit take-up are the SAME behaviour and were previously modelled as two different populations (50% activating a card, 18% taking credit) doing what is in fact one thing. Merged onto the credit figure, which is the better-anchored of the two: Indian gold-loan penetration is under 10% at a point in time, uplifted here for pre-selection since these customers have already cleared a six-payment gate. THE OLD 50% CAME FROM NEOBANK COMPARABLES (PULSE 68.2%, Monzo 68%) WHERE THE CARD IS THE PRODUCT - wrong in kind for a card that only lets you borrow against your own savings. DERIVED.</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>RE-BASED 2026-08-20 from 12 transactions/MONTH once the card became a drawdown on the gold facility. Under that model the customer borrows a lump (limit x drawn share) a couple of times a year and spends it down, so the meaningful unit is transactions PER DRAW, not per month. At 12/month the implied ticket collapsed to ~AED 12, which is a coffee, not a reason to pledge your gold. THE AVERAGE TICKET FALLS OUT AS drawn amount / this number, and the draw events cancel - so the ticket depends only on how large a draw is and how many purchases it is spent across. ⚠ IT ALSO CHANGES WHAT THE CARD IS FOR: not daily groceries, but occasional larger needs - school fees, a medical bill, an emergency - funded by borrowing against savings rather than liquidating them. That is a materially different product story and should be put to the client in those words. ASSUMPTION.</t>
+          <t>RE-BASED 2026-08-20 from 12 transactions/MONTH once the card became a drawdown on the gold facility. Under that model the customer borrows a lump (limit x drawn share) a couple of times a year and spends it down, so the meaningful unit is transactions PER DRAW, not per month. At 12/month the implied ticket collapsed to ~AED 12, which is a coffee, not a reason to pledge your gold. THE AVERAGE TICKET FALLS OUT AS drawn amount / this number, and the draw events cancel - so the ticket depends only on how large a draw is and how many purchases it is spent across. IT ALSO CHANGES WHAT THE CARD IS FOR: not daily groceries, but occasional larger needs - school fees, a medical bill, an emergency - funded by borrowing against savings rather than liquidating them. That is a materially different product story and should be put to the client in those words. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>SET AT 0.15 on 2026-08-21, client instruction - the same day it came DOWN from 0.20 to 0.08, so it has landed close to where it started. What has genuinely changed is not the number but the STRUCTURE. ⚠ THE UNIT ALSO CHANGED, AND THAT MATTERS: it is now the share of NEW customers who take the plan when they join, feeding a SUBSCRIBER BALANCE that then churns - not a standing share of the whole book that could never fall. The steady-state share of paying customers holding a plan therefore lands BELOW this number. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on; 20% is at the top of the normal range for an OPTIONAL PAID extra on a savings product, which is low single digits to low teens. ⚠ IT IS NOT EQUIVALENT TO THE OLD 20% AND SHOULD NOT BE READ AS A PARTIAL REVERSAL: 20% was a permanent share of the whole book that could never decay, while 15% applies once, on joining, to a balance that then churns at ~7.1% a month. The standing share of paying customers holding a plan settles near 10.5%, not 15%. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on. ASSUMPTION.</t>
+          <t>SET AT 0.15 on 2026-08-21, client instruction - the same day it came DOWN from 0.20 to 0.08, so it has landed close to where it started. What has genuinely changed is not the number but the STRUCTURE. THE UNIT ALSO CHANGED, AND THAT MATTERS: it is now the share of NEW customers who take the plan when they join, feeding a SUBSCRIBER BALANCE that then churns - not a standing share of the whole book that could never fall. The steady-state share of paying customers holding a plan therefore lands BELOW this number. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on; 20% is at the top of the normal range for an OPTIONAL PAID extra on a savings product, which is low single digits to low teens. IT IS NOT EQUIVALENT TO THE OLD 20% AND SHOULD NOT BE READ AS A PARTIAL REVERSAL: 20% was a permanent share of the whole book that could never decay, while 15% applies once, on joining, to a balance that then churns at ~7.1% a month. The standing share of paying customers holding a plan settles near 10.5%, not 15%. NOTHING IS STATED ANYWHERE IN THE CORPUS and no attach benchmark exists for this kind of add-on. ASSUMPTION.</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>ADDED 2026-08-21. THE FIRST IS INCLUDED IN THE PLAN PRICE, so only the excess over 1.0 is charged - at 2.5 that is 1.5 chargeable. No platform publishes beneficiaries-per-will. What anchors it is who these customers are: South Asian migrant workers who remit ~80% of income to families at home, typically supporting a spouse, children and parents. Household sizes in the source countries run ~4.4 in India, ~4.5 in Bangladesh and ~6.8 in Pakistan, so naming 2-3 beneficiaries is conservative against the family they actually support. ⚠ NOT THE SAME AS HOUSEHOLD SIZE - a beneficiary is a named, identity-verified person on a legal instrument, and people name fewer than they support. ASSUMPTION anchored on demographics.</t>
+          <t>ADDED 2026-08-21. THE FIRST IS INCLUDED IN THE PLAN PRICE, so only the excess over 1.0 is charged - at 2.5 that is 1.5 chargeable. No platform publishes beneficiaries-per-will. What anchors it is who these customers are: South Asian migrant workers who remit ~80% of income to families at home, typically supporting a spouse, children and parents. Household sizes in the source countries run ~4.4 in India, ~4.5 in Bangladesh and ~6.8 in Pakistan, so naming 2-3 beneficiaries is conservative against the family they actually support. NOT THE SAME AS HOUSEHOLD SIZE - a beneficiary is a named, identity-verified person on a legal instrument, and people name fewer than they support. ASSUMPTION anchored on demographics.</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. ⚠ THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
+          <t>RAISED 2026-08-21. Base now reaches 11 by Y7, against ~20 nameable Gulf candidates without a gold product - roughly a 55% win rate on the addressable partner market, which is aggressive but arguable for a category with one incumbent. Partner 1 signs in Y2, matching the M13 B2B go-live. THE CANDIDATE LIST IS THE JUSTIFICATION AND IT IS FINITE: e&amp; money, Payit, Careem Pay, Al Ansari, LuLu Money, Rise, NOW Money, Wio, Liv, Mashreq Neo, Klip, PayBy, Jingle Pay, Thawani, BenefitPay, CWallet, Amanat and a handful of banks and exchange houses. Going much above this count means claiming partners that have not been named. ASSUMPTION on a sourced candidate set.</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>THE MIX, NOT THE BIGGEST. A realistic six-partner Gulf book is roughly one Botim-scale (1.7m ACTIVE fintech users, of 8.2-8.5m app users), two at e&amp; money scale (~1.5m subscribers), and three small wallets at a few hundred thousand - which averages near 900k. ⚠ USE ACTIVE USERS, NOT REGISTERED: Botim's own numbers separate 8.5m app users, 3m KYC'd and 1.7m active fintech users, and adopting the headline would overstate this by 5x. CITED for the two largest, ASSUMPTION for the tail.</t>
+          <t>THE MIX, NOT THE BIGGEST. A realistic six-partner Gulf book is roughly one Botim-scale (1.7m ACTIVE fintech users, of 8.2-8.5m app users), two at e&amp; money scale (~1.5m subscribers), and three small wallets at a few hundred thousand - which averages near 900k. USE ACTIVE USERS, NOT REGISTERED: Botim's own numbers separate 8.5m app users, 3m KYC'd and 1.7m active fintech users, and adopting the headline would overstate this by 5x. CITED for the two largest, ASSUMPTION for the tail.</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>OBSERVED ANCHOR: O Gold reports 75,000 ACTIVE users against Botim's 1.7m active fintech users - 4.4% - and 775,000 who merely explored the feature. Base is set at 6%, ABOVE the observed 4.4%, because that figure is roughly six months after the gold feature launched and adoption should mature; 6% is a 1.4x maturation, not a doubling. ⚠ THE 4.4% IS THE ONLY OBSERVED GOLD-ADOPTION RATE FOR A GULF WALLET THAT EXISTS. TRIANGULATED.</t>
+          <t>OBSERVED ANCHOR: O Gold reports 75,000 ACTIVE users against Botim's 1.7m active fintech users - 4.4% - and 775,000 who merely explored the feature. Base is set at 6%, ABOVE the observed 4.4%, because that figure is roughly six months after the gold feature launched and adoption should mature; 6% is a 1.4x maturation, not a doubling. THE 4.4% IS THE ONLY OBSERVED GOLD-ADOPTION RATE FOR A GULF WALLET THAT EXISTS. TRIANGULATED.</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>⚠ RISING GOLD CUTS BOTH WAYS AND THE MODEL CAPTURES BOTH. Metal already held appreciates, but a fixed USD contribution BUYS FEWER GRAMS each year - so AUM does NOT simply compound at the headline rate. Only the collateral-linked streams move with this row (card limit, and lending through it); the entry fee is a percentage of a USD contribution and is untouched by the gold price.</t>
+          <t>RISING GOLD CUTS BOTH WAYS AND THE MODEL CAPTURES BOTH. Metal already held appreciates, but a fixed USD contribution BUYS FEWER GRAMS each year - so AUM does NOT simply compound at the headline rate. Only the collateral-linked streams move with this row (card limit, and lending through it); the entry fee is a percentage of a USD contribution and is untouched by the gold price.</t>
         </is>
       </c>
     </row>
@@ -24986,7 +24986,7 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>THE NUMBER TO QUOTE AGAINST OTHER GOLD PLATFORMS, and the only one that compares like for like. Collateral-eligible AUM above is SMALLER because it also removes gold moved out of Aurumix's control - a token in a private wallet cannot back a credit limit, but THE METAL IS STILL IN THE VAULT, so it is still gold under custody. PAXG, Kinesis and Comtech all publish the custody measure. ⚠ COMPARE IN GRAMS, NOT DOLLARS: every published USD figure carries the gold price of its own vintage, so a comparison in dollars is really a comparison of gold prices. Comtech Gold, the closest comparable - Dubai, DMCC-licensed, tokenised gold - holds ~141,000 g.</t>
+          <t>THE NUMBER TO QUOTE AGAINST OTHER GOLD PLATFORMS, and the only one that compares like for like. Collateral-eligible AUM above is SMALLER because it also removes gold moved out of Aurumix's control - a token in a private wallet cannot back a credit limit, but THE METAL IS STILL IN THE VAULT, so it is still gold under custody. PAXG, Kinesis and Comtech all publish the custody measure. COMPARE IN GRAMS, NOT DOLLARS: every published USD figure carries the gold price of its own vintage, so a comparison in dollars is really a comparison of gold prices. Comtech Gold, the closest comparable - Dubai, DMCC-licensed, tokenised gold - holds ~141,000 g.</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25249,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>THE HONEST SERIES FOR JUDGING EXECUTION is the constant-price row: it strips the gold price out and leaves grams accumulated, which is the part Aurumix controls. The headline above will grow even if the business does not. ⚠ SET GOLD APPRECIATION TO THE CONSERVATIVE SCENARIO (0.0%) TO RECOVER THE ORIGINAL FLAT-PRICE MODEL, under which these two rows are identical by construction.</t>
+          <t>THE HONEST SERIES FOR JUDGING EXECUTION is the constant-price row: it strips the gold price out and leaves grams accumulated, which is the part Aurumix controls. The headline above will grow even if the business does not. SET GOLD APPRECIATION TO THE CONSERVATIVE SCENARIO (0.0%) TO RECOVER THE ORIGINAL FLAT-PRICE MODEL, under which these two rows are identical by construction.</t>
         </is>
       </c>
     </row>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>SIZES THE LARGEST STREAM. No UAE/MENA figure is published. FLOOR IS 36% - take that into the sponsor conversation as the walk-away. TRIANGULATED.</t>
+          <t>BANDS CORRECTED 2026-08-21 - THEY WERE INVERTED. Aggressive was 0.85 and conservative 0.55, meaning the OPTIMISTIC scenario handed MORE of the interchange to the programme manager and cut Aurumix's share from 28% to 15%. Every other cost-like parameter in this model improves under Aggressive - redemption, CAC, self-custody, the holder multiplier - and this one moved the other way. Flipping the scenario made interchange fall 46% in the good case and rise 61% in the bad one. Aggressive is now 0.36, THE DOCUMENTED FLOOR, which is the best deal observed anywhere and the right walk-away to take into a sponsor conversation - at that level Aurumix keeps 64% rather than 28%, and interchange more than doubles. Conservative is 0.85. WHY AURUMIX ONLY GETS A SLICE AT ALL: it is not a bank and cannot issue cards, so a programme manager holds the BIN, the scheme membership, settlement and dispute handling, and takes the majority for it. That much is normal. 72% is near the BAD END of the 36-85% range, so the base case is deliberately unfavourable - THIS IS A COMMERCIAL NEGOTIATION, NOT A MODELLING ASSUMPTION, and it is one of the few places where a better contract directly doubles a revenue line. No UAE/MENA figure is published. TRIANGULATED.</t>
         </is>
       </c>
     </row>
@@ -5431,11 +5431,11 @@
         <v>0.72</v>
       </c>
       <c r="D44" s="19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E44" s="19" t="n">
         <v>0.85</v>
       </c>
-      <c r="E44" s="19" t="n">
-        <v>0.55</v>
-      </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
           <t>%</t>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>SIZES THE LARGEST STREAM. No UAE/MENA figure is published. FLOOR IS 36% - take that into the sponsor conversation as the walk-away. TRIANGULATED.</t>
+          <t>BANDS CORRECTED 2026-08-21 - THEY WERE INVERTED. Aggressive was 0.85 and conservative 0.55, meaning the OPTIMISTIC scenario handed MORE of the interchange to the programme manager and cut Aurumix's share from 28% to 15%. Every other cost-like parameter in this model improves under Aggressive - redemption, CAC, self-custody, the holder multiplier - and this one moved the other way. Flipping the scenario made interchange fall 46% in the good case and rise 61% in the bad one. Aggressive is now 0.36, THE DOCUMENTED FLOOR, which is the best deal observed anywhere and the right walk-away to take into a sponsor conversation - at that level Aurumix keeps 64% rather than 28%, and interchange more than doubles. Conservative is 0.85. WHY AURUMIX ONLY GETS A SLICE AT ALL: it is not a bank and cannot issue cards, so a programme manager holds the BIN, the scheme membership, settlement and dispute handling, and takes the majority for it. That much is normal. 72% is near the BAD END of the 36-85% range, so the base case is deliberately unfavourable - THIS IS A COMMERCIAL NEGOTIATION, NOT A MODELLING ASSUMPTION, and it is one of the few places where a better contract directly doubles a revenue line. No UAE/MENA figure is published. TRIANGULATED.</t>
         </is>
       </c>
     </row>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>BANDS CORRECTED 2026-08-21 - THEY WERE INVERTED. Aggressive was 0.85 and conservative 0.55, meaning the OPTIMISTIC scenario handed MORE of the interchange to the programme manager and cut Aurumix's share from 28% to 15%. Every other cost-like parameter in this model improves under Aggressive - redemption, CAC, self-custody, the holder multiplier - and this one moved the other way. Flipping the scenario made interchange fall 46% in the good case and rise 61% in the bad one. Aggressive is now 0.36, THE DOCUMENTED FLOOR, which is the best deal observed anywhere and the right walk-away to take into a sponsor conversation - at that level Aurumix keeps 64% rather than 28%, and interchange more than doubles. Conservative is 0.85. WHY AURUMIX ONLY GETS A SLICE AT ALL: it is not a bank and cannot issue cards, so a programme manager holds the BIN, the scheme membership, settlement and dispute handling, and takes the majority for it. That much is normal. 72% is near the BAD END of the 36-85% range, so the base case is deliberately unfavourable - THIS IS A COMMERCIAL NEGOTIATION, NOT A MODELLING ASSUMPTION, and it is one of the few places where a better contract directly doubles a revenue line. No UAE/MENA figure is published. TRIANGULATED.</t>
+          <t>LOWERED 2026-08-21 from 0.72, client instruction - AURUMIX NOW KEEPS 40% RATHER THAN 28%. 0.60 sits comfortably inside the 36-85% observed range and is roughly its midpoint, so the base case moves from the pessimistic end to a neutral one. It assumes a NEGOTIATED deal rather than a take-it-or-leave-it one, which is reasonable for a programme with a gold-collateral proposition the manager cannot source elsewhere - but it IS an assumption about a contract that does not exist yet, and the only honest way to hold it is to treat 40% as a target to negotiate to, not a rate already won. BANDS CORRECTED earlier the same day - THEY WERE INVERTED. Aggressive was 0.85 and conservative 0.55, meaning the OPTIMISTIC scenario handed MORE of the interchange to the programme manager and cut Aurumix's share from 28% to 15%. Every other cost-like parameter in this model improves under Aggressive - redemption, CAC, self-custody, the holder multiplier - and this one moved the other way. Flipping the scenario made interchange fall 46% in the good case and rise 61% in the bad one. Aggressive is now 0.36, THE DOCUMENTED FLOOR, which is the best deal observed anywhere and the right walk-away to take into a sponsor conversation - at that level Aurumix keeps 64% rather than 28%, and interchange more than doubles. Conservative is 0.85. WHY AURUMIX ONLY GETS A SLICE AT ALL: it is not a bank and cannot issue cards, so a programme manager holds the BIN, the scheme membership, settlement and dispute handling, and takes the majority for it. That much is normal. 72% is near the BAD END of the 36-85% range, so the base case is deliberately unfavourable - THIS IS A COMMERCIAL NEGOTIATION, NOT A MODELLING ASSUMPTION, and it is one of the few places where a better contract directly doubles a revenue line. No UAE/MENA figure is published. TRIANGULATED.</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
         <v/>
       </c>
       <c r="C44" s="19" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="D44" s="19" t="n">
         <v>0.36</v>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>BANDS CORRECTED 2026-08-21 - THEY WERE INVERTED. Aggressive was 0.85 and conservative 0.55, meaning the OPTIMISTIC scenario handed MORE of the interchange to the programme manager and cut Aurumix's share from 28% to 15%. Every other cost-like parameter in this model improves under Aggressive - redemption, CAC, self-custody, the holder multiplier - and this one moved the other way. Flipping the scenario made interchange fall 46% in the good case and rise 61% in the bad one. Aggressive is now 0.36, THE DOCUMENTED FLOOR, which is the best deal observed anywhere and the right walk-away to take into a sponsor conversation - at that level Aurumix keeps 64% rather than 28%, and interchange more than doubles. Conservative is 0.85. WHY AURUMIX ONLY GETS A SLICE AT ALL: it is not a bank and cannot issue cards, so a programme manager holds the BIN, the scheme membership, settlement and dispute handling, and takes the majority for it. That much is normal. 72% is near the BAD END of the 36-85% range, so the base case is deliberately unfavourable - THIS IS A COMMERCIAL NEGOTIATION, NOT A MODELLING ASSUMPTION, and it is one of the few places where a better contract directly doubles a revenue line. No UAE/MENA figure is published. TRIANGULATED.</t>
+          <t>LOWERED 2026-08-21 from 0.72, client instruction - AURUMIX NOW KEEPS 40% RATHER THAN 28%. 0.60 sits comfortably inside the 36-85% observed range and is roughly its midpoint, so the base case moves from the pessimistic end to a neutral one. It assumes a NEGOTIATED deal rather than a take-it-or-leave-it one, which is reasonable for a programme with a gold-collateral proposition the manager cannot source elsewhere - but it IS an assumption about a contract that does not exist yet, and the only honest way to hold it is to treat 40% as a target to negotiate to, not a rate already won. BANDS CORRECTED earlier the same day - THEY WERE INVERTED. Aggressive was 0.85 and conservative 0.55, meaning the OPTIMISTIC scenario handed MORE of the interchange to the programme manager and cut Aurumix's share from 28% to 15%. Every other cost-like parameter in this model improves under Aggressive - redemption, CAC, self-custody, the holder multiplier - and this one moved the other way. Flipping the scenario made interchange fall 46% in the good case and rise 61% in the bad one. Aggressive is now 0.36, THE DOCUMENTED FLOOR, which is the best deal observed anywhere and the right walk-away to take into a sponsor conversation - at that level Aurumix keeps 64% rather than 28%, and interchange more than doubles. Conservative is 0.85. WHY AURUMIX ONLY GETS A SLICE AT ALL: it is not a bank and cannot issue cards, so a programme manager holds the BIN, the scheme membership, settlement and dispute handling, and takes the majority for it. That much is normal. 72% is near the BAD END of the 36-85% range, so the base case is deliberately unfavourable - THIS IS A COMMERCIAL NEGOTIATION, NOT A MODELLING ASSUMPTION, and it is one of the few places where a better contract directly doubles a revenue line. No UAE/MENA figure is published. TRIANGULATED.</t>
         </is>
       </c>
     </row>

--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
@@ -345,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -478,6 +478,7 @@
     </xf>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -9045,7 +9046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE329"/>
+  <dimension ref="A1:AE343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -40422,6 +40423,974 @@
         <v/>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="51" t="inlineStr">
+        <is>
+          <t>UNIT ECONOMICS - payback, the acquisition treadmill and the funding need</t>
+        </is>
+      </c>
+      <c r="B331" s="52" t="n"/>
+      <c r="C331" s="52" t="n"/>
+      <c r="D331" s="52" t="n"/>
+      <c r="E331" s="52" t="n"/>
+      <c r="F331" s="52" t="n"/>
+      <c r="G331" s="52" t="n"/>
+      <c r="H331" s="52" t="n"/>
+      <c r="I331" s="52" t="n"/>
+      <c r="J331" s="52" t="n"/>
+      <c r="K331" s="52" t="n"/>
+      <c r="L331" s="52" t="n"/>
+      <c r="M331" s="52" t="n"/>
+      <c r="N331" s="52" t="n"/>
+      <c r="O331" s="52" t="n"/>
+      <c r="P331" s="52" t="n"/>
+      <c r="Q331" s="52" t="n"/>
+      <c r="R331" s="52" t="n"/>
+      <c r="S331" s="52" t="n"/>
+      <c r="T331" s="52" t="n"/>
+      <c r="U331" s="52" t="n"/>
+      <c r="V331" s="52" t="n"/>
+      <c r="W331" s="52" t="n"/>
+      <c r="X331" s="52" t="n"/>
+      <c r="Y331" s="52" t="n"/>
+      <c r="Z331" s="52" t="n"/>
+      <c r="AA331" s="52" t="n"/>
+      <c r="AB331" s="52" t="n"/>
+      <c r="AC331" s="52" t="n"/>
+      <c r="AD331" s="52" t="n"/>
+      <c r="AE331" s="52" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Customers lost to holders this period</t>
+        </is>
+      </c>
+      <c r="B332" s="23" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="C332" s="50">
+        <f>MAX(0,C162-C159)</f>
+        <v/>
+      </c>
+      <c r="D332" s="50">
+        <f>MAX(0,C159+D162-D159)</f>
+        <v/>
+      </c>
+      <c r="E332" s="50">
+        <f>MAX(0,D159+E162-E159)</f>
+        <v/>
+      </c>
+      <c r="F332" s="50">
+        <f>MAX(0,E159+F162-F159)</f>
+        <v/>
+      </c>
+      <c r="G332" s="50">
+        <f>MAX(0,F159+G162-G159)</f>
+        <v/>
+      </c>
+      <c r="H332" s="50">
+        <f>MAX(0,G159+H162-H159)</f>
+        <v/>
+      </c>
+      <c r="I332" s="50">
+        <f>MAX(0,H159+I162-I159)</f>
+        <v/>
+      </c>
+      <c r="J332" s="50">
+        <f>MAX(0,I159+J162-J159)</f>
+        <v/>
+      </c>
+      <c r="K332" s="50">
+        <f>MAX(0,J159+K162-K159)</f>
+        <v/>
+      </c>
+      <c r="L332" s="50">
+        <f>MAX(0,K159+L162-L159)</f>
+        <v/>
+      </c>
+      <c r="M332" s="50">
+        <f>MAX(0,L159+M162-M159)</f>
+        <v/>
+      </c>
+      <c r="N332" s="50">
+        <f>MAX(0,M159+N162-N159)</f>
+        <v/>
+      </c>
+      <c r="O332" s="50">
+        <f>MAX(0,N159+O162-O159)</f>
+        <v/>
+      </c>
+      <c r="P332" s="50">
+        <f>MAX(0,O159+P162-P159)</f>
+        <v/>
+      </c>
+      <c r="Q332" s="50">
+        <f>MAX(0,P159+Q162-Q159)</f>
+        <v/>
+      </c>
+      <c r="R332" s="50">
+        <f>MAX(0,Q159+R162-R159)</f>
+        <v/>
+      </c>
+      <c r="S332" s="50">
+        <f>MAX(0,R159+S162-S159)</f>
+        <v/>
+      </c>
+      <c r="T332" s="50">
+        <f>MAX(0,S159+T162-T159)</f>
+        <v/>
+      </c>
+      <c r="U332" s="50">
+        <f>MAX(0,T159+U162-U159)</f>
+        <v/>
+      </c>
+      <c r="V332" s="50">
+        <f>MAX(0,U159+V162-V159)</f>
+        <v/>
+      </c>
+      <c r="W332" s="50">
+        <f>MAX(0,V159+W162-W159)</f>
+        <v/>
+      </c>
+      <c r="X332" s="50">
+        <f>MAX(0,W159+X162-X159)</f>
+        <v/>
+      </c>
+      <c r="Y332" s="50">
+        <f>MAX(0,X159+Y162-Y159)</f>
+        <v/>
+      </c>
+      <c r="Z332" s="50">
+        <f>MAX(0,Y159+Z162-Z159)</f>
+        <v/>
+      </c>
+      <c r="AA332" s="50">
+        <f>MAX(0,Z159+AA162-AA159)</f>
+        <v/>
+      </c>
+      <c r="AB332" s="50">
+        <f>MAX(0,AA159+AB162-AB159)</f>
+        <v/>
+      </c>
+      <c r="AC332" s="50">
+        <f>MAX(0,AB159+AC162-AC159)</f>
+        <v/>
+      </c>
+      <c r="AD332" s="50">
+        <f>MAX(0,AC159+AD162-AD159)</f>
+        <v/>
+      </c>
+      <c r="AE332" s="50">
+        <f>MAX(0,AD159+AE162-AE159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="9" t="inlineStr">
+        <is>
+          <t>OPENING BASE PLUS NEW LESS CLOSING BASE. Nobody counts leavers directly; they are what is left when the balance does not tie. THIS IS THE END OF A PAYING RELATIONSHIP, NOT OF THE CUSTOMER: a lapsed customer becomes a holder, keeps their gold and may still carry a card, so the tail is thin but it is not zero. Deliberately NOT converted into an average life here - see the section note above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT BEFORE ACQUISITION COST</t>
+        </is>
+      </c>
+      <c r="B334" s="23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C334" s="63">
+        <f>C197-C304+C282</f>
+        <v/>
+      </c>
+      <c r="D334" s="63">
+        <f>D197-D304+D282</f>
+        <v/>
+      </c>
+      <c r="E334" s="63">
+        <f>E197-E304+E282</f>
+        <v/>
+      </c>
+      <c r="F334" s="63">
+        <f>F197-F304+F282</f>
+        <v/>
+      </c>
+      <c r="G334" s="63">
+        <f>G197-G304+G282</f>
+        <v/>
+      </c>
+      <c r="H334" s="63">
+        <f>H197-H304+H282</f>
+        <v/>
+      </c>
+      <c r="I334" s="63">
+        <f>I197-I304+I282</f>
+        <v/>
+      </c>
+      <c r="J334" s="63">
+        <f>J197-J304+J282</f>
+        <v/>
+      </c>
+      <c r="K334" s="63">
+        <f>K197-K304+K282</f>
+        <v/>
+      </c>
+      <c r="L334" s="63">
+        <f>L197-L304+L282</f>
+        <v/>
+      </c>
+      <c r="M334" s="63">
+        <f>M197-M304+M282</f>
+        <v/>
+      </c>
+      <c r="N334" s="63">
+        <f>N197-N304+N282</f>
+        <v/>
+      </c>
+      <c r="O334" s="63">
+        <f>O197-O304+O282</f>
+        <v/>
+      </c>
+      <c r="P334" s="63">
+        <f>P197-P304+P282</f>
+        <v/>
+      </c>
+      <c r="Q334" s="63">
+        <f>Q197-Q304+Q282</f>
+        <v/>
+      </c>
+      <c r="R334" s="63">
+        <f>R197-R304+R282</f>
+        <v/>
+      </c>
+      <c r="S334" s="63">
+        <f>S197-S304+S282</f>
+        <v/>
+      </c>
+      <c r="T334" s="63">
+        <f>T197-T304+T282</f>
+        <v/>
+      </c>
+      <c r="U334" s="63">
+        <f>U197-U304+U282</f>
+        <v/>
+      </c>
+      <c r="V334" s="63">
+        <f>V197-V304+V282</f>
+        <v/>
+      </c>
+      <c r="W334" s="63">
+        <f>W197-W304+W282</f>
+        <v/>
+      </c>
+      <c r="X334" s="63">
+        <f>X197-X304+X282</f>
+        <v/>
+      </c>
+      <c r="Y334" s="63">
+        <f>Y197-Y304+Y282</f>
+        <v/>
+      </c>
+      <c r="Z334" s="63">
+        <f>Z197-Z304+Z282</f>
+        <v/>
+      </c>
+      <c r="AA334" s="63">
+        <f>AA197-AA304+AA282</f>
+        <v/>
+      </c>
+      <c r="AB334" s="63">
+        <f>AB197-AB304+AB282</f>
+        <v/>
+      </c>
+      <c r="AC334" s="63">
+        <f>AC197-AC304+AC282</f>
+        <v/>
+      </c>
+      <c r="AD334" s="63">
+        <f>AD197-AD304+AD282</f>
+        <v/>
+      </c>
+      <c r="AE334" s="63">
+        <f>AE197-AE304+AE282</f>
+        <v/>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="9" t="inlineStr">
+        <is>
+          <t>THE RIGHT NUMERATOR TO SET AGAINST CAC, because acquisition is the thing being paid for and must not sit on both sides. DELIBERATELY CONSERVATIVE: it still carries the FIXED cost base - licences, insurance, technology - so it understates what a marginal customer contributes and improves with scale by construction. A true marginal contribution would need a fixed/variable split this model does not carry, and inventing one would put a judgement call under the payback below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Contribution per paying customer (annualised)</t>
+        </is>
+      </c>
+      <c r="B336" s="23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C336" s="59">
+        <f>IF(C159=0,0,C334/C159/C7*12)</f>
+        <v/>
+      </c>
+      <c r="D336" s="59">
+        <f>IF(D159=0,0,D334/D159/D7*12)</f>
+        <v/>
+      </c>
+      <c r="E336" s="59">
+        <f>IF(E159=0,0,E334/E159/E7*12)</f>
+        <v/>
+      </c>
+      <c r="F336" s="59">
+        <f>IF(F159=0,0,F334/F159/F7*12)</f>
+        <v/>
+      </c>
+      <c r="G336" s="59">
+        <f>IF(G159=0,0,G334/G159/G7*12)</f>
+        <v/>
+      </c>
+      <c r="H336" s="59">
+        <f>IF(H159=0,0,H334/H159/H7*12)</f>
+        <v/>
+      </c>
+      <c r="I336" s="59">
+        <f>IF(I159=0,0,I334/I159/I7*12)</f>
+        <v/>
+      </c>
+      <c r="J336" s="59">
+        <f>IF(J159=0,0,J334/J159/J7*12)</f>
+        <v/>
+      </c>
+      <c r="K336" s="59">
+        <f>IF(K159=0,0,K334/K159/K7*12)</f>
+        <v/>
+      </c>
+      <c r="L336" s="59">
+        <f>IF(L159=0,0,L334/L159/L7*12)</f>
+        <v/>
+      </c>
+      <c r="M336" s="59">
+        <f>IF(M159=0,0,M334/M159/M7*12)</f>
+        <v/>
+      </c>
+      <c r="N336" s="59">
+        <f>IF(N159=0,0,N334/N159/N7*12)</f>
+        <v/>
+      </c>
+      <c r="O336" s="59">
+        <f>IF(O159=0,0,O334/O159/O7*12)</f>
+        <v/>
+      </c>
+      <c r="P336" s="59">
+        <f>IF(P159=0,0,P334/P159/P7*12)</f>
+        <v/>
+      </c>
+      <c r="Q336" s="59">
+        <f>IF(Q159=0,0,Q334/Q159/Q7*12)</f>
+        <v/>
+      </c>
+      <c r="R336" s="59">
+        <f>IF(R159=0,0,R334/R159/R7*12)</f>
+        <v/>
+      </c>
+      <c r="S336" s="59">
+        <f>IF(S159=0,0,S334/S159/S7*12)</f>
+        <v/>
+      </c>
+      <c r="T336" s="59">
+        <f>IF(T159=0,0,T334/T159/T7*12)</f>
+        <v/>
+      </c>
+      <c r="U336" s="59">
+        <f>IF(U159=0,0,U334/U159/U7*12)</f>
+        <v/>
+      </c>
+      <c r="V336" s="59">
+        <f>IF(V159=0,0,V334/V159/V7*12)</f>
+        <v/>
+      </c>
+      <c r="W336" s="59">
+        <f>IF(W159=0,0,W334/W159/W7*12)</f>
+        <v/>
+      </c>
+      <c r="X336" s="59">
+        <f>IF(X159=0,0,X334/X159/X7*12)</f>
+        <v/>
+      </c>
+      <c r="Y336" s="59">
+        <f>IF(Y159=0,0,Y334/Y159/Y7*12)</f>
+        <v/>
+      </c>
+      <c r="Z336" s="59">
+        <f>IF(Z159=0,0,Z334/Z159/Z7*12)</f>
+        <v/>
+      </c>
+      <c r="AA336" s="59">
+        <f>IF(AA159=0,0,AA334/AA159/AA7*12)</f>
+        <v/>
+      </c>
+      <c r="AB336" s="59">
+        <f>IF(AB159=0,0,AB334/AB159/AB7*12)</f>
+        <v/>
+      </c>
+      <c r="AC336" s="59">
+        <f>IF(AC159=0,0,AC334/AC159/AC7*12)</f>
+        <v/>
+      </c>
+      <c r="AD336" s="59">
+        <f>IF(AD159=0,0,AD334/AD159/AD7*12)</f>
+        <v/>
+      </c>
+      <c r="AE336" s="59">
+        <f>IF(AE159=0,0,AE334/AE159/AE7*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Payback on contribution</t>
+        </is>
+      </c>
+      <c r="B337" s="23" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="C337" s="60">
+        <f>IF(C336&lt;=0,"",C283/(C336/12))</f>
+        <v/>
+      </c>
+      <c r="D337" s="60">
+        <f>IF(D336&lt;=0,"",D283/(D336/12))</f>
+        <v/>
+      </c>
+      <c r="E337" s="60">
+        <f>IF(E336&lt;=0,"",E283/(E336/12))</f>
+        <v/>
+      </c>
+      <c r="F337" s="60">
+        <f>IF(F336&lt;=0,"",F283/(F336/12))</f>
+        <v/>
+      </c>
+      <c r="G337" s="60">
+        <f>IF(G336&lt;=0,"",G283/(G336/12))</f>
+        <v/>
+      </c>
+      <c r="H337" s="60">
+        <f>IF(H336&lt;=0,"",H283/(H336/12))</f>
+        <v/>
+      </c>
+      <c r="I337" s="60">
+        <f>IF(I336&lt;=0,"",I283/(I336/12))</f>
+        <v/>
+      </c>
+      <c r="J337" s="60">
+        <f>IF(J336&lt;=0,"",J283/(J336/12))</f>
+        <v/>
+      </c>
+      <c r="K337" s="60">
+        <f>IF(K336&lt;=0,"",K283/(K336/12))</f>
+        <v/>
+      </c>
+      <c r="L337" s="60">
+        <f>IF(L336&lt;=0,"",L283/(L336/12))</f>
+        <v/>
+      </c>
+      <c r="M337" s="60">
+        <f>IF(M336&lt;=0,"",M283/(M336/12))</f>
+        <v/>
+      </c>
+      <c r="N337" s="60">
+        <f>IF(N336&lt;=0,"",N283/(N336/12))</f>
+        <v/>
+      </c>
+      <c r="O337" s="60">
+        <f>IF(O336&lt;=0,"",O283/(O336/12))</f>
+        <v/>
+      </c>
+      <c r="P337" s="60">
+        <f>IF(P336&lt;=0,"",P283/(P336/12))</f>
+        <v/>
+      </c>
+      <c r="Q337" s="60">
+        <f>IF(Q336&lt;=0,"",Q283/(Q336/12))</f>
+        <v/>
+      </c>
+      <c r="R337" s="60">
+        <f>IF(R336&lt;=0,"",R283/(R336/12))</f>
+        <v/>
+      </c>
+      <c r="S337" s="60">
+        <f>IF(S336&lt;=0,"",S283/(S336/12))</f>
+        <v/>
+      </c>
+      <c r="T337" s="60">
+        <f>IF(T336&lt;=0,"",T283/(T336/12))</f>
+        <v/>
+      </c>
+      <c r="U337" s="60">
+        <f>IF(U336&lt;=0,"",U283/(U336/12))</f>
+        <v/>
+      </c>
+      <c r="V337" s="60">
+        <f>IF(V336&lt;=0,"",V283/(V336/12))</f>
+        <v/>
+      </c>
+      <c r="W337" s="60">
+        <f>IF(W336&lt;=0,"",W283/(W336/12))</f>
+        <v/>
+      </c>
+      <c r="X337" s="60">
+        <f>IF(X336&lt;=0,"",X283/(X336/12))</f>
+        <v/>
+      </c>
+      <c r="Y337" s="60">
+        <f>IF(Y336&lt;=0,"",Y283/(Y336/12))</f>
+        <v/>
+      </c>
+      <c r="Z337" s="60">
+        <f>IF(Z336&lt;=0,"",Z283/(Z336/12))</f>
+        <v/>
+      </c>
+      <c r="AA337" s="60">
+        <f>IF(AA336&lt;=0,"",AA283/(AA336/12))</f>
+        <v/>
+      </c>
+      <c r="AB337" s="60">
+        <f>IF(AB336&lt;=0,"",AB283/(AB336/12))</f>
+        <v/>
+      </c>
+      <c r="AC337" s="60">
+        <f>IF(AC336&lt;=0,"",AC283/(AC336/12))</f>
+        <v/>
+      </c>
+      <c r="AD337" s="60">
+        <f>IF(AD336&lt;=0,"",AD283/(AD336/12))</f>
+        <v/>
+      </c>
+      <c r="AE337" s="60">
+        <f>IF(AE336&lt;=0,"",AE283/(AE336/12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="9" t="inlineStr">
+        <is>
+          <t>CAC OVER MONTHLY CONTRIBUTION - IT NEEDS NO LIFE ESTIMATE, which is why it is here and an LTV:CAC ratio is not. AGAINST THE BLENDED COST PER NEW CUSTOMER, which includes the organic and referred arrivals nobody paid for, so it is the honest denominator for the book as a whole. Set against the UAE PAID CAC alone the payback is materially longer - the marketing CAC prices only the channel it buys. Blank where contribution is negative, which is the early years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="6" t="inlineStr">
+        <is>
+          <t>NEW CUSTOMERS ACQUIRED PER NET CUSTOMER ADDED</t>
+        </is>
+      </c>
+      <c r="B339" s="23" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="C339" s="60">
+        <f>""</f>
+        <v/>
+      </c>
+      <c r="D339" s="60">
+        <f>IF(D159-C159&lt;=0,"",D162/(D159-C159))</f>
+        <v/>
+      </c>
+      <c r="E339" s="60">
+        <f>IF(E159-D159&lt;=0,"",E162/(E159-D159))</f>
+        <v/>
+      </c>
+      <c r="F339" s="60">
+        <f>IF(F159-E159&lt;=0,"",F162/(F159-E159))</f>
+        <v/>
+      </c>
+      <c r="G339" s="60">
+        <f>IF(G159-F159&lt;=0,"",G162/(G159-F159))</f>
+        <v/>
+      </c>
+      <c r="H339" s="60">
+        <f>IF(H159-G159&lt;=0,"",H162/(H159-G159))</f>
+        <v/>
+      </c>
+      <c r="I339" s="60">
+        <f>IF(I159-H159&lt;=0,"",I162/(I159-H159))</f>
+        <v/>
+      </c>
+      <c r="J339" s="60">
+        <f>IF(J159-I159&lt;=0,"",J162/(J159-I159))</f>
+        <v/>
+      </c>
+      <c r="K339" s="60">
+        <f>IF(K159-J159&lt;=0,"",K162/(K159-J159))</f>
+        <v/>
+      </c>
+      <c r="L339" s="60">
+        <f>IF(L159-K159&lt;=0,"",L162/(L159-K159))</f>
+        <v/>
+      </c>
+      <c r="M339" s="60">
+        <f>IF(M159-L159&lt;=0,"",M162/(M159-L159))</f>
+        <v/>
+      </c>
+      <c r="N339" s="60">
+        <f>IF(N159-M159&lt;=0,"",N162/(N159-M159))</f>
+        <v/>
+      </c>
+      <c r="O339" s="60">
+        <f>IF(O159-N159&lt;=0,"",O162/(O159-N159))</f>
+        <v/>
+      </c>
+      <c r="P339" s="60">
+        <f>IF(P159-O159&lt;=0,"",P162/(P159-O159))</f>
+        <v/>
+      </c>
+      <c r="Q339" s="60">
+        <f>IF(Q159-P159&lt;=0,"",Q162/(Q159-P159))</f>
+        <v/>
+      </c>
+      <c r="R339" s="60">
+        <f>IF(R159-Q159&lt;=0,"",R162/(R159-Q159))</f>
+        <v/>
+      </c>
+      <c r="S339" s="60">
+        <f>IF(S159-R159&lt;=0,"",S162/(S159-R159))</f>
+        <v/>
+      </c>
+      <c r="T339" s="60">
+        <f>IF(T159-S159&lt;=0,"",T162/(T159-S159))</f>
+        <v/>
+      </c>
+      <c r="U339" s="60">
+        <f>IF(U159-T159&lt;=0,"",U162/(U159-T159))</f>
+        <v/>
+      </c>
+      <c r="V339" s="60">
+        <f>IF(V159-U159&lt;=0,"",V162/(V159-U159))</f>
+        <v/>
+      </c>
+      <c r="W339" s="60">
+        <f>IF(W159-V159&lt;=0,"",W162/(W159-V159))</f>
+        <v/>
+      </c>
+      <c r="X339" s="60">
+        <f>IF(X159-W159&lt;=0,"",X162/(X159-W159))</f>
+        <v/>
+      </c>
+      <c r="Y339" s="60">
+        <f>IF(Y159-X159&lt;=0,"",Y162/(Y159-X159))</f>
+        <v/>
+      </c>
+      <c r="Z339" s="60">
+        <f>IF(Z159-Y159&lt;=0,"",Z162/(Z159-Y159))</f>
+        <v/>
+      </c>
+      <c r="AA339" s="60">
+        <f>IF(AA159-Z159&lt;=0,"",AA162/(AA159-Z159))</f>
+        <v/>
+      </c>
+      <c r="AB339" s="60">
+        <f>IF(AB159-AA159&lt;=0,"",AB162/(AB159-AA159))</f>
+        <v/>
+      </c>
+      <c r="AC339" s="60">
+        <f>IF(AC159-AB159&lt;=0,"",AC162/(AC159-AB159))</f>
+        <v/>
+      </c>
+      <c r="AD339" s="60">
+        <f>IF(AD159-AC159&lt;=0,"",AD162/(AD159-AC159))</f>
+        <v/>
+      </c>
+      <c r="AE339" s="60">
+        <f>IF(AE159-AD159&lt;=0,"",AE162/(AE159-AD159))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="9" t="inlineStr">
+        <is>
+          <t>THE TREADMILL, AND THE SINGLE MOST IMPORTANT STRUCTURAL FACT IN THIS MODEL. Growth here is BOUGHT, not compounded: by Y7 the base grows by a small fraction of what is acquired and the rest leaks to holders. Blank where the base shrinks, which is a worse outcome than a large ratio, not a better one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Funding required to date (P&amp;L deficit + capital tied up)</t>
+        </is>
+      </c>
+      <c r="B341" s="23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C341" s="61">
+        <f>MAX(0,-C329)+C319</f>
+        <v/>
+      </c>
+      <c r="D341" s="61">
+        <f>MAX(0,-D329)+D319</f>
+        <v/>
+      </c>
+      <c r="E341" s="61">
+        <f>MAX(0,-E329)+E319</f>
+        <v/>
+      </c>
+      <c r="F341" s="61">
+        <f>MAX(0,-F329)+F319</f>
+        <v/>
+      </c>
+      <c r="G341" s="61">
+        <f>MAX(0,-G329)+G319</f>
+        <v/>
+      </c>
+      <c r="H341" s="61">
+        <f>MAX(0,-H329)+H319</f>
+        <v/>
+      </c>
+      <c r="I341" s="61">
+        <f>MAX(0,-I329)+I319</f>
+        <v/>
+      </c>
+      <c r="J341" s="61">
+        <f>MAX(0,-J329)+J319</f>
+        <v/>
+      </c>
+      <c r="K341" s="61">
+        <f>MAX(0,-K329)+K319</f>
+        <v/>
+      </c>
+      <c r="L341" s="61">
+        <f>MAX(0,-L329)+L319</f>
+        <v/>
+      </c>
+      <c r="M341" s="61">
+        <f>MAX(0,-M329)+M319</f>
+        <v/>
+      </c>
+      <c r="N341" s="61">
+        <f>MAX(0,-N329)+N319</f>
+        <v/>
+      </c>
+      <c r="O341" s="61">
+        <f>MAX(0,-O329)+O319</f>
+        <v/>
+      </c>
+      <c r="P341" s="61">
+        <f>MAX(0,-P329)+P319</f>
+        <v/>
+      </c>
+      <c r="Q341" s="61">
+        <f>MAX(0,-Q329)+Q319</f>
+        <v/>
+      </c>
+      <c r="R341" s="61">
+        <f>MAX(0,-R329)+R319</f>
+        <v/>
+      </c>
+      <c r="S341" s="61">
+        <f>MAX(0,-S329)+S319</f>
+        <v/>
+      </c>
+      <c r="T341" s="61">
+        <f>MAX(0,-T329)+T319</f>
+        <v/>
+      </c>
+      <c r="U341" s="61">
+        <f>MAX(0,-U329)+U319</f>
+        <v/>
+      </c>
+      <c r="V341" s="61">
+        <f>MAX(0,-V329)+V319</f>
+        <v/>
+      </c>
+      <c r="W341" s="61">
+        <f>MAX(0,-W329)+W319</f>
+        <v/>
+      </c>
+      <c r="X341" s="61">
+        <f>MAX(0,-X329)+X319</f>
+        <v/>
+      </c>
+      <c r="Y341" s="61">
+        <f>MAX(0,-Y329)+Y319</f>
+        <v/>
+      </c>
+      <c r="Z341" s="61">
+        <f>MAX(0,-Z329)+Z319</f>
+        <v/>
+      </c>
+      <c r="AA341" s="61">
+        <f>MAX(0,-AA329)+AA319</f>
+        <v/>
+      </c>
+      <c r="AB341" s="61">
+        <f>MAX(0,-AB329)+AB319</f>
+        <v/>
+      </c>
+      <c r="AC341" s="61">
+        <f>MAX(0,-AC329)+AC319</f>
+        <v/>
+      </c>
+      <c r="AD341" s="61">
+        <f>MAX(0,-AD329)+AD319</f>
+        <v/>
+      </c>
+      <c r="AE341" s="61">
+        <f>MAX(0,-AE329)+AE319</f>
+        <v/>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>PEAK FUNDING NEED</t>
+        </is>
+      </c>
+      <c r="B342" s="23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C342" s="63">
+        <f>C341</f>
+        <v/>
+      </c>
+      <c r="D342" s="63">
+        <f>MAX(C342,D341)</f>
+        <v/>
+      </c>
+      <c r="E342" s="63">
+        <f>MAX(D342,E341)</f>
+        <v/>
+      </c>
+      <c r="F342" s="63">
+        <f>MAX(E342,F341)</f>
+        <v/>
+      </c>
+      <c r="G342" s="63">
+        <f>MAX(F342,G341)</f>
+        <v/>
+      </c>
+      <c r="H342" s="63">
+        <f>MAX(G342,H341)</f>
+        <v/>
+      </c>
+      <c r="I342" s="63">
+        <f>MAX(H342,I341)</f>
+        <v/>
+      </c>
+      <c r="J342" s="63">
+        <f>MAX(I342,J341)</f>
+        <v/>
+      </c>
+      <c r="K342" s="63">
+        <f>MAX(J342,K341)</f>
+        <v/>
+      </c>
+      <c r="L342" s="63">
+        <f>MAX(K342,L341)</f>
+        <v/>
+      </c>
+      <c r="M342" s="63">
+        <f>MAX(L342,M341)</f>
+        <v/>
+      </c>
+      <c r="N342" s="63">
+        <f>MAX(M342,N341)</f>
+        <v/>
+      </c>
+      <c r="O342" s="63">
+        <f>MAX(N342,O341)</f>
+        <v/>
+      </c>
+      <c r="P342" s="63">
+        <f>MAX(O342,P341)</f>
+        <v/>
+      </c>
+      <c r="Q342" s="63">
+        <f>MAX(P342,Q341)</f>
+        <v/>
+      </c>
+      <c r="R342" s="63">
+        <f>MAX(Q342,R341)</f>
+        <v/>
+      </c>
+      <c r="S342" s="63">
+        <f>MAX(R342,S341)</f>
+        <v/>
+      </c>
+      <c r="T342" s="63">
+        <f>MAX(S342,T341)</f>
+        <v/>
+      </c>
+      <c r="U342" s="63">
+        <f>MAX(T342,U341)</f>
+        <v/>
+      </c>
+      <c r="V342" s="63">
+        <f>MAX(U342,V341)</f>
+        <v/>
+      </c>
+      <c r="W342" s="63">
+        <f>MAX(V342,W341)</f>
+        <v/>
+      </c>
+      <c r="X342" s="63">
+        <f>MAX(W342,X341)</f>
+        <v/>
+      </c>
+      <c r="Y342" s="63">
+        <f>MAX(X342,Y341)</f>
+        <v/>
+      </c>
+      <c r="Z342" s="63">
+        <f>MAX(Y342,Z341)</f>
+        <v/>
+      </c>
+      <c r="AA342" s="63">
+        <f>MAX(Z342,AA341)</f>
+        <v/>
+      </c>
+      <c r="AB342" s="63">
+        <f>MAX(AA342,AB341)</f>
+        <v/>
+      </c>
+      <c r="AC342" s="63">
+        <f>MAX(AB342,AC341)</f>
+        <v/>
+      </c>
+      <c r="AD342" s="63">
+        <f>MAX(AC342,AD341)</f>
+        <v/>
+      </c>
+      <c r="AE342" s="63">
+        <f>MAX(AD342,AE341)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="9" t="inlineStr">
+        <is>
+          <t>A RUNNING PEAK, so it never falls once reached - the business must be funded for the worst point it passes through, not for where it ends. IT INHERITS THE NET PROFIT CAVEAT: headcount, legal, security, corporate and tax are still absent from the cost base, so the deficit is an UNDERSTATEMENT and the real funding need is higher. The capital component is locked, not spent, and comes back.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -40433,7 +41402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -42720,7 +43689,7 @@
     <row r="77" ht="18" customHeight="1">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>REGULATORY CAPITAL (locked, not spent)</t>
+          <t>UNIT ECONOMICS (derived - no new assumptions)</t>
         </is>
       </c>
       <c r="B77" s="13" t="n"/>
@@ -42735,741 +43704,1003 @@
       <c r="K77" s="13" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Paid-up capital - VA Issuance</t>
-        </is>
-      </c>
-      <c r="D78" s="37">
-        <f>Model!N311</f>
-        <v/>
-      </c>
-      <c r="E78" s="37">
-        <f>Model!Z311</f>
-        <v/>
-      </c>
-      <c r="F78" s="37">
-        <f>Model!AA311</f>
-        <v/>
-      </c>
-      <c r="G78" s="37">
-        <f>Model!AB311</f>
-        <v/>
-      </c>
-      <c r="H78" s="37">
-        <f>Model!AC311</f>
-        <v/>
-      </c>
-      <c r="I78" s="37">
-        <f>Model!AD311</f>
-        <v/>
-      </c>
-      <c r="J78" s="37">
-        <f>Model!AE311</f>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>PROFIT BEFORE ACQUISITION COST</t>
+        </is>
+      </c>
+      <c r="D78" s="72">
+        <f>SUM(Model!C334:N334)</f>
+        <v/>
+      </c>
+      <c r="E78" s="72">
+        <f>SUM(Model!O334:Z334)</f>
+        <v/>
+      </c>
+      <c r="F78" s="72">
+        <f>Model!AA334</f>
+        <v/>
+      </c>
+      <c r="G78" s="72">
+        <f>Model!AB334</f>
+        <v/>
+      </c>
+      <c r="H78" s="72">
+        <f>Model!AC334</f>
+        <v/>
+      </c>
+      <c r="I78" s="72">
+        <f>Model!AD334</f>
+        <v/>
+      </c>
+      <c r="J78" s="72">
+        <f>Model!AE334</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Paid-up capital - licensed activities</t>
-        </is>
-      </c>
-      <c r="D79" s="37">
-        <f>Model!N313</f>
-        <v/>
-      </c>
-      <c r="E79" s="37">
-        <f>Model!Z313</f>
-        <v/>
-      </c>
-      <c r="F79" s="37">
-        <f>Model!AA313</f>
-        <v/>
-      </c>
-      <c r="G79" s="37">
-        <f>Model!AB313</f>
-        <v/>
-      </c>
-      <c r="H79" s="37">
-        <f>Model!AC313</f>
-        <v/>
-      </c>
-      <c r="I79" s="37">
-        <f>Model!AD313</f>
-        <v/>
-      </c>
-      <c r="J79" s="37">
-        <f>Model!AE313</f>
+          <t xml:space="preserve">  Contribution per paying customer (annualised)</t>
+        </is>
+      </c>
+      <c r="D79" s="39">
+        <f>Model!N336</f>
+        <v/>
+      </c>
+      <c r="E79" s="39">
+        <f>Model!Z336</f>
+        <v/>
+      </c>
+      <c r="F79" s="39">
+        <f>Model!AA336</f>
+        <v/>
+      </c>
+      <c r="G79" s="39">
+        <f>Model!AB336</f>
+        <v/>
+      </c>
+      <c r="H79" s="39">
+        <f>Model!AC336</f>
+        <v/>
+      </c>
+      <c r="I79" s="39">
+        <f>Model!AD336</f>
+        <v/>
+      </c>
+      <c r="J79" s="39">
+        <f>Model!AE336</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL PAID-UP CAPITAL REQUIRED</t>
-        </is>
-      </c>
-      <c r="D80" s="72">
-        <f>Model!N315</f>
-        <v/>
-      </c>
-      <c r="E80" s="72">
-        <f>Model!Z315</f>
-        <v/>
-      </c>
-      <c r="F80" s="72">
-        <f>Model!AA315</f>
-        <v/>
-      </c>
-      <c r="G80" s="72">
-        <f>Model!AB315</f>
-        <v/>
-      </c>
-      <c r="H80" s="72">
-        <f>Model!AC315</f>
-        <v/>
-      </c>
-      <c r="I80" s="72">
-        <f>Model!AD315</f>
-        <v/>
-      </c>
-      <c r="J80" s="72">
-        <f>Model!AE315</f>
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Customers lost to holders</t>
+        </is>
+      </c>
+      <c r="D80" s="34">
+        <f>SUM(Model!C332:N332)</f>
+        <v/>
+      </c>
+      <c r="E80" s="34">
+        <f>SUM(Model!O332:Z332)</f>
+        <v/>
+      </c>
+      <c r="F80" s="34">
+        <f>Model!AA332</f>
+        <v/>
+      </c>
+      <c r="G80" s="34">
+        <f>Model!AB332</f>
+        <v/>
+      </c>
+      <c r="H80" s="34">
+        <f>Model!AC332</f>
+        <v/>
+      </c>
+      <c r="I80" s="34">
+        <f>Model!AD332</f>
+        <v/>
+      </c>
+      <c r="J80" s="34">
+        <f>Model!AE332</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net liquid assets required (separate test)</t>
-        </is>
-      </c>
-      <c r="D81" s="37">
-        <f>Model!N316</f>
-        <v/>
-      </c>
-      <c r="E81" s="37">
-        <f>Model!Z316</f>
-        <v/>
-      </c>
-      <c r="F81" s="37">
-        <f>Model!AA316</f>
-        <v/>
-      </c>
-      <c r="G81" s="37">
-        <f>Model!AB316</f>
-        <v/>
-      </c>
-      <c r="H81" s="37">
-        <f>Model!AC316</f>
-        <v/>
-      </c>
-      <c r="I81" s="37">
-        <f>Model!AD316</f>
-        <v/>
-      </c>
-      <c r="J81" s="37">
-        <f>Model!AE316</f>
+          <t xml:space="preserve">  Blended CAC (repeated here so payback can be read)</t>
+        </is>
+      </c>
+      <c r="D81" s="39">
+        <f>Model!N283</f>
+        <v/>
+      </c>
+      <c r="E81" s="39">
+        <f>Model!Z283</f>
+        <v/>
+      </c>
+      <c r="F81" s="39">
+        <f>Model!AA283</f>
+        <v/>
+      </c>
+      <c r="G81" s="39">
+        <f>Model!AB283</f>
+        <v/>
+      </c>
+      <c r="H81" s="39">
+        <f>Model!AC283</f>
+        <v/>
+      </c>
+      <c r="I81" s="39">
+        <f>Model!AD283</f>
+        <v/>
+      </c>
+      <c r="J81" s="39">
+        <f>Model!AE283</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Card settlement prefunding</t>
-        </is>
-      </c>
-      <c r="D82" s="37">
-        <f>Model!N214</f>
-        <v/>
-      </c>
-      <c r="E82" s="37">
-        <f>Model!Z214</f>
-        <v/>
-      </c>
-      <c r="F82" s="37">
-        <f>Model!AA214</f>
-        <v/>
-      </c>
-      <c r="G82" s="37">
-        <f>Model!AB214</f>
-        <v/>
-      </c>
-      <c r="H82" s="37">
-        <f>Model!AC214</f>
-        <v/>
-      </c>
-      <c r="I82" s="37">
-        <f>Model!AD214</f>
-        <v/>
-      </c>
-      <c r="J82" s="37">
-        <f>Model!AE214</f>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>PAYBACK ON CONTRIBUTION (months)</t>
+        </is>
+      </c>
+      <c r="D82" s="74">
+        <f>Model!N337</f>
+        <v/>
+      </c>
+      <c r="E82" s="74">
+        <f>Model!Z337</f>
+        <v/>
+      </c>
+      <c r="F82" s="74">
+        <f>Model!AA337</f>
+        <v/>
+      </c>
+      <c r="G82" s="74">
+        <f>Model!AB337</f>
+        <v/>
+      </c>
+      <c r="H82" s="74">
+        <f>Model!AC337</f>
+        <v/>
+      </c>
+      <c r="I82" s="74">
+        <f>Model!AD337</f>
+        <v/>
+      </c>
+      <c r="J82" s="74">
+        <f>Model!AE337</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>TOTAL CAPITAL TIED UP (float + capital + prefunding)</t>
-        </is>
-      </c>
-      <c r="D83" s="72">
-        <f>Model!N319</f>
-        <v/>
-      </c>
-      <c r="E83" s="72">
-        <f>Model!Z319</f>
-        <v/>
-      </c>
-      <c r="F83" s="72">
-        <f>Model!AA319</f>
-        <v/>
-      </c>
-      <c r="G83" s="72">
-        <f>Model!AB319</f>
-        <v/>
-      </c>
-      <c r="H83" s="72">
-        <f>Model!AC319</f>
-        <v/>
-      </c>
-      <c r="I83" s="72">
-        <f>Model!AD319</f>
-        <v/>
-      </c>
-      <c r="J83" s="72">
-        <f>Model!AE319</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t>WORKING CAPITAL - THE FLOAT (not a cost)</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="n"/>
-      <c r="C85" s="13" t="n"/>
-      <c r="D85" s="13" t="n"/>
-      <c r="E85" s="13" t="n"/>
-      <c r="F85" s="13" t="n"/>
-      <c r="G85" s="13" t="n"/>
-      <c r="H85" s="13" t="n"/>
-      <c r="I85" s="13" t="n"/>
-      <c r="J85" s="13" t="n"/>
-      <c r="K85" s="13" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Float required, grams</t>
-        </is>
-      </c>
-      <c r="D86" s="34">
-        <f>Model!N206</f>
-        <v/>
-      </c>
-      <c r="E86" s="34">
-        <f>Model!Z206</f>
-        <v/>
-      </c>
-      <c r="F86" s="34">
-        <f>Model!AA206</f>
-        <v/>
-      </c>
-      <c r="G86" s="34">
-        <f>Model!AB206</f>
-        <v/>
-      </c>
-      <c r="H86" s="34">
-        <f>Model!AC206</f>
-        <v/>
-      </c>
-      <c r="I86" s="34">
-        <f>Model!AD206</f>
-        <v/>
-      </c>
-      <c r="J86" s="34">
-        <f>Model!AE206</f>
-        <v/>
-      </c>
+          <t>NEW CUSTOMERS ACQUIRED PER NET CUSTOMER ADDED</t>
+        </is>
+      </c>
+      <c r="D83" s="74">
+        <f>Model!N339</f>
+        <v/>
+      </c>
+      <c r="E83" s="74">
+        <f>Model!Z339</f>
+        <v/>
+      </c>
+      <c r="F83" s="74">
+        <f>Model!AA339</f>
+        <v/>
+      </c>
+      <c r="G83" s="74">
+        <f>Model!AB339</f>
+        <v/>
+      </c>
+      <c r="H83" s="74">
+        <f>Model!AC339</f>
+        <v/>
+      </c>
+      <c r="I83" s="74">
+        <f>Model!AD339</f>
+        <v/>
+      </c>
+      <c r="J83" s="74">
+        <f>Model!AE339</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>PEAK FUNDING NEED (P&amp;L deficit + capital tied up)</t>
+        </is>
+      </c>
+      <c r="D84" s="72">
+        <f>Model!N342</f>
+        <v/>
+      </c>
+      <c r="E84" s="72">
+        <f>Model!Z342</f>
+        <v/>
+      </c>
+      <c r="F84" s="72">
+        <f>Model!AA342</f>
+        <v/>
+      </c>
+      <c r="G84" s="72">
+        <f>Model!AB342</f>
+        <v/>
+      </c>
+      <c r="H84" s="72">
+        <f>Model!AC342</f>
+        <v/>
+      </c>
+      <c r="I84" s="72">
+        <f>Model!AD342</f>
+        <v/>
+      </c>
+      <c r="J84" s="72">
+        <f>Model!AE342</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>REGULATORY CAPITAL (locked, not spent)</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="n"/>
+      <c r="C86" s="13" t="n"/>
+      <c r="D86" s="13" t="n"/>
+      <c r="E86" s="13" t="n"/>
+      <c r="F86" s="13" t="n"/>
+      <c r="G86" s="13" t="n"/>
+      <c r="H86" s="13" t="n"/>
+      <c r="I86" s="13" t="n"/>
+      <c r="J86" s="13" t="n"/>
+      <c r="K86" s="13" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FLOAT REQUIRED (year-end balance)</t>
-        </is>
-      </c>
-      <c r="D87" s="72">
-        <f>Model!N209</f>
-        <v/>
-      </c>
-      <c r="E87" s="72">
-        <f>Model!Z209</f>
-        <v/>
-      </c>
-      <c r="F87" s="72">
-        <f>Model!AA209</f>
-        <v/>
-      </c>
-      <c r="G87" s="72">
-        <f>Model!AB209</f>
-        <v/>
-      </c>
-      <c r="H87" s="72">
-        <f>Model!AC209</f>
-        <v/>
-      </c>
-      <c r="I87" s="72">
-        <f>Model!AD209</f>
-        <v/>
-      </c>
-      <c r="J87" s="72">
-        <f>Model!AE209</f>
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Paid-up capital - VA Issuance</t>
+        </is>
+      </c>
+      <c r="D87" s="37">
+        <f>Model!N311</f>
+        <v/>
+      </c>
+      <c r="E87" s="37">
+        <f>Model!Z311</f>
+        <v/>
+      </c>
+      <c r="F87" s="37">
+        <f>Model!AA311</f>
+        <v/>
+      </c>
+      <c r="G87" s="37">
+        <f>Model!AB311</f>
+        <v/>
+      </c>
+      <c r="H87" s="37">
+        <f>Model!AC311</f>
+        <v/>
+      </c>
+      <c r="I87" s="37">
+        <f>Model!AD311</f>
+        <v/>
+      </c>
+      <c r="J87" s="37">
+        <f>Model!AE311</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cash needed that year (new grams only)</t>
+          <t xml:space="preserve">  Paid-up capital - licensed activities</t>
         </is>
       </c>
       <c r="D88" s="37">
-        <f>SUM(Model!C211:N211)</f>
+        <f>Model!N313</f>
         <v/>
       </c>
       <c r="E88" s="37">
-        <f>SUM(Model!O211:Z211)</f>
+        <f>Model!Z313</f>
         <v/>
       </c>
       <c r="F88" s="37">
-        <f>Model!AA211</f>
+        <f>Model!AA313</f>
         <v/>
       </c>
       <c r="G88" s="37">
-        <f>Model!AB211</f>
+        <f>Model!AB313</f>
         <v/>
       </c>
       <c r="H88" s="37">
-        <f>Model!AC211</f>
+        <f>Model!AC313</f>
         <v/>
       </c>
       <c r="I88" s="37">
-        <f>Model!AD211</f>
+        <f>Model!AD313</f>
         <v/>
       </c>
       <c r="J88" s="37">
-        <f>Model!AE211</f>
+        <f>Model!AE313</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>CUMULATIVE CASH INVESTED IN THE FLOAT</t>
+          <t>TOTAL PAID-UP CAPITAL REQUIRED</t>
         </is>
       </c>
       <c r="D89" s="72">
-        <f>Model!N213</f>
+        <f>Model!N315</f>
         <v/>
       </c>
       <c r="E89" s="72">
-        <f>Model!Z213</f>
+        <f>Model!Z315</f>
         <v/>
       </c>
       <c r="F89" s="72">
-        <f>Model!AA213</f>
+        <f>Model!AA315</f>
         <v/>
       </c>
       <c r="G89" s="72">
-        <f>Model!AB213</f>
+        <f>Model!AB315</f>
         <v/>
       </c>
       <c r="H89" s="72">
-        <f>Model!AC213</f>
+        <f>Model!AC315</f>
         <v/>
       </c>
       <c r="I89" s="72">
-        <f>Model!AD213</f>
+        <f>Model!AD315</f>
         <v/>
       </c>
       <c r="J89" s="72">
-        <f>Model!AE213</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="A91" s="12" t="inlineStr">
-        <is>
-          <t>CUSTOMERS AND AUM (year end)</t>
-        </is>
-      </c>
-      <c r="B91" s="13" t="n"/>
-      <c r="C91" s="13" t="n"/>
-      <c r="D91" s="13" t="n"/>
-      <c r="E91" s="13" t="n"/>
-      <c r="F91" s="13" t="n"/>
-      <c r="G91" s="13" t="n"/>
-      <c r="H91" s="13" t="n"/>
-      <c r="I91" s="13" t="n"/>
-      <c r="J91" s="13" t="n"/>
-      <c r="K91" s="13" t="n"/>
+        <f>Model!AE315</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net liquid assets required (separate test)</t>
+        </is>
+      </c>
+      <c r="D90" s="37">
+        <f>Model!N316</f>
+        <v/>
+      </c>
+      <c r="E90" s="37">
+        <f>Model!Z316</f>
+        <v/>
+      </c>
+      <c r="F90" s="37">
+        <f>Model!AA316</f>
+        <v/>
+      </c>
+      <c r="G90" s="37">
+        <f>Model!AB316</f>
+        <v/>
+      </c>
+      <c r="H90" s="37">
+        <f>Model!AC316</f>
+        <v/>
+      </c>
+      <c r="I90" s="37">
+        <f>Model!AD316</f>
+        <v/>
+      </c>
+      <c r="J90" s="37">
+        <f>Model!AE316</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Card settlement prefunding</t>
+        </is>
+      </c>
+      <c r="D91" s="37">
+        <f>Model!N214</f>
+        <v/>
+      </c>
+      <c r="E91" s="37">
+        <f>Model!Z214</f>
+        <v/>
+      </c>
+      <c r="F91" s="37">
+        <f>Model!AA214</f>
+        <v/>
+      </c>
+      <c r="G91" s="37">
+        <f>Model!AB214</f>
+        <v/>
+      </c>
+      <c r="H91" s="37">
+        <f>Model!AC214</f>
+        <v/>
+      </c>
+      <c r="I91" s="37">
+        <f>Model!AD214</f>
+        <v/>
+      </c>
+      <c r="J91" s="37">
+        <f>Model!AE214</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>New customers in year</t>
-        </is>
-      </c>
-      <c r="D92" s="34">
-        <f>SUM(Model!C162:N162)</f>
-        <v/>
-      </c>
-      <c r="E92" s="34">
-        <f>SUM(Model!O162:Z162)</f>
-        <v/>
-      </c>
-      <c r="F92" s="34">
-        <f>Model!AA162</f>
-        <v/>
-      </c>
-      <c r="G92" s="34">
-        <f>Model!AB162</f>
-        <v/>
-      </c>
-      <c r="H92" s="34">
-        <f>Model!AC162</f>
-        <v/>
-      </c>
-      <c r="I92" s="34">
-        <f>Model!AD162</f>
-        <v/>
-      </c>
-      <c r="J92" s="34">
-        <f>Model!AE162</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>Paying customers</t>
-        </is>
-      </c>
-      <c r="D93" s="74">
-        <f>Model!N159</f>
-        <v/>
-      </c>
-      <c r="E93" s="74">
-        <f>Model!Z159</f>
-        <v/>
-      </c>
-      <c r="F93" s="74">
-        <f>Model!AA159</f>
-        <v/>
-      </c>
-      <c r="G93" s="74">
-        <f>Model!AB159</f>
-        <v/>
-      </c>
-      <c r="H93" s="74">
-        <f>Model!AC159</f>
-        <v/>
-      </c>
-      <c r="I93" s="74">
-        <f>Model!AD159</f>
-        <v/>
-      </c>
-      <c r="J93" s="74">
-        <f>Model!AE159</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>Holders (stopped paying, still hold gold)</t>
-        </is>
-      </c>
-      <c r="D94" s="34">
-        <f>Model!N160</f>
-        <v/>
-      </c>
-      <c r="E94" s="34">
-        <f>Model!Z160</f>
-        <v/>
-      </c>
-      <c r="F94" s="34">
-        <f>Model!AA160</f>
-        <v/>
-      </c>
-      <c r="G94" s="34">
-        <f>Model!AB160</f>
-        <v/>
-      </c>
-      <c r="H94" s="34">
-        <f>Model!AC160</f>
-        <v/>
-      </c>
-      <c r="I94" s="34">
-        <f>Model!AD160</f>
-        <v/>
-      </c>
-      <c r="J94" s="34">
-        <f>Model!AE160</f>
-        <v/>
-      </c>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL CAPITAL TIED UP (float + capital + prefunding)</t>
+        </is>
+      </c>
+      <c r="D92" s="72">
+        <f>Model!N319</f>
+        <v/>
+      </c>
+      <c r="E92" s="72">
+        <f>Model!Z319</f>
+        <v/>
+      </c>
+      <c r="F92" s="72">
+        <f>Model!AA319</f>
+        <v/>
+      </c>
+      <c r="G92" s="72">
+        <f>Model!AB319</f>
+        <v/>
+      </c>
+      <c r="H92" s="72">
+        <f>Model!AC319</f>
+        <v/>
+      </c>
+      <c r="I92" s="72">
+        <f>Model!AD319</f>
+        <v/>
+      </c>
+      <c r="J92" s="72">
+        <f>Model!AE319</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>WORKING CAPITAL - THE FLOAT (not a cost)</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="n"/>
+      <c r="C94" s="13" t="n"/>
+      <c r="D94" s="13" t="n"/>
+      <c r="E94" s="13" t="n"/>
+      <c r="F94" s="13" t="n"/>
+      <c r="G94" s="13" t="n"/>
+      <c r="H94" s="13" t="n"/>
+      <c r="I94" s="13" t="n"/>
+      <c r="J94" s="13" t="n"/>
+      <c r="K94" s="13" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>Cumulative ever acquired</t>
+          <t xml:space="preserve">  Float required, grams</t>
         </is>
       </c>
       <c r="D95" s="34">
-        <f>Model!N161</f>
+        <f>Model!N206</f>
         <v/>
       </c>
       <c r="E95" s="34">
-        <f>Model!Z161</f>
+        <f>Model!Z206</f>
         <v/>
       </c>
       <c r="F95" s="34">
-        <f>Model!AA161</f>
+        <f>Model!AA206</f>
         <v/>
       </c>
       <c r="G95" s="34">
-        <f>Model!AB161</f>
+        <f>Model!AB206</f>
         <v/>
       </c>
       <c r="H95" s="34">
-        <f>Model!AC161</f>
+        <f>Model!AC206</f>
         <v/>
       </c>
       <c r="I95" s="34">
-        <f>Model!AD161</f>
+        <f>Model!AD206</f>
         <v/>
       </c>
       <c r="J95" s="34">
-        <f>Model!AE161</f>
+        <f>Model!AE206</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>Active cards</t>
-        </is>
-      </c>
-      <c r="D96" s="34">
-        <f>Model!N163</f>
-        <v/>
-      </c>
-      <c r="E96" s="34">
-        <f>Model!Z163</f>
-        <v/>
-      </c>
-      <c r="F96" s="34">
-        <f>Model!AA163</f>
-        <v/>
-      </c>
-      <c r="G96" s="34">
-        <f>Model!AB163</f>
-        <v/>
-      </c>
-      <c r="H96" s="34">
-        <f>Model!AC163</f>
-        <v/>
-      </c>
-      <c r="I96" s="34">
-        <f>Model!AD163</f>
-        <v/>
-      </c>
-      <c r="J96" s="34">
-        <f>Model!AE163</f>
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FLOAT REQUIRED (year-end balance)</t>
+        </is>
+      </c>
+      <c r="D96" s="72">
+        <f>Model!N209</f>
+        <v/>
+      </c>
+      <c r="E96" s="72">
+        <f>Model!Z209</f>
+        <v/>
+      </c>
+      <c r="F96" s="72">
+        <f>Model!AA209</f>
+        <v/>
+      </c>
+      <c r="G96" s="72">
+        <f>Model!AB209</f>
+        <v/>
+      </c>
+      <c r="H96" s="72">
+        <f>Model!AC209</f>
+        <v/>
+      </c>
+      <c r="I96" s="72">
+        <f>Model!AD209</f>
+        <v/>
+      </c>
+      <c r="J96" s="72">
+        <f>Model!AE209</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>Grams under custody</t>
-        </is>
-      </c>
-      <c r="D97" s="34">
-        <f>Model!N165</f>
-        <v/>
-      </c>
-      <c r="E97" s="34">
-        <f>Model!Z165</f>
-        <v/>
-      </c>
-      <c r="F97" s="34">
-        <f>Model!AA165</f>
-        <v/>
-      </c>
-      <c r="G97" s="34">
-        <f>Model!AB165</f>
-        <v/>
-      </c>
-      <c r="H97" s="34">
-        <f>Model!AC165</f>
-        <v/>
-      </c>
-      <c r="I97" s="34">
-        <f>Model!AD165</f>
-        <v/>
-      </c>
-      <c r="J97" s="34">
-        <f>Model!AE165</f>
+          <t xml:space="preserve">  Cash needed that year (new grams only)</t>
+        </is>
+      </c>
+      <c r="D97" s="37">
+        <f>SUM(Model!C211:N211)</f>
+        <v/>
+      </c>
+      <c r="E97" s="37">
+        <f>SUM(Model!O211:Z211)</f>
+        <v/>
+      </c>
+      <c r="F97" s="37">
+        <f>Model!AA211</f>
+        <v/>
+      </c>
+      <c r="G97" s="37">
+        <f>Model!AB211</f>
+        <v/>
+      </c>
+      <c r="H97" s="37">
+        <f>Model!AC211</f>
+        <v/>
+      </c>
+      <c r="I97" s="37">
+        <f>Model!AD211</f>
+        <v/>
+      </c>
+      <c r="J97" s="37">
+        <f>Model!AE211</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Gold under custody (comparable headline)</t>
+          <t>CUMULATIVE CASH INVESTED IN THE FLOAT</t>
         </is>
       </c>
       <c r="D98" s="72">
-        <f>Model!N172</f>
+        <f>Model!N213</f>
         <v/>
       </c>
       <c r="E98" s="72">
-        <f>Model!Z172</f>
+        <f>Model!Z213</f>
         <v/>
       </c>
       <c r="F98" s="72">
-        <f>Model!AA172</f>
+        <f>Model!AA213</f>
         <v/>
       </c>
       <c r="G98" s="72">
-        <f>Model!AB172</f>
+        <f>Model!AB213</f>
         <v/>
       </c>
       <c r="H98" s="72">
-        <f>Model!AC172</f>
+        <f>Model!AC213</f>
         <v/>
       </c>
       <c r="I98" s="72">
-        <f>Model!AD172</f>
+        <f>Model!AD213</f>
         <v/>
       </c>
       <c r="J98" s="72">
-        <f>Model!AE172</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>Grams held (collateral-eligible)</t>
-        </is>
-      </c>
-      <c r="D99" s="34">
-        <f>Model!N164</f>
-        <v/>
-      </c>
-      <c r="E99" s="34">
-        <f>Model!Z164</f>
-        <v/>
-      </c>
-      <c r="F99" s="34">
-        <f>Model!AA164</f>
-        <v/>
-      </c>
-      <c r="G99" s="34">
-        <f>Model!AB164</f>
-        <v/>
-      </c>
-      <c r="H99" s="34">
-        <f>Model!AC164</f>
-        <v/>
-      </c>
-      <c r="I99" s="34">
-        <f>Model!AD164</f>
-        <v/>
-      </c>
-      <c r="J99" s="34">
-        <f>Model!AE164</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>Collateral-eligible AUM</t>
-        </is>
-      </c>
-      <c r="D100" s="72">
-        <f>Model!N167</f>
-        <v/>
-      </c>
-      <c r="E100" s="72">
-        <f>Model!Z167</f>
-        <v/>
-      </c>
-      <c r="F100" s="72">
-        <f>Model!AA167</f>
-        <v/>
-      </c>
-      <c r="G100" s="72">
-        <f>Model!AB167</f>
-        <v/>
-      </c>
-      <c r="H100" s="72">
-        <f>Model!AC167</f>
-        <v/>
-      </c>
-      <c r="I100" s="72">
-        <f>Model!AD167</f>
-        <v/>
-      </c>
-      <c r="J100" s="72">
-        <f>Model!AE167</f>
-        <v/>
-      </c>
+        <f>Model!AE213</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>CUSTOMERS AND AUM (year end)</t>
+        </is>
+      </c>
+      <c r="B100" s="13" t="n"/>
+      <c r="C100" s="13" t="n"/>
+      <c r="D100" s="13" t="n"/>
+      <c r="E100" s="13" t="n"/>
+      <c r="F100" s="13" t="n"/>
+      <c r="G100" s="13" t="n"/>
+      <c r="H100" s="13" t="n"/>
+      <c r="I100" s="13" t="n"/>
+      <c r="J100" s="13" t="n"/>
+      <c r="K100" s="13" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
+          <t>New customers in year</t>
+        </is>
+      </c>
+      <c r="D101" s="34">
+        <f>SUM(Model!C162:N162)</f>
+        <v/>
+      </c>
+      <c r="E101" s="34">
+        <f>SUM(Model!O162:Z162)</f>
+        <v/>
+      </c>
+      <c r="F101" s="34">
+        <f>Model!AA162</f>
+        <v/>
+      </c>
+      <c r="G101" s="34">
+        <f>Model!AB162</f>
+        <v/>
+      </c>
+      <c r="H101" s="34">
+        <f>Model!AC162</f>
+        <v/>
+      </c>
+      <c r="I101" s="34">
+        <f>Model!AD162</f>
+        <v/>
+      </c>
+      <c r="J101" s="34">
+        <f>Model!AE162</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Paying customers</t>
+        </is>
+      </c>
+      <c r="D102" s="75">
+        <f>Model!N159</f>
+        <v/>
+      </c>
+      <c r="E102" s="75">
+        <f>Model!Z159</f>
+        <v/>
+      </c>
+      <c r="F102" s="75">
+        <f>Model!AA159</f>
+        <v/>
+      </c>
+      <c r="G102" s="75">
+        <f>Model!AB159</f>
+        <v/>
+      </c>
+      <c r="H102" s="75">
+        <f>Model!AC159</f>
+        <v/>
+      </c>
+      <c r="I102" s="75">
+        <f>Model!AD159</f>
+        <v/>
+      </c>
+      <c r="J102" s="75">
+        <f>Model!AE159</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Holders (stopped paying, still hold gold)</t>
+        </is>
+      </c>
+      <c r="D103" s="34">
+        <f>Model!N160</f>
+        <v/>
+      </c>
+      <c r="E103" s="34">
+        <f>Model!Z160</f>
+        <v/>
+      </c>
+      <c r="F103" s="34">
+        <f>Model!AA160</f>
+        <v/>
+      </c>
+      <c r="G103" s="34">
+        <f>Model!AB160</f>
+        <v/>
+      </c>
+      <c r="H103" s="34">
+        <f>Model!AC160</f>
+        <v/>
+      </c>
+      <c r="I103" s="34">
+        <f>Model!AD160</f>
+        <v/>
+      </c>
+      <c r="J103" s="34">
+        <f>Model!AE160</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Cumulative ever acquired</t>
+        </is>
+      </c>
+      <c r="D104" s="34">
+        <f>Model!N161</f>
+        <v/>
+      </c>
+      <c r="E104" s="34">
+        <f>Model!Z161</f>
+        <v/>
+      </c>
+      <c r="F104" s="34">
+        <f>Model!AA161</f>
+        <v/>
+      </c>
+      <c r="G104" s="34">
+        <f>Model!AB161</f>
+        <v/>
+      </c>
+      <c r="H104" s="34">
+        <f>Model!AC161</f>
+        <v/>
+      </c>
+      <c r="I104" s="34">
+        <f>Model!AD161</f>
+        <v/>
+      </c>
+      <c r="J104" s="34">
+        <f>Model!AE161</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>Active cards</t>
+        </is>
+      </c>
+      <c r="D105" s="34">
+        <f>Model!N163</f>
+        <v/>
+      </c>
+      <c r="E105" s="34">
+        <f>Model!Z163</f>
+        <v/>
+      </c>
+      <c r="F105" s="34">
+        <f>Model!AA163</f>
+        <v/>
+      </c>
+      <c r="G105" s="34">
+        <f>Model!AB163</f>
+        <v/>
+      </c>
+      <c r="H105" s="34">
+        <f>Model!AC163</f>
+        <v/>
+      </c>
+      <c r="I105" s="34">
+        <f>Model!AD163</f>
+        <v/>
+      </c>
+      <c r="J105" s="34">
+        <f>Model!AE163</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Grams under custody</t>
+        </is>
+      </c>
+      <c r="D106" s="34">
+        <f>Model!N165</f>
+        <v/>
+      </c>
+      <c r="E106" s="34">
+        <f>Model!Z165</f>
+        <v/>
+      </c>
+      <c r="F106" s="34">
+        <f>Model!AA165</f>
+        <v/>
+      </c>
+      <c r="G106" s="34">
+        <f>Model!AB165</f>
+        <v/>
+      </c>
+      <c r="H106" s="34">
+        <f>Model!AC165</f>
+        <v/>
+      </c>
+      <c r="I106" s="34">
+        <f>Model!AD165</f>
+        <v/>
+      </c>
+      <c r="J106" s="34">
+        <f>Model!AE165</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Gold under custody (comparable headline)</t>
+        </is>
+      </c>
+      <c r="D107" s="72">
+        <f>Model!N172</f>
+        <v/>
+      </c>
+      <c r="E107" s="72">
+        <f>Model!Z172</f>
+        <v/>
+      </c>
+      <c r="F107" s="72">
+        <f>Model!AA172</f>
+        <v/>
+      </c>
+      <c r="G107" s="72">
+        <f>Model!AB172</f>
+        <v/>
+      </c>
+      <c r="H107" s="72">
+        <f>Model!AC172</f>
+        <v/>
+      </c>
+      <c r="I107" s="72">
+        <f>Model!AD172</f>
+        <v/>
+      </c>
+      <c r="J107" s="72">
+        <f>Model!AE172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Grams held (collateral-eligible)</t>
+        </is>
+      </c>
+      <c r="D108" s="34">
+        <f>Model!N164</f>
+        <v/>
+      </c>
+      <c r="E108" s="34">
+        <f>Model!Z164</f>
+        <v/>
+      </c>
+      <c r="F108" s="34">
+        <f>Model!AA164</f>
+        <v/>
+      </c>
+      <c r="G108" s="34">
+        <f>Model!AB164</f>
+        <v/>
+      </c>
+      <c r="H108" s="34">
+        <f>Model!AC164</f>
+        <v/>
+      </c>
+      <c r="I108" s="34">
+        <f>Model!AD164</f>
+        <v/>
+      </c>
+      <c r="J108" s="34">
+        <f>Model!AE164</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>Collateral-eligible AUM</t>
+        </is>
+      </c>
+      <c r="D109" s="72">
+        <f>Model!N167</f>
+        <v/>
+      </c>
+      <c r="E109" s="72">
+        <f>Model!Z167</f>
+        <v/>
+      </c>
+      <c r="F109" s="72">
+        <f>Model!AA167</f>
+        <v/>
+      </c>
+      <c r="G109" s="72">
+        <f>Model!AB167</f>
+        <v/>
+      </c>
+      <c r="H109" s="72">
+        <f>Model!AC167</f>
+        <v/>
+      </c>
+      <c r="I109" s="72">
+        <f>Model!AD167</f>
+        <v/>
+      </c>
+      <c r="J109" s="72">
+        <f>Model!AE167</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
           <t>Net revenue per paying customer (annualised)</t>
         </is>
       </c>
-      <c r="D101" s="37">
+      <c r="D110" s="37">
         <f>Model!N198</f>
         <v/>
       </c>
-      <c r="E101" s="37">
+      <c r="E110" s="37">
         <f>Model!Z198</f>
         <v/>
       </c>
-      <c r="F101" s="37">
+      <c r="F110" s="37">
         <f>Model!AA198</f>
         <v/>
       </c>
-      <c r="G101" s="37">
+      <c r="G110" s="37">
         <f>Model!AB198</f>
         <v/>
       </c>
-      <c r="H101" s="37">
+      <c r="H110" s="37">
         <f>Model!AC198</f>
         <v/>
       </c>
-      <c r="I101" s="37">
+      <c r="I110" s="37">
         <f>Model!AD198</f>
         <v/>
       </c>
-      <c r="J101" s="37">
+      <c r="J110" s="37">
         <f>Model!AE198</f>
         <v/>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
         <is>
           <t>REVENUE ONLY. Operating costs, tax, working capital, cash and funding are added in a later build, so there is no profit or break-even line here. Stream 1 IS reported net of the fabrication premium, because that is cost OF REVENUE rather than an operating cost - reporting it gross would read ~43% high.</t>
         </is>
